--- a/PA替代需求列表.xlsx
+++ b/PA替代需求列表.xlsx
@@ -2785,7 +2785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.7" customWidth="1" style="101" min="1" max="1"/>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="D2" s="113" t="inlineStr">
         <is>
-          <t>PA Web界面『策略』章节定义多种策略类型，按用途各自独立配置；对应功能矩阵#2-9/33/52/122/128/129</t>
+          <t>PA Web界面『策略』章节定义多种策略类型，按用途各自独立配置（PA Web帮助p113起）；对应功能矩阵#2-9/33/52/122/128/129</t>
         </is>
       </c>
       <c r="E2" s="112" t="inlineStr">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="51" customHeight="1" s="101">
+    <row r="3" ht="66" customHeight="1" s="101">
       <c r="A3" s="116" t="n"/>
       <c r="B3" s="116" t="n"/>
       <c r="C3" s="113" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D3" s="113" t="inlineStr">
         <is>
-          <t>PA支持将策略规则移动/克隆到虚拟系统或Panorama设备组（含共享位置）；天融信访问控制策略支持移动策略与克隆模板[toc450050600]</t>
+          <t>PA支持将策略规则移动/克隆到虚拟系统或Panorama设备组（含共享位置，PA Web帮助p115）；天融信访问控制策略支持移动策略与克隆模板（天融信手册《配置访问控制策略》页）</t>
         </is>
       </c>
       <c r="E3" s="112" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D4" s="113" t="inlineStr">
         <is>
-          <t>PA记录规则的审核注释历史/配置日志/规则更改历史，可CSV导出，用于策略变更审计；天融信仅规则描述字段，无审核注释存档</t>
+          <t>PA记录规则的审核注释历史/配置日志/规则更改历史，可CSV导出，用于策略变更审计（PA Web帮助p116-117）；天融信仅规则描述字段，无审核注释存档</t>
         </is>
       </c>
       <c r="E4" s="116" t="n"/>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="D5" s="113" t="inlineStr">
         <is>
-          <t>PA支持按时间段查询规则命中数，标识未使用规则以清理；含Reset Rule Hit Count重置功能；天融信策略统计开关可显示规则匹配情况[toc450050600]</t>
+          <t>PA支持按时间段查询规则命中数，标识未使用规则以清理；含Reset Rule Hit Count重置功能（PA Web帮助p118-119）；天融信策略统计开关可显示规则匹配情况（天融信手册《配置访问控制策略》页）</t>
         </is>
       </c>
       <c r="E5" s="116" t="n"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="H5" s="116" t="n"/>
     </row>
-    <row r="6" ht="66" customHeight="1" s="101">
+    <row r="6" ht="111" customHeight="1" s="101">
       <c r="A6" s="116" t="n"/>
       <c r="B6" s="116" t="n"/>
       <c r="C6" s="113" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="D6" s="113" t="inlineStr">
         <is>
-          <t>PA在Panorama管理下策略分为前置规则（设备组共享）/本地规则/后置规则三层按序匹配；天融信为自上而下单层规则链[toc450050600]；迁移评估项：需拆解全局继承策略并映射到天融信策略表顺序</t>
+          <t>PA在Panorama集中管理下策略分为前置规则（设备组共享，最优先）/本地规则/后置规则三层按序匹配（层级机制属Panorama管理平台，PA两册手册未详载）；天融信为自上而下单层规则链一张表走到底（天融信手册《配置访问控制策略》页）；迁移评估项：需制定全局多级策略到单层扁平化策略的合并清洗规则（Pre→本地→Post按序展开映射）</t>
         </is>
       </c>
       <c r="E6" s="116" t="n"/>
@@ -2970,51 +2970,39 @@
       </c>
       <c r="H6" s="116" t="n"/>
     </row>
-    <row r="7" ht="51" customHeight="1" s="101">
+    <row r="7" ht="96" customHeight="1" s="101">
       <c r="A7" s="116" t="n"/>
-      <c r="B7" s="112" t="inlineStr">
+      <c r="B7" s="116" t="n"/>
+      <c r="C7" s="113" t="inlineStr">
+        <is>
+          <t>支持应用级会话超时覆盖（Application Timeout Override）</t>
+        </is>
+      </c>
+      <c r="D7" s="113" t="inlineStr">
+        <is>
+          <t>PA除全局TCP/UDP会话超时外，可在应用程序对象上定义专用超时，匹配该应用的流量覆盖全局值（PA Web帮助p215、p695）；天融信手册未见应用级超时覆盖（仅SSLVPN会话超时设置与黑名单老化）；迁移评估项：需排查现网PA为数据库/长连接业务单独配置的应用超时并逐条转换，否则长连接业务频繁中断</t>
+        </is>
+      </c>
+      <c r="E7" s="116" t="n"/>
+      <c r="F7" s="116" t="n"/>
+      <c r="G7" s="116" t="n"/>
+      <c r="H7" s="116" t="n"/>
+    </row>
+    <row r="8" ht="51" customHeight="1" s="101">
+      <c r="A8" s="116" t="n"/>
+      <c r="B8" s="112" t="inlineStr">
         <is>
           <t>安全策略(Security)</t>
         </is>
       </c>
-      <c r="C7" s="113" t="inlineStr">
+      <c r="C8" s="113" t="inlineStr">
         <is>
           <t>支持基于应用、源/目的区域和地址、用户或用户组、服务（端口/协议）的安全策略</t>
         </is>
       </c>
-      <c r="D7" s="113" t="inlineStr">
+      <c r="D8" s="113" t="inlineStr">
         <is>
           <t>PA安全策略规则基于App-ID应用、用户(User-ID)、区域地址、服务多维匹配并允许/拒绝/跟踪流量；对应矩阵#2/3/4</t>
-        </is>
-      </c>
-      <c r="E7" s="112" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F7" s="113" t="inlineStr"/>
-      <c r="G7" s="112" t="inlineStr">
-        <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="H7" s="112" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1" s="101">
-      <c r="A8" s="116" t="n"/>
-      <c r="B8" s="116" t="n"/>
-      <c r="C8" s="113" t="inlineStr">
-        <is>
-          <t>支持安全策略规则构建块：源用户/HIP/设备/应用/服务/日志等</t>
-        </is>
-      </c>
-      <c r="D8" s="113" t="inlineStr">
-        <is>
-          <t>PA规则构建块含预登录用户、HIP配置文件、设备对象、应用默认端口规避、会话结束日志等；对应矩阵#3/4</t>
         </is>
       </c>
       <c r="E8" s="112" t="inlineStr">
@@ -3028,141 +3016,137 @@
           <t>已支持</t>
         </is>
       </c>
-      <c r="H8" s="112" t="inlineStr"/>
+      <c r="H8" s="112" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="36" customHeight="1" s="101">
       <c r="A9" s="116" t="n"/>
       <c r="B9" s="116" t="n"/>
       <c r="C9" s="113" t="inlineStr">
         <is>
-          <t>支持安全策略优化器（Policy Optimizer）</t>
+          <t>支持安全策略规则构建块：源用户/HIP/设备/应用/服务/日志等</t>
         </is>
       </c>
       <c r="D9" s="113" t="inlineStr">
         <is>
-          <t>PA新应用查看器+端口规则迁移至App-ID规则工作流+规则使用统计，减少攻击面；对应矩阵#132</t>
+          <t>PA规则构建块含预登录用户、HIP配置文件、设备对象、应用默认端口规避、会话结束日志等；对应矩阵#3/4</t>
         </is>
       </c>
       <c r="E9" s="112" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F9" s="116" t="n"/>
-      <c r="G9" s="116" t="n"/>
-      <c r="H9" s="116" t="n"/>
-    </row>
-    <row r="10" ht="36" customHeight="1" s="101">
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F9" s="113" t="inlineStr"/>
+      <c r="G9" s="112" t="inlineStr">
+        <is>
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="H9" s="112" t="inlineStr"/>
+    </row>
+    <row r="10" ht="51" customHeight="1" s="101">
       <c r="A10" s="116" t="n"/>
       <c r="B10" s="116" t="n"/>
       <c r="C10" s="113" t="inlineStr">
         <is>
-          <t>支持配置锁（Config Lock/Commit Lock）</t>
+          <t>支持安全策略优化器（Policy Optimizer）</t>
         </is>
       </c>
       <c r="D10" s="113" t="inlineStr">
         <is>
-          <t>PA可锁定待选配置或提交，防止他管理员并发更改；对应矩阵#135（天融信不支持，PA优势）</t>
-        </is>
-      </c>
-      <c r="E10" s="116" t="n"/>
+          <t>PA新应用查看器+端口规则迁移至App-ID规则工作流+规则使用统计，减少攻击面（PA Web帮助p142）；对应矩阵#132</t>
+        </is>
+      </c>
+      <c r="E10" s="112" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="F10" s="116" t="n"/>
-      <c r="G10" s="112" t="inlineStr">
-        <is>
-          <t>待评估</t>
-        </is>
-      </c>
+      <c r="G10" s="116" t="n"/>
       <c r="H10" s="116" t="n"/>
     </row>
-    <row r="11" ht="81" customHeight="1" s="101">
+    <row r="11" ht="36" customHeight="1" s="101">
       <c r="A11" s="116" t="n"/>
       <c r="B11" s="116" t="n"/>
       <c r="C11" s="113" t="inlineStr">
         <is>
-          <t>支持应用默认端口绑定（Service: application-default）</t>
+          <t>支持配置锁（Config Lock/Commit Lock）</t>
         </is>
       </c>
       <c r="D11" s="113" t="inlineStr">
         <is>
-          <t>PA安全策略默认服务为application-default（应用走标准端口，非标准端口不匹配即拦截）；天融信策略为五元组+应用识别组合[toc450050600]；迁移评估项：策略转换若仅匹配应用不限端口将放宽安全边界，需制定非标准端口转换细则；对应矩阵#2</t>
-        </is>
-      </c>
-      <c r="E11" s="112" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>PA可锁定待选配置或提交，防止他管理员并发更改；对应矩阵#135（天融信不支持，PA优势）</t>
+        </is>
+      </c>
+      <c r="E11" s="116" t="n"/>
       <c r="F11" s="116" t="n"/>
-      <c r="G11" s="116" t="n"/>
+      <c r="G11" s="112" t="inlineStr">
+        <is>
+          <t>待评估</t>
+        </is>
+      </c>
       <c r="H11" s="116" t="n"/>
     </row>
-    <row r="12" ht="81" customHeight="1" s="101">
+    <row r="12" ht="111" customHeight="1" s="101">
       <c r="A12" s="116" t="n"/>
       <c r="B12" s="116" t="n"/>
       <c r="C12" s="113" t="inlineStr">
         <is>
-          <t>支持安全策略绑定安全配置文件组（Profile Group）</t>
+          <t>支持应用默认端口绑定（Service: application-default）</t>
         </is>
       </c>
       <c r="D12" s="113" t="inlineStr">
         <is>
-          <t>PA安全策略Allow动作关联Profile组（反病毒/漏洞防护/URL过滤/文件阻止/WildFire等）；天融信一体化策略引擎自带检测项；迁移评估项：需评估Profile组到天融信各检测引擎的映射与缺省动作差异；对应矩阵#4</t>
+          <t>PA安全策略默认服务为application-default：放行应用同时强制其使用标准端口（如SSH仅22），非标准端口不匹配即拦截（PA管理指南p904）；天融信策略为五元组+应用识别组合（天融信手册《配置访问控制策略》页）；迁移评估项：直接转换若仅保留应用识别不限端口将扩大安全敞口，需制定应用标准端口映射限制（App-Default）转换方案；对应矩阵#2</t>
         </is>
       </c>
       <c r="E12" s="112" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F12" s="116" t="n"/>
       <c r="G12" s="116" t="n"/>
       <c r="H12" s="116" t="n"/>
     </row>
-    <row r="13" ht="36" customHeight="1" s="101">
+    <row r="13" ht="81" customHeight="1" s="101">
       <c r="A13" s="116" t="n"/>
-      <c r="B13" s="112" t="inlineStr">
-        <is>
-          <t>NAT策略</t>
-        </is>
-      </c>
+      <c r="B13" s="116" t="n"/>
       <c r="C13" s="113" t="inlineStr">
         <is>
-          <t>支持源NAT（动态/PAT静态IP）与Hairpin回流</t>
+          <t>支持安全策略绑定安全配置文件组（Profile Group）</t>
         </is>
       </c>
       <c r="D13" s="113" t="inlineStr">
         <is>
-          <t>PA源NAT含DIPP动态IP+端口/静态IP/接口地址/持久NAT等；对应矩阵#6</t>
+          <t>PA安全策略Allow动作关联Profile组（反病毒/漏洞防护/URL过滤/文件阻止/WildFire等，PA Web帮助p304）；天融信一体化策略引擎自带检测项；迁移评估项：需评估Profile组到天融信各检测引擎的映射与缺省动作差异；对应矩阵#4</t>
         </is>
       </c>
       <c r="E13" s="112" t="inlineStr">
         <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F13" s="113" t="inlineStr"/>
-      <c r="G13" s="112" t="inlineStr">
-        <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="H13" s="112" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1" s="101">
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F13" s="116" t="n"/>
+      <c r="G13" s="116" t="n"/>
+      <c r="H13" s="116" t="n"/>
+    </row>
+    <row r="14" ht="111" customHeight="1" s="101">
       <c r="A14" s="116" t="n"/>
       <c r="B14" s="116" t="n"/>
       <c r="C14" s="113" t="inlineStr">
         <is>
-          <t>支持目的NAT（端口映射/服务器发布）</t>
+          <t>支持隐式默认规则显式化迁移（intrazone/interzone-default）</t>
         </is>
       </c>
       <c r="D14" s="113" t="inlineStr">
         <is>
-          <t>PA目标NAT含静态/动态IP、端口转换、DNS Rewrite、FQDN目标；对应矩阵#7</t>
+          <t>PA安全策略库末尾自带两条隐式系统规则：区域内默认（同Zone默认放行）与区域间默认（跨Zone默认拒绝），可被替代配置（PA Web帮助p134）；天融信未见同区域默认放行的隐式规则机制；迁移评估项：必须提取intrazone-default同Zone互访需求并显式转换为放行规则，否则割接后同Zone不同网段/VLAN互访将被默认拦截</t>
         </is>
       </c>
       <c r="E14" s="112" t="inlineStr">
@@ -3170,113 +3154,117 @@
           <t>高</t>
         </is>
       </c>
-      <c r="F14" s="113" t="inlineStr"/>
-      <c r="G14" s="112" t="inlineStr">
+      <c r="F14" s="116" t="n"/>
+      <c r="G14" s="116" t="n"/>
+      <c r="H14" s="116" t="n"/>
+    </row>
+    <row r="15" ht="51" customHeight="1" s="101">
+      <c r="A15" s="116" t="n"/>
+      <c r="B15" s="112" t="inlineStr">
+        <is>
+          <t>NAT策略</t>
+        </is>
+      </c>
+      <c r="C15" s="113" t="inlineStr">
+        <is>
+          <t>支持源NAT（动态/PAT静态IP）与Hairpin回流</t>
+        </is>
+      </c>
+      <c r="D15" s="113" t="inlineStr">
+        <is>
+          <t>PA源NAT含DIPP动态IP+端口/静态IP/接口地址/持久NAT等（PA Web帮助p147）；对应矩阵#6</t>
+        </is>
+      </c>
+      <c r="E15" s="112" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F15" s="113" t="inlineStr"/>
+      <c r="G15" s="112" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H14" s="112" t="inlineStr"/>
-    </row>
-    <row r="15" ht="36" customHeight="1" s="101">
-      <c r="A15" s="116" t="n"/>
-      <c r="B15" s="116" t="n"/>
-      <c r="C15" s="113" t="inlineStr">
-        <is>
-          <t>支持静态/双向NAT一对一转换</t>
-        </is>
-      </c>
-      <c r="D15" s="113" t="inlineStr">
-        <is>
-          <t>PA支持静态IP转换与双向(Bi-directional)转换；对应矩阵#8</t>
-        </is>
-      </c>
-      <c r="E15" s="116" t="n"/>
-      <c r="F15" s="116" t="n"/>
-      <c r="G15" s="116" t="n"/>
-      <c r="H15" s="116" t="n"/>
-    </row>
-    <row r="16" ht="36" customHeight="1" s="101">
+      <c r="H15" s="112" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="51" customHeight="1" s="101">
       <c r="A16" s="116" t="n"/>
       <c r="B16" s="116" t="n"/>
       <c r="C16" s="113" t="inlineStr">
         <is>
-          <t>支持NAT与安全策略解耦独立配置</t>
+          <t>支持目的NAT（端口映射/服务器发布）</t>
         </is>
       </c>
       <c r="D16" s="113" t="inlineStr">
         <is>
-          <t>PA NAT策略库独立于安全策略库(Policies&gt;NAT)，先NAT后安全匹配；对应矩阵#9</t>
-        </is>
-      </c>
-      <c r="E16" s="116" t="n"/>
-      <c r="F16" s="116" t="n"/>
-      <c r="G16" s="116" t="n"/>
-      <c r="H16" s="116" t="n"/>
+          <t>PA目标NAT含静态/动态IP、端口转换、DNS Rewrite、FQDN目标（PA Web帮助p149）；对应矩阵#7</t>
+        </is>
+      </c>
+      <c r="E16" s="112" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F16" s="113" t="inlineStr"/>
+      <c r="G16" s="112" t="inlineStr">
+        <is>
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="H16" s="112" t="inlineStr"/>
     </row>
     <row r="17" ht="36" customHeight="1" s="101">
       <c r="A17" s="116" t="n"/>
       <c r="B17" s="116" t="n"/>
       <c r="C17" s="113" t="inlineStr">
         <is>
-          <t>支持IPv6/NAT64转换（nat64类型）</t>
+          <t>支持静态/双向NAT一对一转换</t>
         </is>
       </c>
       <c r="D17" s="113" t="inlineStr">
         <is>
-          <t>PA NAT规则支持IPv4/IPv6及NAT64转换类型（RFC6146）；对应矩阵#18</t>
-        </is>
-      </c>
-      <c r="E17" s="112" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>PA支持静态IP转换与双向(Bi-directional)转换（PA Web帮助p148）；对应矩阵#8</t>
+        </is>
+      </c>
+      <c r="E17" s="116" t="n"/>
       <c r="F17" s="116" t="n"/>
       <c r="G17" s="116" t="n"/>
       <c r="H17" s="116" t="n"/>
     </row>
-    <row r="18" ht="81" customHeight="1" s="101">
+    <row r="18" ht="36" customHeight="1" s="101">
       <c r="A18" s="116" t="n"/>
       <c r="B18" s="116" t="n"/>
       <c r="C18" s="113" t="inlineStr">
         <is>
-          <t>支持NAT后目的区域路由回查匹配（Dest Zone by route lookup）</t>
+          <t>支持NAT与安全策略解耦独立配置</t>
         </is>
       </c>
       <c r="D18" s="113" t="inlineStr">
         <is>
-          <t>PA NAT策略目的区域按NAT后地址路由回查确定、源区域按NAT前区域；天融信地址转换为独立策略库常规匹配（安全策略&gt;地址转换）[toc398625673]；迁移评估项：Zone/IP匹配计算差异易引发业务不通，需专项评估NAT策略转换映射；对应矩阵#9</t>
-        </is>
-      </c>
-      <c r="E18" s="112" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>PA NAT策略库独立于安全策略库(Policies&gt;NAT)，先NAT后安全匹配；对应矩阵#9</t>
+        </is>
+      </c>
+      <c r="E18" s="116" t="n"/>
       <c r="F18" s="116" t="n"/>
-      <c r="G18" s="112" t="inlineStr">
-        <is>
-          <t>待评估</t>
-        </is>
-      </c>
+      <c r="G18" s="116" t="n"/>
       <c r="H18" s="116" t="n"/>
     </row>
-    <row r="19" ht="51" customHeight="1" s="101">
+    <row r="19" ht="36" customHeight="1" s="101">
       <c r="A19" s="116" t="n"/>
-      <c r="B19" s="112" t="inlineStr">
-        <is>
-          <t>QoS策略</t>
-        </is>
-      </c>
+      <c r="B19" s="116" t="n"/>
       <c r="C19" s="113" t="inlineStr">
         <is>
-          <t>支持按应用/源地址/用户等定义QoS策略并划分优先级类</t>
+          <t>支持IPv6/NAT64转换（nat64类型）</t>
         </is>
       </c>
       <c r="D19" s="113" t="inlineStr">
         <is>
-          <t>PA QoS策略规则分配QoS类（8类+4级优先级），按Egress Guaranteed/Max控制带宽；对应矩阵#33/66</t>
+          <t>PA NAT规则支持IPv4/IPv6及NAT64转换类型（RFC6146）；对应矩阵#18</t>
         </is>
       </c>
       <c r="E19" s="112" t="inlineStr">
@@ -3284,64 +3272,56 @@
           <t>中</t>
         </is>
       </c>
-      <c r="F19" s="113" t="inlineStr"/>
-      <c r="G19" s="112" t="inlineStr">
-        <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="H19" s="112" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="96" customHeight="1" s="101">
+      <c r="F19" s="116" t="n"/>
+      <c r="G19" s="116" t="n"/>
+      <c r="H19" s="116" t="n"/>
+    </row>
+    <row r="20" ht="111" customHeight="1" s="101">
       <c r="A20" s="116" t="n"/>
       <c r="B20" s="116" t="n"/>
       <c r="C20" s="113" t="inlineStr">
         <is>
-          <t>支持基于DSCP/ToS值匹配的QoS</t>
+          <t>支持NAT后目的区域路由回查匹配（Dest Zone by route lookup）</t>
         </is>
       </c>
       <c r="D20" s="113" t="inlineStr">
         <is>
-          <t>PA QoS规则可选按DSCP值或IP优先级/ToS匹配；天融信有流量管理模块（虚拟通道+限制/保证带宽+每IP/每用户限速+通道优先级，匹配维度为应用/用户/区域/地址/服务/时间[toc450050609]），DSCP/CoS识别与重标记在现有NGFW手册未见（ACM产品/新版手册待补证）</t>
+          <t>PA底层为『先NAT判断后安全策略匹配』的因果倒置：安全策略要求源区域(NAT前)+源地址(NAT前)+目的地址(NAT前)+目的区域(NAT后按路由查找)，极其反直觉；天融信地址转换为独立策略库常规直观映射（安全策略&gt;地址转换，天融信手册《服务器映射》页）；迁移评估项：带目的NAT的策略平移后易因Zone填写错误不通，需制定NAT查表逻辑转换映射规范；对应矩阵#9</t>
         </is>
       </c>
       <c r="E20" s="112" t="inlineStr">
         <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="F20" s="113" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F20" s="116" t="n"/>
       <c r="G20" s="112" t="inlineStr">
         <is>
-          <t>不支持</t>
-        </is>
-      </c>
-      <c r="H20" s="112" t="inlineStr"/>
-    </row>
-    <row r="21" ht="36" customHeight="1" s="101">
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="H20" s="116" t="n"/>
+    </row>
+    <row r="21" ht="66" customHeight="1" s="101">
       <c r="A21" s="116" t="n"/>
       <c r="B21" s="112" t="inlineStr">
         <is>
-          <t>基于策略转发(PBF)</t>
+          <t>QoS策略</t>
         </is>
       </c>
       <c r="C21" s="113" t="inlineStr">
         <is>
-          <t>支持按源区域/地址/用户/应用/服务+下一跳的基于策略转发</t>
+          <t>支持按应用/源地址/用户等定义QoS策略并划分优先级类</t>
         </is>
       </c>
       <c r="D21" s="113" t="inlineStr">
         <is>
-          <t>PA PBF策略绕过常规路由表选路，支持路径监控与失效切换、BFD、强制对称返回；对应矩阵#10</t>
+          <t>PA QoS策略规则分配QoS类（8类+4级优先级），按Egress Guaranteed/Max控制带宽（PA Web帮助p154-155）；对应矩阵#33/66</t>
         </is>
       </c>
       <c r="E21" s="112" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F21" s="113" t="inlineStr"/>
@@ -3356,28 +3336,28 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1" s="101">
+    <row r="22" ht="96" customHeight="1" s="101">
       <c r="A22" s="116" t="n"/>
       <c r="B22" s="116" t="n"/>
       <c r="C22" s="113" t="inlineStr">
         <is>
-          <t>支持PBF强制对称返回（非对称路由环境）</t>
+          <t>支持基于DSCP/ToS值匹配的QoS</t>
         </is>
       </c>
       <c r="D22" s="113" t="inlineStr">
         <is>
-          <t>PA Enforce Symmetric Return确保返回流量对称</t>
+          <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
         </is>
       </c>
       <c r="E22" s="112" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="F22" s="113" t="inlineStr"/>
       <c r="G22" s="112" t="inlineStr">
         <is>
-          <t>已支持</t>
+          <t>部分支持</t>
         </is>
       </c>
       <c r="H22" s="112" t="inlineStr"/>
@@ -3386,17 +3366,17 @@
       <c r="A23" s="116" t="n"/>
       <c r="B23" s="112" t="inlineStr">
         <is>
-          <t>解密策略(Decryption)</t>
+          <t>基于策略转发(PBF)</t>
         </is>
       </c>
       <c r="C23" s="113" t="inlineStr">
         <is>
-          <t>支持SSL/TLS解密策略（出站正向/入站反向）</t>
+          <t>支持按源区域/地址/用户/应用/服务+下一跳的基于策略转发</t>
         </is>
       </c>
       <c r="D23" s="113" t="inlineStr">
         <is>
-          <t>PA解密策略区分SSL Forward Proxy/Inbound Inspection/SSH，可解密以获得流量可见性与深度检测；对应矩阵#29/30</t>
+          <t>PA PBF策略绕过常规路由表选路，支持路径监控与失效切换、BFD、强制对称返回（PA Web帮助p156）；对应矩阵#10</t>
         </is>
       </c>
       <c r="E23" s="112" t="inlineStr">
@@ -3421,12 +3401,12 @@
       <c r="B24" s="116" t="n"/>
       <c r="C24" s="113" t="inlineStr">
         <is>
-          <t>支持解密目标选择与证书配置</t>
+          <t>支持PBF强制对称返回（非对称路由环境）</t>
         </is>
       </c>
       <c r="D24" s="113" t="inlineStr">
         <is>
-          <t>PA解密目标允许指定数据包/会话；入站含Certificates证书配置；对应矩阵#31</t>
+          <t>PA Enforce Symmetric Return确保返回流量对称（PA管理指南p1294）</t>
         </is>
       </c>
       <c r="E24" s="112" t="inlineStr">
@@ -3442,103 +3422,99 @@
       </c>
       <c r="H24" s="112" t="inlineStr"/>
     </row>
-    <row r="25" ht="51" customHeight="1" s="101">
+    <row r="25" ht="66" customHeight="1" s="101">
       <c r="A25" s="116" t="n"/>
-      <c r="B25" s="116" t="n"/>
+      <c r="B25" s="112" t="inlineStr">
+        <is>
+          <t>解密策略(Decryption)</t>
+        </is>
+      </c>
       <c r="C25" s="113" t="inlineStr">
         <is>
-          <t>支持解密流量镜像到专用接口（Decryption Port Mirroring）</t>
+          <t>支持SSL/TLS解密策略（出站正向/入站反向）</t>
         </is>
       </c>
       <c r="D25" s="113" t="inlineStr">
         <is>
-          <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
-        </is>
-      </c>
-      <c r="E25" s="116" t="n"/>
-      <c r="F25" s="116" t="n"/>
+          <t>PA解密策略区分SSL Forward Proxy/Inbound Inspection/SSH，可解密以获得流量可见性与深度检测（PA Web帮助p164）；对应矩阵#29/30</t>
+        </is>
+      </c>
+      <c r="E25" s="112" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F25" s="113" t="inlineStr"/>
       <c r="G25" s="112" t="inlineStr">
         <is>
-          <t>不支持</t>
-        </is>
-      </c>
-      <c r="H25" s="116" t="n"/>
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="H25" s="112" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="36" customHeight="1" s="101">
       <c r="A26" s="116" t="n"/>
-      <c r="B26" s="112" t="inlineStr">
-        <is>
-          <t>网络数据包代理(NPBroker)</t>
-        </is>
-      </c>
+      <c r="B26" s="116" t="n"/>
       <c r="C26" s="113" t="inlineStr">
         <is>
-          <t>支持按应用/用户/区域/设备/IP定义NPBroker规则转发到第三方安全链</t>
+          <t>支持解密目标选择与证书配置</t>
         </is>
       </c>
       <c r="D26" s="113" t="inlineStr">
         <is>
-          <t>PA网络数据包代理策略将已解密/未解密TLS/非TLS流量内联转发至第三方安全工具；对应矩阵#122</t>
+          <t>PA解密目标允许指定数据包/会话；入站含Certificates证书配置；对应矩阵#31</t>
         </is>
       </c>
       <c r="E26" s="112" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F26" s="113" t="inlineStr"/>
       <c r="G26" s="112" t="inlineStr">
         <is>
-          <t>部分支持</t>
-        </is>
-      </c>
-      <c r="H26" s="112" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="H26" s="112" t="inlineStr"/>
     </row>
     <row r="27" ht="51" customHeight="1" s="101">
       <c r="A27" s="116" t="n"/>
       <c r="B27" s="116" t="n"/>
       <c r="C27" s="113" t="inlineStr">
         <is>
-          <t>支持NPBroker转发流量类型选择（TLS解密/未解密/非TLS）</t>
+          <t>支持解密流量镜像到专用接口（Decryption Port Mirroring）</t>
         </is>
       </c>
       <c r="D27" s="113" t="inlineStr">
         <is>
-          <t>PA规则可选Forward TLS(Decrypted)/未解密/非TLS多种流量类型；需免费许可证；天融信无网络数据包代理模块（矩阵#122）</t>
-        </is>
-      </c>
-      <c r="E27" s="112" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F27" s="113" t="inlineStr"/>
+          <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证（PA管理指南p1059）；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
+        </is>
+      </c>
+      <c r="E27" s="116" t="n"/>
+      <c r="F27" s="116" t="n"/>
       <c r="G27" s="112" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H27" s="112" t="inlineStr"/>
-    </row>
-    <row r="28" ht="36" customHeight="1" s="101">
+      <c r="H27" s="116" t="n"/>
+    </row>
+    <row r="28" ht="126" customHeight="1" s="101">
       <c r="A28" s="116" t="n"/>
-      <c r="B28" s="112" t="inlineStr">
-        <is>
-          <t>隧道检测(Tunnel Inspection)</t>
-        </is>
-      </c>
+      <c r="B28" s="116" t="n"/>
       <c r="C28" s="113" t="inlineStr">
         <is>
-          <t>支持GRE/GTP-U/HTTP2等明文隧道内层流量检测</t>
+          <t>支持解密不受信证书分离处理（Forward Untrust Certificate）</t>
         </is>
       </c>
       <c r="D28" s="113" t="inlineStr">
         <is>
-          <t>PA隧道检测策略解封装并深度检测GRE/GTP-U/HTTP2等明文隧道内容；对应矩阵#128/37</t>
+          <t>PA转发代理遇外部过期/不受信证书时，不用内部信任CA重签，而是专用Forward Untrust Certificate重签名，让浏览器保留不受信告警（PA管理指南p994、p1030）；天融信SSL解密（透明代理/服务器SSL解密，天融信手册《代理策略》页）未见受信/不受信双证书体系；迁移评估项：需验证天融信对外部无效证书的处理方式，避免直接阻断（白屏）或信任重签（掩盖风险）</t>
         </is>
       </c>
       <c r="E28" s="112" t="inlineStr">
@@ -3546,59 +3522,59 @@
           <t>高</t>
         </is>
       </c>
-      <c r="F28" s="113" t="inlineStr"/>
+      <c r="F28" s="116" t="n"/>
       <c r="G28" s="112" t="inlineStr">
         <is>
-          <t>部分支持</t>
-        </is>
-      </c>
-      <c r="H28" s="112" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1" s="101">
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="H28" s="116" t="n"/>
+    </row>
+    <row r="29" ht="51" customHeight="1" s="101">
       <c r="A29" s="116" t="n"/>
-      <c r="B29" s="116" t="n"/>
+      <c r="B29" s="112" t="inlineStr">
+        <is>
+          <t>网络数据包代理(NPBroker)</t>
+        </is>
+      </c>
       <c r="C29" s="113" t="inlineStr">
         <is>
-          <t>支持最大封装级数防护（max_encap）</t>
+          <t>支持按应用/用户/区域/设备/IP定义NPBroker规则转发到第三方安全链</t>
         </is>
       </c>
       <c r="D29" s="113" t="inlineStr">
         <is>
-          <t>PA对隧道最大封装级数超限丢包防护，防隧道嵌套绕过；天融信手册无封装级数防护（检索无命中）</t>
+          <t>PA网络数据包代理策略将已解密/未解密TLS/非TLS流量内联转发至第三方安全工具（PA Web帮助p167）；对应矩阵#122</t>
         </is>
       </c>
       <c r="E29" s="112" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F29" s="113" t="inlineStr"/>
       <c r="G29" s="112" t="inlineStr">
         <is>
-          <t>不支持</t>
-        </is>
-      </c>
-      <c r="H29" s="112" t="inlineStr"/>
-    </row>
-    <row r="30" ht="36" customHeight="1" s="101">
+          <t>部分支持</t>
+        </is>
+      </c>
+      <c r="H29" s="112" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="66" customHeight="1" s="101">
       <c r="A30" s="116" t="n"/>
-      <c r="B30" s="112" t="inlineStr">
-        <is>
-          <t>应用覆盖(App Override)</t>
-        </is>
-      </c>
+      <c r="B30" s="116" t="n"/>
       <c r="C30" s="113" t="inlineStr">
         <is>
-          <t>支持通过Application Override重定义应用识别</t>
+          <t>支持NPBroker转发流量类型选择（TLS解密/未解密/非TLS）</t>
         </is>
       </c>
       <c r="D30" s="113" t="inlineStr">
         <is>
-          <t>PA应用替代策略改变防火墙对网络通信的应用分类方式（如指定明文协议/端口识别）；对应矩阵#26</t>
+          <t>PA规则可选Forward TLS(Decrypted)/未解密/非TLS多种流量类型；需免费许可证（PA Web帮助p167）；天融信无网络数据包代理模块（矩阵#122）</t>
         </is>
       </c>
       <c r="E30" s="112" t="inlineStr">
@@ -3609,86 +3585,86 @@
       <c r="F30" s="113" t="inlineStr"/>
       <c r="G30" s="112" t="inlineStr">
         <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="H30" s="112" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1" s="101">
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="H30" s="112" t="inlineStr"/>
+    </row>
+    <row r="31" ht="51" customHeight="1" s="101">
       <c r="A31" s="116" t="n"/>
-      <c r="B31" s="116" t="n"/>
+      <c r="B31" s="112" t="inlineStr">
+        <is>
+          <t>隧道检测(Tunnel Inspection)</t>
+        </is>
+      </c>
       <c r="C31" s="113" t="inlineStr">
         <is>
-          <t>支持覆盖类型（端口映射类）识别</t>
+          <t>支持GRE/GTP-U/HTTP2等明文隧道内层流量检测</t>
         </is>
       </c>
       <c r="D31" s="113" t="inlineStr">
         <is>
-          <t>PA支持端口式应用覆盖识别（configurable自定义应用）</t>
+          <t>PA隧道检测策略解封装并深度检测GRE/GTP-U/HTTP2等明文隧道内容（PA Web帮助p172-173）；对应矩阵#128/37</t>
         </is>
       </c>
       <c r="E31" s="112" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F31" s="113" t="inlineStr"/>
       <c r="G31" s="112" t="inlineStr">
         <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="H31" s="112" t="inlineStr"/>
+          <t>部分支持</t>
+        </is>
+      </c>
+      <c r="H31" s="112" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="51" customHeight="1" s="101">
       <c r="A32" s="116" t="n"/>
-      <c r="B32" s="112" t="inlineStr">
-        <is>
-          <t>身份验证(Authentication)</t>
-        </is>
-      </c>
+      <c r="B32" s="116" t="n"/>
       <c r="C32" s="113" t="inlineStr">
         <is>
-          <t>支持基于用户身份的身份验证策略（User-ID）</t>
+          <t>支持最大封装级数防护（max_encap）</t>
         </is>
       </c>
       <c r="D32" s="113" t="inlineStr">
         <is>
-          <t>PA身份验证策略在访问网络资源前对用户鉴权，配合User-ID多源映射（AD/XML/Syslog等）；对应矩阵#3/35</t>
+          <t>PA对隧道最大封装级数超限丢包防护，防隧道嵌套绕过（PA管理指南p655）；天融信手册无封装级数防护（检索无命中）</t>
         </is>
       </c>
       <c r="E32" s="112" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="F32" s="113" t="inlineStr"/>
       <c r="G32" s="112" t="inlineStr">
         <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="H32" s="112" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1" s="101">
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="H32" s="112" t="inlineStr"/>
+    </row>
+    <row r="33" ht="51" customHeight="1" s="101">
       <c r="A33" s="116" t="n"/>
-      <c r="B33" s="116" t="n"/>
+      <c r="B33" s="112" t="inlineStr">
+        <is>
+          <t>应用覆盖(App Override)</t>
+        </is>
+      </c>
       <c r="C33" s="113" t="inlineStr">
         <is>
-          <t>支持认证策略超时与单次认证（SSO）</t>
+          <t>支持通过Application Override重定义应用识别</t>
         </is>
       </c>
       <c r="D33" s="113" t="inlineStr">
         <is>
-          <t>PA支持认证超时减少重复质询、Kerberos/SAML/RADIUS等对接</t>
+          <t>PA应用替代策略改变防火墙对网络通信的应用分类方式（如指定明文协议/端口识别，PA Web帮助p178）；对应矩阵#26</t>
         </is>
       </c>
       <c r="E33" s="112" t="inlineStr">
@@ -3702,28 +3678,28 @@
           <t>已支持</t>
         </is>
       </c>
-      <c r="H33" s="112" t="inlineStr"/>
-    </row>
-    <row r="34" ht="51" customHeight="1" s="101">
+      <c r="H33" s="112" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1" s="101">
       <c r="A34" s="116" t="n"/>
-      <c r="B34" s="112" t="inlineStr">
-        <is>
-          <t>DoS防护(DoS Protection)</t>
-        </is>
-      </c>
+      <c r="B34" s="116" t="n"/>
       <c r="C34" s="113" t="inlineStr">
         <is>
-          <t>支持针对关键资源的分类/聚合DoS防护</t>
+          <t>支持覆盖类型（端口映射类）识别</t>
         </is>
       </c>
       <c r="D34" s="113" t="inlineStr">
         <is>
-          <t>PA DoS策略基于源/目的接口、区域、地址、服务定义允许/拒绝/告警，含分类与聚合双层阈值配置文件；对应矩阵#52/42</t>
+          <t>PA支持端口式应用覆盖识别（configurable自定义应用）</t>
         </is>
       </c>
       <c r="E34" s="112" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="F34" s="113" t="inlineStr"/>
@@ -3732,53 +3708,49 @@
           <t>已支持</t>
         </is>
       </c>
-      <c r="H34" s="112" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1" s="101">
+      <c r="H34" s="112" t="inlineStr"/>
+    </row>
+    <row r="35" ht="96" customHeight="1" s="101">
       <c r="A35" s="116" t="n"/>
       <c r="B35" s="116" t="n"/>
       <c r="C35" s="113" t="inlineStr">
         <is>
-          <t>支持DoS聚合配置文件（连接/秒阈值）</t>
+          <t>支持应用替代流量跳过七层检测等效配置</t>
         </is>
       </c>
       <c r="D35" s="113" t="inlineStr">
         <is>
-          <t>PA聚合DoS配置文件按传入连接数/秒触发告警与最大速率限制</t>
+          <t>PA应用替代策略明确绕过第7层处理与威胁检查，改用第4层状态检查以加速（PA管理指南p1307）；天融信自定义应用加入规则库后仍默认经安全引擎检测（天融信手册《自定义应用》页）；迁移评估项：PA应用替代多为私有大流量业务加速，转换时需同步关闭对应策略的IPS/七层检测，否则性能被拖垮或误阻断</t>
         </is>
       </c>
       <c r="E35" s="112" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F35" s="113" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F35" s="116" t="n"/>
       <c r="G35" s="112" t="inlineStr">
         <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="H35" s="112" t="inlineStr"/>
-    </row>
-    <row r="36" ht="36" customHeight="1" s="101">
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="H35" s="116" t="n"/>
+    </row>
+    <row r="36" ht="51" customHeight="1" s="101">
       <c r="A36" s="116" t="n"/>
       <c r="B36" s="112" t="inlineStr">
         <is>
-          <t>SD-WAN策略</t>
+          <t>身份验证(Authentication)</t>
         </is>
       </c>
       <c r="C36" s="113" t="inlineStr">
         <is>
-          <t>支持按应用配置链路路径管理与链路质量探测</t>
+          <t>支持基于用户身份的身份验证策略（User-ID）</t>
         </is>
       </c>
       <c r="D36" s="113" t="inlineStr">
         <is>
-          <t>PA SD-WAN策略按应用/抖动/延迟/丢包指标分配链路，流量分发；对应矩阵#129/120</t>
+          <t>PA身份验证策略在访问网络资源前对用户鉴权（PA Web帮助p182），配合User-ID多源映射（AD/XML/Syslog等）；对应矩阵#3/35</t>
         </is>
       </c>
       <c r="E36" s="112" t="inlineStr">
@@ -3789,7 +3761,7 @@
       <c r="F36" s="113" t="inlineStr"/>
       <c r="G36" s="112" t="inlineStr">
         <is>
-          <t>部分支持</t>
+          <t>已支持</t>
         </is>
       </c>
       <c r="H36" s="112" t="inlineStr">
@@ -3798,17 +3770,17 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="66" customHeight="1" s="101">
+    <row r="37" ht="36" customHeight="1" s="101">
       <c r="A37" s="116" t="n"/>
       <c r="B37" s="116" t="n"/>
       <c r="C37" s="113" t="inlineStr">
         <is>
-          <t>支持SD-WAN路径选择与链路质量监测（jitter/latency/loss）</t>
+          <t>支持认证策略超时与单次认证（SSO）</t>
         </is>
       </c>
       <c r="D37" s="113" t="inlineStr">
         <is>
-          <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路；天融信有链路探测(ping)+智能选路(最小延迟优先)[toc490041605]，无jitter/latency/loss多维指标</t>
+          <t>PA支持认证超时减少重复质询、Kerberos/SAML/RADIUS等对接</t>
         </is>
       </c>
       <c r="E37" s="112" t="inlineStr">
@@ -3819,41 +3791,189 @@
       <c r="F37" s="113" t="inlineStr"/>
       <c r="G37" s="112" t="inlineStr">
         <is>
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="H37" s="112" t="inlineStr"/>
+    </row>
+    <row r="38" ht="81" customHeight="1" s="101">
+      <c r="A38" s="116" t="n"/>
+      <c r="B38" s="116" t="n"/>
+      <c r="C38" s="113" t="inlineStr">
+        <is>
+          <t>支持User-ID动态映射时效性等效（AD日志毫秒级更新）</t>
+        </is>
+      </c>
+      <c r="D38" s="113" t="inlineStr">
+        <is>
+          <t>PA无代理架构通过读取域控事件日志实现IP-用户毫秒级动态映射，大规模部署有专项规划（PA管理指南p866-867）；天融信AD对接的轮询间隔与并发认证能力手册未量化；迁移评估项：数万AD用户且移动频繁场景需实测天融信映射更新时延，避免基于用户的策略出现间歇性未授权拦截</t>
+        </is>
+      </c>
+      <c r="E38" s="116" t="n"/>
+      <c r="F38" s="116" t="n"/>
+      <c r="G38" s="112" t="inlineStr">
+        <is>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="H38" s="116" t="n"/>
+    </row>
+    <row r="39" ht="51" customHeight="1" s="101">
+      <c r="A39" s="116" t="n"/>
+      <c r="B39" s="112" t="inlineStr">
+        <is>
+          <t>DoS防护(DoS Protection)</t>
+        </is>
+      </c>
+      <c r="C39" s="113" t="inlineStr">
+        <is>
+          <t>支持针对关键资源的分类/聚合DoS防护</t>
+        </is>
+      </c>
+      <c r="D39" s="113" t="inlineStr">
+        <is>
+          <t>PA DoS策略基于源/目的接口、区域、地址、服务定义允许/拒绝/告警，含分类与聚合双层阈值配置文件（PA管理指南p1354）；对应矩阵#52/42</t>
+        </is>
+      </c>
+      <c r="E39" s="112" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F39" s="113" t="inlineStr"/>
+      <c r="G39" s="112" t="inlineStr">
+        <is>
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="H39" s="112" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1" s="101">
+      <c r="A40" s="116" t="n"/>
+      <c r="B40" s="116" t="n"/>
+      <c r="C40" s="113" t="inlineStr">
+        <is>
+          <t>支持DoS聚合配置文件（连接/秒阈值）</t>
+        </is>
+      </c>
+      <c r="D40" s="113" t="inlineStr">
+        <is>
+          <t>PA聚合DoS配置文件按传入连接数/秒触发告警与最大速率限制</t>
+        </is>
+      </c>
+      <c r="E40" s="112" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F40" s="113" t="inlineStr"/>
+      <c r="G40" s="112" t="inlineStr">
+        <is>
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="H40" s="112" t="inlineStr"/>
+    </row>
+    <row r="41" ht="51" customHeight="1" s="101">
+      <c r="A41" s="116" t="n"/>
+      <c r="B41" s="112" t="inlineStr">
+        <is>
+          <t>SD-WAN策略</t>
+        </is>
+      </c>
+      <c r="C41" s="113" t="inlineStr">
+        <is>
+          <t>支持按应用配置链路路径管理与链路质量探测</t>
+        </is>
+      </c>
+      <c r="D41" s="113" t="inlineStr">
+        <is>
+          <t>PA SD-WAN策略按应用/抖动/延迟/丢包指标分配链路，流量分发（PA Web帮助p197）；对应矩阵#129/120</t>
+        </is>
+      </c>
+      <c r="E41" s="112" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F41" s="113" t="inlineStr"/>
+      <c r="G41" s="112" t="inlineStr">
+        <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H37" s="112" t="inlineStr"/>
+      <c r="H41" s="112" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="81" customHeight="1" s="101">
+      <c r="A42" s="116" t="n"/>
+      <c r="B42" s="116" t="n"/>
+      <c r="C42" s="113" t="inlineStr">
+        <is>
+          <t>支持SD-WAN路径选择与链路质量监测（jitter/latency/loss）</t>
+        </is>
+      </c>
+      <c r="D42" s="113" t="inlineStr">
+        <is>
+          <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路（PA Web帮助p195）；天融信有链路探测(ping)+智能选路(最小延迟优先)（天融信手册《策略路由》页），无jitter/latency/loss多维指标</t>
+        </is>
+      </c>
+      <c r="E42" s="112" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F42" s="113" t="inlineStr"/>
+      <c r="G42" s="112" t="inlineStr">
+        <is>
+          <t>部分支持</t>
+        </is>
+      </c>
+      <c r="H42" s="112" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A2:A37"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F14:F18"/>
-    <mergeCell ref="F3:F6"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="H14:H18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="H8:H12"/>
-    <mergeCell ref="G14:G17"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="H3:H6"/>
-    <mergeCell ref="F8:F12"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="E24:E25"/>
+  <mergeCells count="34">
+    <mergeCell ref="H3:H7"/>
+    <mergeCell ref="H16:H20"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="H9:H14"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="H26:H28"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="F3:F7"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="F16:F20"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="A2:A42"/>
+    <mergeCell ref="F9:F14"/>
+    <mergeCell ref="B8:B14"/>
+    <mergeCell ref="G16:G19"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="F34:F35"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G11:G14"/>
+    <mergeCell ref="B31:B32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA替代需求列表.xlsx
+++ b/PA替代需求列表.xlsx
@@ -3279,17 +3279,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.7" customWidth="1" style="1" min="1" max="1"/>
     <col width="19.7" customWidth="1" style="1" min="2" max="2"/>
-    <col width="48" customWidth="1" style="1" min="3" max="3"/>
-    <col width="55" customWidth="1" style="1" min="4" max="4"/>
-    <col width="7.7" customWidth="1" style="1" min="5" max="5"/>
-    <col width="20" customWidth="1" style="1" min="6" max="6"/>
-    <col width="12" customWidth="1" style="1" min="7" max="7"/>
-    <col width="9.699999999999999" customWidth="1" style="1" min="8" max="8"/>
+    <col width="40" customWidth="1" style="1" min="3" max="3"/>
+    <col width="30" customWidth="1" style="1" min="4" max="4"/>
+    <col width="62" customWidth="1" style="1" min="5" max="5"/>
+    <col width="7.7" customWidth="1" style="1" min="6" max="6"/>
+    <col width="18" customWidth="1" style="1" min="7" max="7"/>
+    <col width="10" customWidth="1" style="1" min="8" max="8"/>
+    <col width="9.699999999999999" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" s="1">
@@ -3315,26 +3316,31 @@
       </c>
       <c r="E1" s="79" t="inlineStr">
         <is>
+          <t>对比依据（PA证据·天融信现状）</t>
+        </is>
+      </c>
+      <c r="F1" s="79" t="inlineStr">
+        <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="F1" s="79" t="inlineStr">
+      <c r="G1" s="79" t="inlineStr">
         <is>
           <t>交付/规划说明</t>
         </is>
       </c>
-      <c r="G1" s="79" t="inlineStr">
+      <c r="H1" s="79" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="H1" s="79" t="inlineStr">
+      <c r="I1" s="79" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="96" customHeight="1" s="1">
+    <row r="2" ht="111" customHeight="1" s="1">
       <c r="A2" s="80" t="inlineStr">
         <is>
           <t>策略</t>
@@ -3352,21 +3358,26 @@
       </c>
       <c r="D2" s="81" t="inlineStr">
         <is>
+          <t>安全/NAT/QoS/PBF/解密/隧道/应用覆盖/认证/DoS/SD-WAN各自独立策略库</t>
+        </is>
+      </c>
+      <c r="E2" s="81" t="inlineStr">
+        <is>
           <t>PA Web界面『策略』章节定义多种策略类型，按用途各自独立配置（PA Web帮助p113起）；天融信策略库按用途划分：访问控制策略/地址转换策略/流量管理/策略路由/代理策略各自独立（天融信手册《安全策略》《源NAT》《流量管理》《策略路由》《代理策略》页）；对应功能矩阵#2-9/33/52/122/128/129</t>
         </is>
       </c>
-      <c r="E2" s="80" t="inlineStr">
+      <c r="F2" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F2" s="81" t="inlineStr"/>
-      <c r="G2" s="80" t="inlineStr">
+      <c r="G2" s="81" t="inlineStr"/>
+      <c r="H2" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H2" s="80" t="inlineStr">
+      <c r="I2" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
@@ -3382,21 +3393,26 @@
       </c>
       <c r="D3" s="81" t="inlineStr">
         <is>
+          <t>策略可移动调整顺序、克隆复制，支持跨虚拟系统/设备组</t>
+        </is>
+      </c>
+      <c r="E3" s="81" t="inlineStr">
+        <is>
           <t>PA支持将策略规则移动/克隆到虚拟系统或Panorama设备组（含共享位置，PA Web帮助p115）；天融信访问控制策略支持移动策略与克隆模板（天融信手册《配置访问控制策略》页）</t>
         </is>
       </c>
-      <c r="E3" s="80" t="inlineStr">
+      <c r="F3" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F3" s="81" t="inlineStr"/>
-      <c r="G3" s="80" t="inlineStr">
+      <c r="G3" s="81" t="inlineStr"/>
+      <c r="H3" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H3" s="80" t="inlineStr"/>
+      <c r="I3" s="80" t="inlineStr"/>
     </row>
     <row r="4" ht="51" customHeight="1" s="1">
       <c r="A4" s="84" t="n"/>
@@ -3408,19 +3424,24 @@
       </c>
       <c r="D4" s="81" t="inlineStr">
         <is>
+          <t>提交/修改策略须填写审核注释并留存历史，可导出</t>
+        </is>
+      </c>
+      <c r="E4" s="81" t="inlineStr">
+        <is>
           <t>PA记录规则的审核注释历史/配置日志/规则更改历史，可CSV导出，用于策略变更审计（PA Web帮助p116-117）；天融信仅规则描述字段，无审核注释存档</t>
         </is>
       </c>
-      <c r="E4" s="84" t="n"/>
       <c r="F4" s="84" t="n"/>
-      <c r="G4" s="80" t="inlineStr">
+      <c r="G4" s="84" t="n"/>
+      <c r="H4" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H4" s="84" t="n"/>
-    </row>
-    <row r="5" ht="66" customHeight="1" s="1">
+      <c r="I4" s="84" t="n"/>
+    </row>
+    <row r="5" ht="81" customHeight="1" s="1">
       <c r="A5" s="84" t="n"/>
       <c r="B5" s="84" t="n"/>
       <c r="C5" s="81" t="inlineStr">
@@ -3430,17 +3451,22 @@
       </c>
       <c r="D5" s="81" t="inlineStr">
         <is>
+          <t>按时间段统计规则命中次数，识别未使用规则</t>
+        </is>
+      </c>
+      <c r="E5" s="81" t="inlineStr">
+        <is>
           <t>PA支持按时间段查询规则命中数，标识未使用规则以清理；含Reset Rule Hit Count重置功能（PA Web帮助p118-119）；天融信策略统计开关可显示规则匹配情况（天融信手册《配置访问控制策略》页）</t>
         </is>
       </c>
-      <c r="E5" s="84" t="n"/>
       <c r="F5" s="84" t="n"/>
-      <c r="G5" s="80" t="inlineStr">
+      <c r="G5" s="84" t="n"/>
+      <c r="H5" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H5" s="84" t="n"/>
+      <c r="I5" s="84" t="n"/>
     </row>
     <row r="6" ht="111" customHeight="1" s="1">
       <c r="A6" s="84" t="n"/>
@@ -3452,17 +3478,22 @@
       </c>
       <c r="D6" s="81" t="inlineStr">
         <is>
+          <t>前置规则→本地规则→后置规则三层按序合并为单层规则链</t>
+        </is>
+      </c>
+      <c r="E6" s="81" t="inlineStr">
+        <is>
           <t>PA在Panorama集中管理下策略分为前置规则（设备组共享，最优先）/本地规则/后置规则三层按序匹配（层级机制属Panorama管理平台，PA两册手册未详载）；天融信为自上而下单层规则链一张表走到底（天融信手册《配置访问控制策略》页）；迁移评估项：需制定全局多级策略到单层扁平化策略的合并清洗规则（Pre→本地→Post按序展开映射）</t>
         </is>
       </c>
-      <c r="E6" s="84" t="n"/>
       <c r="F6" s="84" t="n"/>
-      <c r="G6" s="80" t="inlineStr">
+      <c r="G6" s="84" t="n"/>
+      <c r="H6" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H6" s="84" t="n"/>
+      <c r="I6" s="84" t="n"/>
     </row>
     <row r="7" ht="96" customHeight="1" s="1">
       <c r="A7" s="84" t="n"/>
@@ -3474,13 +3505,18 @@
       </c>
       <c r="D7" s="81" t="inlineStr">
         <is>
+          <t>应用程序对象级会话超时，覆盖全局TCP/UDP超时</t>
+        </is>
+      </c>
+      <c r="E7" s="81" t="inlineStr">
+        <is>
           <t>PA除全局TCP/UDP会话超时外，可在应用程序对象上定义专用超时，匹配该应用的流量覆盖全局值（PA Web帮助p215、p695）；天融信手册未见应用级超时覆盖（仅SSLVPN会话超时设置与黑名单老化）；迁移评估项：需排查现网PA为数据库/长连接业务单独配置的应用超时并逐条转换，否则长连接业务频繁中断</t>
         </is>
       </c>
-      <c r="E7" s="85" t="n"/>
       <c r="F7" s="85" t="n"/>
       <c r="G7" s="85" t="n"/>
       <c r="H7" s="85" t="n"/>
+      <c r="I7" s="85" t="n"/>
     </row>
     <row r="8" ht="81" customHeight="1" s="1">
       <c r="A8" s="84" t="n"/>
@@ -3496,27 +3532,32 @@
       </c>
       <c r="D8" s="81" t="inlineStr">
         <is>
+          <t>源/目的区域+地址+用户/用户组+服务+应用+时间多维匹配</t>
+        </is>
+      </c>
+      <c r="E8" s="81" t="inlineStr">
+        <is>
           <t>PA安全策略规则基于App-ID应用、用户(User-ID)、区域地址、服务多维匹配并允许/拒绝/跟踪流量；天融信访问控制策略匹配条件含源/目的区域、地址、用户、服务、应用、时间、域名（天融信手册《配置访问控制策略》页）；对应矩阵#2/3/4</t>
         </is>
       </c>
-      <c r="E8" s="80" t="inlineStr">
+      <c r="F8" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F8" s="81" t="inlineStr"/>
-      <c r="G8" s="80" t="inlineStr">
+      <c r="G8" s="81" t="inlineStr"/>
+      <c r="H8" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H8" s="80" t="inlineStr">
+      <c r="I8" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="81" customHeight="1" s="1">
+    <row r="9" ht="96" customHeight="1" s="1">
       <c r="A9" s="84" t="n"/>
       <c r="B9" s="84" t="n"/>
       <c r="C9" s="81" t="inlineStr">
@@ -3526,21 +3567,26 @@
       </c>
       <c r="D9" s="81" t="inlineStr">
         <is>
+          <t>预登录用户/HIP主机信息/设备对象/应用默认端口规避/会话结束日志等构建块</t>
+        </is>
+      </c>
+      <c r="E9" s="81" t="inlineStr">
+        <is>
           <t>PA规则构建块含预登录用户、HIP配置文件、设备对象、应用默认端口规避、会话结束日志等；天融信支持用户/应用/服务/日志构建块，但无HIP主机信息配置文件与设备对象等价物，仅有EDR联动上报终端资产并下发管控策略（天融信手册《与EDR联动》页）；对应矩阵#3/4</t>
         </is>
       </c>
-      <c r="E9" s="80" t="inlineStr">
+      <c r="F9" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F9" s="81" t="inlineStr"/>
-      <c r="G9" s="80" t="inlineStr">
+      <c r="G9" s="81" t="inlineStr"/>
+      <c r="H9" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H9" s="80" t="inlineStr"/>
+      <c r="I9" s="80" t="inlineStr"/>
     </row>
     <row r="10" ht="81" customHeight="1" s="1">
       <c r="A10" s="84" t="n"/>
@@ -3552,13 +3598,18 @@
       </c>
       <c r="D10" s="81" t="inlineStr">
         <is>
+          <t>端口(L4)规则一键迁移为应用(L7)规则+新应用查看器</t>
+        </is>
+      </c>
+      <c r="E10" s="81" t="inlineStr">
+        <is>
           <t>PA新应用查看器+端口规则迁移至App-ID规则工作流+规则使用统计，减少攻击面（PA Web帮助p142）；天融信策略统计开关可显示规则匹配命中情况（天融信手册《配置访问控制策略》页），但无新应用查看器与端口→应用规则迁移工作流；对应矩阵#132</t>
         </is>
       </c>
-      <c r="E10" s="84" t="n"/>
       <c r="F10" s="84" t="n"/>
-      <c r="G10" s="85" t="n"/>
-      <c r="H10" s="84" t="n"/>
+      <c r="G10" s="84" t="n"/>
+      <c r="H10" s="85" t="n"/>
+      <c r="I10" s="84" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1" s="1">
       <c r="A11" s="84" t="n"/>
@@ -3570,17 +3621,22 @@
       </c>
       <c r="D11" s="81" t="inlineStr">
         <is>
+          <t>配置锁/提交锁，防止多管理员并发修改</t>
+        </is>
+      </c>
+      <c r="E11" s="81" t="inlineStr">
+        <is>
           <t>PA可锁定待选配置或提交，防止他管理员并发更改；对应矩阵#135（天融信不支持，PA优势）</t>
         </is>
       </c>
-      <c r="E11" s="85" t="n"/>
-      <c r="F11" s="84" t="n"/>
-      <c r="G11" s="80" t="inlineStr">
+      <c r="F11" s="85" t="n"/>
+      <c r="G11" s="84" t="n"/>
+      <c r="H11" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H11" s="84" t="n"/>
+      <c r="I11" s="84" t="n"/>
     </row>
     <row r="12" ht="111" customHeight="1" s="1">
       <c r="A12" s="84" t="n"/>
@@ -3592,17 +3648,22 @@
       </c>
       <c r="D12" s="81" t="inlineStr">
         <is>
+          <t>应用匹配同时强制使用标准端口，非标端口拒绝</t>
+        </is>
+      </c>
+      <c r="E12" s="81" t="inlineStr">
+        <is>
           <t>PA安全策略默认服务为application-default：放行应用同时强制其使用标准端口（如SSH仅22），非标准端口不匹配即拦截（PA管理指南p904）；天融信策略为五元组+应用识别组合（天融信手册《配置访问控制策略》页）；迁移评估项：直接转换若仅保留应用识别不限端口将扩大安全敞口，需制定应用标准端口映射限制（App-Default）转换方案；对应矩阵#2</t>
         </is>
       </c>
-      <c r="E12" s="80" t="inlineStr">
+      <c r="F12" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F12" s="84" t="n"/>
       <c r="G12" s="84" t="n"/>
       <c r="H12" s="84" t="n"/>
+      <c r="I12" s="84" t="n"/>
     </row>
     <row r="13" ht="81" customHeight="1" s="1">
       <c r="A13" s="84" t="n"/>
@@ -3614,17 +3675,22 @@
       </c>
       <c r="D13" s="81" t="inlineStr">
         <is>
+          <t>Allow动作关联反病毒/漏洞防护/URL过滤/文件阻断/WildFire配置文件组</t>
+        </is>
+      </c>
+      <c r="E13" s="81" t="inlineStr">
+        <is>
           <t>PA安全策略Allow动作关联Profile组（反病毒/漏洞防护/URL过滤/文件阻止/WildFire等，PA Web帮助p304）；天融信一体化策略引擎自带检测项；迁移评估项：需评估Profile组到天融信各检测引擎的映射与缺省动作差异；对应矩阵#4</t>
         </is>
       </c>
-      <c r="E13" s="80" t="inlineStr">
+      <c r="F13" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F13" s="84" t="n"/>
       <c r="G13" s="84" t="n"/>
       <c r="H13" s="84" t="n"/>
+      <c r="I13" s="84" t="n"/>
     </row>
     <row r="14" ht="156" customHeight="1" s="1">
       <c r="A14" s="84" t="n"/>
@@ -3636,17 +3702,22 @@
       </c>
       <c r="D14" s="81" t="inlineStr">
         <is>
+          <t>同区域默认放行/跨区域默认拒绝，支持替代与日志转发</t>
+        </is>
+      </c>
+      <c r="E14" s="81" t="inlineStr">
+        <is>
           <t>PA安全策略库末尾自带两条隐式系统规则：区域内默认（同Zone默认放行）与区域间默认（跨Zone默认拒绝），可被替代配置，替代字段含日志转发配置文件与Log at Session End在会话结束时记录（PA Web帮助p134-136）；天融信未见同区域默认放行的隐式规则机制；迁移评估项：①必须提取intrazone-default同Zone互访需求并显式转换为放行规则，否则割接后同Zone不同网段/VLAN互访将被默认拦截；②需在新设备补齐底部兜底Deny-All并开启日志，否则被拒流量查无日志、排障困难</t>
         </is>
       </c>
-      <c r="E14" s="80" t="inlineStr">
+      <c r="F14" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F14" s="85" t="n"/>
       <c r="G14" s="85" t="n"/>
       <c r="H14" s="85" t="n"/>
+      <c r="I14" s="85" t="n"/>
     </row>
     <row r="15" ht="81" customHeight="1" s="1">
       <c r="A15" s="84" t="n"/>
@@ -3662,21 +3733,26 @@
       </c>
       <c r="D15" s="81" t="inlineStr">
         <is>
+          <t>动态IP+端口(DIPP)/静态IP/接口地址，含回流(Hairpin)</t>
+        </is>
+      </c>
+      <c r="E15" s="81" t="inlineStr">
+        <is>
           <t>PA源NAT含DIPP动态IP+端口/静态IP/接口地址/持久NAT等（PA Web帮助p147）；天融信SNAT地址池（多对一/多对多/一对一/PAT）与仅源IP转换等（天融信手册《源NAT》《配置源转换》页）；对应矩阵#6</t>
         </is>
       </c>
-      <c r="E15" s="80" t="inlineStr">
+      <c r="F15" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F15" s="81" t="inlineStr"/>
-      <c r="G15" s="80" t="inlineStr">
+      <c r="G15" s="81" t="inlineStr"/>
+      <c r="H15" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H15" s="80" t="inlineStr">
+      <c r="I15" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
@@ -3692,23 +3768,28 @@
       </c>
       <c r="D16" s="81" t="inlineStr">
         <is>
+          <t>静态映射/端口转换/DNS重写/FQDN目标</t>
+        </is>
+      </c>
+      <c r="E16" s="81" t="inlineStr">
+        <is>
           <t>PA目标NAT含静态/动态IP、端口转换、DNS Rewrite、FQDN目标（PA Web帮助p149）；天融信服务器映射含静态映射+服务器负载均衡两种模式，NAT46/NAT66全系列（天融信手册《服务器映射》页）；对应矩阵#7</t>
         </is>
       </c>
-      <c r="E16" s="80" t="inlineStr">
+      <c r="F16" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F16" s="81" t="inlineStr"/>
-      <c r="G16" s="80" t="inlineStr">
+      <c r="G16" s="81" t="inlineStr"/>
+      <c r="H16" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H16" s="80" t="inlineStr"/>
-    </row>
-    <row r="17" ht="66" customHeight="1" s="1">
+      <c r="I16" s="80" t="inlineStr"/>
+    </row>
+    <row r="17" ht="81" customHeight="1" s="1">
       <c r="A17" s="84" t="n"/>
       <c r="B17" s="84" t="n"/>
       <c r="C17" s="81" t="inlineStr">
@@ -3718,15 +3799,20 @@
       </c>
       <c r="D17" s="81" t="inlineStr">
         <is>
+          <t>一对一转换，支持双向映射</t>
+        </is>
+      </c>
+      <c r="E17" s="81" t="inlineStr">
+        <is>
           <t>PA支持静态IP转换与双向(Bi-directional)转换（PA Web帮助p148）；天融信支持一对一转换（SNAT地址池一对一/NAT66一对一）（天融信手册《源NAT》《配置一对一转换》页）；对应矩阵#8</t>
         </is>
       </c>
-      <c r="E17" s="84" t="n"/>
       <c r="F17" s="84" t="n"/>
       <c r="G17" s="84" t="n"/>
       <c r="H17" s="84" t="n"/>
-    </row>
-    <row r="18" ht="66" customHeight="1" s="1">
+      <c r="I17" s="84" t="n"/>
+    </row>
+    <row r="18" ht="81" customHeight="1" s="1">
       <c r="A18" s="84" t="n"/>
       <c r="B18" s="84" t="n"/>
       <c r="C18" s="81" t="inlineStr">
@@ -3736,13 +3822,18 @@
       </c>
       <c r="D18" s="81" t="inlineStr">
         <is>
+          <t>NAT独立策略库，先NAT后安全策略匹配</t>
+        </is>
+      </c>
+      <c r="E18" s="81" t="inlineStr">
+        <is>
           <t>PA NAT策略库独立于安全策略库(Policies&gt;NAT)，先NAT后安全匹配；天融信地址转换为独立策略库（安全策略&gt;地址转换），与访问控制策略分离配置（天融信手册《安全策略》《工作原理》页）；对应矩阵#9</t>
         </is>
       </c>
-      <c r="E18" s="85" t="n"/>
-      <c r="F18" s="84" t="n"/>
+      <c r="F18" s="85" t="n"/>
       <c r="G18" s="84" t="n"/>
       <c r="H18" s="84" t="n"/>
+      <c r="I18" s="84" t="n"/>
     </row>
     <row r="19" ht="81" customHeight="1" s="1">
       <c r="A19" s="84" t="n"/>
@@ -3754,19 +3845,24 @@
       </c>
       <c r="D19" s="81" t="inlineStr">
         <is>
+          <t>IPv4↔IPv6转换类型（nat64）</t>
+        </is>
+      </c>
+      <c r="E19" s="81" t="inlineStr">
+        <is>
           <t>PA NAT规则支持IPv4/IPv6及NAT64转换类型（RFC6146）；天融信NAT64含静态转换+前缀转换+动态算法（IVI/普通前缀），另有NAT46（天融信手册《NAT64》《NAT46》页）；对应矩阵#18</t>
         </is>
       </c>
-      <c r="E19" s="80" t="inlineStr">
+      <c r="F19" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F19" s="84" t="n"/>
-      <c r="G19" s="85" t="n"/>
-      <c r="H19" s="84" t="n"/>
-    </row>
-    <row r="20" ht="111" customHeight="1" s="1">
+      <c r="G19" s="84" t="n"/>
+      <c r="H19" s="85" t="n"/>
+      <c r="I19" s="84" t="n"/>
+    </row>
+    <row r="20" ht="126" customHeight="1" s="1">
       <c r="A20" s="84" t="n"/>
       <c r="B20" s="84" t="n"/>
       <c r="C20" s="81" t="inlineStr">
@@ -3776,21 +3872,26 @@
       </c>
       <c r="D20" s="81" t="inlineStr">
         <is>
+          <t>目的区域按NAT后路由查找；源/目的地址用NAT前值</t>
+        </is>
+      </c>
+      <c r="E20" s="81" t="inlineStr">
+        <is>
           <t>PA底层为『先NAT判断后安全策略匹配』的因果倒置：安全策略要求源区域(NAT前)+源地址(NAT前)+目的地址(NAT前)+目的区域(NAT后按路由查找)，极其反直觉；天融信地址转换为独立策略库常规直观映射（安全策略&gt;地址转换，天融信手册《服务器映射》页）；迁移评估项：带目的NAT的策略平移后易因Zone填写错误不通，需制定NAT查表逻辑转换映射规范；对应矩阵#9</t>
         </is>
       </c>
-      <c r="E20" s="80" t="inlineStr">
+      <c r="F20" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F20" s="84" t="n"/>
-      <c r="G20" s="80" t="inlineStr">
+      <c r="G20" s="84" t="n"/>
+      <c r="H20" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H20" s="84" t="n"/>
+      <c r="I20" s="84" t="n"/>
     </row>
     <row r="21" ht="81" customHeight="1" s="1">
       <c r="A21" s="84" t="n"/>
@@ -3802,21 +3903,26 @@
       </c>
       <c r="D21" s="81" t="inlineStr">
         <is>
+          <t>主动/主动HA下NAT规则绑定会话所有者</t>
+        </is>
+      </c>
+      <c r="E21" s="81" t="inlineStr">
+        <is>
           <t>PA主动/主动HA配置下NAT规则可绑定会话所有者/会话设置，控制NAT会话的设备绑定，仅A/A模式可见（PA Web帮助p150）；天融信HA为主备双机热备模式（天融信手册《配置双机热备功能》页），无主动/主动模式及NAT规则绑定机制</t>
         </is>
       </c>
-      <c r="E21" s="80" t="inlineStr">
+      <c r="F21" s="80" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="F21" s="85" t="n"/>
-      <c r="G21" s="80" t="inlineStr">
+      <c r="G21" s="85" t="n"/>
+      <c r="H21" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H21" s="85" t="n"/>
+      <c r="I21" s="85" t="n"/>
     </row>
     <row r="22" ht="96" customHeight="1" s="1">
       <c r="A22" s="84" t="n"/>
@@ -3832,21 +3938,26 @@
       </c>
       <c r="D22" s="81" t="inlineStr">
         <is>
+          <t>8类流量分类+4级优先级，保证/最大带宽控制</t>
+        </is>
+      </c>
+      <c r="E22" s="81" t="inlineStr">
+        <is>
           <t>PA QoS策略规则分配QoS类（8类+4级优先级），按Egress Guaranteed/Max控制带宽（PA Web帮助p154-155）；天融信流量管理基于应用/用户/源目的区域/地址/服务/时间+通道优先级，虚拟通道限制与保证带宽（天融信手册《流量管理》页）；对应矩阵#33/66</t>
         </is>
       </c>
-      <c r="E22" s="80" t="inlineStr">
+      <c r="F22" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F22" s="81" t="inlineStr"/>
-      <c r="G22" s="80" t="inlineStr">
+      <c r="G22" s="81" t="inlineStr"/>
+      <c r="H22" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H22" s="80" t="inlineStr">
+      <c r="I22" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
@@ -3862,21 +3973,26 @@
       </c>
       <c r="D23" s="81" t="inlineStr">
         <is>
+          <t>QoS规则按DSCP/ToS值匹配调度</t>
+        </is>
+      </c>
+      <c r="E23" s="81" t="inlineStr">
+        <is>
           <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
         </is>
       </c>
-      <c r="E23" s="80" t="inlineStr">
+      <c r="F23" s="80" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="F23" s="81" t="inlineStr"/>
-      <c r="G23" s="80" t="inlineStr">
+      <c r="G23" s="81" t="inlineStr"/>
+      <c r="H23" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H23" s="80" t="inlineStr"/>
+      <c r="I23" s="80" t="inlineStr"/>
     </row>
     <row r="24" ht="81" customHeight="1" s="1">
       <c r="A24" s="84" t="n"/>
@@ -3892,27 +4008,32 @@
       </c>
       <c r="D24" s="81" t="inlineStr">
         <is>
+          <t>按源区域/地址/用户/应用/服务+下一跳转发，路径监控失效切换</t>
+        </is>
+      </c>
+      <c r="E24" s="81" t="inlineStr">
+        <is>
           <t>PA PBF策略绕过常规路由表选路，支持路径监控与失效切换、BFD、强制对称返回（PA Web帮助p156）；天融信策略路由按源/目的地址端口、ISP名称、协议、角色等参数选路（天融信手册《策略路由》页）；对应矩阵#10</t>
         </is>
       </c>
-      <c r="E24" s="80" t="inlineStr">
+      <c r="F24" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F24" s="81" t="inlineStr"/>
-      <c r="G24" s="80" t="inlineStr">
+      <c r="G24" s="81" t="inlineStr"/>
+      <c r="H24" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H24" s="80" t="inlineStr">
+      <c r="I24" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="96" customHeight="1" s="1">
+    <row r="25" ht="111" customHeight="1" s="1">
       <c r="A25" s="84" t="n"/>
       <c r="B25" s="85" t="n"/>
       <c r="C25" s="81" t="inlineStr">
@@ -3922,21 +4043,26 @@
       </c>
       <c r="D25" s="81" t="inlineStr">
         <is>
+          <t>记录入接口MAC，回包强制原路返回</t>
+        </is>
+      </c>
+      <c r="E25" s="81" t="inlineStr">
+        <is>
           <t>PA对称返回：虚拟路由器替代返回流量的路由查找，将流量引导回接收SYN数据包的MAC地址（ARP表确定下一跳），双ISP双活/非对称路由核心机制（PA管理指南p1294）；天融信手册检索无对称返回/回程机制命中，策略路由与LLB的回程保障能力待验证；迁移评估项：多ISP双活环境需实测天融信回包路由对称性，否则现网业务中断</t>
         </is>
       </c>
-      <c r="E25" s="80" t="inlineStr">
+      <c r="F25" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F25" s="81" t="inlineStr"/>
-      <c r="G25" s="80" t="inlineStr">
+      <c r="G25" s="81" t="inlineStr"/>
+      <c r="H25" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H25" s="80" t="inlineStr"/>
+      <c r="I25" s="80" t="inlineStr"/>
     </row>
     <row r="26" ht="96" customHeight="1" s="1">
       <c r="A26" s="84" t="n"/>
@@ -3952,27 +4078,32 @@
       </c>
       <c r="D26" s="81" t="inlineStr">
         <is>
+          <t>出站正向代理+入站检查双向解密</t>
+        </is>
+      </c>
+      <c r="E26" s="81" t="inlineStr">
+        <is>
           <t>PA解密策略区分SSL Forward Proxy/Inbound Inspection/SSH，可解密以获得流量可见性与深度检测（PA Web帮助p164）；天融信代理策略将NGFW作为代理服务器，对加密流量解密还原明文完成内容安全检查后重新加密（天融信手册《代理策略》页）；对应矩阵#29/30</t>
         </is>
       </c>
-      <c r="E26" s="80" t="inlineStr">
+      <c r="F26" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F26" s="81" t="inlineStr"/>
-      <c r="G26" s="80" t="inlineStr">
+      <c r="G26" s="81" t="inlineStr"/>
+      <c r="H26" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H26" s="80" t="inlineStr">
+      <c r="I26" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="51" customHeight="1" s="1">
+    <row r="27" ht="66" customHeight="1" s="1">
       <c r="A27" s="84" t="n"/>
       <c r="B27" s="84" t="n"/>
       <c r="C27" s="81" t="inlineStr">
@@ -3982,21 +4113,26 @@
       </c>
       <c r="D27" s="81" t="inlineStr">
         <is>
+          <t>入站证书配置/解密目标（数据包/会话）</t>
+        </is>
+      </c>
+      <c r="E27" s="81" t="inlineStr">
+        <is>
           <t>PA解密目标允许指定数据包/会话；入站含Certificates证书配置；对应矩阵#31；天融信代理模板支持证书选择与预置动态证书模板（天融信手册《代理模板》页）</t>
         </is>
       </c>
-      <c r="E27" s="80" t="inlineStr">
+      <c r="F27" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F27" s="81" t="inlineStr"/>
-      <c r="G27" s="80" t="inlineStr">
+      <c r="G27" s="81" t="inlineStr"/>
+      <c r="H27" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H27" s="80" t="inlineStr"/>
+      <c r="I27" s="80" t="inlineStr"/>
     </row>
     <row r="28" ht="51" customHeight="1" s="1">
       <c r="A28" s="84" t="n"/>
@@ -4008,17 +4144,22 @@
       </c>
       <c r="D28" s="81" t="inlineStr">
         <is>
+          <t>解密后明文流量镜像至专用接口供第三方分析</t>
+        </is>
+      </c>
+      <c r="E28" s="81" t="inlineStr">
+        <is>
           <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证（PA管理指南p1059）；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
         </is>
       </c>
-      <c r="E28" s="85" t="n"/>
-      <c r="F28" s="84" t="n"/>
-      <c r="G28" s="80" t="inlineStr">
+      <c r="F28" s="85" t="n"/>
+      <c r="G28" s="84" t="n"/>
+      <c r="H28" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H28" s="84" t="n"/>
+      <c r="I28" s="84" t="n"/>
     </row>
     <row r="29" ht="126" customHeight="1" s="1">
       <c r="A29" s="84" t="n"/>
@@ -4030,21 +4171,26 @@
       </c>
       <c r="D29" s="81" t="inlineStr">
         <is>
+          <t>外部无效证书以不受信转发证书重签，保留浏览器告警</t>
+        </is>
+      </c>
+      <c r="E29" s="81" t="inlineStr">
+        <is>
           <t>PA转发代理遇外部过期/不受信证书时，不用内部信任CA重签，而是专用Forward Untrust Certificate重签名，让浏览器保留不受信告警（PA管理指南p994、p1030）；天融信SSL解密（透明代理/服务器SSL解密，天融信手册《代理策略》页）未见受信/不受信双证书体系；迁移评估项：需验证天融信对外部无效证书的处理方式，避免直接阻断（白屏）或信任重签（掩盖风险）</t>
         </is>
       </c>
-      <c r="E29" s="80" t="inlineStr">
+      <c r="F29" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F29" s="84" t="n"/>
-      <c r="G29" s="80" t="inlineStr">
+      <c r="G29" s="84" t="n"/>
+      <c r="H29" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H29" s="84" t="n"/>
+      <c r="I29" s="84" t="n"/>
     </row>
     <row r="30" ht="66" customHeight="1" s="1">
       <c r="A30" s="84" t="n"/>
@@ -4056,21 +4202,26 @@
       </c>
       <c r="D30" s="81" t="inlineStr">
         <is>
+          <t>按URL类别圈定解密范围，排除银行/医疗等敏感类</t>
+        </is>
+      </c>
+      <c r="E30" s="81" t="inlineStr">
+        <is>
           <t>PA解密规则可按URL类别（含自定义类别）选择解密范围，可排除银行/医疗等敏感类别不解密（PA Web帮助p164）；天融信SSL解密（代理策略/代理模板）无按URL类别选择解密机制（检索无命中）</t>
         </is>
       </c>
-      <c r="E30" s="80" t="inlineStr">
+      <c r="F30" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F30" s="84" t="n"/>
-      <c r="G30" s="80" t="inlineStr">
+      <c r="G30" s="84" t="n"/>
+      <c r="H30" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H30" s="84" t="n"/>
+      <c r="I30" s="84" t="n"/>
     </row>
     <row r="31" ht="96" customHeight="1" s="1">
       <c r="A31" s="84" t="n"/>
@@ -4082,13 +4233,18 @@
       </c>
       <c r="D31" s="81" t="inlineStr">
         <is>
+          <t>SSH代理解密+SSH隧道(ssh-tunnel)识别控制</t>
+        </is>
+      </c>
+      <c r="E31" s="81" t="inlineStr">
+        <is>
           <t>PA解密策略SSH Proxy类型解密SSH通信，可通过ssh-tunnel App-ID在策略中控制SSH隧道（端口转发/内网穿透），正常SSH管理流量放行；含不受支持算法检查/资源不足阻断会话等防护（PA Web帮助p164、p318-319）；天融信手册检索无SSH代理/SSH隧道控制命中</t>
         </is>
       </c>
-      <c r="E31" s="85" t="n"/>
       <c r="F31" s="85" t="n"/>
       <c r="G31" s="85" t="n"/>
       <c r="H31" s="85" t="n"/>
+      <c r="I31" s="85" t="n"/>
     </row>
     <row r="32" ht="66" customHeight="1" s="1">
       <c r="A32" s="84" t="n"/>
@@ -4104,21 +4260,26 @@
       </c>
       <c r="D32" s="81" t="inlineStr">
         <is>
+          <t>已解密/未解密流量内联转发第三方安全链，L3路由转发</t>
+        </is>
+      </c>
+      <c r="E32" s="81" t="inlineStr">
+        <is>
           <t>PA网络数据包代理策略将已解密/未解密TLS/非TLS流量内联转发至第三方安全工具，路径选择选项卡应用数据包代理配置文件定义经路由L3安全链的转发方式（PA Web帮助p167-170）；对应矩阵#122</t>
         </is>
       </c>
-      <c r="E32" s="80" t="inlineStr">
+      <c r="F32" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F32" s="81" t="inlineStr"/>
-      <c r="G32" s="80" t="inlineStr">
+      <c r="G32" s="81" t="inlineStr"/>
+      <c r="H32" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H32" s="80" t="inlineStr">
+      <c r="I32" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
@@ -4134,21 +4295,26 @@
       </c>
       <c r="D33" s="81" t="inlineStr">
         <is>
+          <t>TLS解密/未解密/非TLS流量类型选择</t>
+        </is>
+      </c>
+      <c r="E33" s="81" t="inlineStr">
+        <is>
           <t>PA规则可选Forward TLS(Decrypted)/未解密/非TLS多种流量类型；需免费许可证（PA Web帮助p167）；天融信无网络数据包代理模块（矩阵#122）</t>
         </is>
       </c>
-      <c r="E33" s="80" t="inlineStr">
+      <c r="F33" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F33" s="81" t="inlineStr"/>
-      <c r="G33" s="80" t="inlineStr">
+      <c r="G33" s="81" t="inlineStr"/>
+      <c r="H33" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H33" s="80" t="inlineStr"/>
+      <c r="I33" s="80" t="inlineStr"/>
     </row>
     <row r="34" ht="66" customHeight="1" s="1">
       <c r="A34" s="84" t="n"/>
@@ -4164,21 +4330,26 @@
       </c>
       <c r="D34" s="81" t="inlineStr">
         <is>
+          <t>GRE/GTP-U/VXLAN/非加密IPSec隧道内层流量解封装检测</t>
+        </is>
+      </c>
+      <c r="E34" s="81" t="inlineStr">
+        <is>
           <t>PA隧道检测策略解封装并深度检测GRE/GTP-U/VXLAN/非加密IPSec（NULL加密/AH传输模式）等明文隧道内容（PA Web帮助p172-173）；对应矩阵#128/37</t>
         </is>
       </c>
-      <c r="E34" s="80" t="inlineStr">
+      <c r="F34" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F34" s="81" t="inlineStr"/>
-      <c r="G34" s="80" t="inlineStr">
+      <c r="G34" s="81" t="inlineStr"/>
+      <c r="H34" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H34" s="80" t="inlineStr">
+      <c r="I34" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
@@ -4194,21 +4365,26 @@
       </c>
       <c r="D35" s="81" t="inlineStr">
         <is>
+          <t>隧道嵌套封装最大级数限制，超限丢弃</t>
+        </is>
+      </c>
+      <c r="E35" s="81" t="inlineStr">
+        <is>
           <t>PA对隧道最大封装级数超限丢包防护，防隧道嵌套绕过（PA管理指南p655）；天融信手册无封装级数防护（检索无命中）</t>
         </is>
       </c>
-      <c r="E35" s="80" t="inlineStr">
+      <c r="F35" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F35" s="81" t="inlineStr"/>
-      <c r="G35" s="80" t="inlineStr">
+      <c r="G35" s="81" t="inlineStr"/>
+      <c r="H35" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H35" s="80" t="inlineStr"/>
+      <c r="I35" s="80" t="inlineStr"/>
     </row>
     <row r="36" ht="81" customHeight="1" s="1">
       <c r="A36" s="84" t="n"/>
@@ -4224,21 +4400,26 @@
       </c>
       <c r="D36" s="81" t="inlineStr">
         <is>
+          <t>按协议/端口自定义应用识别结果</t>
+        </is>
+      </c>
+      <c r="E36" s="81" t="inlineStr">
+        <is>
           <t>PA应用替代策略改变防火墙对网络通信的应用分类方式（如指定明文协议/端口识别，PA Web帮助p178）；天融信自定义应用允许管理员按需自定义应用协议（含端口匹配）并加入应用规则库（天融信手册《自定义应用》页）；对应矩阵#26</t>
         </is>
       </c>
-      <c r="E36" s="80" t="inlineStr">
+      <c r="F36" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F36" s="81" t="inlineStr"/>
-      <c r="G36" s="80" t="inlineStr">
+      <c r="G36" s="81" t="inlineStr"/>
+      <c r="H36" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H36" s="80" t="inlineStr">
+      <c r="I36" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
@@ -4254,21 +4435,26 @@
       </c>
       <c r="D37" s="81" t="inlineStr">
         <is>
+          <t>端口映射类覆盖识别</t>
+        </is>
+      </c>
+      <c r="E37" s="81" t="inlineStr">
+        <is>
           <t>PA支持端口式应用覆盖识别（configurable自定义应用）；天融信自定义应用允许管理员按特定需要自行定义应用协议（含端口匹配），自动添加到应用规则库供安全策略引用（天融信手册《自定义应用》页）</t>
         </is>
       </c>
-      <c r="E37" s="80" t="inlineStr">
+      <c r="F37" s="80" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="F37" s="81" t="inlineStr"/>
-      <c r="G37" s="80" t="inlineStr">
+      <c r="G37" s="81" t="inlineStr"/>
+      <c r="H37" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H37" s="80" t="inlineStr"/>
+      <c r="I37" s="80" t="inlineStr"/>
     </row>
     <row r="38" ht="96" customHeight="1" s="1">
       <c r="A38" s="84" t="n"/>
@@ -4280,21 +4466,26 @@
       </c>
       <c r="D38" s="81" t="inlineStr">
         <is>
+          <t>匹配覆盖策略的流量跳过七层检测，四层快速转发</t>
+        </is>
+      </c>
+      <c r="E38" s="81" t="inlineStr">
+        <is>
           <t>PA应用替代策略明确绕过第7层处理与威胁检查，改用第4层状态检查以加速（PA管理指南p1307）；天融信自定义应用加入规则库后仍默认经安全引擎检测（天融信手册《自定义应用》页）；迁移评估项：PA应用替代多为私有大流量业务加速，转换时需同步关闭对应策略的IPS/七层检测，否则性能被拖垮或误阻断</t>
         </is>
       </c>
-      <c r="E38" s="80" t="inlineStr">
+      <c r="F38" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F38" s="85" t="n"/>
-      <c r="G38" s="80" t="inlineStr">
+      <c r="G38" s="85" t="n"/>
+      <c r="H38" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H38" s="85" t="n"/>
+      <c r="I38" s="85" t="n"/>
     </row>
     <row r="39" ht="111" customHeight="1" s="1">
       <c r="A39" s="84" t="n"/>
@@ -4310,21 +4501,26 @@
       </c>
       <c r="D39" s="81" t="inlineStr">
         <is>
+          <t>基于用户/用户组策略，多源IP-用户映射（AD/Syslog/XML API）</t>
+        </is>
+      </c>
+      <c r="E39" s="81" t="inlineStr">
+        <is>
           <t>PA身份验证策略在访问网络资源前对用户鉴权（PA Web帮助p182），配合User-ID多源映射（AD/XML/Syslog等）；天融信用户访问网络资源前经认证，认证通过后检查关联的用户访问策略，支持门户认证（本地/外部）与LDAP/RADIUS对接（天融信手册《管理用户》《添加Radius服务器》页）；对应矩阵#3/35</t>
         </is>
       </c>
-      <c r="E39" s="80" t="inlineStr">
+      <c r="F39" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F39" s="81" t="inlineStr"/>
-      <c r="G39" s="80" t="inlineStr">
+      <c r="G39" s="81" t="inlineStr"/>
+      <c r="H39" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H39" s="80" t="inlineStr">
+      <c r="I39" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
@@ -4340,21 +4536,26 @@
       </c>
       <c r="D40" s="81" t="inlineStr">
         <is>
+          <t>认证超时+单次认证(SSO)</t>
+        </is>
+      </c>
+      <c r="E40" s="81" t="inlineStr">
+        <is>
           <t>PA支持认证超时减少重复质询、Kerberos/SAML/RADIUS等对接（PA Web帮助p186）；天融信手册检索认证超时/单点登录/SSO无命中（仅在线用户在线时长查看与强制下线）；迁移评估项：需核实天融信认证会话有效期配置与SSO对接能力</t>
         </is>
       </c>
-      <c r="E40" s="80" t="inlineStr">
+      <c r="F40" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F40" s="81" t="inlineStr"/>
-      <c r="G40" s="80" t="inlineStr">
+      <c r="G40" s="81" t="inlineStr"/>
+      <c r="H40" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H40" s="80" t="inlineStr"/>
+      <c r="I40" s="80" t="inlineStr"/>
     </row>
     <row r="41" ht="126" customHeight="1" s="1">
       <c r="A41" s="84" t="n"/>
@@ -4366,19 +4567,24 @@
       </c>
       <c r="D41" s="81" t="inlineStr">
         <is>
+          <t>策略匹配触发多因素认证质询（MFA供应商API/RADIUS）</t>
+        </is>
+      </c>
+      <c r="E41" s="81" t="inlineStr">
+        <is>
           <t>PA身份验证策略通过Authentication Enforcement对象对匹配流量强制质询，支持多因素身份验证（每因素独立超时，防火墙记录时间戳），MFA供应商API/RADIUS对接（PA Web帮助p185-186、p310、p735-742）；天融信双因子认证（密码+短信/证书/Ukey）仅限管理员/用户登录场景（天融信手册《登录安全策略》页），未见流量策略触发MFA质询</t>
         </is>
       </c>
-      <c r="E41" s="84" t="n"/>
       <c r="F41" s="84" t="n"/>
-      <c r="G41" s="80" t="inlineStr">
+      <c r="G41" s="84" t="n"/>
+      <c r="H41" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H41" s="84" t="n"/>
-    </row>
-    <row r="42" ht="81" customHeight="1" s="1">
+      <c r="I41" s="84" t="n"/>
+    </row>
+    <row r="42" ht="96" customHeight="1" s="1">
       <c r="A42" s="84" t="n"/>
       <c r="B42" s="85" t="n"/>
       <c r="C42" s="81" t="inlineStr">
@@ -4388,17 +4594,22 @@
       </c>
       <c r="D42" s="81" t="inlineStr">
         <is>
+          <t>AD域事件日志毫秒级IP-用户映射更新</t>
+        </is>
+      </c>
+      <c r="E42" s="81" t="inlineStr">
+        <is>
           <t>PA无代理架构通过读取域控事件日志实现IP-用户毫秒级动态映射，大规模部署有专项规划（PA管理指南p866-867）；天融信AD对接的轮询间隔与并发认证能力手册未量化；迁移评估项：数万AD用户且移动频繁场景需实测天融信映射更新时延，避免基于用户的策略出现间歇性未授权拦截</t>
         </is>
       </c>
-      <c r="E42" s="85" t="n"/>
       <c r="F42" s="85" t="n"/>
-      <c r="G42" s="80" t="inlineStr">
+      <c r="G42" s="85" t="n"/>
+      <c r="H42" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H42" s="85" t="n"/>
+      <c r="I42" s="85" t="n"/>
     </row>
     <row r="43" ht="111" customHeight="1" s="1">
       <c r="A43" s="84" t="n"/>
@@ -4414,21 +4625,26 @@
       </c>
       <c r="D43" s="81" t="inlineStr">
         <is>
+          <t>分类(源/目的IP粒度)+聚合(全局)双层阈值限流</t>
+        </is>
+      </c>
+      <c r="E43" s="81" t="inlineStr">
+        <is>
           <t>PA DoS策略基于源/目的接口、区域、地址、服务定义允许/拒绝/告警，规则可选聚合与分类双层DoS保护配置文件设定阈值速率（PA Web帮助p189-191、PA管理指南p1354）；天融信DDoS防护模块按防护对象（目的服务器）设阈值（pps/bps），可达目的IP粒度（天融信手册《配置策略模板》《日志查看》页）；对应矩阵#52/42</t>
         </is>
       </c>
-      <c r="E43" s="80" t="inlineStr">
+      <c r="F43" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F43" s="81" t="inlineStr"/>
-      <c r="G43" s="80" t="inlineStr">
+      <c r="G43" s="81" t="inlineStr"/>
+      <c r="H43" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H43" s="80" t="inlineStr">
+      <c r="I43" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
@@ -4444,23 +4660,28 @@
       </c>
       <c r="D44" s="81" t="inlineStr">
         <is>
+          <t>连接数/秒阈值告警+最大速率限制</t>
+        </is>
+      </c>
+      <c r="E44" s="81" t="inlineStr">
+        <is>
           <t>PA聚合DoS配置文件按传入连接数/秒触发告警与最大速率限制；天融信DDoS防护模块按阈值（pps/bps）监视并触发防护（天融信手册《配置策略模板》页）</t>
         </is>
       </c>
-      <c r="E44" s="80" t="inlineStr">
+      <c r="F44" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F44" s="81" t="inlineStr"/>
-      <c r="G44" s="80" t="inlineStr">
+      <c r="G44" s="81" t="inlineStr"/>
+      <c r="H44" s="80" t="inlineStr">
         <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="H44" s="80" t="inlineStr"/>
-    </row>
-    <row r="45" ht="156" customHeight="1" s="1">
+      <c r="I44" s="80" t="inlineStr"/>
+    </row>
+    <row r="45" ht="171" customHeight="1" s="1">
       <c r="A45" s="84" t="n"/>
       <c r="B45" s="80" t="inlineStr">
         <is>
@@ -4474,21 +4695,26 @@
       </c>
       <c r="D45" s="81" t="inlineStr">
         <is>
+          <t>HTTP/HTTPS外部文本列表(IP/域名/URL)自动拉取，策略直接引用</t>
+        </is>
+      </c>
+      <c r="E45" s="81" t="inlineStr">
+        <is>
           <t>PA外部动态列表：基于HTTP/HTTPS托管的文本文件创建IP/URL/域名/IMEI/IMSI地址对象，防火墙定时自动拉取更新，策略中直接引用（Objects&gt;External Dynamic Lists，PA Web帮助p236-239；策略源/目标可直接选EDL，p196-197）；天融信手册检索外部动态列表/EDL无命中，仅内置威胁情报库与云端威胁情报库（规则集管理，天融信手册《威胁情报》《配置规则集》页），无策略直接引用任意外部文本列表机制；迁移评估项：PA策略中引用的EDL需转换为天融信静态地址组定期导入或威胁情报联动</t>
         </is>
       </c>
-      <c r="E45" s="80" t="inlineStr">
+      <c r="F45" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F45" s="81" t="inlineStr"/>
-      <c r="G45" s="80" t="inlineStr">
+      <c r="G45" s="81" t="inlineStr"/>
+      <c r="H45" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H45" s="80" t="inlineStr"/>
+      <c r="I45" s="80" t="inlineStr"/>
     </row>
     <row r="46" ht="126" customHeight="1" s="1">
       <c r="A46" s="84" t="n"/>
@@ -4500,21 +4726,26 @@
       </c>
       <c r="D46" s="81" t="inlineStr">
         <is>
+          <t>Tag标记过滤器动态地址组，成员随IP变化自动更新</t>
+        </is>
+      </c>
+      <c r="E46" s="81" t="inlineStr">
+        <is>
           <t>PA动态地址组：查找标记(Tag)+基于标记的过滤器（AND/OR匹配）动态填充成员，VM信息源注册或XML/REST API定义标记，IP变化时策略自动生效（PA Web帮助p207-208、p228）；天融信手册检索动态地址组/标签/SDN/云平台联动无命中，地址组为静态IP/子网绑定（天融信手册《地址》页）；迁移评估项：PA云环境Tag微隔离策略需转换为静态地址组，IP漂移场景需人工或API维护</t>
         </is>
       </c>
-      <c r="E46" s="80" t="inlineStr">
+      <c r="F46" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F46" s="81" t="inlineStr"/>
-      <c r="G46" s="80" t="inlineStr">
+      <c r="G46" s="81" t="inlineStr"/>
+      <c r="H46" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H46" s="80" t="inlineStr"/>
+      <c r="I46" s="80" t="inlineStr"/>
     </row>
     <row r="47" ht="51" customHeight="1" s="1">
       <c r="A47" s="84" t="n"/>
@@ -4530,21 +4761,26 @@
       </c>
       <c r="D47" s="81" t="inlineStr">
         <is>
+          <t>按应用/区域/地址分配链路与流量分发</t>
+        </is>
+      </c>
+      <c r="E47" s="81" t="inlineStr">
+        <is>
           <t>PA SD-WAN策略按应用/抖动/延迟/丢包指标分配链路，流量分发（PA Web帮助p197）；对应矩阵#129/120</t>
         </is>
       </c>
-      <c r="E47" s="80" t="inlineStr">
+      <c r="F47" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F47" s="81" t="inlineStr"/>
-      <c r="G47" s="80" t="inlineStr">
+      <c r="G47" s="81" t="inlineStr"/>
+      <c r="H47" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H47" s="80" t="inlineStr">
+      <c r="I47" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
@@ -4560,61 +4796,66 @@
       </c>
       <c r="D48" s="81" t="inlineStr">
         <is>
+          <t>抖动/延迟/丢包(jitter/latency/loss)指标选路</t>
+        </is>
+      </c>
+      <c r="E48" s="81" t="inlineStr">
+        <is>
           <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路（PA Web帮助p195）；天融信有链路探测(ping)+智能选路(最小延迟优先)（天融信手册《策略路由》页），无jitter/latency/loss多维指标</t>
         </is>
       </c>
-      <c r="E48" s="80" t="inlineStr">
+      <c r="F48" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F48" s="81" t="inlineStr"/>
-      <c r="G48" s="80" t="inlineStr">
+      <c r="G48" s="81" t="inlineStr"/>
+      <c r="H48" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H48" s="80" t="inlineStr"/>
+      <c r="I48" s="80" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="I9:I14"/>
     <mergeCell ref="B26:B31"/>
     <mergeCell ref="B47:B48"/>
+    <mergeCell ref="H9:H10"/>
     <mergeCell ref="B43:B44"/>
-    <mergeCell ref="H3:H7"/>
-    <mergeCell ref="F16:F21"/>
+    <mergeCell ref="H6:H7"/>
     <mergeCell ref="B15:B21"/>
-    <mergeCell ref="F27:F31"/>
     <mergeCell ref="B36:B38"/>
-    <mergeCell ref="H9:H14"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="I40:I42"/>
     <mergeCell ref="B39:B42"/>
-    <mergeCell ref="E16:E18"/>
     <mergeCell ref="B2:B7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H27:H31"/>
+    <mergeCell ref="H11:H14"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="I16:I21"/>
     <mergeCell ref="B34:B35"/>
-    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="I37:I38"/>
     <mergeCell ref="B24:B25"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="F27:F28"/>
     <mergeCell ref="F40:F42"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="H16:H21"/>
-    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="H16:H19"/>
     <mergeCell ref="F3:F7"/>
+    <mergeCell ref="G27:G31"/>
+    <mergeCell ref="I27:I31"/>
     <mergeCell ref="B45:B46"/>
-    <mergeCell ref="H40:H42"/>
-    <mergeCell ref="G9:G10"/>
     <mergeCell ref="B32:B33"/>
+    <mergeCell ref="H30:H31"/>
     <mergeCell ref="B22:B23"/>
-    <mergeCell ref="F9:F14"/>
+    <mergeCell ref="G3:G7"/>
     <mergeCell ref="B8:B14"/>
-    <mergeCell ref="G16:G19"/>
+    <mergeCell ref="I3:I7"/>
+    <mergeCell ref="G16:G21"/>
     <mergeCell ref="A2:A48"/>
-    <mergeCell ref="G11:G14"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="G9:G14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4626,17 +4867,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.2"/>
   <cols>
     <col width="11.7" customWidth="1" style="1" min="1" max="1"/>
     <col width="19.7" customWidth="1" style="1" min="2" max="2"/>
-    <col width="48" customWidth="1" style="1" min="3" max="3"/>
-    <col width="55" customWidth="1" style="1" min="4" max="4"/>
-    <col width="7.7" customWidth="1" style="1" min="5" max="5"/>
-    <col width="20" customWidth="1" style="1" min="6" max="6"/>
-    <col width="12" customWidth="1" style="1" min="7" max="7"/>
-    <col width="9.699999999999999" customWidth="1" style="1" min="8" max="8"/>
+    <col width="40" customWidth="1" style="1" min="3" max="3"/>
+    <col width="30" customWidth="1" style="1" min="4" max="4"/>
+    <col width="62" customWidth="1" style="1" min="5" max="5"/>
+    <col width="7.7" customWidth="1" style="1" min="6" max="6"/>
+    <col width="18" customWidth="1" style="1" min="7" max="7"/>
+    <col width="10" customWidth="1" style="1" min="8" max="8"/>
+    <col width="9.699999999999999" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" s="1">
@@ -4662,20 +4904,25 @@
       </c>
       <c r="E1" s="79" t="inlineStr">
         <is>
+          <t>对比依据（PA证据·天融信现状）</t>
+        </is>
+      </c>
+      <c r="F1" s="79" t="inlineStr">
+        <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="F1" s="79" t="inlineStr">
+      <c r="G1" s="79" t="inlineStr">
         <is>
           <t>交付/规划说明</t>
         </is>
       </c>
-      <c r="G1" s="79" t="inlineStr">
+      <c r="H1" s="79" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="H1" s="79" t="inlineStr">
+      <c r="I1" s="79" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
@@ -4699,21 +4946,26 @@
       </c>
       <c r="D2" s="81" t="inlineStr">
         <is>
+          <t>提交/修改策略须填写审核注释并留存历史，可导出</t>
+        </is>
+      </c>
+      <c r="E2" s="81" t="inlineStr">
+        <is>
           <t>PA记录规则的审核注释历史/配置日志/规则更改历史，可CSV导出，用于策略变更审计（PA Web帮助p116-117）；天融信仅规则描述字段，无审核注释存档</t>
         </is>
       </c>
-      <c r="E2" s="80" t="inlineStr">
+      <c r="F2" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F2" s="81" t="inlineStr"/>
-      <c r="G2" s="80" t="inlineStr">
+      <c r="G2" s="81" t="inlineStr"/>
+      <c r="H2" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H2" s="80" t="inlineStr"/>
+      <c r="I2" s="80" t="inlineStr"/>
     </row>
     <row r="3" ht="111" customHeight="1" s="1">
       <c r="A3" s="82" t="n"/>
@@ -4725,21 +4977,26 @@
       </c>
       <c r="D3" s="81" t="inlineStr">
         <is>
+          <t>前置规则→本地规则→后置规则三层按序合并为单层规则链</t>
+        </is>
+      </c>
+      <c r="E3" s="81" t="inlineStr">
+        <is>
           <t>PA在Panorama集中管理下策略分为前置规则（设备组共享，最优先）/本地规则/后置规则三层按序匹配（层级机制属Panorama管理平台，PA两册手册未详载）；天融信为自上而下单层规则链一张表走到底（天融信手册《配置访问控制策略》页）；迁移评估项：需制定全局多级策略到单层扁平化策略的合并清洗规则（Pre→本地→Post按序展开映射）</t>
         </is>
       </c>
-      <c r="E3" s="80" t="inlineStr">
+      <c r="F3" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F3" s="81" t="inlineStr"/>
-      <c r="G3" s="80" t="inlineStr">
+      <c r="G3" s="81" t="inlineStr"/>
+      <c r="H3" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H3" s="80" t="inlineStr"/>
+      <c r="I3" s="80" t="inlineStr"/>
     </row>
     <row r="4" ht="96" customHeight="1" s="1">
       <c r="A4" s="82" t="n"/>
@@ -4751,15 +5008,20 @@
       </c>
       <c r="D4" s="81" t="inlineStr">
         <is>
+          <t>应用程序对象级会话超时，覆盖全局TCP/UDP超时</t>
+        </is>
+      </c>
+      <c r="E4" s="81" t="inlineStr">
+        <is>
           <t>PA除全局TCP/UDP会话超时外，可在应用程序对象上定义专用超时，匹配该应用的流量覆盖全局值（PA Web帮助p215、p695）；天融信手册未见应用级超时覆盖（仅SSLVPN会话超时设置与黑名单老化）；迁移评估项：需排查现网PA为数据库/长连接业务单独配置的应用超时并逐条转换，否则长连接业务频繁中断</t>
         </is>
       </c>
-      <c r="E4" s="82" t="n"/>
       <c r="F4" s="82" t="n"/>
       <c r="G4" s="82" t="n"/>
       <c r="H4" s="82" t="n"/>
-    </row>
-    <row r="5" ht="81" customHeight="1" s="1">
+      <c r="I4" s="82" t="n"/>
+    </row>
+    <row r="5" ht="96" customHeight="1" s="1">
       <c r="A5" s="82" t="n"/>
       <c r="B5" s="80" t="inlineStr">
         <is>
@@ -4773,21 +5035,26 @@
       </c>
       <c r="D5" s="81" t="inlineStr">
         <is>
+          <t>预登录用户/HIP主机信息/设备对象/应用默认端口规避/会话结束日志等构建块</t>
+        </is>
+      </c>
+      <c r="E5" s="81" t="inlineStr">
+        <is>
           <t>PA规则构建块含预登录用户、HIP配置文件、设备对象、应用默认端口规避、会话结束日志等；天融信支持用户/应用/服务/日志构建块，但无HIP主机信息配置文件与设备对象等价物，仅有EDR联动上报终端资产并下发管控策略（天融信手册《与EDR联动》页）；对应矩阵#3/4</t>
         </is>
       </c>
-      <c r="E5" s="80" t="inlineStr">
+      <c r="F5" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F5" s="81" t="inlineStr"/>
-      <c r="G5" s="80" t="inlineStr">
+      <c r="G5" s="81" t="inlineStr"/>
+      <c r="H5" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H5" s="80" t="inlineStr"/>
+      <c r="I5" s="80" t="inlineStr"/>
     </row>
     <row r="6" ht="81" customHeight="1" s="1">
       <c r="A6" s="82" t="n"/>
@@ -4799,21 +5066,26 @@
       </c>
       <c r="D6" s="81" t="inlineStr">
         <is>
+          <t>端口(L4)规则一键迁移为应用(L7)规则+新应用查看器</t>
+        </is>
+      </c>
+      <c r="E6" s="81" t="inlineStr">
+        <is>
           <t>PA新应用查看器+端口规则迁移至App-ID规则工作流+规则使用统计，减少攻击面（PA Web帮助p142）；天融信策略统计开关可显示规则匹配命中情况（天融信手册《配置访问控制策略》页），但无新应用查看器与端口→应用规则迁移工作流；对应矩阵#132</t>
         </is>
       </c>
-      <c r="E6" s="80" t="inlineStr">
+      <c r="F6" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F6" s="81" t="inlineStr"/>
-      <c r="G6" s="80" t="inlineStr">
+      <c r="G6" s="81" t="inlineStr"/>
+      <c r="H6" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H6" s="80" t="inlineStr"/>
+      <c r="I6" s="80" t="inlineStr"/>
     </row>
     <row r="7" ht="36" customHeight="1" s="1">
       <c r="A7" s="82" t="n"/>
@@ -4825,17 +5097,22 @@
       </c>
       <c r="D7" s="81" t="inlineStr">
         <is>
+          <t>配置锁/提交锁，防止多管理员并发修改</t>
+        </is>
+      </c>
+      <c r="E7" s="81" t="inlineStr">
+        <is>
           <t>PA可锁定待选配置或提交，防止他管理员并发更改；对应矩阵#135（天融信不支持，PA优势）</t>
         </is>
       </c>
-      <c r="E7" s="82" t="n"/>
       <c r="F7" s="82" t="n"/>
-      <c r="G7" s="80" t="inlineStr">
+      <c r="G7" s="82" t="n"/>
+      <c r="H7" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H7" s="82" t="n"/>
+      <c r="I7" s="82" t="n"/>
     </row>
     <row r="8" ht="111" customHeight="1" s="1">
       <c r="A8" s="82" t="n"/>
@@ -4847,17 +5124,22 @@
       </c>
       <c r="D8" s="81" t="inlineStr">
         <is>
+          <t>应用匹配同时强制使用标准端口，非标端口拒绝</t>
+        </is>
+      </c>
+      <c r="E8" s="81" t="inlineStr">
+        <is>
           <t>PA安全策略默认服务为application-default：放行应用同时强制其使用标准端口（如SSH仅22），非标准端口不匹配即拦截（PA管理指南p904）；天融信策略为五元组+应用识别组合（天融信手册《配置访问控制策略》页）；迁移评估项：直接转换若仅保留应用识别不限端口将扩大安全敞口，需制定应用标准端口映射限制（App-Default）转换方案；对应矩阵#2</t>
         </is>
       </c>
-      <c r="E8" s="80" t="inlineStr">
+      <c r="F8" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F8" s="82" t="n"/>
       <c r="G8" s="82" t="n"/>
       <c r="H8" s="82" t="n"/>
+      <c r="I8" s="82" t="n"/>
     </row>
     <row r="9" ht="81" customHeight="1" s="1">
       <c r="A9" s="82" t="n"/>
@@ -4869,17 +5151,22 @@
       </c>
       <c r="D9" s="81" t="inlineStr">
         <is>
+          <t>Allow动作关联反病毒/漏洞防护/URL过滤/文件阻断/WildFire配置文件组</t>
+        </is>
+      </c>
+      <c r="E9" s="81" t="inlineStr">
+        <is>
           <t>PA安全策略Allow动作关联Profile组（反病毒/漏洞防护/URL过滤/文件阻止/WildFire等，PA Web帮助p304）；天融信一体化策略引擎自带检测项；迁移评估项：需评估Profile组到天融信各检测引擎的映射与缺省动作差异；对应矩阵#4</t>
         </is>
       </c>
-      <c r="E9" s="80" t="inlineStr">
+      <c r="F9" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F9" s="82" t="n"/>
       <c r="G9" s="82" t="n"/>
       <c r="H9" s="82" t="n"/>
+      <c r="I9" s="82" t="n"/>
     </row>
     <row r="10" ht="156" customHeight="1" s="1">
       <c r="A10" s="82" t="n"/>
@@ -4891,19 +5178,24 @@
       </c>
       <c r="D10" s="81" t="inlineStr">
         <is>
+          <t>同区域默认放行/跨区域默认拒绝，支持替代与日志转发</t>
+        </is>
+      </c>
+      <c r="E10" s="81" t="inlineStr">
+        <is>
           <t>PA安全策略库末尾自带两条隐式系统规则：区域内默认（同Zone默认放行）与区域间默认（跨Zone默认拒绝），可被替代配置，替代字段含日志转发配置文件与Log at Session End在会话结束时记录（PA Web帮助p134-136）；天融信未见同区域默认放行的隐式规则机制；迁移评估项：①必须提取intrazone-default同Zone互访需求并显式转换为放行规则，否则割接后同Zone不同网段/VLAN互访将被默认拦截；②需在新设备补齐底部兜底Deny-All并开启日志，否则被拒流量查无日志、排障困难</t>
         </is>
       </c>
-      <c r="E10" s="80" t="inlineStr">
+      <c r="F10" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F10" s="82" t="n"/>
       <c r="G10" s="82" t="n"/>
       <c r="H10" s="82" t="n"/>
-    </row>
-    <row r="11" ht="111" customHeight="1" s="1">
+      <c r="I10" s="82" t="n"/>
+    </row>
+    <row r="11" ht="126" customHeight="1" s="1">
       <c r="A11" s="82" t="n"/>
       <c r="B11" s="80" t="inlineStr">
         <is>
@@ -4917,21 +5209,26 @@
       </c>
       <c r="D11" s="81" t="inlineStr">
         <is>
+          <t>目的区域按NAT后路由查找；源/目的地址用NAT前值</t>
+        </is>
+      </c>
+      <c r="E11" s="81" t="inlineStr">
+        <is>
           <t>PA底层为『先NAT判断后安全策略匹配』的因果倒置：安全策略要求源区域(NAT前)+源地址(NAT前)+目的地址(NAT前)+目的区域(NAT后按路由查找)，极其反直觉；天融信地址转换为独立策略库常规直观映射（安全策略&gt;地址转换，天融信手册《服务器映射》页）；迁移评估项：带目的NAT的策略平移后易因Zone填写错误不通，需制定NAT查表逻辑转换映射规范；对应矩阵#9</t>
         </is>
       </c>
-      <c r="E11" s="80" t="inlineStr">
+      <c r="F11" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F11" s="81" t="inlineStr"/>
-      <c r="G11" s="80" t="inlineStr">
+      <c r="G11" s="81" t="inlineStr"/>
+      <c r="H11" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H11" s="80" t="inlineStr"/>
+      <c r="I11" s="80" t="inlineStr"/>
     </row>
     <row r="12" ht="81" customHeight="1" s="1">
       <c r="A12" s="82" t="n"/>
@@ -4943,21 +5240,26 @@
       </c>
       <c r="D12" s="81" t="inlineStr">
         <is>
+          <t>主动/主动HA下NAT规则绑定会话所有者</t>
+        </is>
+      </c>
+      <c r="E12" s="81" t="inlineStr">
+        <is>
           <t>PA主动/主动HA配置下NAT规则可绑定会话所有者/会话设置，控制NAT会话的设备绑定，仅A/A模式可见（PA Web帮助p150）；天融信HA为主备双机热备模式（天融信手册《配置双机热备功能》页），无主动/主动模式及NAT规则绑定机制</t>
         </is>
       </c>
-      <c r="E12" s="80" t="inlineStr">
+      <c r="F12" s="80" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="F12" s="81" t="inlineStr"/>
-      <c r="G12" s="80" t="inlineStr">
+      <c r="G12" s="81" t="inlineStr"/>
+      <c r="H12" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H12" s="80" t="inlineStr"/>
+      <c r="I12" s="80" t="inlineStr"/>
     </row>
     <row r="13" ht="96" customHeight="1" s="1">
       <c r="A13" s="82" t="n"/>
@@ -4973,23 +5275,28 @@
       </c>
       <c r="D13" s="81" t="inlineStr">
         <is>
+          <t>QoS规则按DSCP/ToS值匹配调度</t>
+        </is>
+      </c>
+      <c r="E13" s="81" t="inlineStr">
+        <is>
           <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
         </is>
       </c>
-      <c r="E13" s="80" t="inlineStr">
+      <c r="F13" s="80" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="F13" s="81" t="inlineStr"/>
-      <c r="G13" s="80" t="inlineStr">
+      <c r="G13" s="81" t="inlineStr"/>
+      <c r="H13" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H13" s="80" t="inlineStr"/>
-    </row>
-    <row r="14" ht="96" customHeight="1" s="1">
+      <c r="I13" s="80" t="inlineStr"/>
+    </row>
+    <row r="14" ht="111" customHeight="1" s="1">
       <c r="A14" s="82" t="n"/>
       <c r="B14" s="80" t="inlineStr">
         <is>
@@ -5003,21 +5310,26 @@
       </c>
       <c r="D14" s="81" t="inlineStr">
         <is>
+          <t>记录入接口MAC，回包强制原路返回</t>
+        </is>
+      </c>
+      <c r="E14" s="81" t="inlineStr">
+        <is>
           <t>PA对称返回：虚拟路由器替代返回流量的路由查找，将流量引导回接收SYN数据包的MAC地址（ARP表确定下一跳），双ISP双活/非对称路由核心机制（PA管理指南p1294）；天融信手册检索无对称返回/回程机制命中，策略路由与LLB的回程保障能力待验证；迁移评估项：多ISP双活环境需实测天融信回包路由对称性，否则现网业务中断</t>
         </is>
       </c>
-      <c r="E14" s="80" t="inlineStr">
+      <c r="F14" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F14" s="81" t="inlineStr"/>
-      <c r="G14" s="80" t="inlineStr">
+      <c r="G14" s="81" t="inlineStr"/>
+      <c r="H14" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H14" s="80" t="inlineStr"/>
+      <c r="I14" s="80" t="inlineStr"/>
     </row>
     <row r="15" ht="51" customHeight="1" s="1">
       <c r="A15" s="82" t="n"/>
@@ -5033,21 +5345,26 @@
       </c>
       <c r="D15" s="81" t="inlineStr">
         <is>
+          <t>解密后明文流量镜像至专用接口供第三方分析</t>
+        </is>
+      </c>
+      <c r="E15" s="81" t="inlineStr">
+        <is>
           <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证（PA管理指南p1059）；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
         </is>
       </c>
-      <c r="E15" s="80" t="inlineStr">
+      <c r="F15" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F15" s="81" t="inlineStr"/>
-      <c r="G15" s="80" t="inlineStr">
+      <c r="G15" s="81" t="inlineStr"/>
+      <c r="H15" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H15" s="80" t="inlineStr"/>
+      <c r="I15" s="80" t="inlineStr"/>
     </row>
     <row r="16" ht="126" customHeight="1" s="1">
       <c r="A16" s="82" t="n"/>
@@ -5059,21 +5376,26 @@
       </c>
       <c r="D16" s="81" t="inlineStr">
         <is>
+          <t>外部无效证书以不受信转发证书重签，保留浏览器告警</t>
+        </is>
+      </c>
+      <c r="E16" s="81" t="inlineStr">
+        <is>
           <t>PA转发代理遇外部过期/不受信证书时，不用内部信任CA重签，而是专用Forward Untrust Certificate重签名，让浏览器保留不受信告警（PA管理指南p994、p1030）；天融信SSL解密（透明代理/服务器SSL解密，天融信手册《代理策略》页）未见受信/不受信双证书体系；迁移评估项：需验证天融信对外部无效证书的处理方式，避免直接阻断（白屏）或信任重签（掩盖风险）</t>
         </is>
       </c>
-      <c r="E16" s="80" t="inlineStr">
+      <c r="F16" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F16" s="81" t="inlineStr"/>
-      <c r="G16" s="80" t="inlineStr">
+      <c r="G16" s="81" t="inlineStr"/>
+      <c r="H16" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H16" s="80" t="inlineStr"/>
+      <c r="I16" s="80" t="inlineStr"/>
     </row>
     <row r="17" ht="66" customHeight="1" s="1">
       <c r="A17" s="82" t="n"/>
@@ -5085,21 +5407,26 @@
       </c>
       <c r="D17" s="81" t="inlineStr">
         <is>
+          <t>按URL类别圈定解密范围，排除银行/医疗等敏感类</t>
+        </is>
+      </c>
+      <c r="E17" s="81" t="inlineStr">
+        <is>
           <t>PA解密规则可按URL类别（含自定义类别）选择解密范围，可排除银行/医疗等敏感类别不解密（PA Web帮助p164）；天融信SSL解密（代理策略/代理模板）无按URL类别选择解密机制（检索无命中）</t>
         </is>
       </c>
-      <c r="E17" s="80" t="inlineStr">
+      <c r="F17" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F17" s="82" t="n"/>
-      <c r="G17" s="80" t="inlineStr">
+      <c r="G17" s="82" t="n"/>
+      <c r="H17" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H17" s="82" t="n"/>
+      <c r="I17" s="82" t="n"/>
     </row>
     <row r="18" ht="96" customHeight="1" s="1">
       <c r="A18" s="82" t="n"/>
@@ -5111,13 +5438,18 @@
       </c>
       <c r="D18" s="81" t="inlineStr">
         <is>
+          <t>SSH代理解密+SSH隧道(ssh-tunnel)识别控制</t>
+        </is>
+      </c>
+      <c r="E18" s="81" t="inlineStr">
+        <is>
           <t>PA解密策略SSH Proxy类型解密SSH通信，可通过ssh-tunnel App-ID在策略中控制SSH隧道（端口转发/内网穿透），正常SSH管理流量放行；含不受支持算法检查/资源不足阻断会话等防护（PA Web帮助p164、p318-319）；天融信手册检索无SSH代理/SSH隧道控制命中</t>
         </is>
       </c>
-      <c r="E18" s="82" t="n"/>
       <c r="F18" s="82" t="n"/>
       <c r="G18" s="82" t="n"/>
       <c r="H18" s="82" t="n"/>
+      <c r="I18" s="82" t="n"/>
     </row>
     <row r="19" ht="66" customHeight="1" s="1">
       <c r="A19" s="82" t="n"/>
@@ -5133,21 +5465,26 @@
       </c>
       <c r="D19" s="81" t="inlineStr">
         <is>
+          <t>已解密/未解密流量内联转发第三方安全链，L3路由转发</t>
+        </is>
+      </c>
+      <c r="E19" s="81" t="inlineStr">
+        <is>
           <t>PA网络数据包代理策略将已解密/未解密TLS/非TLS流量内联转发至第三方安全工具，路径选择选项卡应用数据包代理配置文件定义经路由L3安全链的转发方式（PA Web帮助p167-170）；对应矩阵#122</t>
         </is>
       </c>
-      <c r="E19" s="80" t="inlineStr">
+      <c r="F19" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F19" s="81" t="inlineStr"/>
-      <c r="G19" s="80" t="inlineStr">
+      <c r="G19" s="81" t="inlineStr"/>
+      <c r="H19" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H19" s="80" t="inlineStr">
+      <c r="I19" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
@@ -5163,21 +5500,26 @@
       </c>
       <c r="D20" s="81" t="inlineStr">
         <is>
+          <t>TLS解密/未解密/非TLS流量类型选择</t>
+        </is>
+      </c>
+      <c r="E20" s="81" t="inlineStr">
+        <is>
           <t>PA规则可选Forward TLS(Decrypted)/未解密/非TLS多种流量类型；需免费许可证（PA Web帮助p167）；天融信无网络数据包代理模块（矩阵#122）</t>
         </is>
       </c>
-      <c r="E20" s="80" t="inlineStr">
+      <c r="F20" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F20" s="81" t="inlineStr"/>
-      <c r="G20" s="80" t="inlineStr">
+      <c r="G20" s="81" t="inlineStr"/>
+      <c r="H20" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H20" s="80" t="inlineStr"/>
+      <c r="I20" s="80" t="inlineStr"/>
     </row>
     <row r="21" ht="66" customHeight="1" s="1">
       <c r="A21" s="82" t="n"/>
@@ -5193,21 +5535,26 @@
       </c>
       <c r="D21" s="81" t="inlineStr">
         <is>
+          <t>GRE/GTP-U/VXLAN/非加密IPSec隧道内层流量解封装检测</t>
+        </is>
+      </c>
+      <c r="E21" s="81" t="inlineStr">
+        <is>
           <t>PA隧道检测策略解封装并深度检测GRE/GTP-U/VXLAN/非加密IPSec（NULL加密/AH传输模式）等明文隧道内容（PA Web帮助p172-173）；对应矩阵#128/37</t>
         </is>
       </c>
-      <c r="E21" s="80" t="inlineStr">
+      <c r="F21" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F21" s="81" t="inlineStr"/>
-      <c r="G21" s="80" t="inlineStr">
+      <c r="G21" s="81" t="inlineStr"/>
+      <c r="H21" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H21" s="80" t="inlineStr">
+      <c r="I21" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
@@ -5223,21 +5570,26 @@
       </c>
       <c r="D22" s="81" t="inlineStr">
         <is>
+          <t>隧道嵌套封装最大级数限制，超限丢弃</t>
+        </is>
+      </c>
+      <c r="E22" s="81" t="inlineStr">
+        <is>
           <t>PA对隧道最大封装级数超限丢包防护，防隧道嵌套绕过（PA管理指南p655）；天融信手册无封装级数防护（检索无命中）</t>
         </is>
       </c>
-      <c r="E22" s="80" t="inlineStr">
+      <c r="F22" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F22" s="81" t="inlineStr"/>
-      <c r="G22" s="80" t="inlineStr">
+      <c r="G22" s="81" t="inlineStr"/>
+      <c r="H22" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H22" s="80" t="inlineStr"/>
+      <c r="I22" s="80" t="inlineStr"/>
     </row>
     <row r="23" ht="96" customHeight="1" s="1">
       <c r="A23" s="82" t="n"/>
@@ -5253,21 +5605,26 @@
       </c>
       <c r="D23" s="81" t="inlineStr">
         <is>
+          <t>匹配覆盖策略的流量跳过七层检测，四层快速转发</t>
+        </is>
+      </c>
+      <c r="E23" s="81" t="inlineStr">
+        <is>
           <t>PA应用替代策略明确绕过第7层处理与威胁检查，改用第4层状态检查以加速（PA管理指南p1307）；天融信自定义应用加入规则库后仍默认经安全引擎检测（天融信手册《自定义应用》页）；迁移评估项：PA应用替代多为私有大流量业务加速，转换时需同步关闭对应策略的IPS/七层检测，否则性能被拖垮或误阻断</t>
         </is>
       </c>
-      <c r="E23" s="80" t="inlineStr">
+      <c r="F23" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F23" s="81" t="inlineStr"/>
-      <c r="G23" s="80" t="inlineStr">
+      <c r="G23" s="81" t="inlineStr"/>
+      <c r="H23" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H23" s="80" t="inlineStr"/>
+      <c r="I23" s="80" t="inlineStr"/>
     </row>
     <row r="24" ht="81" customHeight="1" s="1">
       <c r="A24" s="82" t="n"/>
@@ -5283,21 +5640,26 @@
       </c>
       <c r="D24" s="81" t="inlineStr">
         <is>
+          <t>认证超时+单次认证(SSO)</t>
+        </is>
+      </c>
+      <c r="E24" s="81" t="inlineStr">
+        <is>
           <t>PA支持认证超时减少重复质询、Kerberos/SAML/RADIUS等对接（PA Web帮助p186）；天融信手册检索认证超时/单点登录/SSO无命中（仅在线用户在线时长查看与强制下线）；迁移评估项：需核实天融信认证会话有效期配置与SSO对接能力</t>
         </is>
       </c>
-      <c r="E24" s="80" t="inlineStr">
+      <c r="F24" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F24" s="81" t="inlineStr"/>
-      <c r="G24" s="80" t="inlineStr">
+      <c r="G24" s="81" t="inlineStr"/>
+      <c r="H24" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H24" s="80" t="inlineStr"/>
+      <c r="I24" s="80" t="inlineStr"/>
     </row>
     <row r="25" ht="126" customHeight="1" s="1">
       <c r="A25" s="82" t="n"/>
@@ -5309,23 +5671,28 @@
       </c>
       <c r="D25" s="81" t="inlineStr">
         <is>
+          <t>策略匹配触发多因素认证质询（MFA供应商API/RADIUS）</t>
+        </is>
+      </c>
+      <c r="E25" s="81" t="inlineStr">
+        <is>
           <t>PA身份验证策略通过Authentication Enforcement对象对匹配流量强制质询，支持多因素身份验证（每因素独立超时，防火墙记录时间戳），MFA供应商API/RADIUS对接（PA Web帮助p185-186、p310、p735-742）；天融信双因子认证（密码+短信/证书/Ukey）仅限管理员/用户登录场景（天融信手册《登录安全策略》页），未见流量策略触发MFA质询</t>
         </is>
       </c>
-      <c r="E25" s="80" t="inlineStr">
+      <c r="F25" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F25" s="81" t="inlineStr"/>
-      <c r="G25" s="80" t="inlineStr">
+      <c r="G25" s="81" t="inlineStr"/>
+      <c r="H25" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H25" s="80" t="inlineStr"/>
-    </row>
-    <row r="26" ht="81" customHeight="1" s="1">
+      <c r="I25" s="80" t="inlineStr"/>
+    </row>
+    <row r="26" ht="96" customHeight="1" s="1">
       <c r="A26" s="82" t="n"/>
       <c r="B26" s="82" t="n"/>
       <c r="C26" s="81" t="inlineStr">
@@ -5335,19 +5702,24 @@
       </c>
       <c r="D26" s="81" t="inlineStr">
         <is>
+          <t>AD域事件日志毫秒级IP-用户映射更新</t>
+        </is>
+      </c>
+      <c r="E26" s="81" t="inlineStr">
+        <is>
           <t>PA无代理架构通过读取域控事件日志实现IP-用户毫秒级动态映射，大规模部署有专项规划（PA管理指南p866-867）；天融信AD对接的轮询间隔与并发认证能力手册未量化；迁移评估项：数万AD用户且移动频繁场景需实测天融信映射更新时延，避免基于用户的策略出现间歇性未授权拦截</t>
         </is>
       </c>
-      <c r="E26" s="82" t="n"/>
       <c r="F26" s="82" t="n"/>
-      <c r="G26" s="80" t="inlineStr">
+      <c r="G26" s="82" t="n"/>
+      <c r="H26" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="H26" s="82" t="n"/>
-    </row>
-    <row r="27" ht="156" customHeight="1" s="1">
+      <c r="I26" s="82" t="n"/>
+    </row>
+    <row r="27" ht="171" customHeight="1" s="1">
       <c r="A27" s="82" t="n"/>
       <c r="B27" s="80" t="inlineStr">
         <is>
@@ -5361,21 +5733,26 @@
       </c>
       <c r="D27" s="81" t="inlineStr">
         <is>
+          <t>HTTP/HTTPS外部文本列表(IP/域名/URL)自动拉取，策略直接引用</t>
+        </is>
+      </c>
+      <c r="E27" s="81" t="inlineStr">
+        <is>
           <t>PA外部动态列表：基于HTTP/HTTPS托管的文本文件创建IP/URL/域名/IMEI/IMSI地址对象，防火墙定时自动拉取更新，策略中直接引用（Objects&gt;External Dynamic Lists，PA Web帮助p236-239；策略源/目标可直接选EDL，p196-197）；天融信手册检索外部动态列表/EDL无命中，仅内置威胁情报库与云端威胁情报库（规则集管理，天融信手册《威胁情报》《配置规则集》页），无策略直接引用任意外部文本列表机制；迁移评估项：PA策略中引用的EDL需转换为天融信静态地址组定期导入或威胁情报联动</t>
         </is>
       </c>
-      <c r="E27" s="80" t="inlineStr">
+      <c r="F27" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F27" s="81" t="inlineStr"/>
-      <c r="G27" s="80" t="inlineStr">
+      <c r="G27" s="81" t="inlineStr"/>
+      <c r="H27" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H27" s="80" t="inlineStr"/>
+      <c r="I27" s="80" t="inlineStr"/>
     </row>
     <row r="28" ht="126" customHeight="1" s="1">
       <c r="A28" s="82" t="n"/>
@@ -5387,21 +5764,26 @@
       </c>
       <c r="D28" s="81" t="inlineStr">
         <is>
+          <t>Tag标记过滤器动态地址组，成员随IP变化自动更新</t>
+        </is>
+      </c>
+      <c r="E28" s="81" t="inlineStr">
+        <is>
           <t>PA动态地址组：查找标记(Tag)+基于标记的过滤器（AND/OR匹配）动态填充成员，VM信息源注册或XML/REST API定义标记，IP变化时策略自动生效（PA Web帮助p207-208、p228）；天融信手册检索动态地址组/标签/SDN/云平台联动无命中，地址组为静态IP/子网绑定（天融信手册《地址》页）；迁移评估项：PA云环境Tag微隔离策略需转换为静态地址组，IP漂移场景需人工或API维护</t>
         </is>
       </c>
-      <c r="E28" s="80" t="inlineStr">
+      <c r="F28" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F28" s="81" t="inlineStr"/>
-      <c r="G28" s="80" t="inlineStr">
+      <c r="G28" s="81" t="inlineStr"/>
+      <c r="H28" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="H28" s="80" t="inlineStr"/>
+      <c r="I28" s="80" t="inlineStr"/>
     </row>
     <row r="29" ht="51" customHeight="1" s="1">
       <c r="A29" s="82" t="n"/>
@@ -5417,21 +5799,26 @@
       </c>
       <c r="D29" s="81" t="inlineStr">
         <is>
+          <t>按应用/区域/地址分配链路与流量分发</t>
+        </is>
+      </c>
+      <c r="E29" s="81" t="inlineStr">
+        <is>
           <t>PA SD-WAN策略按应用/抖动/延迟/丢包指标分配链路，流量分发（PA Web帮助p197）；对应矩阵#129/120</t>
         </is>
       </c>
-      <c r="E29" s="80" t="inlineStr">
+      <c r="F29" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="F29" s="81" t="inlineStr"/>
-      <c r="G29" s="80" t="inlineStr">
+      <c r="G29" s="81" t="inlineStr"/>
+      <c r="H29" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H29" s="80" t="inlineStr">
+      <c r="I29" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
@@ -5447,49 +5834,54 @@
       </c>
       <c r="D30" s="81" t="inlineStr">
         <is>
+          <t>抖动/延迟/丢包(jitter/latency/loss)指标选路</t>
+        </is>
+      </c>
+      <c r="E30" s="81" t="inlineStr">
+        <is>
           <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路（PA Web帮助p195）；天融信有链路探测(ping)+智能选路(最小延迟优先)（天融信手册《策略路由》页），无jitter/latency/loss多维指标</t>
         </is>
       </c>
-      <c r="E30" s="80" t="inlineStr">
+      <c r="F30" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F30" s="81" t="inlineStr"/>
-      <c r="G30" s="80" t="inlineStr">
+      <c r="G30" s="81" t="inlineStr"/>
+      <c r="H30" s="80" t="inlineStr">
         <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="H30" s="80" t="inlineStr"/>
+      <c r="I30" s="80" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="25">
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="G17:G18"/>
     <mergeCell ref="F25:F26"/>
-    <mergeCell ref="H16:H18"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="B24:B26"/>
-    <mergeCell ref="G7:G10"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="A2:A30"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="F17:F18"/>
     <mergeCell ref="G3:G4"/>
-    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="I6:I10"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="H7:H10"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="F6:F10"/>
     <mergeCell ref="B15:B18"/>
     <mergeCell ref="B2:B4"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="I16:I18"/>
     <mergeCell ref="B5:B10"/>
-    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="G6:G10"/>
     <mergeCell ref="B21:B22"/>
+    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA替代需求列表.xlsx
+++ b/PA替代需求列表.xlsx
@@ -3279,7 +3279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.7" customWidth="1" style="1" min="1" max="1"/>
@@ -3557,22 +3557,22 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="96" customHeight="1" s="1">
+    <row r="9" ht="51" customHeight="1" s="1">
       <c r="A9" s="84" t="n"/>
       <c r="B9" s="84" t="n"/>
       <c r="C9" s="81" t="inlineStr">
         <is>
-          <t>支持安全策略规则构建块：源用户/HIP/设备/应用/服务/日志等</t>
+          <t>支持HIP主机信息配置文件策略匹配（Host Information Profile）</t>
         </is>
       </c>
       <c r="D9" s="81" t="inlineStr">
         <is>
-          <t>预登录用户/HIP主机信息/设备对象/应用默认端口规避/会话结束日志等构建块</t>
+          <t>终端安全态势（补丁/杀软/磁盘加密等）作为策略匹配条件</t>
         </is>
       </c>
       <c r="E9" s="81" t="inlineStr">
         <is>
-          <t>PA规则构建块含预登录用户、HIP配置文件、设备对象、应用默认端口规避、会话结束日志等；天融信支持用户/应用/服务/日志构建块，但无HIP主机信息配置文件与设备对象等价物，仅有EDR联动上报终端资产并下发管控策略（天融信手册《与EDR联动》页）；对应矩阵#3/4</t>
+          <t>PA规则构建块支持HIP配置文件匹配终端安全态势（对应矩阵#3/4）；天融信手册检索HIP/主机信息配置文件无命中，无终端安全态势匹配等价物</t>
         </is>
       </c>
       <c r="F9" s="80" t="inlineStr">
@@ -3583,197 +3583,201 @@
       <c r="G9" s="81" t="inlineStr"/>
       <c r="H9" s="80" t="inlineStr">
         <is>
-          <t>部分支持</t>
+          <t>不支持</t>
         </is>
       </c>
       <c r="I9" s="80" t="inlineStr"/>
     </row>
-    <row r="10" ht="81" customHeight="1" s="1">
+    <row r="10" ht="51" customHeight="1" s="1">
       <c r="A10" s="84" t="n"/>
       <c r="B10" s="84" t="n"/>
       <c r="C10" s="81" t="inlineStr">
         <is>
-          <t>支持安全策略优化器（Policy Optimizer）</t>
+          <t>支持终端设备对象作为策略匹配条件</t>
         </is>
       </c>
       <c r="D10" s="81" t="inlineStr">
         <is>
-          <t>端口(L4)规则一键迁移为应用(L7)规则+新应用查看器</t>
+          <t>终端设备类型（手机/平板/IoT等设备对象）作为策略构建块</t>
         </is>
       </c>
       <c r="E10" s="81" t="inlineStr">
         <is>
-          <t>PA新应用查看器+端口规则迁移至App-ID规则工作流+规则使用统计，减少攻击面（PA Web帮助p142）；天融信策略统计开关可显示规则匹配命中情况（天融信手册《配置访问控制策略》页），但无新应用查看器与端口→应用规则迁移工作流；对应矩阵#132</t>
-        </is>
-      </c>
-      <c r="F10" s="84" t="n"/>
+          <t>PA支持设备对象构建块（对应矩阵#3/4）；天融信经EDR联动上报终端资产并下发管控策略（天融信手册《与EDR联动》页），无独立设备对象</t>
+        </is>
+      </c>
+      <c r="F10" s="80" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
       <c r="G10" s="84" t="n"/>
-      <c r="H10" s="85" t="n"/>
+      <c r="H10" s="80" t="inlineStr">
+        <is>
+          <t>部分支持</t>
+        </is>
+      </c>
       <c r="I10" s="84" t="n"/>
     </row>
-    <row r="11" ht="36" customHeight="1" s="1">
+    <row r="11" ht="81" customHeight="1" s="1">
       <c r="A11" s="84" t="n"/>
       <c r="B11" s="84" t="n"/>
       <c r="C11" s="81" t="inlineStr">
         <is>
-          <t>支持配置锁（Config Lock/Commit Lock）</t>
+          <t>支持端口(L4)规则向应用(L7)规则迁移工作流（Policy Optimizer）</t>
         </is>
       </c>
       <c r="D11" s="81" t="inlineStr">
         <is>
-          <t>配置锁/提交锁，防止多管理员并发修改</t>
+          <t>端口规则一键迁移为应用规则+新应用查看器</t>
         </is>
       </c>
       <c r="E11" s="81" t="inlineStr">
         <is>
-          <t>PA可锁定待选配置或提交，防止他管理员并发更改；对应矩阵#135（天融信不支持，PA优势）</t>
-        </is>
-      </c>
-      <c r="F11" s="85" t="n"/>
+          <t>PA策略优化器提供新应用查看器与端口→App-ID规则迁移工作流（PA Web帮助p142）；天融信策略统计仅显示规则命中数（天融信手册《配置访问控制策略》页），无迁移工具（命中统计能力已另列已支持行）；对应矩阵#132</t>
+        </is>
+      </c>
+      <c r="F11" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="G11" s="84" t="n"/>
       <c r="H11" s="80" t="inlineStr">
         <is>
-          <t>待评估</t>
+          <t>不支持</t>
         </is>
       </c>
       <c r="I11" s="84" t="n"/>
     </row>
-    <row r="12" ht="111" customHeight="1" s="1">
+    <row r="12" ht="36" customHeight="1" s="1">
       <c r="A12" s="84" t="n"/>
       <c r="B12" s="84" t="n"/>
       <c r="C12" s="81" t="inlineStr">
         <is>
-          <t>支持应用默认端口绑定（Service: application-default）</t>
+          <t>支持配置锁（Config Lock/Commit Lock）</t>
         </is>
       </c>
       <c r="D12" s="81" t="inlineStr">
         <is>
-          <t>应用匹配同时强制使用标准端口，非标端口拒绝</t>
+          <t>配置锁/提交锁，防止多管理员并发修改</t>
         </is>
       </c>
       <c r="E12" s="81" t="inlineStr">
         <is>
-          <t>PA安全策略默认服务为application-default：放行应用同时强制其使用标准端口（如SSH仅22），非标准端口不匹配即拦截（PA管理指南p904）；天融信策略为五元组+应用识别组合（天融信手册《配置访问控制策略》页）；迁移评估项：直接转换若仅保留应用识别不限端口将扩大安全敞口，需制定应用标准端口映射限制（App-Default）转换方案；对应矩阵#2</t>
-        </is>
-      </c>
-      <c r="F12" s="80" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>PA可锁定待选配置或提交，防止他管理员并发更改；对应矩阵#135（天融信不支持，PA优势）</t>
+        </is>
+      </c>
+      <c r="F12" s="85" t="n"/>
       <c r="G12" s="84" t="n"/>
-      <c r="H12" s="84" t="n"/>
+      <c r="H12" s="80" t="inlineStr">
+        <is>
+          <t>待评估</t>
+        </is>
+      </c>
       <c r="I12" s="84" t="n"/>
     </row>
-    <row r="13" ht="81" customHeight="1" s="1">
+    <row r="13" ht="111" customHeight="1" s="1">
       <c r="A13" s="84" t="n"/>
       <c r="B13" s="84" t="n"/>
       <c r="C13" s="81" t="inlineStr">
         <is>
-          <t>支持安全策略绑定安全配置文件组（Profile Group）</t>
+          <t>支持应用默认端口绑定（Service: application-default）</t>
         </is>
       </c>
       <c r="D13" s="81" t="inlineStr">
         <is>
-          <t>Allow动作关联反病毒/漏洞防护/URL过滤/文件阻断/WildFire配置文件组</t>
+          <t>应用匹配同时强制使用标准端口，非标端口拒绝</t>
         </is>
       </c>
       <c r="E13" s="81" t="inlineStr">
         <is>
-          <t>PA安全策略Allow动作关联Profile组（反病毒/漏洞防护/URL过滤/文件阻止/WildFire等，PA Web帮助p304）；天融信一体化策略引擎自带检测项；迁移评估项：需评估Profile组到天融信各检测引擎的映射与缺省动作差异；对应矩阵#4</t>
+          <t>PA安全策略默认服务为application-default：放行应用同时强制其使用标准端口（如SSH仅22），非标准端口不匹配即拦截（PA管理指南p904）；天融信策略为五元组+应用识别组合（天融信手册《配置访问控制策略》页）；迁移评估项：直接转换若仅保留应用识别不限端口将扩大安全敞口，需制定应用标准端口映射限制（App-Default）转换方案；对应矩阵#2</t>
         </is>
       </c>
       <c r="F13" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G13" s="84" t="n"/>
       <c r="H13" s="84" t="n"/>
       <c r="I13" s="84" t="n"/>
     </row>
-    <row r="14" ht="156" customHeight="1" s="1">
+    <row r="14" ht="81" customHeight="1" s="1">
       <c r="A14" s="84" t="n"/>
-      <c r="B14" s="85" t="n"/>
+      <c r="B14" s="84" t="n"/>
       <c r="C14" s="81" t="inlineStr">
         <is>
+          <t>支持安全策略绑定安全配置文件组（Profile Group）</t>
+        </is>
+      </c>
+      <c r="D14" s="81" t="inlineStr">
+        <is>
+          <t>Allow动作关联反病毒/漏洞防护/URL过滤/文件阻断/WildFire配置文件组</t>
+        </is>
+      </c>
+      <c r="E14" s="81" t="inlineStr">
+        <is>
+          <t>PA安全策略Allow动作关联Profile组（反病毒/漏洞防护/URL过滤/文件阻止/WildFire等，PA Web帮助p304）；天融信一体化策略引擎自带检测项；迁移评估项：需评估Profile组到天融信各检测引擎的映射与缺省动作差异；对应矩阵#4</t>
+        </is>
+      </c>
+      <c r="F14" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G14" s="84" t="n"/>
+      <c r="H14" s="84" t="n"/>
+      <c r="I14" s="84" t="n"/>
+    </row>
+    <row r="15" ht="156" customHeight="1" s="1">
+      <c r="A15" s="84" t="n"/>
+      <c r="B15" s="85" t="n"/>
+      <c r="C15" s="81" t="inlineStr">
+        <is>
           <t>支持隐式默认规则显式化迁移（intrazone/interzone-default）</t>
         </is>
       </c>
-      <c r="D14" s="81" t="inlineStr">
+      <c r="D15" s="81" t="inlineStr">
         <is>
           <t>同区域默认放行/跨区域默认拒绝，支持替代与日志转发</t>
         </is>
       </c>
-      <c r="E14" s="81" t="inlineStr">
+      <c r="E15" s="81" t="inlineStr">
         <is>
           <t>PA安全策略库末尾自带两条隐式系统规则：区域内默认（同Zone默认放行）与区域间默认（跨Zone默认拒绝），可被替代配置，替代字段含日志转发配置文件与Log at Session End在会话结束时记录（PA Web帮助p134-136）；天融信未见同区域默认放行的隐式规则机制；迁移评估项：①必须提取intrazone-default同Zone互访需求并显式转换为放行规则，否则割接后同Zone不同网段/VLAN互访将被默认拦截；②需在新设备补齐底部兜底Deny-All并开启日志，否则被拒流量查无日志、排障困难</t>
         </is>
       </c>
-      <c r="F14" s="80" t="inlineStr">
+      <c r="F15" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G14" s="85" t="n"/>
-      <c r="H14" s="85" t="n"/>
-      <c r="I14" s="85" t="n"/>
-    </row>
-    <row r="15" ht="81" customHeight="1" s="1">
-      <c r="A15" s="84" t="n"/>
-      <c r="B15" s="80" t="inlineStr">
-        <is>
-          <t>NAT策略</t>
-        </is>
-      </c>
-      <c r="C15" s="81" t="inlineStr">
-        <is>
-          <t>支持源NAT（动态/PAT静态IP）与Hairpin回流</t>
-        </is>
-      </c>
-      <c r="D15" s="81" t="inlineStr">
-        <is>
-          <t>动态IP+端口(DIPP)/静态IP/接口地址，含回流(Hairpin)</t>
-        </is>
-      </c>
-      <c r="E15" s="81" t="inlineStr">
-        <is>
-          <t>PA源NAT含DIPP动态IP+端口/静态IP/接口地址/持久NAT等（PA Web帮助p147）；天融信SNAT地址池（多对一/多对多/一对一/PAT）与仅源IP转换等（天融信手册《源NAT》《配置源转换》页）；对应矩阵#6</t>
-        </is>
-      </c>
-      <c r="F15" s="80" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="G15" s="81" t="inlineStr"/>
-      <c r="H15" s="80" t="inlineStr">
-        <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I15" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
+      <c r="G15" s="85" t="n"/>
+      <c r="H15" s="85" t="n"/>
+      <c r="I15" s="85" t="n"/>
     </row>
     <row r="16" ht="81" customHeight="1" s="1">
       <c r="A16" s="84" t="n"/>
-      <c r="B16" s="84" t="n"/>
+      <c r="B16" s="80" t="inlineStr">
+        <is>
+          <t>NAT策略</t>
+        </is>
+      </c>
       <c r="C16" s="81" t="inlineStr">
         <is>
-          <t>支持目的NAT（端口映射/服务器发布）</t>
+          <t>支持源NAT（动态/PAT静态IP）与Hairpin回流</t>
         </is>
       </c>
       <c r="D16" s="81" t="inlineStr">
         <is>
-          <t>静态映射/端口转换/DNS重写/FQDN目标</t>
+          <t>动态IP+端口(DIPP)/静态IP/接口地址，含回流(Hairpin)</t>
         </is>
       </c>
       <c r="E16" s="81" t="inlineStr">
         <is>
-          <t>PA目标NAT含静态/动态IP、端口转换、DNS Rewrite、FQDN目标（PA Web帮助p149）；天融信服务器映射含静态映射+服务器负载均衡两种模式，NAT46/NAT66全系列（天融信手册《服务器映射》页）；对应矩阵#7</t>
+          <t>PA源NAT含DIPP动态IP+端口/静态IP/接口地址/持久NAT等（PA Web帮助p147）；天融信SNAT地址池（多对一/多对多/一对一/PAT）与仅源IP转换等（天融信手册《源NAT》《配置源转换》页）；对应矩阵#6</t>
         </is>
       </c>
       <c r="F16" s="80" t="inlineStr">
@@ -3787,50 +3791,62 @@
           <t>已支持</t>
         </is>
       </c>
-      <c r="I16" s="80" t="inlineStr"/>
+      <c r="I16" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="81" customHeight="1" s="1">
       <c r="A17" s="84" t="n"/>
       <c r="B17" s="84" t="n"/>
       <c r="C17" s="81" t="inlineStr">
         <is>
-          <t>支持静态/双向NAT一对一转换</t>
+          <t>支持目的NAT（端口映射/服务器发布）</t>
         </is>
       </c>
       <c r="D17" s="81" t="inlineStr">
         <is>
-          <t>一对一转换，支持双向映射</t>
+          <t>静态映射/端口转换/DNS重写/FQDN目标</t>
         </is>
       </c>
       <c r="E17" s="81" t="inlineStr">
         <is>
-          <t>PA支持静态IP转换与双向(Bi-directional)转换（PA Web帮助p148）；天融信支持一对一转换（SNAT地址池一对一/NAT66一对一）（天融信手册《源NAT》《配置一对一转换》页）；对应矩阵#8</t>
-        </is>
-      </c>
-      <c r="F17" s="84" t="n"/>
-      <c r="G17" s="84" t="n"/>
-      <c r="H17" s="84" t="n"/>
-      <c r="I17" s="84" t="n"/>
+          <t>PA目标NAT含静态/动态IP、端口转换、DNS Rewrite、FQDN目标（PA Web帮助p149）；天融信服务器映射含静态映射+服务器负载均衡两种模式，NAT46/NAT66全系列（天融信手册《服务器映射》页）；对应矩阵#7</t>
+        </is>
+      </c>
+      <c r="F17" s="80" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G17" s="81" t="inlineStr"/>
+      <c r="H17" s="80" t="inlineStr">
+        <is>
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I17" s="80" t="inlineStr"/>
     </row>
     <row r="18" ht="81" customHeight="1" s="1">
       <c r="A18" s="84" t="n"/>
       <c r="B18" s="84" t="n"/>
       <c r="C18" s="81" t="inlineStr">
         <is>
-          <t>支持NAT与安全策略解耦独立配置</t>
+          <t>支持静态/双向NAT一对一转换</t>
         </is>
       </c>
       <c r="D18" s="81" t="inlineStr">
         <is>
-          <t>NAT独立策略库，先NAT后安全策略匹配</t>
+          <t>一对一转换，支持双向映射</t>
         </is>
       </c>
       <c r="E18" s="81" t="inlineStr">
         <is>
-          <t>PA NAT策略库独立于安全策略库(Policies&gt;NAT)，先NAT后安全匹配；天融信地址转换为独立策略库（安全策略&gt;地址转换），与访问控制策略分离配置（天融信手册《安全策略》《工作原理》页）；对应矩阵#9</t>
-        </is>
-      </c>
-      <c r="F18" s="85" t="n"/>
+          <t>PA支持静态IP转换与双向(Bi-directional)转换（PA Web帮助p148）；天融信支持一对一转换（SNAT地址池一对一/NAT66一对一）（天融信手册《源NAT》《配置一对一转换》页）；对应矩阵#8</t>
+        </is>
+      </c>
+      <c r="F18" s="84" t="n"/>
       <c r="G18" s="84" t="n"/>
       <c r="H18" s="84" t="n"/>
       <c r="I18" s="84" t="n"/>
@@ -3840,215 +3856,203 @@
       <c r="B19" s="84" t="n"/>
       <c r="C19" s="81" t="inlineStr">
         <is>
-          <t>支持IPv6/NAT64转换（nat64类型）</t>
+          <t>支持NAT与安全策略解耦独立配置</t>
         </is>
       </c>
       <c r="D19" s="81" t="inlineStr">
         <is>
-          <t>IPv4↔IPv6转换类型（nat64）</t>
+          <t>NAT独立策略库，先NAT后安全策略匹配</t>
         </is>
       </c>
       <c r="E19" s="81" t="inlineStr">
         <is>
-          <t>PA NAT规则支持IPv4/IPv6及NAT64转换类型（RFC6146）；天融信NAT64含静态转换+前缀转换+动态算法（IVI/普通前缀），另有NAT46（天融信手册《NAT64》《NAT46》页）；对应矩阵#18</t>
-        </is>
-      </c>
-      <c r="F19" s="80" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>PA NAT策略库独立于安全策略库(Policies&gt;NAT)，先NAT后安全匹配；天融信地址转换为独立策略库（安全策略&gt;地址转换），与访问控制策略分离配置（天融信手册《安全策略》《工作原理》页）；对应矩阵#9</t>
+        </is>
+      </c>
+      <c r="F19" s="85" t="n"/>
       <c r="G19" s="84" t="n"/>
-      <c r="H19" s="85" t="n"/>
+      <c r="H19" s="84" t="n"/>
       <c r="I19" s="84" t="n"/>
     </row>
-    <row r="20" ht="126" customHeight="1" s="1">
+    <row r="20" ht="81" customHeight="1" s="1">
       <c r="A20" s="84" t="n"/>
       <c r="B20" s="84" t="n"/>
       <c r="C20" s="81" t="inlineStr">
         <is>
+          <t>支持IPv6/NAT64转换（nat64类型）</t>
+        </is>
+      </c>
+      <c r="D20" s="81" t="inlineStr">
+        <is>
+          <t>IPv4↔IPv6转换类型（nat64）</t>
+        </is>
+      </c>
+      <c r="E20" s="81" t="inlineStr">
+        <is>
+          <t>PA NAT规则支持IPv4/IPv6及NAT64转换类型（RFC6146）；天融信NAT64含静态转换+前缀转换+动态算法（IVI/普通前缀），另有NAT46（天融信手册《NAT64》《NAT46》页）；对应矩阵#18</t>
+        </is>
+      </c>
+      <c r="F20" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G20" s="84" t="n"/>
+      <c r="H20" s="85" t="n"/>
+      <c r="I20" s="84" t="n"/>
+    </row>
+    <row r="21" ht="126" customHeight="1" s="1">
+      <c r="A21" s="84" t="n"/>
+      <c r="B21" s="84" t="n"/>
+      <c r="C21" s="81" t="inlineStr">
+        <is>
           <t>支持NAT后目的区域路由回查匹配（Dest Zone by route lookup）</t>
         </is>
       </c>
-      <c r="D20" s="81" t="inlineStr">
+      <c r="D21" s="81" t="inlineStr">
         <is>
           <t>目的区域按NAT后路由查找；源/目的地址用NAT前值</t>
         </is>
       </c>
-      <c r="E20" s="81" t="inlineStr">
+      <c r="E21" s="81" t="inlineStr">
         <is>
           <t>PA底层为『先NAT判断后安全策略匹配』的因果倒置：安全策略要求源区域(NAT前)+源地址(NAT前)+目的地址(NAT前)+目的区域(NAT后按路由查找)，极其反直觉；天融信地址转换为独立策略库常规直观映射（安全策略&gt;地址转换，天融信手册《服务器映射》页）；迁移评估项：带目的NAT的策略平移后易因Zone填写错误不通，需制定NAT查表逻辑转换映射规范；对应矩阵#9</t>
         </is>
       </c>
-      <c r="F20" s="80" t="inlineStr">
+      <c r="F21" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G20" s="84" t="n"/>
-      <c r="H20" s="80" t="inlineStr">
+      <c r="G21" s="84" t="n"/>
+      <c r="H21" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="I20" s="84" t="n"/>
-    </row>
-    <row r="21" ht="81" customHeight="1" s="1">
-      <c r="A21" s="84" t="n"/>
-      <c r="B21" s="85" t="n"/>
-      <c r="C21" s="81" t="inlineStr">
+      <c r="I21" s="84" t="n"/>
+    </row>
+    <row r="22" ht="81" customHeight="1" s="1">
+      <c r="A22" s="84" t="n"/>
+      <c r="B22" s="85" t="n"/>
+      <c r="C22" s="81" t="inlineStr">
         <is>
           <t>支持NAT规则主动/主动HA绑定（Active/Active HA Binding）</t>
         </is>
       </c>
-      <c r="D21" s="81" t="inlineStr">
+      <c r="D22" s="81" t="inlineStr">
         <is>
           <t>主动/主动HA下NAT规则绑定会话所有者</t>
         </is>
       </c>
-      <c r="E21" s="81" t="inlineStr">
+      <c r="E22" s="81" t="inlineStr">
         <is>
           <t>PA主动/主动HA配置下NAT规则可绑定会话所有者/会话设置，控制NAT会话的设备绑定，仅A/A模式可见（PA Web帮助p150）；天融信HA为主备双机热备模式（天融信手册《配置双机热备功能》页），无主动/主动模式及NAT规则绑定机制</t>
         </is>
       </c>
-      <c r="F21" s="80" t="inlineStr">
+      <c r="F22" s="80" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G21" s="85" t="n"/>
-      <c r="H21" s="80" t="inlineStr">
+      <c r="G22" s="85" t="n"/>
+      <c r="H22" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="I21" s="85" t="n"/>
-    </row>
-    <row r="22" ht="96" customHeight="1" s="1">
-      <c r="A22" s="84" t="n"/>
-      <c r="B22" s="80" t="inlineStr">
-        <is>
-          <t>QoS策略</t>
-        </is>
-      </c>
-      <c r="C22" s="81" t="inlineStr">
-        <is>
-          <t>支持按应用/源地址/用户等定义QoS策略并划分优先级类</t>
-        </is>
-      </c>
-      <c r="D22" s="81" t="inlineStr">
-        <is>
-          <t>8类流量分类+4级优先级，保证/最大带宽控制</t>
-        </is>
-      </c>
-      <c r="E22" s="81" t="inlineStr">
-        <is>
-          <t>PA QoS策略规则分配QoS类（8类+4级优先级），按Egress Guaranteed/Max控制带宽（PA Web帮助p154-155）；天融信流量管理基于应用/用户/源目的区域/地址/服务/时间+通道优先级，虚拟通道限制与保证带宽（天融信手册《流量管理》页）；对应矩阵#33/66</t>
-        </is>
-      </c>
-      <c r="F22" s="80" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G22" s="81" t="inlineStr"/>
-      <c r="H22" s="80" t="inlineStr">
-        <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I22" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
+      <c r="I22" s="85" t="n"/>
     </row>
     <row r="23" ht="96" customHeight="1" s="1">
       <c r="A23" s="84" t="n"/>
-      <c r="B23" s="85" t="n"/>
+      <c r="B23" s="80" t="inlineStr">
+        <is>
+          <t>QoS策略</t>
+        </is>
+      </c>
       <c r="C23" s="81" t="inlineStr">
         <is>
-          <t>支持基于DSCP/ToS值匹配的QoS</t>
+          <t>支持按应用/源地址/用户等定义QoS策略并划分优先级类</t>
         </is>
       </c>
       <c r="D23" s="81" t="inlineStr">
         <is>
-          <t>QoS规则按DSCP/ToS值匹配调度</t>
+          <t>8类流量分类+4级优先级，保证/最大带宽控制</t>
         </is>
       </c>
       <c r="E23" s="81" t="inlineStr">
         <is>
-          <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
+          <t>PA QoS策略规则分配QoS类（8类+4级优先级），按Egress Guaranteed/Max控制带宽（PA Web帮助p154-155）；天融信流量管理基于应用/用户/源目的区域/地址/服务/时间+通道优先级，虚拟通道限制与保证带宽（天融信手册《流量管理》页）；对应矩阵#33/66</t>
         </is>
       </c>
       <c r="F23" s="80" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G23" s="81" t="inlineStr"/>
       <c r="H23" s="80" t="inlineStr">
         <is>
-          <t>部分支持</t>
-        </is>
-      </c>
-      <c r="I23" s="80" t="inlineStr"/>
-    </row>
-    <row r="24" ht="81" customHeight="1" s="1">
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I23" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="96" customHeight="1" s="1">
       <c r="A24" s="84" t="n"/>
-      <c r="B24" s="80" t="inlineStr">
-        <is>
-          <t>基于策略转发(PBF)</t>
-        </is>
-      </c>
+      <c r="B24" s="85" t="n"/>
       <c r="C24" s="81" t="inlineStr">
         <is>
-          <t>支持按源区域/地址/用户/应用/服务+下一跳的基于策略转发</t>
+          <t>支持QoS策略规则内直接按DSCP/ToS匹配调度</t>
         </is>
       </c>
       <c r="D24" s="81" t="inlineStr">
         <is>
-          <t>按源区域/地址/用户/应用/服务+下一跳转发，路径监控失效切换</t>
+          <t>QoS策略规则DSCP/ToS直接匹配（非独立流控模块配置）</t>
         </is>
       </c>
       <c r="E24" s="81" t="inlineStr">
         <is>
-          <t>PA PBF策略绕过常规路由表选路，支持路径监控与失效切换、BFD、强制对称返回（PA Web帮助p156）；天融信策略路由按源/目的地址端口、ISP名称、协议、角色等参数选路（天融信手册《策略路由》页）；对应矩阵#10</t>
+          <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
         </is>
       </c>
       <c r="F24" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G24" s="81" t="inlineStr"/>
       <c r="H24" s="80" t="inlineStr">
         <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I24" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="111" customHeight="1" s="1">
+          <t>部分支持</t>
+        </is>
+      </c>
+      <c r="I24" s="80" t="inlineStr"/>
+    </row>
+    <row r="25" ht="81" customHeight="1" s="1">
       <c r="A25" s="84" t="n"/>
-      <c r="B25" s="85" t="n"/>
+      <c r="B25" s="80" t="inlineStr">
+        <is>
+          <t>基于策略转发(PBF)</t>
+        </is>
+      </c>
       <c r="C25" s="81" t="inlineStr">
         <is>
-          <t>支持PBF强制对称返回（非对称路由环境）</t>
+          <t>支持按源区域/地址/用户/应用/服务+下一跳的基于策略转发</t>
         </is>
       </c>
       <c r="D25" s="81" t="inlineStr">
         <is>
-          <t>记录入接口MAC，回包强制原路返回</t>
+          <t>按源区域/地址/用户/应用/服务+下一跳转发，路径监控失效切换</t>
         </is>
       </c>
       <c r="E25" s="81" t="inlineStr">
         <is>
-          <t>PA对称返回：虚拟路由器替代返回流量的路由查找，将流量引导回接收SYN数据包的MAC地址（ARP表确定下一跳），双ISP双活/非对称路由核心机制（PA管理指南p1294）；天融信手册检索无对称返回/回程机制命中，策略路由与LLB的回程保障能力待验证；迁移评估项：多ISP双活环境需实测天融信回包路由对称性，否则现网业务中断</t>
+          <t>PA PBF策略绕过常规路由表选路，支持路径监控与失效切换、BFD、强制对称返回（PA Web帮助p156）；天融信策略路由按源/目的地址端口、ISP名称、协议、角色等参数选路（天融信手册《策略路由》页）；对应矩阵#10</t>
         </is>
       </c>
       <c r="F25" s="80" t="inlineStr">
@@ -4059,31 +4063,31 @@
       <c r="G25" s="81" t="inlineStr"/>
       <c r="H25" s="80" t="inlineStr">
         <is>
-          <t>待评估</t>
-        </is>
-      </c>
-      <c r="I25" s="80" t="inlineStr"/>
-    </row>
-    <row r="26" ht="96" customHeight="1" s="1">
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I25" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="111" customHeight="1" s="1">
       <c r="A26" s="84" t="n"/>
-      <c r="B26" s="80" t="inlineStr">
-        <is>
-          <t>解密策略(Decryption)</t>
-        </is>
-      </c>
+      <c r="B26" s="85" t="n"/>
       <c r="C26" s="81" t="inlineStr">
         <is>
-          <t>支持SSL/TLS解密策略（出站正向/入站反向）</t>
+          <t>支持PBF强制对称返回（非对称路由环境）</t>
         </is>
       </c>
       <c r="D26" s="81" t="inlineStr">
         <is>
-          <t>出站正向代理+入站检查双向解密</t>
+          <t>记录入接口MAC，回包强制原路返回</t>
         </is>
       </c>
       <c r="E26" s="81" t="inlineStr">
         <is>
-          <t>PA解密策略区分SSL Forward Proxy/Inbound Inspection/SSH，可解密以获得流量可见性与深度检测（PA Web帮助p164）；天融信代理策略将NGFW作为代理服务器，对加密流量解密还原明文完成内容安全检查后重新加密（天融信手册《代理策略》页）；对应矩阵#29/30</t>
+          <t>PA对称返回：虚拟路由器替代返回流量的路由查找，将流量引导回接收SYN数据包的MAC地址（ARP表确定下一跳），双ISP双活/非对称路由核心机制（PA管理指南p1294）；天融信手册检索无对称返回/回程机制命中，策略路由与LLB的回程保障能力待验证；迁移评估项：多ISP双活环境需实测天融信回包路由对称性，否则现网业务中断</t>
         </is>
       </c>
       <c r="F26" s="80" t="inlineStr">
@@ -4094,36 +4098,36 @@
       <c r="G26" s="81" t="inlineStr"/>
       <c r="H26" s="80" t="inlineStr">
         <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I26" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="66" customHeight="1" s="1">
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="I26" s="80" t="inlineStr"/>
+    </row>
+    <row r="27" ht="96" customHeight="1" s="1">
       <c r="A27" s="84" t="n"/>
-      <c r="B27" s="84" t="n"/>
+      <c r="B27" s="80" t="inlineStr">
+        <is>
+          <t>解密策略(Decryption)</t>
+        </is>
+      </c>
       <c r="C27" s="81" t="inlineStr">
         <is>
-          <t>支持解密目标选择与证书配置</t>
+          <t>支持SSL/TLS解密策略（出站正向/入站反向）</t>
         </is>
       </c>
       <c r="D27" s="81" t="inlineStr">
         <is>
-          <t>入站证书配置/解密目标（数据包/会话）</t>
+          <t>出站正向代理+入站检查双向解密</t>
         </is>
       </c>
       <c r="E27" s="81" t="inlineStr">
         <is>
-          <t>PA解密目标允许指定数据包/会话；入站含Certificates证书配置；对应矩阵#31；天融信代理模板支持证书选择与预置动态证书模板（天融信手册《代理模板》页）</t>
+          <t>PA解密策略区分SSL Forward Proxy/Inbound Inspection/SSH，可解密以获得流量可见性与深度检测（PA Web帮助p164）；天融信代理策略将NGFW作为代理服务器，对加密流量解密还原明文完成内容安全检查后重新加密（天融信手册《代理策略》页）；对应矩阵#29/30</t>
         </is>
       </c>
       <c r="F27" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G27" s="81" t="inlineStr"/>
@@ -4132,180 +4136,180 @@
           <t>已支持</t>
         </is>
       </c>
-      <c r="I27" s="80" t="inlineStr"/>
-    </row>
-    <row r="28" ht="51" customHeight="1" s="1">
+      <c r="I27" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="66" customHeight="1" s="1">
       <c r="A28" s="84" t="n"/>
       <c r="B28" s="84" t="n"/>
       <c r="C28" s="81" t="inlineStr">
         <is>
-          <t>支持解密流量镜像到专用接口（Decryption Port Mirroring）</t>
+          <t>支持解密目标选择与证书配置</t>
         </is>
       </c>
       <c r="D28" s="81" t="inlineStr">
         <is>
-          <t>解密后明文流量镜像至专用接口供第三方分析</t>
+          <t>入站证书配置/解密目标（数据包/会话）</t>
         </is>
       </c>
       <c r="E28" s="81" t="inlineStr">
         <is>
-          <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证（PA管理指南p1059）；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
-        </is>
-      </c>
-      <c r="F28" s="85" t="n"/>
-      <c r="G28" s="84" t="n"/>
+          <t>PA解密目标允许指定数据包/会话；入站含Certificates证书配置；对应矩阵#31；天融信代理模板支持证书选择与预置动态证书模板（天融信手册《代理模板》页）</t>
+        </is>
+      </c>
+      <c r="F28" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G28" s="81" t="inlineStr"/>
       <c r="H28" s="80" t="inlineStr">
         <is>
-          <t>不支持</t>
-        </is>
-      </c>
-      <c r="I28" s="84" t="n"/>
-    </row>
-    <row r="29" ht="126" customHeight="1" s="1">
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I28" s="80" t="inlineStr"/>
+    </row>
+    <row r="29" ht="51" customHeight="1" s="1">
       <c r="A29" s="84" t="n"/>
       <c r="B29" s="84" t="n"/>
       <c r="C29" s="81" t="inlineStr">
         <is>
-          <t>支持解密不受信证书分离处理（Forward Untrust Certificate）</t>
+          <t>支持解密流量镜像到专用接口（Decryption Port Mirroring）</t>
         </is>
       </c>
       <c r="D29" s="81" t="inlineStr">
         <is>
-          <t>外部无效证书以不受信转发证书重签，保留浏览器告警</t>
+          <t>解密后明文流量镜像至专用接口供第三方分析</t>
         </is>
       </c>
       <c r="E29" s="81" t="inlineStr">
         <is>
-          <t>PA转发代理遇外部过期/不受信证书时，不用内部信任CA重签，而是专用Forward Untrust Certificate重签名，让浏览器保留不受信告警（PA管理指南p994、p1030）；天融信SSL解密（透明代理/服务器SSL解密，天融信手册《代理策略》页）未见受信/不受信双证书体系；迁移评估项：需验证天融信对外部无效证书的处理方式，避免直接阻断（白屏）或信任重签（掩盖风险）</t>
-        </is>
-      </c>
-      <c r="F29" s="80" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证（PA管理指南p1059）；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
+        </is>
+      </c>
+      <c r="F29" s="85" t="n"/>
       <c r="G29" s="84" t="n"/>
       <c r="H29" s="80" t="inlineStr">
         <is>
-          <t>待评估</t>
+          <t>不支持</t>
         </is>
       </c>
       <c r="I29" s="84" t="n"/>
     </row>
-    <row r="30" ht="66" customHeight="1" s="1">
+    <row r="30" ht="126" customHeight="1" s="1">
       <c r="A30" s="84" t="n"/>
       <c r="B30" s="84" t="n"/>
       <c r="C30" s="81" t="inlineStr">
         <is>
-          <t>支持解密规则按URL类别选择性解密（URL Category）</t>
+          <t>支持解密不受信证书分离处理（Forward Untrust Certificate）</t>
         </is>
       </c>
       <c r="D30" s="81" t="inlineStr">
         <is>
-          <t>按URL类别圈定解密范围，排除银行/医疗等敏感类</t>
+          <t>外部无效证书以不受信转发证书重签，保留浏览器告警</t>
         </is>
       </c>
       <c r="E30" s="81" t="inlineStr">
         <is>
-          <t>PA解密规则可按URL类别（含自定义类别）选择解密范围，可排除银行/医疗等敏感类别不解密（PA Web帮助p164）；天融信SSL解密（代理策略/代理模板）无按URL类别选择解密机制（检索无命中）</t>
+          <t>PA转发代理遇外部过期/不受信证书时，不用内部信任CA重签，而是专用Forward Untrust Certificate重签名，让浏览器保留不受信告警（PA管理指南p994、p1030）；天融信SSL解密（透明代理/服务器SSL解密，天融信手册《代理策略》页）未见受信/不受信双证书体系；迁移评估项：需验证天融信对外部无效证书的处理方式，避免直接阻断（白屏）或信任重签（掩盖风险）</t>
         </is>
       </c>
       <c r="F30" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G30" s="84" t="n"/>
       <c r="H30" s="80" t="inlineStr">
         <is>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="I30" s="84" t="n"/>
+    </row>
+    <row r="31" ht="66" customHeight="1" s="1">
+      <c r="A31" s="84" t="n"/>
+      <c r="B31" s="84" t="n"/>
+      <c r="C31" s="81" t="inlineStr">
+        <is>
+          <t>支持解密规则按URL类别选择性解密（URL Category）</t>
+        </is>
+      </c>
+      <c r="D31" s="81" t="inlineStr">
+        <is>
+          <t>按URL类别圈定解密范围，排除银行/医疗等敏感类</t>
+        </is>
+      </c>
+      <c r="E31" s="81" t="inlineStr">
+        <is>
+          <t>PA解密规则可按URL类别（含自定义类别）选择解密范围，可排除银行/医疗等敏感类别不解密（PA Web帮助p164）；天融信SSL解密（代理策略/代理模板）无按URL类别选择解密机制（检索无命中）</t>
+        </is>
+      </c>
+      <c r="F31" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G31" s="84" t="n"/>
+      <c r="H31" s="80" t="inlineStr">
+        <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="I30" s="84" t="n"/>
-    </row>
-    <row r="31" ht="96" customHeight="1" s="1">
-      <c r="A31" s="84" t="n"/>
-      <c r="B31" s="85" t="n"/>
-      <c r="C31" s="81" t="inlineStr">
+      <c r="I31" s="84" t="n"/>
+    </row>
+    <row r="32" ht="96" customHeight="1" s="1">
+      <c r="A32" s="84" t="n"/>
+      <c r="B32" s="85" t="n"/>
+      <c r="C32" s="81" t="inlineStr">
         <is>
           <t>支持SSH代理解密与SSH隧道控制（SSH Proxy）</t>
         </is>
       </c>
-      <c r="D31" s="81" t="inlineStr">
+      <c r="D32" s="81" t="inlineStr">
         <is>
           <t>SSH代理解密+SSH隧道(ssh-tunnel)识别控制</t>
         </is>
       </c>
-      <c r="E31" s="81" t="inlineStr">
+      <c r="E32" s="81" t="inlineStr">
         <is>
           <t>PA解密策略SSH Proxy类型解密SSH通信，可通过ssh-tunnel App-ID在策略中控制SSH隧道（端口转发/内网穿透），正常SSH管理流量放行；含不受支持算法检查/资源不足阻断会话等防护（PA Web帮助p164、p318-319）；天融信手册检索无SSH代理/SSH隧道控制命中</t>
         </is>
       </c>
-      <c r="F31" s="85" t="n"/>
-      <c r="G31" s="85" t="n"/>
-      <c r="H31" s="85" t="n"/>
-      <c r="I31" s="85" t="n"/>
-    </row>
-    <row r="32" ht="66" customHeight="1" s="1">
-      <c r="A32" s="84" t="n"/>
-      <c r="B32" s="80" t="inlineStr">
+      <c r="F32" s="85" t="n"/>
+      <c r="G32" s="85" t="n"/>
+      <c r="H32" s="85" t="n"/>
+      <c r="I32" s="85" t="n"/>
+    </row>
+    <row r="33" ht="111" customHeight="1" s="1">
+      <c r="A33" s="84" t="n"/>
+      <c r="B33" s="80" t="inlineStr">
         <is>
           <t>网络数据包代理(NPBroker)</t>
         </is>
       </c>
-      <c r="C32" s="81" t="inlineStr">
-        <is>
-          <t>支持按应用/用户/区域/设备/IP定义NPBroker规则转发到第三方安全链</t>
-        </is>
-      </c>
-      <c r="D32" s="81" t="inlineStr">
+      <c r="C33" s="81" t="inlineStr">
+        <is>
+          <t>支持内联数据包代理策略将流量转发第三方安全链（NPBroker）</t>
+        </is>
+      </c>
+      <c r="D33" s="81" t="inlineStr">
         <is>
           <t>已解密/未解密流量内联转发第三方安全链，L3路由转发</t>
         </is>
       </c>
-      <c r="E32" s="81" t="inlineStr">
-        <is>
-          <t>PA网络数据包代理策略将已解密/未解密TLS/非TLS流量内联转发至第三方安全工具，路径选择选项卡应用数据包代理配置文件定义经路由L3安全链的转发方式（PA Web帮助p167-170）；对应矩阵#122</t>
-        </is>
-      </c>
-      <c r="F32" s="80" t="inlineStr">
+      <c r="E33" s="81" t="inlineStr">
+        <is>
+          <t>PA网络数据包代理策略将已解密/未解密TLS/非TLS流量内联转发至第三方安全工具，路径选择选项卡应用数据包代理配置文件定义经路由L3安全链的转发方式（PA Web帮助p167-170）；天融信无网络数据包代理模块，最接近手段为WAF旁路联动（经交换机镜像引流，天融信手册《与WAF联动》页），非内联且无回注路径；对应矩阵#122</t>
+        </is>
+      </c>
+      <c r="F33" s="80" t="inlineStr">
         <is>
           <t>高</t>
-        </is>
-      </c>
-      <c r="G32" s="81" t="inlineStr"/>
-      <c r="H32" s="80" t="inlineStr">
-        <is>
-          <t>部分支持</t>
-        </is>
-      </c>
-      <c r="I32" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="66" customHeight="1" s="1">
-      <c r="A33" s="84" t="n"/>
-      <c r="B33" s="85" t="n"/>
-      <c r="C33" s="81" t="inlineStr">
-        <is>
-          <t>支持NPBroker转发流量类型选择（TLS解密/未解密/非TLS）</t>
-        </is>
-      </c>
-      <c r="D33" s="81" t="inlineStr">
-        <is>
-          <t>TLS解密/未解密/非TLS流量类型选择</t>
-        </is>
-      </c>
-      <c r="E33" s="81" t="inlineStr">
-        <is>
-          <t>PA规则可选Forward TLS(Decrypted)/未解密/非TLS多种流量类型；需免费许可证（PA Web帮助p167）；天融信无网络数据包代理模块（矩阵#122）</t>
-        </is>
-      </c>
-      <c r="F33" s="80" t="inlineStr">
-        <is>
-          <t>中</t>
         </is>
       </c>
       <c r="G33" s="81" t="inlineStr"/>
@@ -4314,63 +4318,63 @@
           <t>不支持</t>
         </is>
       </c>
-      <c r="I33" s="80" t="inlineStr"/>
+      <c r="I33" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="66" customHeight="1" s="1">
       <c r="A34" s="84" t="n"/>
-      <c r="B34" s="80" t="inlineStr">
-        <is>
-          <t>隧道检测(Tunnel Inspection)</t>
-        </is>
-      </c>
+      <c r="B34" s="85" t="n"/>
       <c r="C34" s="81" t="inlineStr">
         <is>
-          <t>支持GRE/GTP-U/HTTP2等明文隧道内层流量检测</t>
+          <t>支持NPBroker转发流量类型选择（TLS解密/未解密/非TLS）</t>
         </is>
       </c>
       <c r="D34" s="81" t="inlineStr">
         <is>
-          <t>GRE/GTP-U/VXLAN/非加密IPSec隧道内层流量解封装检测</t>
+          <t>TLS解密/未解密/非TLS流量类型选择</t>
         </is>
       </c>
       <c r="E34" s="81" t="inlineStr">
         <is>
-          <t>PA隧道检测策略解封装并深度检测GRE/GTP-U/VXLAN/非加密IPSec（NULL加密/AH传输模式）等明文隧道内容（PA Web帮助p172-173）；对应矩阵#128/37</t>
+          <t>PA规则可选Forward TLS(Decrypted)/未解密/非TLS多种流量类型；需免费许可证（PA Web帮助p167）；天融信无网络数据包代理模块（矩阵#122）</t>
         </is>
       </c>
       <c r="F34" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G34" s="81" t="inlineStr"/>
       <c r="H34" s="80" t="inlineStr">
         <is>
-          <t>部分支持</t>
-        </is>
-      </c>
-      <c r="I34" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="51" customHeight="1" s="1">
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I34" s="80" t="inlineStr"/>
+    </row>
+    <row r="35" ht="66" customHeight="1" s="1">
       <c r="A35" s="84" t="n"/>
-      <c r="B35" s="85" t="n"/>
+      <c r="B35" s="80" t="inlineStr">
+        <is>
+          <t>隧道检测(Tunnel Inspection)</t>
+        </is>
+      </c>
       <c r="C35" s="81" t="inlineStr">
         <is>
-          <t>支持最大封装级数防护（max_encap）</t>
+          <t>支持GRE隧道终结与内层流量检测</t>
         </is>
       </c>
       <c r="D35" s="81" t="inlineStr">
         <is>
-          <t>隧道嵌套封装最大级数限制，超限丢弃</t>
+          <t>GRE隧道封装/解封装，内层流量按普通流量检测</t>
         </is>
       </c>
       <c r="E35" s="81" t="inlineStr">
         <is>
-          <t>PA对隧道最大封装级数超限丢包防护，防隧道嵌套绕过（PA管理指南p655）；天融信手册无封装级数防护（检索无命中）</t>
+          <t>PA隧道检测策略解封装并检测GRE隧道内容（PA Web帮助p172-173）；天融信GRE隧道支持封装与解封装，解封装后内层报文按普通流量处理检测（天融信手册《GRE隧道》页）；对应矩阵#128/37</t>
         </is>
       </c>
       <c r="F35" s="80" t="inlineStr">
@@ -4381,137 +4385,133 @@
       <c r="G35" s="81" t="inlineStr"/>
       <c r="H35" s="80" t="inlineStr">
         <is>
-          <t>不支持</t>
-        </is>
-      </c>
-      <c r="I35" s="80" t="inlineStr"/>
-    </row>
-    <row r="36" ht="81" customHeight="1" s="1">
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I35" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="96" customHeight="1" s="1">
       <c r="A36" s="84" t="n"/>
-      <c r="B36" s="80" t="inlineStr">
-        <is>
-          <t>应用覆盖(App Override)</t>
-        </is>
-      </c>
+      <c r="B36" s="84" t="n"/>
       <c r="C36" s="81" t="inlineStr">
         <is>
-          <t>支持通过Application Override重定义应用识别</t>
+          <t>支持GTP-U/VXLAN/非加密IPSec隧道内层检测</t>
         </is>
       </c>
       <c r="D36" s="81" t="inlineStr">
         <is>
-          <t>按协议/端口自定义应用识别结果</t>
+          <t>GTP-U/VXLAN/NULL加密IPSec(AH)隧道内层流量检测</t>
         </is>
       </c>
       <c r="E36" s="81" t="inlineStr">
         <is>
-          <t>PA应用替代策略改变防火墙对网络通信的应用分类方式（如指定明文协议/端口识别，PA Web帮助p178）；天融信自定义应用允许管理员按需自定义应用协议（含端口匹配）并加入应用规则库（天融信手册《自定义应用》页）；对应矩阵#26</t>
+          <t>PA隧道检测支持GTP-U/VXLAN/非加密IPSec（NULL加密/AH传输模式）内层检测（PA Web帮助p172-173）；天融信VXLAN仅隧道封装转发与三层网关（天融信手册《业务接入端》《三层VXLAN网关》页），无内层安全检测，GTP检测检索无命中；对应矩阵#128/37</t>
         </is>
       </c>
       <c r="F36" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G36" s="81" t="inlineStr"/>
       <c r="H36" s="80" t="inlineStr">
         <is>
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I36" s="80" t="inlineStr"/>
+    </row>
+    <row r="37" ht="51" customHeight="1" s="1">
+      <c r="A37" s="84" t="n"/>
+      <c r="B37" s="85" t="n"/>
+      <c r="C37" s="81" t="inlineStr">
+        <is>
+          <t>支持最大封装级数防护（max_encap）</t>
+        </is>
+      </c>
+      <c r="D37" s="81" t="inlineStr">
+        <is>
+          <t>隧道嵌套封装最大级数限制，超限丢弃</t>
+        </is>
+      </c>
+      <c r="E37" s="81" t="inlineStr">
+        <is>
+          <t>PA对隧道最大封装级数超限丢包防护，防隧道嵌套绕过（PA管理指南p655）；天融信手册无封装级数防护（检索无命中）</t>
+        </is>
+      </c>
+      <c r="F37" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G37" s="85" t="n"/>
+      <c r="H37" s="85" t="n"/>
+      <c r="I37" s="85" t="n"/>
+    </row>
+    <row r="38" ht="81" customHeight="1" s="1">
+      <c r="A38" s="84" t="n"/>
+      <c r="B38" s="80" t="inlineStr">
+        <is>
+          <t>应用覆盖(App Override)</t>
+        </is>
+      </c>
+      <c r="C38" s="81" t="inlineStr">
+        <is>
+          <t>支持通过Application Override重定义应用识别</t>
+        </is>
+      </c>
+      <c r="D38" s="81" t="inlineStr">
+        <is>
+          <t>按协议/端口自定义应用识别结果</t>
+        </is>
+      </c>
+      <c r="E38" s="81" t="inlineStr">
+        <is>
+          <t>PA应用替代策略改变防火墙对网络通信的应用分类方式（如指定明文协议/端口识别，PA Web帮助p178）；天融信自定义应用允许管理员按需自定义应用协议（含端口匹配）并加入应用规则库（天融信手册《自定义应用》页）；对应矩阵#26</t>
+        </is>
+      </c>
+      <c r="F38" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G38" s="81" t="inlineStr"/>
+      <c r="H38" s="80" t="inlineStr">
+        <is>
           <t>已支持</t>
         </is>
       </c>
-      <c r="I36" s="80" t="inlineStr">
+      <c r="I38" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="66" customHeight="1" s="1">
-      <c r="A37" s="84" t="n"/>
-      <c r="B37" s="84" t="n"/>
-      <c r="C37" s="81" t="inlineStr">
+    <row r="39" ht="66" customHeight="1" s="1">
+      <c r="A39" s="84" t="n"/>
+      <c r="B39" s="84" t="n"/>
+      <c r="C39" s="81" t="inlineStr">
         <is>
           <t>支持覆盖类型（端口映射类）识别</t>
         </is>
       </c>
-      <c r="D37" s="81" t="inlineStr">
+      <c r="D39" s="81" t="inlineStr">
         <is>
           <t>端口映射类覆盖识别</t>
         </is>
       </c>
-      <c r="E37" s="81" t="inlineStr">
+      <c r="E39" s="81" t="inlineStr">
         <is>
           <t>PA支持端口式应用覆盖识别（configurable自定义应用）；天融信自定义应用允许管理员按特定需要自行定义应用协议（含端口匹配），自动添加到应用规则库供安全策略引用（天融信手册《自定义应用》页）</t>
         </is>
       </c>
-      <c r="F37" s="80" t="inlineStr">
+      <c r="F39" s="80" t="inlineStr">
         <is>
           <t>低</t>
-        </is>
-      </c>
-      <c r="G37" s="81" t="inlineStr"/>
-      <c r="H37" s="80" t="inlineStr">
-        <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I37" s="80" t="inlineStr"/>
-    </row>
-    <row r="38" ht="96" customHeight="1" s="1">
-      <c r="A38" s="84" t="n"/>
-      <c r="B38" s="85" t="n"/>
-      <c r="C38" s="81" t="inlineStr">
-        <is>
-          <t>支持应用替代流量跳过七层检测等效配置</t>
-        </is>
-      </c>
-      <c r="D38" s="81" t="inlineStr">
-        <is>
-          <t>匹配覆盖策略的流量跳过七层检测，四层快速转发</t>
-        </is>
-      </c>
-      <c r="E38" s="81" t="inlineStr">
-        <is>
-          <t>PA应用替代策略明确绕过第7层处理与威胁检查，改用第4层状态检查以加速（PA管理指南p1307）；天融信自定义应用加入规则库后仍默认经安全引擎检测（天融信手册《自定义应用》页）；迁移评估项：PA应用替代多为私有大流量业务加速，转换时需同步关闭对应策略的IPS/七层检测，否则性能被拖垮或误阻断</t>
-        </is>
-      </c>
-      <c r="F38" s="80" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="G38" s="85" t="n"/>
-      <c r="H38" s="80" t="inlineStr">
-        <is>
-          <t>待评估</t>
-        </is>
-      </c>
-      <c r="I38" s="85" t="n"/>
-    </row>
-    <row r="39" ht="111" customHeight="1" s="1">
-      <c r="A39" s="84" t="n"/>
-      <c r="B39" s="80" t="inlineStr">
-        <is>
-          <t>身份验证(Authentication)</t>
-        </is>
-      </c>
-      <c r="C39" s="81" t="inlineStr">
-        <is>
-          <t>支持基于用户身份的身份验证策略（User-ID）</t>
-        </is>
-      </c>
-      <c r="D39" s="81" t="inlineStr">
-        <is>
-          <t>基于用户/用户组策略，多源IP-用户映射（AD/Syslog/XML API）</t>
-        </is>
-      </c>
-      <c r="E39" s="81" t="inlineStr">
-        <is>
-          <t>PA身份验证策略在访问网络资源前对用户鉴权（PA Web帮助p182），配合User-ID多源映射（AD/XML/Syslog等）；天融信用户访问网络资源前经认证，认证通过后检查关联的用户访问策略，支持门户认证（本地/外部）与LDAP/RADIUS对接（天融信手册《管理用户》《添加Radius服务器》页）；对应矩阵#3/35</t>
-        </is>
-      </c>
-      <c r="F39" s="80" t="inlineStr">
-        <is>
-          <t>高</t>
         </is>
       </c>
       <c r="G39" s="81" t="inlineStr"/>
@@ -4520,218 +4520,218 @@
           <t>已支持</t>
         </is>
       </c>
-      <c r="I39" s="80" t="inlineStr">
+      <c r="I39" s="80" t="inlineStr"/>
+    </row>
+    <row r="40" ht="96" customHeight="1" s="1">
+      <c r="A40" s="84" t="n"/>
+      <c r="B40" s="85" t="n"/>
+      <c r="C40" s="81" t="inlineStr">
+        <is>
+          <t>支持应用替代流量跳过七层检测等效配置</t>
+        </is>
+      </c>
+      <c r="D40" s="81" t="inlineStr">
+        <is>
+          <t>匹配覆盖策略的流量跳过七层检测，四层快速转发</t>
+        </is>
+      </c>
+      <c r="E40" s="81" t="inlineStr">
+        <is>
+          <t>PA应用替代策略明确绕过第7层处理与威胁检查，改用第4层状态检查以加速（PA管理指南p1307）；天融信自定义应用加入规则库后仍默认经安全引擎检测（天融信手册《自定义应用》页）；迁移评估项：PA应用替代多为私有大流量业务加速，转换时需同步关闭对应策略的IPS/七层检测，否则性能被拖垮或误阻断</t>
+        </is>
+      </c>
+      <c r="F40" s="80" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G40" s="85" t="n"/>
+      <c r="H40" s="80" t="inlineStr">
+        <is>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="I40" s="85" t="n"/>
+    </row>
+    <row r="41" ht="111" customHeight="1" s="1">
+      <c r="A41" s="84" t="n"/>
+      <c r="B41" s="80" t="inlineStr">
+        <is>
+          <t>身份验证(Authentication)</t>
+        </is>
+      </c>
+      <c r="C41" s="81" t="inlineStr">
+        <is>
+          <t>支持基于用户身份的身份验证策略（User-ID）</t>
+        </is>
+      </c>
+      <c r="D41" s="81" t="inlineStr">
+        <is>
+          <t>基于用户/用户组策略，多源IP-用户映射（AD/Syslog/XML API）</t>
+        </is>
+      </c>
+      <c r="E41" s="81" t="inlineStr">
+        <is>
+          <t>PA身份验证策略在访问网络资源前对用户鉴权（PA Web帮助p182），配合User-ID多源映射（AD/XML/Syslog等）；天融信用户访问网络资源前经认证，认证通过后检查关联的用户访问策略，支持门户认证（本地/外部）与LDAP/RADIUS对接（天融信手册《管理用户》《添加Radius服务器》页）；对应矩阵#3/35</t>
+        </is>
+      </c>
+      <c r="F41" s="80" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G41" s="81" t="inlineStr"/>
+      <c r="H41" s="80" t="inlineStr">
+        <is>
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I41" s="80" t="inlineStr">
         <is>
           <t>产品线</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="81" customHeight="1" s="1">
-      <c r="A40" s="84" t="n"/>
-      <c r="B40" s="84" t="n"/>
-      <c r="C40" s="81" t="inlineStr">
+    <row r="42" ht="81" customHeight="1" s="1">
+      <c r="A42" s="84" t="n"/>
+      <c r="B42" s="84" t="n"/>
+      <c r="C42" s="81" t="inlineStr">
         <is>
           <t>支持认证策略超时与单次认证（SSO）</t>
         </is>
       </c>
-      <c r="D40" s="81" t="inlineStr">
+      <c r="D42" s="81" t="inlineStr">
         <is>
           <t>认证超时+单次认证(SSO)</t>
         </is>
       </c>
-      <c r="E40" s="81" t="inlineStr">
+      <c r="E42" s="81" t="inlineStr">
         <is>
           <t>PA支持认证超时减少重复质询、Kerberos/SAML/RADIUS等对接（PA Web帮助p186）；天融信手册检索认证超时/单点登录/SSO无命中（仅在线用户在线时长查看与强制下线）；迁移评估项：需核实天融信认证会话有效期配置与SSO对接能力</t>
         </is>
       </c>
-      <c r="F40" s="80" t="inlineStr">
+      <c r="F42" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G40" s="81" t="inlineStr"/>
-      <c r="H40" s="80" t="inlineStr">
+      <c r="G42" s="81" t="inlineStr"/>
+      <c r="H42" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="I40" s="80" t="inlineStr"/>
-    </row>
-    <row r="41" ht="126" customHeight="1" s="1">
-      <c r="A41" s="84" t="n"/>
-      <c r="B41" s="84" t="n"/>
-      <c r="C41" s="81" t="inlineStr">
-        <is>
-          <t>支持基于策略触发多因素认证质询（MFA Enforcement）</t>
-        </is>
-      </c>
-      <c r="D41" s="81" t="inlineStr">
-        <is>
-          <t>策略匹配触发多因素认证质询（MFA供应商API/RADIUS）</t>
-        </is>
-      </c>
-      <c r="E41" s="81" t="inlineStr">
-        <is>
-          <t>PA身份验证策略通过Authentication Enforcement对象对匹配流量强制质询，支持多因素身份验证（每因素独立超时，防火墙记录时间戳），MFA供应商API/RADIUS对接（PA Web帮助p185-186、p310、p735-742）；天融信双因子认证（密码+短信/证书/Ukey）仅限管理员/用户登录场景（天融信手册《登录安全策略》页），未见流量策略触发MFA质询</t>
-        </is>
-      </c>
-      <c r="F41" s="84" t="n"/>
-      <c r="G41" s="84" t="n"/>
-      <c r="H41" s="80" t="inlineStr">
-        <is>
-          <t>部分支持</t>
-        </is>
-      </c>
-      <c r="I41" s="84" t="n"/>
-    </row>
-    <row r="42" ht="96" customHeight="1" s="1">
-      <c r="A42" s="84" t="n"/>
-      <c r="B42" s="85" t="n"/>
-      <c r="C42" s="81" t="inlineStr">
-        <is>
-          <t>支持User-ID动态映射时效性等效（AD日志毫秒级更新）</t>
-        </is>
-      </c>
-      <c r="D42" s="81" t="inlineStr">
-        <is>
-          <t>AD域事件日志毫秒级IP-用户映射更新</t>
-        </is>
-      </c>
-      <c r="E42" s="81" t="inlineStr">
-        <is>
-          <t>PA无代理架构通过读取域控事件日志实现IP-用户毫秒级动态映射，大规模部署有专项规划（PA管理指南p866-867）；天融信AD对接的轮询间隔与并发认证能力手册未量化；迁移评估项：数万AD用户且移动频繁场景需实测天融信映射更新时延，避免基于用户的策略出现间歇性未授权拦截</t>
-        </is>
-      </c>
-      <c r="F42" s="85" t="n"/>
-      <c r="G42" s="85" t="n"/>
-      <c r="H42" s="80" t="inlineStr">
-        <is>
-          <t>待评估</t>
-        </is>
-      </c>
-      <c r="I42" s="85" t="n"/>
-    </row>
-    <row r="43" ht="111" customHeight="1" s="1">
+      <c r="I42" s="80" t="inlineStr"/>
+    </row>
+    <row r="43" ht="126" customHeight="1" s="1">
       <c r="A43" s="84" t="n"/>
-      <c r="B43" s="80" t="inlineStr">
-        <is>
-          <t>DoS防护(DoS Protection)</t>
-        </is>
-      </c>
+      <c r="B43" s="84" t="n"/>
       <c r="C43" s="81" t="inlineStr">
         <is>
-          <t>支持针对关键资源的分类/聚合DoS防护</t>
+          <t>支持流量策略触发多因素认证质询（MFA Enforcement）</t>
         </is>
       </c>
       <c r="D43" s="81" t="inlineStr">
         <is>
-          <t>分类(源/目的IP粒度)+聚合(全局)双层阈值限流</t>
+          <t>流量策略匹配触发MFA质询（非登录场景，MFA供应商API/RADIUS）</t>
         </is>
       </c>
       <c r="E43" s="81" t="inlineStr">
         <is>
-          <t>PA DoS策略基于源/目的接口、区域、地址、服务定义允许/拒绝/告警，规则可选聚合与分类双层DoS保护配置文件设定阈值速率（PA Web帮助p189-191、PA管理指南p1354）；天融信DDoS防护模块按防护对象（目的服务器）设阈值（pps/bps），可达目的IP粒度（天融信手册《配置策略模板》《日志查看》页）；对应矩阵#52/42</t>
-        </is>
-      </c>
-      <c r="F43" s="80" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="G43" s="81" t="inlineStr"/>
+          <t>PA身份验证策略通过Authentication Enforcement对象对匹配流量强制质询，支持多因素身份验证（每因素独立超时，防火墙记录时间戳），MFA供应商API/RADIUS对接（PA Web帮助p185-186、p310、p735-742）；天融信双因子认证（密码+短信/证书/Ukey）仅限管理员/用户登录场景（天融信手册《登录安全策略》页），无流量策略触发MFA质询</t>
+        </is>
+      </c>
+      <c r="F43" s="84" t="n"/>
+      <c r="G43" s="84" t="n"/>
       <c r="H43" s="80" t="inlineStr">
         <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I43" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="51" customHeight="1" s="1">
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I43" s="84" t="n"/>
+    </row>
+    <row r="44" ht="96" customHeight="1" s="1">
       <c r="A44" s="84" t="n"/>
       <c r="B44" s="85" t="n"/>
       <c r="C44" s="81" t="inlineStr">
         <is>
-          <t>支持DoS聚合配置文件（连接/秒阈值）</t>
+          <t>支持User-ID动态映射时效性等效（AD日志毫秒级更新）</t>
         </is>
       </c>
       <c r="D44" s="81" t="inlineStr">
         <is>
-          <t>连接数/秒阈值告警+最大速率限制</t>
+          <t>AD域事件日志毫秒级IP-用户映射更新</t>
         </is>
       </c>
       <c r="E44" s="81" t="inlineStr">
         <is>
-          <t>PA聚合DoS配置文件按传入连接数/秒触发告警与最大速率限制；天融信DDoS防护模块按阈值（pps/bps）监视并触发防护（天融信手册《配置策略模板》页）</t>
-        </is>
-      </c>
-      <c r="F44" s="80" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G44" s="81" t="inlineStr"/>
+          <t>PA无代理架构通过读取域控事件日志实现IP-用户毫秒级动态映射，大规模部署有专项规划（PA管理指南p866-867）；天融信AD对接的轮询间隔与并发认证能力手册未量化；迁移评估项：数万AD用户且移动频繁场景需实测天融信映射更新时延，避免基于用户的策略出现间歇性未授权拦截</t>
+        </is>
+      </c>
+      <c r="F44" s="85" t="n"/>
+      <c r="G44" s="85" t="n"/>
       <c r="H44" s="80" t="inlineStr">
         <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I44" s="80" t="inlineStr"/>
-    </row>
-    <row r="45" ht="171" customHeight="1" s="1">
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="I44" s="85" t="n"/>
+    </row>
+    <row r="45" ht="111" customHeight="1" s="1">
       <c r="A45" s="84" t="n"/>
       <c r="B45" s="80" t="inlineStr">
         <is>
-          <t>动态对象(Dynamic Objects)</t>
+          <t>DoS防护(DoS Protection)</t>
         </is>
       </c>
       <c r="C45" s="81" t="inlineStr">
         <is>
-          <t>支持外部动态列表作为策略地址对象（EDL）</t>
+          <t>支持针对关键资源的分类/聚合DoS防护</t>
         </is>
       </c>
       <c r="D45" s="81" t="inlineStr">
         <is>
-          <t>HTTP/HTTPS外部文本列表(IP/域名/URL)自动拉取，策略直接引用</t>
+          <t>分类(源/目的IP粒度)+聚合(全局)双层阈值限流</t>
         </is>
       </c>
       <c r="E45" s="81" t="inlineStr">
         <is>
-          <t>PA外部动态列表：基于HTTP/HTTPS托管的文本文件创建IP/URL/域名/IMEI/IMSI地址对象，防火墙定时自动拉取更新，策略中直接引用（Objects&gt;External Dynamic Lists，PA Web帮助p236-239；策略源/目标可直接选EDL，p196-197）；天融信手册检索外部动态列表/EDL无命中，仅内置威胁情报库与云端威胁情报库（规则集管理，天融信手册《威胁情报》《配置规则集》页），无策略直接引用任意外部文本列表机制；迁移评估项：PA策略中引用的EDL需转换为天融信静态地址组定期导入或威胁情报联动</t>
+          <t>PA DoS策略基于源/目的接口、区域、地址、服务定义允许/拒绝/告警，规则可选聚合与分类双层DoS保护配置文件设定阈值速率（PA Web帮助p189-191、PA管理指南p1354）；天融信DDoS防护模块按防护对象（目的服务器）设阈值（pps/bps），可达目的IP粒度（天融信手册《配置策略模板》《日志查看》页）；对应矩阵#52/42</t>
         </is>
       </c>
       <c r="F45" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G45" s="81" t="inlineStr"/>
       <c r="H45" s="80" t="inlineStr">
         <is>
-          <t>不支持</t>
-        </is>
-      </c>
-      <c r="I45" s="80" t="inlineStr"/>
-    </row>
-    <row r="46" ht="126" customHeight="1" s="1">
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I45" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="51" customHeight="1" s="1">
       <c r="A46" s="84" t="n"/>
       <c r="B46" s="85" t="n"/>
       <c r="C46" s="81" t="inlineStr">
         <is>
-          <t>支持基于标记的动态地址组（DAG）</t>
+          <t>支持DoS聚合配置文件（连接/秒阈值）</t>
         </is>
       </c>
       <c r="D46" s="81" t="inlineStr">
         <is>
-          <t>Tag标记过滤器动态地址组，成员随IP变化自动更新</t>
+          <t>连接数/秒阈值告警+最大速率限制</t>
         </is>
       </c>
       <c r="E46" s="81" t="inlineStr">
         <is>
-          <t>PA动态地址组：查找标记(Tag)+基于标记的过滤器（AND/OR匹配）动态填充成员，VM信息源注册或XML/REST API定义标记，IP变化时策略自动生效（PA Web帮助p207-208、p228）；天融信手册检索动态地址组/标签/SDN/云平台联动无命中，地址组为静态IP/子网绑定（天融信手册《地址》页）；迁移评估项：PA云环境Tag微隔离策略需转换为静态地址组，IP漂移场景需人工或API维护</t>
+          <t>PA聚合DoS配置文件按传入连接数/秒触发告警与最大速率限制；天融信DDoS防护模块按阈值（pps/bps）监视并触发防护（天融信手册《配置策略模板》页）</t>
         </is>
       </c>
       <c r="F46" s="80" t="inlineStr">
@@ -4742,66 +4742,62 @@
       <c r="G46" s="81" t="inlineStr"/>
       <c r="H46" s="80" t="inlineStr">
         <is>
-          <t>不支持</t>
+          <t>已支持</t>
         </is>
       </c>
       <c r="I46" s="80" t="inlineStr"/>
     </row>
-    <row r="47" ht="51" customHeight="1" s="1">
+    <row r="47" ht="171" customHeight="1" s="1">
       <c r="A47" s="84" t="n"/>
       <c r="B47" s="80" t="inlineStr">
         <is>
-          <t>SD-WAN策略</t>
+          <t>动态对象(Dynamic Objects)</t>
         </is>
       </c>
       <c r="C47" s="81" t="inlineStr">
         <is>
-          <t>支持按应用配置链路路径管理与链路质量探测</t>
+          <t>支持外部动态列表作为策略地址对象（EDL）</t>
         </is>
       </c>
       <c r="D47" s="81" t="inlineStr">
         <is>
-          <t>按应用/区域/地址分配链路与流量分发</t>
+          <t>HTTP/HTTPS外部文本列表(IP/域名/URL)自动拉取，策略直接引用</t>
         </is>
       </c>
       <c r="E47" s="81" t="inlineStr">
         <is>
-          <t>PA SD-WAN策略按应用/抖动/延迟/丢包指标分配链路，流量分发（PA Web帮助p197）；对应矩阵#129/120</t>
+          <t>PA外部动态列表：基于HTTP/HTTPS托管的文本文件创建IP/URL/域名/IMEI/IMSI地址对象，防火墙定时自动拉取更新，策略中直接引用（Objects&gt;External Dynamic Lists，PA Web帮助p236-239；策略源/目标可直接选EDL，p196-197）；天融信手册检索外部动态列表/EDL无命中，仅内置威胁情报库与云端威胁情报库（规则集管理，天融信手册《威胁情报》《配置规则集》页），无策略直接引用任意外部文本列表机制；迁移评估项：PA策略中引用的EDL需转换为天融信静态地址组定期导入或威胁情报联动</t>
         </is>
       </c>
       <c r="F47" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G47" s="81" t="inlineStr"/>
       <c r="H47" s="80" t="inlineStr">
         <is>
-          <t>部分支持</t>
-        </is>
-      </c>
-      <c r="I47" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="81" customHeight="1" s="1">
-      <c r="A48" s="85" t="n"/>
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I47" s="80" t="inlineStr"/>
+    </row>
+    <row r="48" ht="126" customHeight="1" s="1">
+      <c r="A48" s="84" t="n"/>
       <c r="B48" s="85" t="n"/>
       <c r="C48" s="81" t="inlineStr">
         <is>
-          <t>支持SD-WAN路径选择与链路质量监测（jitter/latency/loss）</t>
+          <t>支持基于标记的动态地址组（DAG）</t>
         </is>
       </c>
       <c r="D48" s="81" t="inlineStr">
         <is>
-          <t>抖动/延迟/丢包(jitter/latency/loss)指标选路</t>
+          <t>Tag标记过滤器动态地址组，成员随IP变化自动更新</t>
         </is>
       </c>
       <c r="E48" s="81" t="inlineStr">
         <is>
-          <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路（PA Web帮助p195）；天融信有链路探测(ping)+智能选路(最小延迟优先)（天融信手册《策略路由》页），无jitter/latency/loss多维指标</t>
+          <t>PA动态地址组：查找标记(Tag)+基于标记的过滤器（AND/OR匹配）动态填充成员，VM信息源注册或XML/REST API定义标记，IP变化时策略自动生效（PA Web帮助p207-208、p228）；天融信手册检索动态地址组/标签/SDN/云平台联动无命中，地址组为静态IP/子网绑定（天融信手册《地址》页）；迁移评估项：PA云环境Tag微隔离策略需转换为静态地址组，IP漂移场景需人工或API维护</t>
         </is>
       </c>
       <c r="F48" s="80" t="inlineStr">
@@ -4812,50 +4808,122 @@
       <c r="G48" s="81" t="inlineStr"/>
       <c r="H48" s="80" t="inlineStr">
         <is>
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I48" s="80" t="inlineStr"/>
+    </row>
+    <row r="49" ht="81" customHeight="1" s="1">
+      <c r="A49" s="84" t="n"/>
+      <c r="B49" s="80" t="inlineStr">
+        <is>
+          <t>SD-WAN策略</t>
+        </is>
+      </c>
+      <c r="C49" s="81" t="inlineStr">
+        <is>
+          <t>支持按应用配置链路路径管理与链路质量探测</t>
+        </is>
+      </c>
+      <c r="D49" s="81" t="inlineStr">
+        <is>
+          <t>按应用分配链路与流量分发（天融信以策略路由+LLB近似实现）</t>
+        </is>
+      </c>
+      <c r="E49" s="81" t="inlineStr">
+        <is>
+          <t>PA SD-WAN策略按应用/抖动/延迟/丢包指标分配链路，流量分发（PA Web帮助p197）；天融信为策略路由+链路负载均衡近似实现（天融信手册《策略路由》《链路负载均衡》页），无SD-WAN策略模型；对应矩阵#129/120</t>
+        </is>
+      </c>
+      <c r="F49" s="80" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G49" s="81" t="inlineStr"/>
+      <c r="H49" s="80" t="inlineStr">
+        <is>
           <t>部分支持</t>
         </is>
       </c>
-      <c r="I48" s="80" t="inlineStr"/>
+      <c r="I49" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="81" customHeight="1" s="1">
+      <c r="A50" s="85" t="n"/>
+      <c r="B50" s="85" t="n"/>
+      <c r="C50" s="81" t="inlineStr">
+        <is>
+          <t>支持SD-WAN路径选择与链路质量监测（jitter/latency/loss）</t>
+        </is>
+      </c>
+      <c r="D50" s="81" t="inlineStr">
+        <is>
+          <t>抖动/延迟/丢包多维指标选路（天融信现仅延迟探测）</t>
+        </is>
+      </c>
+      <c r="E50" s="81" t="inlineStr">
+        <is>
+          <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路（PA Web帮助p195）；天融信有链路探测(ping)+智能选路(最小延迟优先)（天融信手册《策略路由》页），无jitter/latency/loss多维指标</t>
+        </is>
+      </c>
+      <c r="F50" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G50" s="81" t="inlineStr"/>
+      <c r="H50" s="80" t="inlineStr">
+        <is>
+          <t>部分支持</t>
+        </is>
+      </c>
+      <c r="I50" s="80" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="I9:I14"/>
-    <mergeCell ref="B26:B31"/>
+  <mergeCells count="39">
+    <mergeCell ref="F17:F19"/>
     <mergeCell ref="B47:B48"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="A2:A50"/>
     <mergeCell ref="H6:H7"/>
-    <mergeCell ref="B15:B21"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="I40:I42"/>
-    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="B27:B32"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="G17:G22"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="H17:H20"/>
     <mergeCell ref="B2:B7"/>
-    <mergeCell ref="H11:H14"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="I16:I21"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="F40:F42"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="H16:H19"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="B8:B15"/>
+    <mergeCell ref="B16:B22"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G9:G15"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="I9:I15"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="H12:H15"/>
     <mergeCell ref="F3:F7"/>
-    <mergeCell ref="G27:G31"/>
-    <mergeCell ref="I27:I31"/>
+    <mergeCell ref="F11:F12"/>
     <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="I17:I22"/>
     <mergeCell ref="G3:G7"/>
-    <mergeCell ref="B8:B14"/>
     <mergeCell ref="I3:I7"/>
-    <mergeCell ref="G16:G21"/>
-    <mergeCell ref="A2:A48"/>
-    <mergeCell ref="G9:G14"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="G28:G32"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="I28:I32"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="I42:I44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4867,7 +4935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.2"/>
   <cols>
     <col width="11.7" customWidth="1" style="1" min="1" max="1"/>
@@ -5021,7 +5089,7 @@
       <c r="H4" s="82" t="n"/>
       <c r="I4" s="82" t="n"/>
     </row>
-    <row r="5" ht="96" customHeight="1" s="1">
+    <row r="5" ht="51" customHeight="1" s="1">
       <c r="A5" s="82" t="n"/>
       <c r="B5" s="80" t="inlineStr">
         <is>
@@ -5030,17 +5098,17 @@
       </c>
       <c r="C5" s="81" t="inlineStr">
         <is>
-          <t>支持安全策略规则构建块：源用户/HIP/设备/应用/服务/日志等</t>
+          <t>支持HIP主机信息配置文件策略匹配（Host Information Profile）</t>
         </is>
       </c>
       <c r="D5" s="81" t="inlineStr">
         <is>
-          <t>预登录用户/HIP主机信息/设备对象/应用默认端口规避/会话结束日志等构建块</t>
+          <t>终端安全态势（补丁/杀软/磁盘加密等）作为策略匹配条件</t>
         </is>
       </c>
       <c r="E5" s="81" t="inlineStr">
         <is>
-          <t>PA规则构建块含预登录用户、HIP配置文件、设备对象、应用默认端口规避、会话结束日志等；天融信支持用户/应用/服务/日志构建块，但无HIP主机信息配置文件与设备对象等价物，仅有EDR联动上报终端资产并下发管控策略（天融信手册《与EDR联动》页）；对应矩阵#3/4</t>
+          <t>PA规则构建块支持HIP配置文件匹配终端安全态势（对应矩阵#3/4）；天融信手册检索HIP/主机信息配置文件无命中，无终端安全态势匹配等价物</t>
         </is>
       </c>
       <c r="F5" s="80" t="inlineStr">
@@ -5051,32 +5119,32 @@
       <c r="G5" s="81" t="inlineStr"/>
       <c r="H5" s="80" t="inlineStr">
         <is>
-          <t>部分支持</t>
+          <t>不支持</t>
         </is>
       </c>
       <c r="I5" s="80" t="inlineStr"/>
     </row>
-    <row r="6" ht="81" customHeight="1" s="1">
+    <row r="6" ht="51" customHeight="1" s="1">
       <c r="A6" s="82" t="n"/>
       <c r="B6" s="82" t="n"/>
       <c r="C6" s="81" t="inlineStr">
         <is>
-          <t>支持安全策略优化器（Policy Optimizer）</t>
+          <t>支持终端设备对象作为策略匹配条件</t>
         </is>
       </c>
       <c r="D6" s="81" t="inlineStr">
         <is>
-          <t>端口(L4)规则一键迁移为应用(L7)规则+新应用查看器</t>
+          <t>终端设备类型（手机/平板/IoT等设备对象）作为策略构建块</t>
         </is>
       </c>
       <c r="E6" s="81" t="inlineStr">
         <is>
-          <t>PA新应用查看器+端口规则迁移至App-ID规则工作流+规则使用统计，减少攻击面（PA Web帮助p142）；天融信策略统计开关可显示规则匹配命中情况（天融信手册《配置访问控制策略》页），但无新应用查看器与端口→应用规则迁移工作流；对应矩阵#132</t>
+          <t>PA支持设备对象构建块（对应矩阵#3/4）；天融信经EDR联动上报终端资产并下发管控策略（天融信手册《与EDR联动》页），无独立设备对象</t>
         </is>
       </c>
       <c r="F6" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G6" s="81" t="inlineStr"/>
@@ -5087,200 +5155,196 @@
       </c>
       <c r="I6" s="80" t="inlineStr"/>
     </row>
-    <row r="7" ht="36" customHeight="1" s="1">
+    <row r="7" ht="81" customHeight="1" s="1">
       <c r="A7" s="82" t="n"/>
       <c r="B7" s="82" t="n"/>
       <c r="C7" s="81" t="inlineStr">
         <is>
-          <t>支持配置锁（Config Lock/Commit Lock）</t>
+          <t>支持端口(L4)规则向应用(L7)规则迁移工作流（Policy Optimizer）</t>
         </is>
       </c>
       <c r="D7" s="81" t="inlineStr">
         <is>
-          <t>配置锁/提交锁，防止多管理员并发修改</t>
+          <t>端口规则一键迁移为应用规则+新应用查看器</t>
         </is>
       </c>
       <c r="E7" s="81" t="inlineStr">
         <is>
-          <t>PA可锁定待选配置或提交，防止他管理员并发更改；对应矩阵#135（天融信不支持，PA优势）</t>
-        </is>
-      </c>
-      <c r="F7" s="82" t="n"/>
+          <t>PA策略优化器提供新应用查看器与端口→App-ID规则迁移工作流（PA Web帮助p142）；天融信策略统计仅显示规则命中数（天融信手册《配置访问控制策略》页），无迁移工具（命中统计能力已另列已支持行）；对应矩阵#132</t>
+        </is>
+      </c>
+      <c r="F7" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
       <c r="G7" s="82" t="n"/>
       <c r="H7" s="80" t="inlineStr">
         <is>
-          <t>待评估</t>
+          <t>不支持</t>
         </is>
       </c>
       <c r="I7" s="82" t="n"/>
     </row>
-    <row r="8" ht="111" customHeight="1" s="1">
+    <row r="8" ht="36" customHeight="1" s="1">
       <c r="A8" s="82" t="n"/>
       <c r="B8" s="82" t="n"/>
       <c r="C8" s="81" t="inlineStr">
         <is>
-          <t>支持应用默认端口绑定（Service: application-default）</t>
+          <t>支持配置锁（Config Lock/Commit Lock）</t>
         </is>
       </c>
       <c r="D8" s="81" t="inlineStr">
         <is>
-          <t>应用匹配同时强制使用标准端口，非标端口拒绝</t>
+          <t>配置锁/提交锁，防止多管理员并发修改</t>
         </is>
       </c>
       <c r="E8" s="81" t="inlineStr">
         <is>
-          <t>PA安全策略默认服务为application-default：放行应用同时强制其使用标准端口（如SSH仅22），非标准端口不匹配即拦截（PA管理指南p904）；天融信策略为五元组+应用识别组合（天融信手册《配置访问控制策略》页）；迁移评估项：直接转换若仅保留应用识别不限端口将扩大安全敞口，需制定应用标准端口映射限制（App-Default）转换方案；对应矩阵#2</t>
-        </is>
-      </c>
-      <c r="F8" s="80" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>PA可锁定待选配置或提交，防止他管理员并发更改；对应矩阵#135（天融信不支持，PA优势）</t>
+        </is>
+      </c>
+      <c r="F8" s="82" t="n"/>
       <c r="G8" s="82" t="n"/>
-      <c r="H8" s="82" t="n"/>
+      <c r="H8" s="80" t="inlineStr">
+        <is>
+          <t>待评估</t>
+        </is>
+      </c>
       <c r="I8" s="82" t="n"/>
     </row>
-    <row r="9" ht="81" customHeight="1" s="1">
+    <row r="9" ht="111" customHeight="1" s="1">
       <c r="A9" s="82" t="n"/>
       <c r="B9" s="82" t="n"/>
       <c r="C9" s="81" t="inlineStr">
         <is>
-          <t>支持安全策略绑定安全配置文件组（Profile Group）</t>
+          <t>支持应用默认端口绑定（Service: application-default）</t>
         </is>
       </c>
       <c r="D9" s="81" t="inlineStr">
         <is>
-          <t>Allow动作关联反病毒/漏洞防护/URL过滤/文件阻断/WildFire配置文件组</t>
+          <t>应用匹配同时强制使用标准端口，非标端口拒绝</t>
         </is>
       </c>
       <c r="E9" s="81" t="inlineStr">
         <is>
-          <t>PA安全策略Allow动作关联Profile组（反病毒/漏洞防护/URL过滤/文件阻止/WildFire等，PA Web帮助p304）；天融信一体化策略引擎自带检测项；迁移评估项：需评估Profile组到天融信各检测引擎的映射与缺省动作差异；对应矩阵#4</t>
+          <t>PA安全策略默认服务为application-default：放行应用同时强制其使用标准端口（如SSH仅22），非标准端口不匹配即拦截（PA管理指南p904）；天融信策略为五元组+应用识别组合（天融信手册《配置访问控制策略》页）；迁移评估项：直接转换若仅保留应用识别不限端口将扩大安全敞口，需制定应用标准端口映射限制（App-Default）转换方案；对应矩阵#2</t>
         </is>
       </c>
       <c r="F9" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G9" s="82" t="n"/>
       <c r="H9" s="82" t="n"/>
       <c r="I9" s="82" t="n"/>
     </row>
-    <row r="10" ht="156" customHeight="1" s="1">
+    <row r="10" ht="81" customHeight="1" s="1">
       <c r="A10" s="82" t="n"/>
       <c r="B10" s="82" t="n"/>
       <c r="C10" s="81" t="inlineStr">
         <is>
-          <t>支持隐式默认规则显式化迁移（intrazone/interzone-default）</t>
+          <t>支持安全策略绑定安全配置文件组（Profile Group）</t>
         </is>
       </c>
       <c r="D10" s="81" t="inlineStr">
         <is>
-          <t>同区域默认放行/跨区域默认拒绝，支持替代与日志转发</t>
+          <t>Allow动作关联反病毒/漏洞防护/URL过滤/文件阻断/WildFire配置文件组</t>
         </is>
       </c>
       <c r="E10" s="81" t="inlineStr">
         <is>
-          <t>PA安全策略库末尾自带两条隐式系统规则：区域内默认（同Zone默认放行）与区域间默认（跨Zone默认拒绝），可被替代配置，替代字段含日志转发配置文件与Log at Session End在会话结束时记录（PA Web帮助p134-136）；天融信未见同区域默认放行的隐式规则机制；迁移评估项：①必须提取intrazone-default同Zone互访需求并显式转换为放行规则，否则割接后同Zone不同网段/VLAN互访将被默认拦截；②需在新设备补齐底部兜底Deny-All并开启日志，否则被拒流量查无日志、排障困难</t>
+          <t>PA安全策略Allow动作关联Profile组（反病毒/漏洞防护/URL过滤/文件阻止/WildFire等，PA Web帮助p304）；天融信一体化策略引擎自带检测项；迁移评估项：需评估Profile组到天融信各检测引擎的映射与缺省动作差异；对应矩阵#4</t>
         </is>
       </c>
       <c r="F10" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G10" s="82" t="n"/>
       <c r="H10" s="82" t="n"/>
       <c r="I10" s="82" t="n"/>
     </row>
-    <row r="11" ht="126" customHeight="1" s="1">
+    <row r="11" ht="156" customHeight="1" s="1">
       <c r="A11" s="82" t="n"/>
-      <c r="B11" s="80" t="inlineStr">
+      <c r="B11" s="82" t="n"/>
+      <c r="C11" s="81" t="inlineStr">
+        <is>
+          <t>支持隐式默认规则显式化迁移（intrazone/interzone-default）</t>
+        </is>
+      </c>
+      <c r="D11" s="81" t="inlineStr">
+        <is>
+          <t>同区域默认放行/跨区域默认拒绝，支持替代与日志转发</t>
+        </is>
+      </c>
+      <c r="E11" s="81" t="inlineStr">
+        <is>
+          <t>PA安全策略库末尾自带两条隐式系统规则：区域内默认（同Zone默认放行）与区域间默认（跨Zone默认拒绝），可被替代配置，替代字段含日志转发配置文件与Log at Session End在会话结束时记录（PA Web帮助p134-136）；天融信未见同区域默认放行的隐式规则机制；迁移评估项：①必须提取intrazone-default同Zone互访需求并显式转换为放行规则，否则割接后同Zone不同网段/VLAN互访将被默认拦截；②需在新设备补齐底部兜底Deny-All并开启日志，否则被拒流量查无日志、排障困难</t>
+        </is>
+      </c>
+      <c r="F11" s="80" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G11" s="82" t="n"/>
+      <c r="H11" s="82" t="n"/>
+      <c r="I11" s="82" t="n"/>
+    </row>
+    <row r="12" ht="126" customHeight="1" s="1">
+      <c r="A12" s="82" t="n"/>
+      <c r="B12" s="80" t="inlineStr">
         <is>
           <t>NAT策略</t>
         </is>
       </c>
-      <c r="C11" s="81" t="inlineStr">
+      <c r="C12" s="81" t="inlineStr">
         <is>
           <t>支持NAT后目的区域路由回查匹配（Dest Zone by route lookup）</t>
         </is>
       </c>
-      <c r="D11" s="81" t="inlineStr">
+      <c r="D12" s="81" t="inlineStr">
         <is>
           <t>目的区域按NAT后路由查找；源/目的地址用NAT前值</t>
         </is>
       </c>
-      <c r="E11" s="81" t="inlineStr">
+      <c r="E12" s="81" t="inlineStr">
         <is>
           <t>PA底层为『先NAT判断后安全策略匹配』的因果倒置：安全策略要求源区域(NAT前)+源地址(NAT前)+目的地址(NAT前)+目的区域(NAT后按路由查找)，极其反直觉；天融信地址转换为独立策略库常规直观映射（安全策略&gt;地址转换，天融信手册《服务器映射》页）；迁移评估项：带目的NAT的策略平移后易因Zone填写错误不通，需制定NAT查表逻辑转换映射规范；对应矩阵#9</t>
         </is>
       </c>
-      <c r="F11" s="80" t="inlineStr">
+      <c r="F12" s="80" t="inlineStr">
         <is>
           <t>高</t>
-        </is>
-      </c>
-      <c r="G11" s="81" t="inlineStr"/>
-      <c r="H11" s="80" t="inlineStr">
-        <is>
-          <t>待评估</t>
-        </is>
-      </c>
-      <c r="I11" s="80" t="inlineStr"/>
-    </row>
-    <row r="12" ht="81" customHeight="1" s="1">
-      <c r="A12" s="82" t="n"/>
-      <c r="B12" s="82" t="n"/>
-      <c r="C12" s="81" t="inlineStr">
-        <is>
-          <t>支持NAT规则主动/主动HA绑定（Active/Active HA Binding）</t>
-        </is>
-      </c>
-      <c r="D12" s="81" t="inlineStr">
-        <is>
-          <t>主动/主动HA下NAT规则绑定会话所有者</t>
-        </is>
-      </c>
-      <c r="E12" s="81" t="inlineStr">
-        <is>
-          <t>PA主动/主动HA配置下NAT规则可绑定会话所有者/会话设置，控制NAT会话的设备绑定，仅A/A模式可见（PA Web帮助p150）；天融信HA为主备双机热备模式（天融信手册《配置双机热备功能》页），无主动/主动模式及NAT规则绑定机制</t>
-        </is>
-      </c>
-      <c r="F12" s="80" t="inlineStr">
-        <is>
-          <t>低</t>
         </is>
       </c>
       <c r="G12" s="81" t="inlineStr"/>
       <c r="H12" s="80" t="inlineStr">
         <is>
-          <t>不支持</t>
+          <t>待评估</t>
         </is>
       </c>
       <c r="I12" s="80" t="inlineStr"/>
     </row>
-    <row r="13" ht="96" customHeight="1" s="1">
+    <row r="13" ht="81" customHeight="1" s="1">
       <c r="A13" s="82" t="n"/>
-      <c r="B13" s="80" t="inlineStr">
-        <is>
-          <t>QoS策略</t>
-        </is>
-      </c>
+      <c r="B13" s="82" t="n"/>
       <c r="C13" s="81" t="inlineStr">
         <is>
-          <t>支持基于DSCP/ToS值匹配的QoS</t>
+          <t>支持NAT规则主动/主动HA绑定（Active/Active HA Binding）</t>
         </is>
       </c>
       <c r="D13" s="81" t="inlineStr">
         <is>
-          <t>QoS规则按DSCP/ToS值匹配调度</t>
+          <t>主动/主动HA下NAT规则绑定会话所有者</t>
         </is>
       </c>
       <c r="E13" s="81" t="inlineStr">
         <is>
-          <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
+          <t>PA主动/主动HA配置下NAT规则可绑定会话所有者/会话设置，控制NAT会话的设备绑定，仅A/A模式可见（PA Web帮助p150）；天融信HA为主备双机热备模式（天融信手册《配置双机热备功能》页），无主动/主动模式及NAT规则绑定机制</t>
         </is>
       </c>
       <c r="F13" s="80" t="inlineStr">
@@ -5291,226 +5355,226 @@
       <c r="G13" s="81" t="inlineStr"/>
       <c r="H13" s="80" t="inlineStr">
         <is>
-          <t>部分支持</t>
+          <t>不支持</t>
         </is>
       </c>
       <c r="I13" s="80" t="inlineStr"/>
     </row>
-    <row r="14" ht="111" customHeight="1" s="1">
+    <row r="14" ht="96" customHeight="1" s="1">
       <c r="A14" s="82" t="n"/>
       <c r="B14" s="80" t="inlineStr">
         <is>
-          <t>基于策略转发(PBF)</t>
+          <t>QoS策略</t>
         </is>
       </c>
       <c r="C14" s="81" t="inlineStr">
         <is>
-          <t>支持PBF强制对称返回（非对称路由环境）</t>
+          <t>支持QoS策略规则内直接按DSCP/ToS匹配调度</t>
         </is>
       </c>
       <c r="D14" s="81" t="inlineStr">
         <is>
-          <t>记录入接口MAC，回包强制原路返回</t>
+          <t>QoS策略规则DSCP/ToS直接匹配（非独立流控模块配置）</t>
         </is>
       </c>
       <c r="E14" s="81" t="inlineStr">
         <is>
-          <t>PA对称返回：虚拟路由器替代返回流量的路由查找，将流量引导回接收SYN数据包的MAC地址（ARP表确定下一跳），双ISP双活/非对称路由核心机制（PA管理指南p1294）；天融信手册检索无对称返回/回程机制命中，策略路由与LLB的回程保障能力待验证；迁移评估项：多ISP双活环境需实测天融信回包路由对称性，否则现网业务中断</t>
+          <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
         </is>
       </c>
       <c r="F14" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G14" s="81" t="inlineStr"/>
       <c r="H14" s="80" t="inlineStr">
         <is>
-          <t>待评估</t>
+          <t>部分支持</t>
         </is>
       </c>
       <c r="I14" s="80" t="inlineStr"/>
     </row>
-    <row r="15" ht="51" customHeight="1" s="1">
+    <row r="15" ht="111" customHeight="1" s="1">
       <c r="A15" s="82" t="n"/>
       <c r="B15" s="80" t="inlineStr">
         <is>
-          <t>解密策略(Decryption)</t>
+          <t>基于策略转发(PBF)</t>
         </is>
       </c>
       <c r="C15" s="81" t="inlineStr">
         <is>
-          <t>支持解密流量镜像到专用接口（Decryption Port Mirroring）</t>
+          <t>支持PBF强制对称返回（非对称路由环境）</t>
         </is>
       </c>
       <c r="D15" s="81" t="inlineStr">
         <is>
-          <t>解密后明文流量镜像至专用接口供第三方分析</t>
+          <t>记录入接口MAC，回包强制原路返回</t>
         </is>
       </c>
       <c r="E15" s="81" t="inlineStr">
         <is>
-          <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证（PA管理指南p1059）；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
+          <t>PA对称返回：虚拟路由器替代返回流量的路由查找，将流量引导回接收SYN数据包的MAC地址（ARP表确定下一跳），双ISP双活/非对称路由核心机制（PA管理指南p1294）；天融信手册检索无对称返回/回程机制命中，策略路由与LLB的回程保障能力待验证；迁移评估项：多ISP双活环境需实测天融信回包路由对称性，否则现网业务中断</t>
         </is>
       </c>
       <c r="F15" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G15" s="81" t="inlineStr"/>
       <c r="H15" s="80" t="inlineStr">
         <is>
-          <t>不支持</t>
+          <t>待评估</t>
         </is>
       </c>
       <c r="I15" s="80" t="inlineStr"/>
     </row>
-    <row r="16" ht="126" customHeight="1" s="1">
+    <row r="16" ht="51" customHeight="1" s="1">
       <c r="A16" s="82" t="n"/>
-      <c r="B16" s="82" t="n"/>
+      <c r="B16" s="80" t="inlineStr">
+        <is>
+          <t>解密策略(Decryption)</t>
+        </is>
+      </c>
       <c r="C16" s="81" t="inlineStr">
         <is>
-          <t>支持解密不受信证书分离处理（Forward Untrust Certificate）</t>
+          <t>支持解密流量镜像到专用接口（Decryption Port Mirroring）</t>
         </is>
       </c>
       <c r="D16" s="81" t="inlineStr">
         <is>
-          <t>外部无效证书以不受信转发证书重签，保留浏览器告警</t>
+          <t>解密后明文流量镜像至专用接口供第三方分析</t>
         </is>
       </c>
       <c r="E16" s="81" t="inlineStr">
         <is>
-          <t>PA转发代理遇外部过期/不受信证书时，不用内部信任CA重签，而是专用Forward Untrust Certificate重签名，让浏览器保留不受信告警（PA管理指南p994、p1030）；天融信SSL解密（透明代理/服务器SSL解密，天融信手册《代理策略》页）未见受信/不受信双证书体系；迁移评估项：需验证天融信对外部无效证书的处理方式，避免直接阻断（白屏）或信任重签（掩盖风险）</t>
+          <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证（PA管理指南p1059）；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
         </is>
       </c>
       <c r="F16" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G16" s="81" t="inlineStr"/>
       <c r="H16" s="80" t="inlineStr">
         <is>
-          <t>待评估</t>
+          <t>不支持</t>
         </is>
       </c>
       <c r="I16" s="80" t="inlineStr"/>
     </row>
-    <row r="17" ht="66" customHeight="1" s="1">
+    <row r="17" ht="126" customHeight="1" s="1">
       <c r="A17" s="82" t="n"/>
       <c r="B17" s="82" t="n"/>
       <c r="C17" s="81" t="inlineStr">
         <is>
-          <t>支持解密规则按URL类别选择性解密（URL Category）</t>
+          <t>支持解密不受信证书分离处理（Forward Untrust Certificate）</t>
         </is>
       </c>
       <c r="D17" s="81" t="inlineStr">
         <is>
-          <t>按URL类别圈定解密范围，排除银行/医疗等敏感类</t>
+          <t>外部无效证书以不受信转发证书重签，保留浏览器告警</t>
         </is>
       </c>
       <c r="E17" s="81" t="inlineStr">
         <is>
-          <t>PA解密规则可按URL类别（含自定义类别）选择解密范围，可排除银行/医疗等敏感类别不解密（PA Web帮助p164）；天融信SSL解密（代理策略/代理模板）无按URL类别选择解密机制（检索无命中）</t>
+          <t>PA转发代理遇外部过期/不受信证书时，不用内部信任CA重签，而是专用Forward Untrust Certificate重签名，让浏览器保留不受信告警（PA管理指南p994、p1030）；天融信SSL解密（透明代理/服务器SSL解密，天融信手册《代理策略》页）未见受信/不受信双证书体系；迁移评估项：需验证天融信对外部无效证书的处理方式，避免直接阻断（白屏）或信任重签（掩盖风险）</t>
         </is>
       </c>
       <c r="F17" s="80" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G17" s="82" t="n"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G17" s="81" t="inlineStr"/>
       <c r="H17" s="80" t="inlineStr">
         <is>
-          <t>不支持</t>
-        </is>
-      </c>
-      <c r="I17" s="82" t="n"/>
-    </row>
-    <row r="18" ht="96" customHeight="1" s="1">
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="I17" s="80" t="inlineStr"/>
+    </row>
+    <row r="18" ht="66" customHeight="1" s="1">
       <c r="A18" s="82" t="n"/>
       <c r="B18" s="82" t="n"/>
       <c r="C18" s="81" t="inlineStr">
         <is>
+          <t>支持解密规则按URL类别选择性解密（URL Category）</t>
+        </is>
+      </c>
+      <c r="D18" s="81" t="inlineStr">
+        <is>
+          <t>按URL类别圈定解密范围，排除银行/医疗等敏感类</t>
+        </is>
+      </c>
+      <c r="E18" s="81" t="inlineStr">
+        <is>
+          <t>PA解密规则可按URL类别（含自定义类别）选择解密范围，可排除银行/医疗等敏感类别不解密（PA Web帮助p164）；天融信SSL解密（代理策略/代理模板）无按URL类别选择解密机制（检索无命中）</t>
+        </is>
+      </c>
+      <c r="F18" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G18" s="82" t="n"/>
+      <c r="H18" s="80" t="inlineStr">
+        <is>
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I18" s="82" t="n"/>
+    </row>
+    <row r="19" ht="96" customHeight="1" s="1">
+      <c r="A19" s="82" t="n"/>
+      <c r="B19" s="82" t="n"/>
+      <c r="C19" s="81" t="inlineStr">
+        <is>
           <t>支持SSH代理解密与SSH隧道控制（SSH Proxy）</t>
         </is>
       </c>
-      <c r="D18" s="81" t="inlineStr">
+      <c r="D19" s="81" t="inlineStr">
         <is>
           <t>SSH代理解密+SSH隧道(ssh-tunnel)识别控制</t>
         </is>
       </c>
-      <c r="E18" s="81" t="inlineStr">
+      <c r="E19" s="81" t="inlineStr">
         <is>
           <t>PA解密策略SSH Proxy类型解密SSH通信，可通过ssh-tunnel App-ID在策略中控制SSH隧道（端口转发/内网穿透），正常SSH管理流量放行；含不受支持算法检查/资源不足阻断会话等防护（PA Web帮助p164、p318-319）；天融信手册检索无SSH代理/SSH隧道控制命中</t>
         </is>
       </c>
-      <c r="F18" s="82" t="n"/>
-      <c r="G18" s="82" t="n"/>
-      <c r="H18" s="82" t="n"/>
-      <c r="I18" s="82" t="n"/>
-    </row>
-    <row r="19" ht="66" customHeight="1" s="1">
-      <c r="A19" s="82" t="n"/>
-      <c r="B19" s="80" t="inlineStr">
+      <c r="F19" s="82" t="n"/>
+      <c r="G19" s="82" t="n"/>
+      <c r="H19" s="82" t="n"/>
+      <c r="I19" s="82" t="n"/>
+    </row>
+    <row r="20" ht="111" customHeight="1" s="1">
+      <c r="A20" s="82" t="n"/>
+      <c r="B20" s="80" t="inlineStr">
         <is>
           <t>网络数据包代理(NPBroker)</t>
         </is>
       </c>
-      <c r="C19" s="81" t="inlineStr">
-        <is>
-          <t>支持按应用/用户/区域/设备/IP定义NPBroker规则转发到第三方安全链</t>
-        </is>
-      </c>
-      <c r="D19" s="81" t="inlineStr">
+      <c r="C20" s="81" t="inlineStr">
+        <is>
+          <t>支持内联数据包代理策略将流量转发第三方安全链（NPBroker）</t>
+        </is>
+      </c>
+      <c r="D20" s="81" t="inlineStr">
         <is>
           <t>已解密/未解密流量内联转发第三方安全链，L3路由转发</t>
         </is>
       </c>
-      <c r="E19" s="81" t="inlineStr">
-        <is>
-          <t>PA网络数据包代理策略将已解密/未解密TLS/非TLS流量内联转发至第三方安全工具，路径选择选项卡应用数据包代理配置文件定义经路由L3安全链的转发方式（PA Web帮助p167-170）；对应矩阵#122</t>
-        </is>
-      </c>
-      <c r="F19" s="80" t="inlineStr">
+      <c r="E20" s="81" t="inlineStr">
+        <is>
+          <t>PA网络数据包代理策略将已解密/未解密TLS/非TLS流量内联转发至第三方安全工具，路径选择选项卡应用数据包代理配置文件定义经路由L3安全链的转发方式（PA Web帮助p167-170）；天融信无网络数据包代理模块，最接近手段为WAF旁路联动（经交换机镜像引流，天融信手册《与WAF联动》页），非内联且无回注路径；对应矩阵#122</t>
+        </is>
+      </c>
+      <c r="F20" s="80" t="inlineStr">
         <is>
           <t>高</t>
-        </is>
-      </c>
-      <c r="G19" s="81" t="inlineStr"/>
-      <c r="H19" s="80" t="inlineStr">
-        <is>
-          <t>部分支持</t>
-        </is>
-      </c>
-      <c r="I19" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="66" customHeight="1" s="1">
-      <c r="A20" s="82" t="n"/>
-      <c r="B20" s="82" t="n"/>
-      <c r="C20" s="81" t="inlineStr">
-        <is>
-          <t>支持NPBroker转发流量类型选择（TLS解密/未解密/非TLS）</t>
-        </is>
-      </c>
-      <c r="D20" s="81" t="inlineStr">
-        <is>
-          <t>TLS解密/未解密/非TLS流量类型选择</t>
-        </is>
-      </c>
-      <c r="E20" s="81" t="inlineStr">
-        <is>
-          <t>PA规则可选Forward TLS(Decrypted)/未解密/非TLS多种流量类型；需免费许可证（PA Web帮助p167）；天融信无网络数据包代理模块（矩阵#122）</t>
-        </is>
-      </c>
-      <c r="F20" s="80" t="inlineStr">
-        <is>
-          <t>中</t>
         </is>
       </c>
       <c r="G20" s="81" t="inlineStr"/>
@@ -5519,68 +5583,68 @@
           <t>不支持</t>
         </is>
       </c>
-      <c r="I20" s="80" t="inlineStr"/>
+      <c r="I20" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="66" customHeight="1" s="1">
       <c r="A21" s="82" t="n"/>
-      <c r="B21" s="80" t="inlineStr">
-        <is>
-          <t>隧道检测(Tunnel Inspection)</t>
-        </is>
-      </c>
+      <c r="B21" s="82" t="n"/>
       <c r="C21" s="81" t="inlineStr">
         <is>
-          <t>支持GRE/GTP-U/HTTP2等明文隧道内层流量检测</t>
+          <t>支持NPBroker转发流量类型选择（TLS解密/未解密/非TLS）</t>
         </is>
       </c>
       <c r="D21" s="81" t="inlineStr">
         <is>
-          <t>GRE/GTP-U/VXLAN/非加密IPSec隧道内层流量解封装检测</t>
+          <t>TLS解密/未解密/非TLS流量类型选择</t>
         </is>
       </c>
       <c r="E21" s="81" t="inlineStr">
         <is>
-          <t>PA隧道检测策略解封装并深度检测GRE/GTP-U/VXLAN/非加密IPSec（NULL加密/AH传输模式）等明文隧道内容（PA Web帮助p172-173）；对应矩阵#128/37</t>
+          <t>PA规则可选Forward TLS(Decrypted)/未解密/非TLS多种流量类型；需免费许可证（PA Web帮助p167）；天融信无网络数据包代理模块（矩阵#122）</t>
         </is>
       </c>
       <c r="F21" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G21" s="81" t="inlineStr"/>
       <c r="H21" s="80" t="inlineStr">
         <is>
-          <t>部分支持</t>
-        </is>
-      </c>
-      <c r="I21" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="51" customHeight="1" s="1">
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I21" s="80" t="inlineStr"/>
+    </row>
+    <row r="22" ht="96" customHeight="1" s="1">
       <c r="A22" s="82" t="n"/>
-      <c r="B22" s="82" t="n"/>
+      <c r="B22" s="80" t="inlineStr">
+        <is>
+          <t>隧道检测(Tunnel Inspection)</t>
+        </is>
+      </c>
       <c r="C22" s="81" t="inlineStr">
         <is>
-          <t>支持最大封装级数防护（max_encap）</t>
+          <t>支持GTP-U/VXLAN/非加密IPSec隧道内层检测</t>
         </is>
       </c>
       <c r="D22" s="81" t="inlineStr">
         <is>
-          <t>隧道嵌套封装最大级数限制，超限丢弃</t>
+          <t>GTP-U/VXLAN/NULL加密IPSec(AH)隧道内层流量检测</t>
         </is>
       </c>
       <c r="E22" s="81" t="inlineStr">
         <is>
-          <t>PA对隧道最大封装级数超限丢包防护，防隧道嵌套绕过（PA管理指南p655）；天融信手册无封装级数防护（检索无命中）</t>
+          <t>PA隧道检测支持GTP-U/VXLAN/非加密IPSec（NULL加密/AH传输模式）内层检测（PA Web帮助p172-173）；天融信VXLAN仅隧道封装转发与三层网关（天融信手册《业务接入端》《三层VXLAN网关》页），无内层安全检测，GTP检测检索无命中；对应矩阵#128/37</t>
         </is>
       </c>
       <c r="F22" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G22" s="81" t="inlineStr"/>
@@ -5591,66 +5655,62 @@
       </c>
       <c r="I22" s="80" t="inlineStr"/>
     </row>
-    <row r="23" ht="96" customHeight="1" s="1">
+    <row r="23" ht="51" customHeight="1" s="1">
       <c r="A23" s="82" t="n"/>
-      <c r="B23" s="80" t="inlineStr">
-        <is>
-          <t>应用覆盖(App Override)</t>
-        </is>
-      </c>
+      <c r="B23" s="82" t="n"/>
       <c r="C23" s="81" t="inlineStr">
         <is>
-          <t>支持应用替代流量跳过七层检测等效配置</t>
+          <t>支持最大封装级数防护（max_encap）</t>
         </is>
       </c>
       <c r="D23" s="81" t="inlineStr">
         <is>
-          <t>匹配覆盖策略的流量跳过七层检测，四层快速转发</t>
+          <t>隧道嵌套封装最大级数限制，超限丢弃</t>
         </is>
       </c>
       <c r="E23" s="81" t="inlineStr">
         <is>
-          <t>PA应用替代策略明确绕过第7层处理与威胁检查，改用第4层状态检查以加速（PA管理指南p1307）；天融信自定义应用加入规则库后仍默认经安全引擎检测（天融信手册《自定义应用》页）；迁移评估项：PA应用替代多为私有大流量业务加速，转换时需同步关闭对应策略的IPS/七层检测，否则性能被拖垮或误阻断</t>
+          <t>PA对隧道最大封装级数超限丢包防护，防隧道嵌套绕过（PA管理指南p655）；天融信手册无封装级数防护（检索无命中）</t>
         </is>
       </c>
       <c r="F23" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G23" s="81" t="inlineStr"/>
       <c r="H23" s="80" t="inlineStr">
         <is>
-          <t>待评估</t>
+          <t>不支持</t>
         </is>
       </c>
       <c r="I23" s="80" t="inlineStr"/>
     </row>
-    <row r="24" ht="81" customHeight="1" s="1">
+    <row r="24" ht="96" customHeight="1" s="1">
       <c r="A24" s="82" t="n"/>
       <c r="B24" s="80" t="inlineStr">
         <is>
-          <t>身份验证(Authentication)</t>
+          <t>应用覆盖(App Override)</t>
         </is>
       </c>
       <c r="C24" s="81" t="inlineStr">
         <is>
-          <t>支持认证策略超时与单次认证（SSO）</t>
+          <t>支持应用替代流量跳过七层检测等效配置</t>
         </is>
       </c>
       <c r="D24" s="81" t="inlineStr">
         <is>
-          <t>认证超时+单次认证(SSO)</t>
+          <t>匹配覆盖策略的流量跳过七层检测，四层快速转发</t>
         </is>
       </c>
       <c r="E24" s="81" t="inlineStr">
         <is>
-          <t>PA支持认证超时减少重复质询、Kerberos/SAML/RADIUS等对接（PA Web帮助p186）；天融信手册检索认证超时/单点登录/SSO无命中（仅在线用户在线时长查看与强制下线）；迁移评估项：需核实天融信认证会话有效期配置与SSO对接能力</t>
+          <t>PA应用替代策略明确绕过第7层处理与威胁检查，改用第4层状态检查以加速（PA管理指南p1307）；天融信自定义应用加入规则库后仍默认经安全引擎检测（天融信手册《自定义应用》页）；迁移评估项：PA应用替代多为私有大流量业务加速，转换时需同步关闭对应策略的IPS/七层检测，否则性能被拖垮或误阻断</t>
         </is>
       </c>
       <c r="F24" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G24" s="81" t="inlineStr"/>
@@ -5661,22 +5721,26 @@
       </c>
       <c r="I24" s="80" t="inlineStr"/>
     </row>
-    <row r="25" ht="126" customHeight="1" s="1">
+    <row r="25" ht="81" customHeight="1" s="1">
       <c r="A25" s="82" t="n"/>
-      <c r="B25" s="82" t="n"/>
+      <c r="B25" s="80" t="inlineStr">
+        <is>
+          <t>身份验证(Authentication)</t>
+        </is>
+      </c>
       <c r="C25" s="81" t="inlineStr">
         <is>
-          <t>支持基于策略触发多因素认证质询（MFA Enforcement）</t>
+          <t>支持认证策略超时与单次认证（SSO）</t>
         </is>
       </c>
       <c r="D25" s="81" t="inlineStr">
         <is>
-          <t>策略匹配触发多因素认证质询（MFA供应商API/RADIUS）</t>
+          <t>认证超时+单次认证(SSO)</t>
         </is>
       </c>
       <c r="E25" s="81" t="inlineStr">
         <is>
-          <t>PA身份验证策略通过Authentication Enforcement对象对匹配流量强制质询，支持多因素身份验证（每因素独立超时，防火墙记录时间戳），MFA供应商API/RADIUS对接（PA Web帮助p185-186、p310、p735-742）；天融信双因子认证（密码+短信/证书/Ukey）仅限管理员/用户登录场景（天融信手册《登录安全策略》页），未见流量策略触发MFA质询</t>
+          <t>PA支持认证超时减少重复质询、Kerberos/SAML/RADIUS等对接（PA Web帮助p186）；天融信手册检索认证超时/单点登录/SSO无命中（仅在线用户在线时长查看与强制下线）；迁移评估项：需核实天融信认证会话有效期配置与SSO对接能力</t>
         </is>
       </c>
       <c r="F25" s="80" t="inlineStr">
@@ -5687,89 +5751,89 @@
       <c r="G25" s="81" t="inlineStr"/>
       <c r="H25" s="80" t="inlineStr">
         <is>
-          <t>部分支持</t>
+          <t>待评估</t>
         </is>
       </c>
       <c r="I25" s="80" t="inlineStr"/>
     </row>
-    <row r="26" ht="96" customHeight="1" s="1">
+    <row r="26" ht="126" customHeight="1" s="1">
       <c r="A26" s="82" t="n"/>
       <c r="B26" s="82" t="n"/>
       <c r="C26" s="81" t="inlineStr">
         <is>
+          <t>支持流量策略触发多因素认证质询（MFA Enforcement）</t>
+        </is>
+      </c>
+      <c r="D26" s="81" t="inlineStr">
+        <is>
+          <t>流量策略匹配触发MFA质询（非登录场景，MFA供应商API/RADIUS）</t>
+        </is>
+      </c>
+      <c r="E26" s="81" t="inlineStr">
+        <is>
+          <t>PA身份验证策略通过Authentication Enforcement对象对匹配流量强制质询，支持多因素身份验证（每因素独立超时，防火墙记录时间戳），MFA供应商API/RADIUS对接（PA Web帮助p185-186、p310、p735-742）；天融信双因子认证（密码+短信/证书/Ukey）仅限管理员/用户登录场景（天融信手册《登录安全策略》页），无流量策略触发MFA质询</t>
+        </is>
+      </c>
+      <c r="F26" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G26" s="81" t="inlineStr"/>
+      <c r="H26" s="80" t="inlineStr">
+        <is>
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I26" s="80" t="inlineStr"/>
+    </row>
+    <row r="27" ht="96" customHeight="1" s="1">
+      <c r="A27" s="82" t="n"/>
+      <c r="B27" s="82" t="n"/>
+      <c r="C27" s="81" t="inlineStr">
+        <is>
           <t>支持User-ID动态映射时效性等效（AD日志毫秒级更新）</t>
         </is>
       </c>
-      <c r="D26" s="81" t="inlineStr">
+      <c r="D27" s="81" t="inlineStr">
         <is>
           <t>AD域事件日志毫秒级IP-用户映射更新</t>
         </is>
       </c>
-      <c r="E26" s="81" t="inlineStr">
+      <c r="E27" s="81" t="inlineStr">
         <is>
           <t>PA无代理架构通过读取域控事件日志实现IP-用户毫秒级动态映射，大规模部署有专项规划（PA管理指南p866-867）；天融信AD对接的轮询间隔与并发认证能力手册未量化；迁移评估项：数万AD用户且移动频繁场景需实测天融信映射更新时延，避免基于用户的策略出现间歇性未授权拦截</t>
         </is>
       </c>
-      <c r="F26" s="82" t="n"/>
-      <c r="G26" s="82" t="n"/>
-      <c r="H26" s="80" t="inlineStr">
+      <c r="F27" s="82" t="n"/>
+      <c r="G27" s="82" t="n"/>
+      <c r="H27" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="I26" s="82" t="n"/>
-    </row>
-    <row r="27" ht="171" customHeight="1" s="1">
-      <c r="A27" s="82" t="n"/>
-      <c r="B27" s="80" t="inlineStr">
+      <c r="I27" s="82" t="n"/>
+    </row>
+    <row r="28" ht="171" customHeight="1" s="1">
+      <c r="A28" s="82" t="n"/>
+      <c r="B28" s="80" t="inlineStr">
         <is>
           <t>动态对象(Dynamic Objects)</t>
         </is>
       </c>
-      <c r="C27" s="81" t="inlineStr">
+      <c r="C28" s="81" t="inlineStr">
         <is>
           <t>支持外部动态列表作为策略地址对象（EDL）</t>
         </is>
       </c>
-      <c r="D27" s="81" t="inlineStr">
+      <c r="D28" s="81" t="inlineStr">
         <is>
           <t>HTTP/HTTPS外部文本列表(IP/域名/URL)自动拉取，策略直接引用</t>
         </is>
       </c>
-      <c r="E27" s="81" t="inlineStr">
+      <c r="E28" s="81" t="inlineStr">
         <is>
           <t>PA外部动态列表：基于HTTP/HTTPS托管的文本文件创建IP/URL/域名/IMEI/IMSI地址对象，防火墙定时自动拉取更新，策略中直接引用（Objects&gt;External Dynamic Lists，PA Web帮助p236-239；策略源/目标可直接选EDL，p196-197）；天融信手册检索外部动态列表/EDL无命中，仅内置威胁情报库与云端威胁情报库（规则集管理，天融信手册《威胁情报》《配置规则集》页），无策略直接引用任意外部文本列表机制；迁移评估项：PA策略中引用的EDL需转换为天融信静态地址组定期导入或威胁情报联动</t>
-        </is>
-      </c>
-      <c r="F27" s="80" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G27" s="81" t="inlineStr"/>
-      <c r="H27" s="80" t="inlineStr">
-        <is>
-          <t>不支持</t>
-        </is>
-      </c>
-      <c r="I27" s="80" t="inlineStr"/>
-    </row>
-    <row r="28" ht="126" customHeight="1" s="1">
-      <c r="A28" s="82" t="n"/>
-      <c r="B28" s="82" t="n"/>
-      <c r="C28" s="81" t="inlineStr">
-        <is>
-          <t>支持基于标记的动态地址组（DAG）</t>
-        </is>
-      </c>
-      <c r="D28" s="81" t="inlineStr">
-        <is>
-          <t>Tag标记过滤器动态地址组，成员随IP变化自动更新</t>
-        </is>
-      </c>
-      <c r="E28" s="81" t="inlineStr">
-        <is>
-          <t>PA动态地址组：查找标记(Tag)+基于标记的过滤器（AND/OR匹配）动态填充成员，VM信息源注册或XML/REST API定义标记，IP变化时策略自动生效（PA Web帮助p207-208、p228）；天融信手册检索动态地址组/标签/SDN/云平台联动无命中，地址组为静态IP/子网绑定（天融信手册《地址》页）；迁移评估项：PA云环境Tag微隔离策略需转换为静态地址组，IP漂移场景需人工或API维护</t>
         </is>
       </c>
       <c r="F28" s="80" t="inlineStr">
@@ -5785,66 +5849,62 @@
       </c>
       <c r="I28" s="80" t="inlineStr"/>
     </row>
-    <row r="29" ht="51" customHeight="1" s="1">
+    <row r="29" ht="126" customHeight="1" s="1">
       <c r="A29" s="82" t="n"/>
-      <c r="B29" s="80" t="inlineStr">
-        <is>
-          <t>SD-WAN策略</t>
-        </is>
-      </c>
+      <c r="B29" s="82" t="n"/>
       <c r="C29" s="81" t="inlineStr">
         <is>
-          <t>支持按应用配置链路路径管理与链路质量探测</t>
+          <t>支持基于标记的动态地址组（DAG）</t>
         </is>
       </c>
       <c r="D29" s="81" t="inlineStr">
         <is>
-          <t>按应用/区域/地址分配链路与流量分发</t>
+          <t>Tag标记过滤器动态地址组，成员随IP变化自动更新</t>
         </is>
       </c>
       <c r="E29" s="81" t="inlineStr">
         <is>
-          <t>PA SD-WAN策略按应用/抖动/延迟/丢包指标分配链路，流量分发（PA Web帮助p197）；对应矩阵#129/120</t>
+          <t>PA动态地址组：查找标记(Tag)+基于标记的过滤器（AND/OR匹配）动态填充成员，VM信息源注册或XML/REST API定义标记，IP变化时策略自动生效（PA Web帮助p207-208、p228）；天融信手册检索动态地址组/标签/SDN/云平台联动无命中，地址组为静态IP/子网绑定（天融信手册《地址》页）；迁移评估项：PA云环境Tag微隔离策略需转换为静态地址组，IP漂移场景需人工或API维护</t>
         </is>
       </c>
       <c r="F29" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G29" s="81" t="inlineStr"/>
       <c r="H29" s="80" t="inlineStr">
         <is>
-          <t>部分支持</t>
-        </is>
-      </c>
-      <c r="I29" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I29" s="80" t="inlineStr"/>
     </row>
     <row r="30" ht="81" customHeight="1" s="1">
       <c r="A30" s="82" t="n"/>
-      <c r="B30" s="82" t="n"/>
+      <c r="B30" s="80" t="inlineStr">
+        <is>
+          <t>SD-WAN策略</t>
+        </is>
+      </c>
       <c r="C30" s="81" t="inlineStr">
         <is>
-          <t>支持SD-WAN路径选择与链路质量监测（jitter/latency/loss）</t>
+          <t>支持按应用配置链路路径管理与链路质量探测</t>
         </is>
       </c>
       <c r="D30" s="81" t="inlineStr">
         <is>
-          <t>抖动/延迟/丢包(jitter/latency/loss)指标选路</t>
+          <t>按应用分配链路与流量分发（天融信以策略路由+LLB近似实现）</t>
         </is>
       </c>
       <c r="E30" s="81" t="inlineStr">
         <is>
-          <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路（PA Web帮助p195）；天融信有链路探测(ping)+智能选路(最小延迟优先)（天融信手册《策略路由》页），无jitter/latency/loss多维指标</t>
+          <t>PA SD-WAN策略按应用/抖动/延迟/丢包指标分配链路，流量分发（PA Web帮助p197）；天融信为策略路由+链路负载均衡近似实现（天融信手册《策略路由》《链路负载均衡》页），无SD-WAN策略模型；对应矩阵#129/120</t>
         </is>
       </c>
       <c r="F30" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G30" s="81" t="inlineStr"/>
@@ -5853,35 +5913,70 @@
           <t>部分支持</t>
         </is>
       </c>
-      <c r="I30" s="80" t="inlineStr"/>
+      <c r="I30" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="81" customHeight="1" s="1">
+      <c r="A31" s="82" t="n"/>
+      <c r="B31" s="82" t="n"/>
+      <c r="C31" s="81" t="inlineStr">
+        <is>
+          <t>支持SD-WAN路径选择与链路质量监测（jitter/latency/loss）</t>
+        </is>
+      </c>
+      <c r="D31" s="81" t="inlineStr">
+        <is>
+          <t>抖动/延迟/丢包多维指标选路（天融信现仅延迟探测）</t>
+        </is>
+      </c>
+      <c r="E31" s="81" t="inlineStr">
+        <is>
+          <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路（PA Web帮助p195）；天融信有链路探测(ping)+智能选路(最小延迟优先)（天融信手册《策略路由》页），无jitter/latency/loss多维指标</t>
+        </is>
+      </c>
+      <c r="F31" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G31" s="81" t="inlineStr"/>
+      <c r="H31" s="80" t="inlineStr">
+        <is>
+          <t>部分支持</t>
+        </is>
+      </c>
+      <c r="I31" s="80" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="I6:I11"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="A2:A30"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B5:B11"/>
+    <mergeCell ref="F26:F27"/>
     <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G16:G18"/>
     <mergeCell ref="I3:I4"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="H7:H10"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="G17:G19"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="G6:G11"/>
+    <mergeCell ref="B20:B21"/>
     <mergeCell ref="B2:B4"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="B5:B10"/>
-    <mergeCell ref="G6:G10"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A2:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="B16:B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA替代需求列表.xlsx
+++ b/PA替代需求列表.xlsx
@@ -3279,7 +3279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.7" customWidth="1" style="1" min="1" max="1"/>
@@ -3733,7 +3733,7 @@
     </row>
     <row r="15" ht="156" customHeight="1" s="1">
       <c r="A15" s="84" t="n"/>
-      <c r="B15" s="85" t="n"/>
+      <c r="B15" s="84" t="n"/>
       <c r="C15" s="81" t="inlineStr">
         <is>
           <t>支持隐式默认规则显式化迁移（intrazone/interzone-default）</t>
@@ -3754,41 +3754,33 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G15" s="85" t="n"/>
+      <c r="G15" s="84" t="n"/>
       <c r="H15" s="85" t="n"/>
       <c r="I15" s="85" t="n"/>
     </row>
-    <row r="16" ht="81" customHeight="1" s="1">
+    <row r="16" ht="171" customHeight="1" s="1">
       <c r="A16" s="84" t="n"/>
-      <c r="B16" s="80" t="inlineStr">
-        <is>
-          <t>NAT策略</t>
-        </is>
-      </c>
+      <c r="B16" s="85" t="n"/>
       <c r="C16" s="81" t="inlineStr">
         <is>
-          <t>支持源NAT（动态/PAT静态IP）与Hairpin回流</t>
+          <t>支持WildFire云沙箱文件检测联动（Advanced WildFire）</t>
         </is>
       </c>
       <c r="D16" s="81" t="inlineStr">
         <is>
-          <t>动态IP+端口(DIPP)/静态IP/接口地址，含回流(Hairpin)</t>
+          <t>未知文件云沙箱实时分析+签名秒级下发，策略Actions绑定WildFire配置文件</t>
         </is>
       </c>
       <c r="E16" s="81" t="inlineStr">
         <is>
-          <t>PA源NAT含DIPP动态IP+端口/静态IP/接口地址/持久NAT等（PA Web帮助p147）；天融信SNAT地址池（多对一/多对多/一对一/PAT）与仅源IP转换等（天融信手册《源NAT》《配置源转换》页）；对应矩阵#6</t>
-        </is>
-      </c>
-      <c r="F16" s="80" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="G16" s="81" t="inlineStr"/>
+          <t>PA策略Actions可绑定WildFire Analysis配置文件（安全配置文件组含反病毒/漏洞/URL/文件阻断/WildFire，PA Web帮助p304；WildFire提交日志转发p305-306），云沙箱动态分析未知/零日威胁并秒级下发签名；天融信有内置APT沙箱（虚拟运行环境检测未知漏洞威胁）与沙箱联动（天融信手册《高级威胁防护》《APT联动配置》页），无云端动态分析与秒级签名下发证据；工作表1已登记云沙箱联动需求（不支持：公司无此产品），勿重复跟踪；迁移评估项：评估天融信本地APT沙箱与PA云沙箱检测能力等效性</t>
+        </is>
+      </c>
+      <c r="F16" s="85" t="n"/>
+      <c r="G16" s="85" t="n"/>
       <c r="H16" s="80" t="inlineStr">
         <is>
-          <t>已支持</t>
+          <t>部分支持</t>
         </is>
       </c>
       <c r="I16" s="80" t="inlineStr">
@@ -3799,20 +3791,24 @@
     </row>
     <row r="17" ht="81" customHeight="1" s="1">
       <c r="A17" s="84" t="n"/>
-      <c r="B17" s="84" t="n"/>
+      <c r="B17" s="80" t="inlineStr">
+        <is>
+          <t>NAT策略</t>
+        </is>
+      </c>
       <c r="C17" s="81" t="inlineStr">
         <is>
-          <t>支持目的NAT（端口映射/服务器发布）</t>
+          <t>支持源NAT（动态/PAT静态IP）与Hairpin回流</t>
         </is>
       </c>
       <c r="D17" s="81" t="inlineStr">
         <is>
-          <t>静态映射/端口转换/DNS重写/FQDN目标</t>
+          <t>动态IP+端口(DIPP)/静态IP/接口地址，含回流(Hairpin)</t>
         </is>
       </c>
       <c r="E17" s="81" t="inlineStr">
         <is>
-          <t>PA目标NAT含静态/动态IP、端口转换、DNS Rewrite、FQDN目标（PA Web帮助p149）；天融信服务器映射含静态映射+服务器负载均衡两种模式，NAT46/NAT66全系列（天融信手册《服务器映射》页）；对应矩阵#7</t>
+          <t>PA源NAT含DIPP动态IP+端口/静态IP/接口地址/持久NAT等（PA Web帮助p147）；天融信SNAT地址池（多对一/多对多/一对一/PAT）与仅源IP转换等（天融信手册《源NAT》《配置源转换》页）；对应矩阵#6</t>
         </is>
       </c>
       <c r="F17" s="80" t="inlineStr">
@@ -3826,50 +3822,62 @@
           <t>已支持</t>
         </is>
       </c>
-      <c r="I17" s="80" t="inlineStr"/>
+      <c r="I17" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="81" customHeight="1" s="1">
       <c r="A18" s="84" t="n"/>
       <c r="B18" s="84" t="n"/>
       <c r="C18" s="81" t="inlineStr">
         <is>
-          <t>支持静态/双向NAT一对一转换</t>
+          <t>支持目的NAT（端口映射/服务器发布）</t>
         </is>
       </c>
       <c r="D18" s="81" t="inlineStr">
         <is>
-          <t>一对一转换，支持双向映射</t>
+          <t>静态映射/端口转换/DNS重写/FQDN目标</t>
         </is>
       </c>
       <c r="E18" s="81" t="inlineStr">
         <is>
-          <t>PA支持静态IP转换与双向(Bi-directional)转换（PA Web帮助p148）；天融信支持一对一转换（SNAT地址池一对一/NAT66一对一）（天融信手册《源NAT》《配置一对一转换》页）；对应矩阵#8</t>
-        </is>
-      </c>
-      <c r="F18" s="84" t="n"/>
-      <c r="G18" s="84" t="n"/>
-      <c r="H18" s="84" t="n"/>
-      <c r="I18" s="84" t="n"/>
+          <t>PA目标NAT含静态/动态IP、端口转换、DNS Rewrite、FQDN目标（PA Web帮助p149）；天融信服务器映射含静态映射+服务器负载均衡两种模式，NAT46/NAT66全系列（天融信手册《服务器映射》页）；对应矩阵#7</t>
+        </is>
+      </c>
+      <c r="F18" s="80" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G18" s="81" t="inlineStr"/>
+      <c r="H18" s="80" t="inlineStr">
+        <is>
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I18" s="80" t="inlineStr"/>
     </row>
     <row r="19" ht="81" customHeight="1" s="1">
       <c r="A19" s="84" t="n"/>
       <c r="B19" s="84" t="n"/>
       <c r="C19" s="81" t="inlineStr">
         <is>
-          <t>支持NAT与安全策略解耦独立配置</t>
+          <t>支持静态/双向NAT一对一转换</t>
         </is>
       </c>
       <c r="D19" s="81" t="inlineStr">
         <is>
-          <t>NAT独立策略库，先NAT后安全策略匹配</t>
+          <t>一对一转换，支持双向映射</t>
         </is>
       </c>
       <c r="E19" s="81" t="inlineStr">
         <is>
-          <t>PA NAT策略库独立于安全策略库(Policies&gt;NAT)，先NAT后安全匹配；天融信地址转换为独立策略库（安全策略&gt;地址转换），与访问控制策略分离配置（天融信手册《安全策略》《工作原理》页）；对应矩阵#9</t>
-        </is>
-      </c>
-      <c r="F19" s="85" t="n"/>
+          <t>PA支持静态IP转换与双向(Bi-directional)转换（PA Web帮助p148）；天融信支持一对一转换（SNAT地址池一对一/NAT66一对一）（天融信手册《源NAT》《配置一对一转换》页）；对应矩阵#8</t>
+        </is>
+      </c>
+      <c r="F19" s="84" t="n"/>
       <c r="G19" s="84" t="n"/>
       <c r="H19" s="84" t="n"/>
       <c r="I19" s="84" t="n"/>
@@ -3879,215 +3887,203 @@
       <c r="B20" s="84" t="n"/>
       <c r="C20" s="81" t="inlineStr">
         <is>
-          <t>支持IPv6/NAT64转换（nat64类型）</t>
+          <t>支持NAT与安全策略解耦独立配置</t>
         </is>
       </c>
       <c r="D20" s="81" t="inlineStr">
         <is>
-          <t>IPv4↔IPv6转换类型（nat64）</t>
+          <t>NAT独立策略库，先NAT后安全策略匹配</t>
         </is>
       </c>
       <c r="E20" s="81" t="inlineStr">
         <is>
-          <t>PA NAT规则支持IPv4/IPv6及NAT64转换类型（RFC6146）；天融信NAT64含静态转换+前缀转换+动态算法（IVI/普通前缀），另有NAT46（天融信手册《NAT64》《NAT46》页）；对应矩阵#18</t>
-        </is>
-      </c>
-      <c r="F20" s="80" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
+          <t>PA NAT策略库独立于安全策略库(Policies&gt;NAT)，先NAT后安全匹配；天融信地址转换为独立策略库（安全策略&gt;地址转换），与访问控制策略分离配置（天融信手册《安全策略》《工作原理》页）；对应矩阵#9</t>
+        </is>
+      </c>
+      <c r="F20" s="85" t="n"/>
       <c r="G20" s="84" t="n"/>
-      <c r="H20" s="85" t="n"/>
+      <c r="H20" s="84" t="n"/>
       <c r="I20" s="84" t="n"/>
     </row>
-    <row r="21" ht="126" customHeight="1" s="1">
+    <row r="21" ht="81" customHeight="1" s="1">
       <c r="A21" s="84" t="n"/>
       <c r="B21" s="84" t="n"/>
       <c r="C21" s="81" t="inlineStr">
         <is>
+          <t>支持IPv6/NAT64转换（nat64类型）</t>
+        </is>
+      </c>
+      <c r="D21" s="81" t="inlineStr">
+        <is>
+          <t>IPv4↔IPv6转换类型（nat64）</t>
+        </is>
+      </c>
+      <c r="E21" s="81" t="inlineStr">
+        <is>
+          <t>PA NAT规则支持IPv4/IPv6及NAT64转换类型（RFC6146）；天融信NAT64含静态转换+前缀转换+动态算法（IVI/普通前缀），另有NAT46（天融信手册《NAT64》《NAT46》页）；对应矩阵#18</t>
+        </is>
+      </c>
+      <c r="F21" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G21" s="84" t="n"/>
+      <c r="H21" s="85" t="n"/>
+      <c r="I21" s="84" t="n"/>
+    </row>
+    <row r="22" ht="126" customHeight="1" s="1">
+      <c r="A22" s="84" t="n"/>
+      <c r="B22" s="84" t="n"/>
+      <c r="C22" s="81" t="inlineStr">
+        <is>
           <t>支持NAT后目的区域路由回查匹配（Dest Zone by route lookup）</t>
         </is>
       </c>
-      <c r="D21" s="81" t="inlineStr">
+      <c r="D22" s="81" t="inlineStr">
         <is>
           <t>目的区域按NAT后路由查找；源/目的地址用NAT前值</t>
         </is>
       </c>
-      <c r="E21" s="81" t="inlineStr">
+      <c r="E22" s="81" t="inlineStr">
         <is>
           <t>PA底层为『先NAT判断后安全策略匹配』的因果倒置：安全策略要求源区域(NAT前)+源地址(NAT前)+目的地址(NAT前)+目的区域(NAT后按路由查找)，极其反直觉；天融信地址转换为独立策略库常规直观映射（安全策略&gt;地址转换，天融信手册《服务器映射》页）；迁移评估项：带目的NAT的策略平移后易因Zone填写错误不通，需制定NAT查表逻辑转换映射规范；对应矩阵#9</t>
         </is>
       </c>
-      <c r="F21" s="80" t="inlineStr">
+      <c r="F22" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G21" s="84" t="n"/>
-      <c r="H21" s="80" t="inlineStr">
+      <c r="G22" s="84" t="n"/>
+      <c r="H22" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="I21" s="84" t="n"/>
-    </row>
-    <row r="22" ht="81" customHeight="1" s="1">
-      <c r="A22" s="84" t="n"/>
-      <c r="B22" s="85" t="n"/>
-      <c r="C22" s="81" t="inlineStr">
+      <c r="I22" s="84" t="n"/>
+    </row>
+    <row r="23" ht="81" customHeight="1" s="1">
+      <c r="A23" s="84" t="n"/>
+      <c r="B23" s="85" t="n"/>
+      <c r="C23" s="81" t="inlineStr">
         <is>
           <t>支持NAT规则主动/主动HA绑定（Active/Active HA Binding）</t>
         </is>
       </c>
-      <c r="D22" s="81" t="inlineStr">
+      <c r="D23" s="81" t="inlineStr">
         <is>
           <t>主动/主动HA下NAT规则绑定会话所有者</t>
         </is>
       </c>
-      <c r="E22" s="81" t="inlineStr">
+      <c r="E23" s="81" t="inlineStr">
         <is>
           <t>PA主动/主动HA配置下NAT规则可绑定会话所有者/会话设置，控制NAT会话的设备绑定，仅A/A模式可见（PA Web帮助p150）；天融信HA为主备双机热备模式（天融信手册《配置双机热备功能》页），无主动/主动模式及NAT规则绑定机制</t>
         </is>
       </c>
-      <c r="F22" s="80" t="inlineStr">
+      <c r="F23" s="80" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="G22" s="85" t="n"/>
-      <c r="H22" s="80" t="inlineStr">
+      <c r="G23" s="85" t="n"/>
+      <c r="H23" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="I22" s="85" t="n"/>
-    </row>
-    <row r="23" ht="96" customHeight="1" s="1">
-      <c r="A23" s="84" t="n"/>
-      <c r="B23" s="80" t="inlineStr">
-        <is>
-          <t>QoS策略</t>
-        </is>
-      </c>
-      <c r="C23" s="81" t="inlineStr">
-        <is>
-          <t>支持按应用/源地址/用户等定义QoS策略并划分优先级类</t>
-        </is>
-      </c>
-      <c r="D23" s="81" t="inlineStr">
-        <is>
-          <t>8类流量分类+4级优先级，保证/最大带宽控制</t>
-        </is>
-      </c>
-      <c r="E23" s="81" t="inlineStr">
-        <is>
-          <t>PA QoS策略规则分配QoS类（8类+4级优先级），按Egress Guaranteed/Max控制带宽（PA Web帮助p154-155）；天融信流量管理基于应用/用户/源目的区域/地址/服务/时间+通道优先级，虚拟通道限制与保证带宽（天融信手册《流量管理》页）；对应矩阵#33/66</t>
-        </is>
-      </c>
-      <c r="F23" s="80" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G23" s="81" t="inlineStr"/>
-      <c r="H23" s="80" t="inlineStr">
-        <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I23" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
+      <c r="I23" s="85" t="n"/>
     </row>
     <row r="24" ht="96" customHeight="1" s="1">
       <c r="A24" s="84" t="n"/>
-      <c r="B24" s="85" t="n"/>
+      <c r="B24" s="80" t="inlineStr">
+        <is>
+          <t>QoS策略</t>
+        </is>
+      </c>
       <c r="C24" s="81" t="inlineStr">
         <is>
-          <t>支持QoS策略规则内直接按DSCP/ToS匹配调度</t>
+          <t>支持按应用/源地址/用户等定义QoS策略并划分优先级类</t>
         </is>
       </c>
       <c r="D24" s="81" t="inlineStr">
         <is>
-          <t>QoS策略规则DSCP/ToS直接匹配（非独立流控模块配置）</t>
+          <t>8类流量分类+4级优先级，保证/最大带宽控制</t>
         </is>
       </c>
       <c r="E24" s="81" t="inlineStr">
         <is>
-          <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
+          <t>PA QoS策略规则分配QoS类（8类+4级优先级），按Egress Guaranteed/Max控制带宽（PA Web帮助p154-155）；天融信流量管理基于应用/用户/源目的区域/地址/服务/时间+通道优先级，虚拟通道限制与保证带宽（天融信手册《流量管理》页）；对应矩阵#33/66</t>
         </is>
       </c>
       <c r="F24" s="80" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G24" s="81" t="inlineStr"/>
       <c r="H24" s="80" t="inlineStr">
         <is>
-          <t>部分支持</t>
-        </is>
-      </c>
-      <c r="I24" s="80" t="inlineStr"/>
-    </row>
-    <row r="25" ht="81" customHeight="1" s="1">
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I24" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="96" customHeight="1" s="1">
       <c r="A25" s="84" t="n"/>
-      <c r="B25" s="80" t="inlineStr">
-        <is>
-          <t>基于策略转发(PBF)</t>
-        </is>
-      </c>
+      <c r="B25" s="85" t="n"/>
       <c r="C25" s="81" t="inlineStr">
         <is>
-          <t>支持按源区域/地址/用户/应用/服务+下一跳的基于策略转发</t>
+          <t>支持QoS策略规则内直接按DSCP/ToS匹配调度</t>
         </is>
       </c>
       <c r="D25" s="81" t="inlineStr">
         <is>
-          <t>按源区域/地址/用户/应用/服务+下一跳转发，路径监控失效切换</t>
+          <t>QoS策略规则DSCP/ToS直接匹配（非独立流控模块配置）</t>
         </is>
       </c>
       <c r="E25" s="81" t="inlineStr">
         <is>
-          <t>PA PBF策略绕过常规路由表选路，支持路径监控与失效切换、BFD、强制对称返回（PA Web帮助p156）；天融信策略路由按源/目的地址端口、ISP名称、协议、角色等参数选路（天融信手册《策略路由》页）；对应矩阵#10</t>
+          <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
         </is>
       </c>
       <c r="F25" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G25" s="81" t="inlineStr"/>
       <c r="H25" s="80" t="inlineStr">
         <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I25" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="111" customHeight="1" s="1">
+          <t>部分支持</t>
+        </is>
+      </c>
+      <c r="I25" s="80" t="inlineStr"/>
+    </row>
+    <row r="26" ht="81" customHeight="1" s="1">
       <c r="A26" s="84" t="n"/>
-      <c r="B26" s="85" t="n"/>
+      <c r="B26" s="80" t="inlineStr">
+        <is>
+          <t>基于策略转发(PBF)</t>
+        </is>
+      </c>
       <c r="C26" s="81" t="inlineStr">
         <is>
-          <t>支持PBF强制对称返回（非对称路由环境）</t>
+          <t>支持按源区域/地址/用户/应用/服务+下一跳的基于策略转发</t>
         </is>
       </c>
       <c r="D26" s="81" t="inlineStr">
         <is>
-          <t>记录入接口MAC，回包强制原路返回</t>
+          <t>按源区域/地址/用户/应用/服务+下一跳转发，路径监控失效切换</t>
         </is>
       </c>
       <c r="E26" s="81" t="inlineStr">
         <is>
-          <t>PA对称返回：虚拟路由器替代返回流量的路由查找，将流量引导回接收SYN数据包的MAC地址（ARP表确定下一跳），双ISP双活/非对称路由核心机制（PA管理指南p1294）；天融信手册检索无对称返回/回程机制命中，策略路由与LLB的回程保障能力待验证；迁移评估项：多ISP双活环境需实测天融信回包路由对称性，否则现网业务中断</t>
+          <t>PA PBF策略绕过常规路由表选路，支持路径监控与失效切换、BFD、强制对称返回（PA Web帮助p156）；天融信策略路由按源/目的地址端口、ISP名称、协议、角色等参数选路（天融信手册《策略路由》页）；对应矩阵#10</t>
         </is>
       </c>
       <c r="F26" s="80" t="inlineStr">
@@ -4098,31 +4094,31 @@
       <c r="G26" s="81" t="inlineStr"/>
       <c r="H26" s="80" t="inlineStr">
         <is>
-          <t>待评估</t>
-        </is>
-      </c>
-      <c r="I26" s="80" t="inlineStr"/>
-    </row>
-    <row r="27" ht="96" customHeight="1" s="1">
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I26" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="111" customHeight="1" s="1">
       <c r="A27" s="84" t="n"/>
-      <c r="B27" s="80" t="inlineStr">
-        <is>
-          <t>解密策略(Decryption)</t>
-        </is>
-      </c>
+      <c r="B27" s="85" t="n"/>
       <c r="C27" s="81" t="inlineStr">
         <is>
-          <t>支持SSL/TLS解密策略（出站正向/入站反向）</t>
+          <t>支持PBF强制对称返回（非对称路由环境）</t>
         </is>
       </c>
       <c r="D27" s="81" t="inlineStr">
         <is>
-          <t>出站正向代理+入站检查双向解密</t>
+          <t>记录入接口MAC，回包强制原路返回</t>
         </is>
       </c>
       <c r="E27" s="81" t="inlineStr">
         <is>
-          <t>PA解密策略区分SSL Forward Proxy/Inbound Inspection/SSH，可解密以获得流量可见性与深度检测（PA Web帮助p164）；天融信代理策略将NGFW作为代理服务器，对加密流量解密还原明文完成内容安全检查后重新加密（天融信手册《代理策略》页）；对应矩阵#29/30</t>
+          <t>PA对称返回：虚拟路由器替代返回流量的路由查找，将流量引导回接收SYN数据包的MAC地址（ARP表确定下一跳），双ISP双活/非对称路由核心机制（PA管理指南p1294）；天融信手册检索无对称返回/回程机制命中，策略路由与LLB的回程保障能力待验证；迁移评估项：多ISP双活环境需实测天融信回包路由对称性，否则现网业务中断</t>
         </is>
       </c>
       <c r="F27" s="80" t="inlineStr">
@@ -4133,36 +4129,36 @@
       <c r="G27" s="81" t="inlineStr"/>
       <c r="H27" s="80" t="inlineStr">
         <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I27" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="66" customHeight="1" s="1">
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="I27" s="80" t="inlineStr"/>
+    </row>
+    <row r="28" ht="96" customHeight="1" s="1">
       <c r="A28" s="84" t="n"/>
-      <c r="B28" s="84" t="n"/>
+      <c r="B28" s="80" t="inlineStr">
+        <is>
+          <t>解密策略(Decryption)</t>
+        </is>
+      </c>
       <c r="C28" s="81" t="inlineStr">
         <is>
-          <t>支持解密目标选择与证书配置</t>
+          <t>支持SSL/TLS解密策略（出站正向/入站反向）</t>
         </is>
       </c>
       <c r="D28" s="81" t="inlineStr">
         <is>
-          <t>入站证书配置/解密目标（数据包/会话）</t>
+          <t>出站正向代理+入站检查双向解密</t>
         </is>
       </c>
       <c r="E28" s="81" t="inlineStr">
         <is>
-          <t>PA解密目标允许指定数据包/会话；入站含Certificates证书配置；对应矩阵#31；天融信代理模板支持证书选择与预置动态证书模板（天融信手册《代理模板》页）</t>
+          <t>PA解密策略区分SSL Forward Proxy/Inbound Inspection/SSH，可解密以获得流量可见性与深度检测（PA Web帮助p164）；天融信代理策略将NGFW作为代理服务器，对加密流量解密还原明文完成内容安全检查后重新加密（天融信手册《代理策略》页）；对应矩阵#29/30</t>
         </is>
       </c>
       <c r="F28" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G28" s="81" t="inlineStr"/>
@@ -4171,180 +4167,180 @@
           <t>已支持</t>
         </is>
       </c>
-      <c r="I28" s="80" t="inlineStr"/>
-    </row>
-    <row r="29" ht="51" customHeight="1" s="1">
+      <c r="I28" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="66" customHeight="1" s="1">
       <c r="A29" s="84" t="n"/>
       <c r="B29" s="84" t="n"/>
       <c r="C29" s="81" t="inlineStr">
         <is>
-          <t>支持解密流量镜像到专用接口（Decryption Port Mirroring）</t>
+          <t>支持解密目标选择与证书配置</t>
         </is>
       </c>
       <c r="D29" s="81" t="inlineStr">
         <is>
-          <t>解密后明文流量镜像至专用接口供第三方分析</t>
+          <t>入站证书配置/解密目标（数据包/会话）</t>
         </is>
       </c>
       <c r="E29" s="81" t="inlineStr">
         <is>
-          <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证（PA管理指南p1059）；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
-        </is>
-      </c>
-      <c r="F29" s="85" t="n"/>
-      <c r="G29" s="84" t="n"/>
+          <t>PA解密目标允许指定数据包/会话；入站含Certificates证书配置；对应矩阵#31；天融信代理模板支持证书选择与预置动态证书模板（天融信手册《代理模板》页）</t>
+        </is>
+      </c>
+      <c r="F29" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G29" s="81" t="inlineStr"/>
       <c r="H29" s="80" t="inlineStr">
         <is>
-          <t>不支持</t>
-        </is>
-      </c>
-      <c r="I29" s="84" t="n"/>
-    </row>
-    <row r="30" ht="126" customHeight="1" s="1">
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I29" s="80" t="inlineStr"/>
+    </row>
+    <row r="30" ht="51" customHeight="1" s="1">
       <c r="A30" s="84" t="n"/>
       <c r="B30" s="84" t="n"/>
       <c r="C30" s="81" t="inlineStr">
         <is>
-          <t>支持解密不受信证书分离处理（Forward Untrust Certificate）</t>
+          <t>支持解密流量镜像到专用接口（Decryption Port Mirroring）</t>
         </is>
       </c>
       <c r="D30" s="81" t="inlineStr">
         <is>
-          <t>外部无效证书以不受信转发证书重签，保留浏览器告警</t>
+          <t>解密后明文流量镜像至专用接口供第三方分析</t>
         </is>
       </c>
       <c r="E30" s="81" t="inlineStr">
         <is>
-          <t>PA转发代理遇外部过期/不受信证书时，不用内部信任CA重签，而是专用Forward Untrust Certificate重签名，让浏览器保留不受信告警（PA管理指南p994、p1030）；天融信SSL解密（透明代理/服务器SSL解密，天融信手册《代理策略》页）未见受信/不受信双证书体系；迁移评估项：需验证天融信对外部无效证书的处理方式，避免直接阻断（白屏）或信任重签（掩盖风险）</t>
-        </is>
-      </c>
-      <c r="F30" s="80" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
+          <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证（PA管理指南p1059）；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
+        </is>
+      </c>
+      <c r="F30" s="85" t="n"/>
       <c r="G30" s="84" t="n"/>
       <c r="H30" s="80" t="inlineStr">
         <is>
-          <t>待评估</t>
+          <t>不支持</t>
         </is>
       </c>
       <c r="I30" s="84" t="n"/>
     </row>
-    <row r="31" ht="66" customHeight="1" s="1">
+    <row r="31" ht="126" customHeight="1" s="1">
       <c r="A31" s="84" t="n"/>
       <c r="B31" s="84" t="n"/>
       <c r="C31" s="81" t="inlineStr">
         <is>
-          <t>支持解密规则按URL类别选择性解密（URL Category）</t>
+          <t>支持解密不受信证书分离处理（Forward Untrust Certificate）</t>
         </is>
       </c>
       <c r="D31" s="81" t="inlineStr">
         <is>
-          <t>按URL类别圈定解密范围，排除银行/医疗等敏感类</t>
+          <t>外部无效证书以不受信转发证书重签，保留浏览器告警</t>
         </is>
       </c>
       <c r="E31" s="81" t="inlineStr">
         <is>
-          <t>PA解密规则可按URL类别（含自定义类别）选择解密范围，可排除银行/医疗等敏感类别不解密（PA Web帮助p164）；天融信SSL解密（代理策略/代理模板）无按URL类别选择解密机制（检索无命中）</t>
+          <t>PA转发代理遇外部过期/不受信证书时，不用内部信任CA重签，而是专用Forward Untrust Certificate重签名，让浏览器保留不受信告警（PA管理指南p994、p1030）；天融信SSL解密（透明代理/服务器SSL解密，天融信手册《代理策略》页）未见受信/不受信双证书体系；迁移评估项：需验证天融信对外部无效证书的处理方式，避免直接阻断（白屏）或信任重签（掩盖风险）</t>
         </is>
       </c>
       <c r="F31" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G31" s="84" t="n"/>
       <c r="H31" s="80" t="inlineStr">
         <is>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="I31" s="84" t="n"/>
+    </row>
+    <row r="32" ht="66" customHeight="1" s="1">
+      <c r="A32" s="84" t="n"/>
+      <c r="B32" s="84" t="n"/>
+      <c r="C32" s="81" t="inlineStr">
+        <is>
+          <t>支持解密规则按URL类别选择性解密（URL Category）</t>
+        </is>
+      </c>
+      <c r="D32" s="81" t="inlineStr">
+        <is>
+          <t>按URL类别圈定解密范围，排除银行/医疗等敏感类</t>
+        </is>
+      </c>
+      <c r="E32" s="81" t="inlineStr">
+        <is>
+          <t>PA解密规则可按URL类别（含自定义类别）选择解密范围，可排除银行/医疗等敏感类别不解密（PA Web帮助p164）；天融信SSL解密（代理策略/代理模板）无按URL类别选择解密机制（检索无命中）</t>
+        </is>
+      </c>
+      <c r="F32" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G32" s="84" t="n"/>
+      <c r="H32" s="80" t="inlineStr">
+        <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="I31" s="84" t="n"/>
-    </row>
-    <row r="32" ht="96" customHeight="1" s="1">
-      <c r="A32" s="84" t="n"/>
-      <c r="B32" s="85" t="n"/>
-      <c r="C32" s="81" t="inlineStr">
+      <c r="I32" s="84" t="n"/>
+    </row>
+    <row r="33" ht="96" customHeight="1" s="1">
+      <c r="A33" s="84" t="n"/>
+      <c r="B33" s="85" t="n"/>
+      <c r="C33" s="81" t="inlineStr">
         <is>
           <t>支持SSH代理解密与SSH隧道控制（SSH Proxy）</t>
         </is>
       </c>
-      <c r="D32" s="81" t="inlineStr">
+      <c r="D33" s="81" t="inlineStr">
         <is>
           <t>SSH代理解密+SSH隧道(ssh-tunnel)识别控制</t>
         </is>
       </c>
-      <c r="E32" s="81" t="inlineStr">
+      <c r="E33" s="81" t="inlineStr">
         <is>
           <t>PA解密策略SSH Proxy类型解密SSH通信，可通过ssh-tunnel App-ID在策略中控制SSH隧道（端口转发/内网穿透），正常SSH管理流量放行；含不受支持算法检查/资源不足阻断会话等防护（PA Web帮助p164、p318-319）；天融信手册检索无SSH代理/SSH隧道控制命中</t>
         </is>
       </c>
-      <c r="F32" s="85" t="n"/>
-      <c r="G32" s="85" t="n"/>
-      <c r="H32" s="85" t="n"/>
-      <c r="I32" s="85" t="n"/>
-    </row>
-    <row r="33" ht="111" customHeight="1" s="1">
-      <c r="A33" s="84" t="n"/>
-      <c r="B33" s="80" t="inlineStr">
+      <c r="F33" s="85" t="n"/>
+      <c r="G33" s="85" t="n"/>
+      <c r="H33" s="85" t="n"/>
+      <c r="I33" s="85" t="n"/>
+    </row>
+    <row r="34" ht="111" customHeight="1" s="1">
+      <c r="A34" s="84" t="n"/>
+      <c r="B34" s="80" t="inlineStr">
         <is>
           <t>网络数据包代理(NPBroker)</t>
         </is>
       </c>
-      <c r="C33" s="81" t="inlineStr">
+      <c r="C34" s="81" t="inlineStr">
         <is>
           <t>支持内联数据包代理策略将流量转发第三方安全链（NPBroker）</t>
         </is>
       </c>
-      <c r="D33" s="81" t="inlineStr">
+      <c r="D34" s="81" t="inlineStr">
         <is>
           <t>已解密/未解密流量内联转发第三方安全链，L3路由转发</t>
         </is>
       </c>
-      <c r="E33" s="81" t="inlineStr">
+      <c r="E34" s="81" t="inlineStr">
         <is>
           <t>PA网络数据包代理策略将已解密/未解密TLS/非TLS流量内联转发至第三方安全工具，路径选择选项卡应用数据包代理配置文件定义经路由L3安全链的转发方式（PA Web帮助p167-170）；天融信无网络数据包代理模块，最接近手段为WAF旁路联动（经交换机镜像引流，天融信手册《与WAF联动》页），非内联且无回注路径；对应矩阵#122</t>
         </is>
       </c>
-      <c r="F33" s="80" t="inlineStr">
+      <c r="F34" s="80" t="inlineStr">
         <is>
           <t>高</t>
-        </is>
-      </c>
-      <c r="G33" s="81" t="inlineStr"/>
-      <c r="H33" s="80" t="inlineStr">
-        <is>
-          <t>不支持</t>
-        </is>
-      </c>
-      <c r="I33" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="66" customHeight="1" s="1">
-      <c r="A34" s="84" t="n"/>
-      <c r="B34" s="85" t="n"/>
-      <c r="C34" s="81" t="inlineStr">
-        <is>
-          <t>支持NPBroker转发流量类型选择（TLS解密/未解密/非TLS）</t>
-        </is>
-      </c>
-      <c r="D34" s="81" t="inlineStr">
-        <is>
-          <t>TLS解密/未解密/非TLS流量类型选择</t>
-        </is>
-      </c>
-      <c r="E34" s="81" t="inlineStr">
-        <is>
-          <t>PA规则可选Forward TLS(Decrypted)/未解密/非TLS多种流量类型；需免费许可证（PA Web帮助p167）；天融信无网络数据包代理模块（矩阵#122）</t>
-        </is>
-      </c>
-      <c r="F34" s="80" t="inlineStr">
-        <is>
-          <t>中</t>
         </is>
       </c>
       <c r="G34" s="81" t="inlineStr"/>
@@ -4353,28 +4349,28 @@
           <t>不支持</t>
         </is>
       </c>
-      <c r="I34" s="80" t="inlineStr"/>
+      <c r="I34" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="66" customHeight="1" s="1">
       <c r="A35" s="84" t="n"/>
-      <c r="B35" s="80" t="inlineStr">
-        <is>
-          <t>隧道检测(Tunnel Inspection)</t>
-        </is>
-      </c>
+      <c r="B35" s="85" t="n"/>
       <c r="C35" s="81" t="inlineStr">
         <is>
-          <t>支持GRE隧道终结与内层流量检测</t>
+          <t>支持NPBroker转发流量类型选择（TLS解密/未解密/非TLS）</t>
         </is>
       </c>
       <c r="D35" s="81" t="inlineStr">
         <is>
-          <t>GRE隧道封装/解封装，内层流量按普通流量检测</t>
+          <t>TLS解密/未解密/非TLS流量类型选择</t>
         </is>
       </c>
       <c r="E35" s="81" t="inlineStr">
         <is>
-          <t>PA隧道检测策略解封装并检测GRE隧道内容（PA Web帮助p172-173）；天融信GRE隧道支持封装与解封装，解封装后内层报文按普通流量处理检测（天融信手册《GRE隧道》页）；对应矩阵#128/37</t>
+          <t>PA规则可选Forward TLS(Decrypted)/未解密/非TLS多种流量类型；需免费许可证（PA Web帮助p167）；天融信无网络数据包代理模块（矩阵#122）</t>
         </is>
       </c>
       <c r="F35" s="80" t="inlineStr">
@@ -4385,133 +4381,133 @@
       <c r="G35" s="81" t="inlineStr"/>
       <c r="H35" s="80" t="inlineStr">
         <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I35" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="96" customHeight="1" s="1">
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I35" s="80" t="inlineStr"/>
+    </row>
+    <row r="36" ht="66" customHeight="1" s="1">
       <c r="A36" s="84" t="n"/>
-      <c r="B36" s="84" t="n"/>
+      <c r="B36" s="80" t="inlineStr">
+        <is>
+          <t>隧道检测(Tunnel Inspection)</t>
+        </is>
+      </c>
       <c r="C36" s="81" t="inlineStr">
         <is>
-          <t>支持GTP-U/VXLAN/非加密IPSec隧道内层检测</t>
+          <t>支持GRE隧道终结与内层流量检测</t>
         </is>
       </c>
       <c r="D36" s="81" t="inlineStr">
         <is>
-          <t>GTP-U/VXLAN/NULL加密IPSec(AH)隧道内层流量检测</t>
+          <t>GRE隧道封装/解封装，内层流量按普通流量检测</t>
         </is>
       </c>
       <c r="E36" s="81" t="inlineStr">
         <is>
-          <t>PA隧道检测支持GTP-U/VXLAN/非加密IPSec（NULL加密/AH传输模式）内层检测（PA Web帮助p172-173）；天融信VXLAN仅隧道封装转发与三层网关（天融信手册《业务接入端》《三层VXLAN网关》页），无内层安全检测，GTP检测检索无命中；对应矩阵#128/37</t>
+          <t>PA隧道检测策略解封装并检测GRE隧道内容（PA Web帮助p172-173）；天融信GRE隧道支持封装与解封装，解封装后内层报文按普通流量处理检测（天融信手册《GRE隧道》页）；对应矩阵#128/37</t>
         </is>
       </c>
       <c r="F36" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G36" s="81" t="inlineStr"/>
       <c r="H36" s="80" t="inlineStr">
         <is>
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I36" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="96" customHeight="1" s="1">
+      <c r="A37" s="84" t="n"/>
+      <c r="B37" s="84" t="n"/>
+      <c r="C37" s="81" t="inlineStr">
+        <is>
+          <t>支持GTP-U/VXLAN/非加密IPSec隧道内层检测</t>
+        </is>
+      </c>
+      <c r="D37" s="81" t="inlineStr">
+        <is>
+          <t>GTP-U/VXLAN/NULL加密IPSec(AH)隧道内层流量检测</t>
+        </is>
+      </c>
+      <c r="E37" s="81" t="inlineStr">
+        <is>
+          <t>PA隧道检测支持GTP-U/VXLAN/非加密IPSec（NULL加密/AH传输模式）内层检测（PA Web帮助p172-173）；天融信VXLAN仅隧道封装转发与三层网关（天融信手册《业务接入端》《三层VXLAN网关》页），无内层安全检测，GTP检测检索无命中；对应矩阵#128/37</t>
+        </is>
+      </c>
+      <c r="F37" s="80" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G37" s="81" t="inlineStr"/>
+      <c r="H37" s="80" t="inlineStr">
+        <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="I36" s="80" t="inlineStr"/>
-    </row>
-    <row r="37" ht="51" customHeight="1" s="1">
-      <c r="A37" s="84" t="n"/>
-      <c r="B37" s="85" t="n"/>
-      <c r="C37" s="81" t="inlineStr">
+      <c r="I37" s="80" t="inlineStr"/>
+    </row>
+    <row r="38" ht="51" customHeight="1" s="1">
+      <c r="A38" s="84" t="n"/>
+      <c r="B38" s="85" t="n"/>
+      <c r="C38" s="81" t="inlineStr">
         <is>
           <t>支持最大封装级数防护（max_encap）</t>
         </is>
       </c>
-      <c r="D37" s="81" t="inlineStr">
+      <c r="D38" s="81" t="inlineStr">
         <is>
           <t>隧道嵌套封装最大级数限制，超限丢弃</t>
         </is>
       </c>
-      <c r="E37" s="81" t="inlineStr">
+      <c r="E38" s="81" t="inlineStr">
         <is>
           <t>PA对隧道最大封装级数超限丢包防护，防隧道嵌套绕过（PA管理指南p655）；天融信手册无封装级数防护（检索无命中）</t>
         </is>
       </c>
-      <c r="F37" s="80" t="inlineStr">
+      <c r="F38" s="80" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G37" s="85" t="n"/>
-      <c r="H37" s="85" t="n"/>
-      <c r="I37" s="85" t="n"/>
-    </row>
-    <row r="38" ht="81" customHeight="1" s="1">
-      <c r="A38" s="84" t="n"/>
-      <c r="B38" s="80" t="inlineStr">
+      <c r="G38" s="85" t="n"/>
+      <c r="H38" s="85" t="n"/>
+      <c r="I38" s="85" t="n"/>
+    </row>
+    <row r="39" ht="81" customHeight="1" s="1">
+      <c r="A39" s="84" t="n"/>
+      <c r="B39" s="80" t="inlineStr">
         <is>
           <t>应用覆盖(App Override)</t>
         </is>
       </c>
-      <c r="C38" s="81" t="inlineStr">
+      <c r="C39" s="81" t="inlineStr">
         <is>
           <t>支持通过Application Override重定义应用识别</t>
         </is>
       </c>
-      <c r="D38" s="81" t="inlineStr">
+      <c r="D39" s="81" t="inlineStr">
         <is>
           <t>按协议/端口自定义应用识别结果</t>
         </is>
       </c>
-      <c r="E38" s="81" t="inlineStr">
+      <c r="E39" s="81" t="inlineStr">
         <is>
           <t>PA应用替代策略改变防火墙对网络通信的应用分类方式（如指定明文协议/端口识别，PA Web帮助p178）；天融信自定义应用允许管理员按需自定义应用协议（含端口匹配）并加入应用规则库（天融信手册《自定义应用》页）；对应矩阵#26</t>
         </is>
       </c>
-      <c r="F38" s="80" t="inlineStr">
+      <c r="F39" s="80" t="inlineStr">
         <is>
           <t>中</t>
-        </is>
-      </c>
-      <c r="G38" s="81" t="inlineStr"/>
-      <c r="H38" s="80" t="inlineStr">
-        <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I38" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="66" customHeight="1" s="1">
-      <c r="A39" s="84" t="n"/>
-      <c r="B39" s="84" t="n"/>
-      <c r="C39" s="81" t="inlineStr">
-        <is>
-          <t>支持覆盖类型（端口映射类）识别</t>
-        </is>
-      </c>
-      <c r="D39" s="81" t="inlineStr">
-        <is>
-          <t>端口映射类覆盖识别</t>
-        </is>
-      </c>
-      <c r="E39" s="81" t="inlineStr">
-        <is>
-          <t>PA支持端口式应用覆盖识别（configurable自定义应用）；天融信自定义应用允许管理员按特定需要自行定义应用协议（含端口匹配），自动添加到应用规则库供安全策略引用（天融信手册《自定义应用》页）</t>
-        </is>
-      </c>
-      <c r="F39" s="80" t="inlineStr">
-        <is>
-          <t>低</t>
         </is>
       </c>
       <c r="G39" s="81" t="inlineStr"/>
@@ -4520,223 +4516,223 @@
           <t>已支持</t>
         </is>
       </c>
-      <c r="I39" s="80" t="inlineStr"/>
-    </row>
-    <row r="40" ht="96" customHeight="1" s="1">
+      <c r="I39" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="66" customHeight="1" s="1">
       <c r="A40" s="84" t="n"/>
-      <c r="B40" s="85" t="n"/>
+      <c r="B40" s="84" t="n"/>
       <c r="C40" s="81" t="inlineStr">
         <is>
+          <t>支持覆盖类型（端口映射类）识别</t>
+        </is>
+      </c>
+      <c r="D40" s="81" t="inlineStr">
+        <is>
+          <t>端口映射类覆盖识别</t>
+        </is>
+      </c>
+      <c r="E40" s="81" t="inlineStr">
+        <is>
+          <t>PA支持端口式应用覆盖识别（configurable自定义应用）；天融信自定义应用允许管理员按特定需要自行定义应用协议（含端口匹配），自动添加到应用规则库供安全策略引用（天融信手册《自定义应用》页）</t>
+        </is>
+      </c>
+      <c r="F40" s="80" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G40" s="81" t="inlineStr"/>
+      <c r="H40" s="80" t="inlineStr">
+        <is>
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I40" s="80" t="inlineStr"/>
+    </row>
+    <row r="41" ht="96" customHeight="1" s="1">
+      <c r="A41" s="84" t="n"/>
+      <c r="B41" s="85" t="n"/>
+      <c r="C41" s="81" t="inlineStr">
+        <is>
           <t>支持应用替代流量跳过七层检测等效配置</t>
         </is>
       </c>
-      <c r="D40" s="81" t="inlineStr">
+      <c r="D41" s="81" t="inlineStr">
         <is>
           <t>匹配覆盖策略的流量跳过七层检测，四层快速转发</t>
         </is>
       </c>
-      <c r="E40" s="81" t="inlineStr">
+      <c r="E41" s="81" t="inlineStr">
         <is>
           <t>PA应用替代策略明确绕过第7层处理与威胁检查，改用第4层状态检查以加速（PA管理指南p1307）；天融信自定义应用加入规则库后仍默认经安全引擎检测（天融信手册《自定义应用》页）；迁移评估项：PA应用替代多为私有大流量业务加速，转换时需同步关闭对应策略的IPS/七层检测，否则性能被拖垮或误阻断</t>
         </is>
       </c>
-      <c r="F40" s="80" t="inlineStr">
+      <c r="F41" s="80" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G40" s="85" t="n"/>
-      <c r="H40" s="80" t="inlineStr">
+      <c r="G41" s="85" t="n"/>
+      <c r="H41" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="I40" s="85" t="n"/>
-    </row>
-    <row r="41" ht="111" customHeight="1" s="1">
-      <c r="A41" s="84" t="n"/>
-      <c r="B41" s="80" t="inlineStr">
+      <c r="I41" s="85" t="n"/>
+    </row>
+    <row r="42" ht="111" customHeight="1" s="1">
+      <c r="A42" s="84" t="n"/>
+      <c r="B42" s="80" t="inlineStr">
         <is>
           <t>身份验证(Authentication)</t>
         </is>
       </c>
-      <c r="C41" s="81" t="inlineStr">
+      <c r="C42" s="81" t="inlineStr">
         <is>
           <t>支持基于用户身份的身份验证策略（User-ID）</t>
         </is>
       </c>
-      <c r="D41" s="81" t="inlineStr">
+      <c r="D42" s="81" t="inlineStr">
         <is>
           <t>基于用户/用户组策略，多源IP-用户映射（AD/Syslog/XML API）</t>
         </is>
       </c>
-      <c r="E41" s="81" t="inlineStr">
+      <c r="E42" s="81" t="inlineStr">
         <is>
           <t>PA身份验证策略在访问网络资源前对用户鉴权（PA Web帮助p182），配合User-ID多源映射（AD/XML/Syslog等）；天融信用户访问网络资源前经认证，认证通过后检查关联的用户访问策略，支持门户认证（本地/外部）与LDAP/RADIUS对接（天融信手册《管理用户》《添加Radius服务器》页）；对应矩阵#3/35</t>
         </is>
       </c>
-      <c r="F41" s="80" t="inlineStr">
+      <c r="F42" s="80" t="inlineStr">
         <is>
           <t>高</t>
-        </is>
-      </c>
-      <c r="G41" s="81" t="inlineStr"/>
-      <c r="H41" s="80" t="inlineStr">
-        <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I41" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="81" customHeight="1" s="1">
-      <c r="A42" s="84" t="n"/>
-      <c r="B42" s="84" t="n"/>
-      <c r="C42" s="81" t="inlineStr">
-        <is>
-          <t>支持认证策略超时与单次认证（SSO）</t>
-        </is>
-      </c>
-      <c r="D42" s="81" t="inlineStr">
-        <is>
-          <t>认证超时+单次认证(SSO)</t>
-        </is>
-      </c>
-      <c r="E42" s="81" t="inlineStr">
-        <is>
-          <t>PA支持认证超时减少重复质询、Kerberos/SAML/RADIUS等对接（PA Web帮助p186）；天融信手册检索认证超时/单点登录/SSO无命中（仅在线用户在线时长查看与强制下线）；迁移评估项：需核实天融信认证会话有效期配置与SSO对接能力</t>
-        </is>
-      </c>
-      <c r="F42" s="80" t="inlineStr">
-        <is>
-          <t>中</t>
         </is>
       </c>
       <c r="G42" s="81" t="inlineStr"/>
       <c r="H42" s="80" t="inlineStr">
         <is>
-          <t>待评估</t>
-        </is>
-      </c>
-      <c r="I42" s="80" t="inlineStr"/>
-    </row>
-    <row r="43" ht="126" customHeight="1" s="1">
+          <t>已支持</t>
+        </is>
+      </c>
+      <c r="I42" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="81" customHeight="1" s="1">
       <c r="A43" s="84" t="n"/>
       <c r="B43" s="84" t="n"/>
       <c r="C43" s="81" t="inlineStr">
         <is>
+          <t>支持认证策略超时与单次认证（SSO）</t>
+        </is>
+      </c>
+      <c r="D43" s="81" t="inlineStr">
+        <is>
+          <t>认证超时+单次认证(SSO)</t>
+        </is>
+      </c>
+      <c r="E43" s="81" t="inlineStr">
+        <is>
+          <t>PA支持认证超时减少重复质询、Kerberos/SAML/RADIUS等对接（PA Web帮助p186）；天融信手册检索认证超时/单点登录/SSO无命中（仅在线用户在线时长查看与强制下线）；迁移评估项：需核实天融信认证会话有效期配置与SSO对接能力</t>
+        </is>
+      </c>
+      <c r="F43" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G43" s="81" t="inlineStr"/>
+      <c r="H43" s="80" t="inlineStr">
+        <is>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="I43" s="80" t="inlineStr"/>
+    </row>
+    <row r="44" ht="126" customHeight="1" s="1">
+      <c r="A44" s="84" t="n"/>
+      <c r="B44" s="84" t="n"/>
+      <c r="C44" s="81" t="inlineStr">
+        <is>
           <t>支持流量策略触发多因素认证质询（MFA Enforcement）</t>
         </is>
       </c>
-      <c r="D43" s="81" t="inlineStr">
+      <c r="D44" s="81" t="inlineStr">
         <is>
           <t>流量策略匹配触发MFA质询（非登录场景，MFA供应商API/RADIUS）</t>
         </is>
       </c>
-      <c r="E43" s="81" t="inlineStr">
+      <c r="E44" s="81" t="inlineStr">
         <is>
           <t>PA身份验证策略通过Authentication Enforcement对象对匹配流量强制质询，支持多因素身份验证（每因素独立超时，防火墙记录时间戳），MFA供应商API/RADIUS对接（PA Web帮助p185-186、p310、p735-742）；天融信双因子认证（密码+短信/证书/Ukey）仅限管理员/用户登录场景（天融信手册《登录安全策略》页），无流量策略触发MFA质询</t>
         </is>
       </c>
-      <c r="F43" s="84" t="n"/>
-      <c r="G43" s="84" t="n"/>
-      <c r="H43" s="80" t="inlineStr">
+      <c r="F44" s="84" t="n"/>
+      <c r="G44" s="84" t="n"/>
+      <c r="H44" s="80" t="inlineStr">
         <is>
           <t>不支持</t>
         </is>
       </c>
-      <c r="I43" s="84" t="n"/>
-    </row>
-    <row r="44" ht="96" customHeight="1" s="1">
-      <c r="A44" s="84" t="n"/>
-      <c r="B44" s="85" t="n"/>
-      <c r="C44" s="81" t="inlineStr">
+      <c r="I44" s="84" t="n"/>
+    </row>
+    <row r="45" ht="96" customHeight="1" s="1">
+      <c r="A45" s="84" t="n"/>
+      <c r="B45" s="85" t="n"/>
+      <c r="C45" s="81" t="inlineStr">
         <is>
           <t>支持User-ID动态映射时效性等效（AD日志毫秒级更新）</t>
         </is>
       </c>
-      <c r="D44" s="81" t="inlineStr">
+      <c r="D45" s="81" t="inlineStr">
         <is>
           <t>AD域事件日志毫秒级IP-用户映射更新</t>
         </is>
       </c>
-      <c r="E44" s="81" t="inlineStr">
+      <c r="E45" s="81" t="inlineStr">
         <is>
           <t>PA无代理架构通过读取域控事件日志实现IP-用户毫秒级动态映射，大规模部署有专项规划（PA管理指南p866-867）；天融信AD对接的轮询间隔与并发认证能力手册未量化；迁移评估项：数万AD用户且移动频繁场景需实测天融信映射更新时延，避免基于用户的策略出现间歇性未授权拦截</t>
         </is>
       </c>
-      <c r="F44" s="85" t="n"/>
-      <c r="G44" s="85" t="n"/>
-      <c r="H44" s="80" t="inlineStr">
+      <c r="F45" s="85" t="n"/>
+      <c r="G45" s="85" t="n"/>
+      <c r="H45" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="I44" s="85" t="n"/>
-    </row>
-    <row r="45" ht="111" customHeight="1" s="1">
-      <c r="A45" s="84" t="n"/>
-      <c r="B45" s="80" t="inlineStr">
+      <c r="I45" s="85" t="n"/>
+    </row>
+    <row r="46" ht="111" customHeight="1" s="1">
+      <c r="A46" s="84" t="n"/>
+      <c r="B46" s="80" t="inlineStr">
         <is>
           <t>DoS防护(DoS Protection)</t>
         </is>
       </c>
-      <c r="C45" s="81" t="inlineStr">
+      <c r="C46" s="81" t="inlineStr">
         <is>
           <t>支持针对关键资源的分类/聚合DoS防护</t>
         </is>
       </c>
-      <c r="D45" s="81" t="inlineStr">
+      <c r="D46" s="81" t="inlineStr">
         <is>
           <t>分类(源/目的IP粒度)+聚合(全局)双层阈值限流</t>
         </is>
       </c>
-      <c r="E45" s="81" t="inlineStr">
+      <c r="E46" s="81" t="inlineStr">
         <is>
           <t>PA DoS策略基于源/目的接口、区域、地址、服务定义允许/拒绝/告警，规则可选聚合与分类双层DoS保护配置文件设定阈值速率（PA Web帮助p189-191、PA管理指南p1354）；天融信DDoS防护模块按防护对象（目的服务器）设阈值（pps/bps），可达目的IP粒度（天融信手册《配置策略模板》《日志查看》页）；对应矩阵#52/42</t>
         </is>
       </c>
-      <c r="F45" s="80" t="inlineStr">
+      <c r="F46" s="80" t="inlineStr">
         <is>
           <t>高</t>
-        </is>
-      </c>
-      <c r="G45" s="81" t="inlineStr"/>
-      <c r="H45" s="80" t="inlineStr">
-        <is>
-          <t>已支持</t>
-        </is>
-      </c>
-      <c r="I45" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="51" customHeight="1" s="1">
-      <c r="A46" s="84" t="n"/>
-      <c r="B46" s="85" t="n"/>
-      <c r="C46" s="81" t="inlineStr">
-        <is>
-          <t>支持DoS聚合配置文件（连接/秒阈值）</t>
-        </is>
-      </c>
-      <c r="D46" s="81" t="inlineStr">
-        <is>
-          <t>连接数/秒阈值告警+最大速率限制</t>
-        </is>
-      </c>
-      <c r="E46" s="81" t="inlineStr">
-        <is>
-          <t>PA聚合DoS配置文件按传入连接数/秒触发告警与最大速率限制；天融信DDoS防护模块按阈值（pps/bps）监视并触发防护（天融信手册《配置策略模板》页）</t>
-        </is>
-      </c>
-      <c r="F46" s="80" t="inlineStr">
-        <is>
-          <t>中</t>
         </is>
       </c>
       <c r="G46" s="81" t="inlineStr"/>
@@ -4745,28 +4741,28 @@
           <t>已支持</t>
         </is>
       </c>
-      <c r="I46" s="80" t="inlineStr"/>
-    </row>
-    <row r="47" ht="171" customHeight="1" s="1">
+      <c r="I46" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="51" customHeight="1" s="1">
       <c r="A47" s="84" t="n"/>
-      <c r="B47" s="80" t="inlineStr">
-        <is>
-          <t>动态对象(Dynamic Objects)</t>
-        </is>
-      </c>
+      <c r="B47" s="85" t="n"/>
       <c r="C47" s="81" t="inlineStr">
         <is>
-          <t>支持外部动态列表作为策略地址对象（EDL）</t>
+          <t>支持DoS聚合配置文件（连接/秒阈值）</t>
         </is>
       </c>
       <c r="D47" s="81" t="inlineStr">
         <is>
-          <t>HTTP/HTTPS外部文本列表(IP/域名/URL)自动拉取，策略直接引用</t>
+          <t>连接数/秒阈值告警+最大速率限制</t>
         </is>
       </c>
       <c r="E47" s="81" t="inlineStr">
         <is>
-          <t>PA外部动态列表：基于HTTP/HTTPS托管的文本文件创建IP/URL/域名/IMEI/IMSI地址对象，防火墙定时自动拉取更新，策略中直接引用（Objects&gt;External Dynamic Lists，PA Web帮助p236-239；策略源/目标可直接选EDL，p196-197）；天融信手册检索外部动态列表/EDL无命中，仅内置威胁情报库与云端威胁情报库（规则集管理，天融信手册《威胁情报》《配置规则集》页），无策略直接引用任意外部文本列表机制；迁移评估项：PA策略中引用的EDL需转换为天融信静态地址组定期导入或威胁情报联动</t>
+          <t>PA聚合DoS配置文件按传入连接数/秒触发告警与最大速率限制；天融信DDoS防护模块按阈值（pps/bps）监视并触发防护（天融信手册《配置策略模板》页）</t>
         </is>
       </c>
       <c r="F47" s="80" t="inlineStr">
@@ -4777,27 +4773,31 @@
       <c r="G47" s="81" t="inlineStr"/>
       <c r="H47" s="80" t="inlineStr">
         <is>
-          <t>不支持</t>
+          <t>已支持</t>
         </is>
       </c>
       <c r="I47" s="80" t="inlineStr"/>
     </row>
-    <row r="48" ht="126" customHeight="1" s="1">
+    <row r="48" ht="171" customHeight="1" s="1">
       <c r="A48" s="84" t="n"/>
-      <c r="B48" s="85" t="n"/>
+      <c r="B48" s="80" t="inlineStr">
+        <is>
+          <t>动态对象(Dynamic Objects)</t>
+        </is>
+      </c>
       <c r="C48" s="81" t="inlineStr">
         <is>
-          <t>支持基于标记的动态地址组（DAG）</t>
+          <t>支持外部动态列表作为策略地址对象（EDL）</t>
         </is>
       </c>
       <c r="D48" s="81" t="inlineStr">
         <is>
-          <t>Tag标记过滤器动态地址组，成员随IP变化自动更新</t>
+          <t>HTTP/HTTPS外部文本列表(IP/域名/URL)自动拉取，策略直接引用</t>
         </is>
       </c>
       <c r="E48" s="81" t="inlineStr">
         <is>
-          <t>PA动态地址组：查找标记(Tag)+基于标记的过滤器（AND/OR匹配）动态填充成员，VM信息源注册或XML/REST API定义标记，IP变化时策略自动生效（PA Web帮助p207-208、p228）；天融信手册检索动态地址组/标签/SDN/云平台联动无命中，地址组为静态IP/子网绑定（天融信手册《地址》页）；迁移评估项：PA云环境Tag微隔离策略需转换为静态地址组，IP漂移场景需人工或API维护</t>
+          <t>PA外部动态列表：基于HTTP/HTTPS托管的文本文件创建IP/URL/域名/IMEI/IMSI地址对象，防火墙定时自动拉取更新，策略中直接引用（Objects&gt;External Dynamic Lists，PA Web帮助p236-239；策略源/目标可直接选EDL，p196-197）；天融信手册检索外部动态列表/EDL无命中，仅内置威胁情报库与云端威胁情报库（规则集管理，天融信手册《威胁情报》《配置规则集》页），无策略直接引用任意外部文本列表机制；迁移评估项：PA策略中引用的EDL需转换为天融信静态地址组定期导入或威胁情报联动</t>
         </is>
       </c>
       <c r="F48" s="80" t="inlineStr">
@@ -4813,66 +4813,62 @@
       </c>
       <c r="I48" s="80" t="inlineStr"/>
     </row>
-    <row r="49" ht="81" customHeight="1" s="1">
+    <row r="49" ht="126" customHeight="1" s="1">
       <c r="A49" s="84" t="n"/>
-      <c r="B49" s="80" t="inlineStr">
-        <is>
-          <t>SD-WAN策略</t>
-        </is>
-      </c>
+      <c r="B49" s="85" t="n"/>
       <c r="C49" s="81" t="inlineStr">
         <is>
-          <t>支持按应用配置链路路径管理与链路质量探测</t>
+          <t>支持基于标记的动态地址组（DAG）</t>
         </is>
       </c>
       <c r="D49" s="81" t="inlineStr">
         <is>
-          <t>按应用分配链路与流量分发（天融信以策略路由+LLB近似实现）</t>
+          <t>Tag标记过滤器动态地址组，成员随IP变化自动更新</t>
         </is>
       </c>
       <c r="E49" s="81" t="inlineStr">
         <is>
-          <t>PA SD-WAN策略按应用/抖动/延迟/丢包指标分配链路，流量分发（PA Web帮助p197）；天融信为策略路由+链路负载均衡近似实现（天融信手册《策略路由》《链路负载均衡》页），无SD-WAN策略模型；对应矩阵#129/120</t>
+          <t>PA动态地址组：查找标记(Tag)+基于标记的过滤器（AND/OR匹配）动态填充成员，VM信息源注册或XML/REST API定义标记，IP变化时策略自动生效（PA Web帮助p207-208、p228）；天融信手册检索动态地址组/标签/SDN/云平台联动无命中，地址组为静态IP/子网绑定（天融信手册《地址》页）；迁移评估项：PA云环境Tag微隔离策略需转换为静态地址组，IP漂移场景需人工或API维护</t>
         </is>
       </c>
       <c r="F49" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G49" s="81" t="inlineStr"/>
       <c r="H49" s="80" t="inlineStr">
         <is>
-          <t>部分支持</t>
-        </is>
-      </c>
-      <c r="I49" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I49" s="80" t="inlineStr"/>
     </row>
     <row r="50" ht="81" customHeight="1" s="1">
-      <c r="A50" s="85" t="n"/>
-      <c r="B50" s="85" t="n"/>
+      <c r="A50" s="84" t="n"/>
+      <c r="B50" s="80" t="inlineStr">
+        <is>
+          <t>SD-WAN策略</t>
+        </is>
+      </c>
       <c r="C50" s="81" t="inlineStr">
         <is>
-          <t>支持SD-WAN路径选择与链路质量监测（jitter/latency/loss）</t>
+          <t>支持按应用配置链路路径管理与链路质量探测</t>
         </is>
       </c>
       <c r="D50" s="81" t="inlineStr">
         <is>
-          <t>抖动/延迟/丢包多维指标选路（天融信现仅延迟探测）</t>
+          <t>按应用分配链路与流量分发（天融信以策略路由+LLB近似实现）</t>
         </is>
       </c>
       <c r="E50" s="81" t="inlineStr">
         <is>
-          <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路（PA Web帮助p195）；天融信有链路探测(ping)+智能选路(最小延迟优先)（天融信手册《策略路由》页），无jitter/latency/loss多维指标</t>
+          <t>PA SD-WAN策略按应用/抖动/延迟/丢包指标分配链路，流量分发（PA Web帮助p197）；天融信为策略路由+链路负载均衡近似实现（天融信手册《策略路由》《链路负载均衡》页），无SD-WAN策略模型；对应矩阵#129/120</t>
         </is>
       </c>
       <c r="F50" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G50" s="81" t="inlineStr"/>
@@ -4881,49 +4877,85 @@
           <t>部分支持</t>
         </is>
       </c>
-      <c r="I50" s="80" t="inlineStr"/>
+      <c r="I50" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="81" customHeight="1" s="1">
+      <c r="A51" s="85" t="n"/>
+      <c r="B51" s="85" t="n"/>
+      <c r="C51" s="81" t="inlineStr">
+        <is>
+          <t>支持SD-WAN路径选择与链路质量监测（jitter/latency/loss）</t>
+        </is>
+      </c>
+      <c r="D51" s="81" t="inlineStr">
+        <is>
+          <t>抖动/延迟/丢包多维指标选路（天融信现仅延迟探测）</t>
+        </is>
+      </c>
+      <c r="E51" s="81" t="inlineStr">
+        <is>
+          <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路（PA Web帮助p195）；天融信有链路探测(ping)+智能选路(最小延迟优先)（天融信手册《策略路由》页），无jitter/latency/loss多维指标</t>
+        </is>
+      </c>
+      <c r="F51" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G51" s="81" t="inlineStr"/>
+      <c r="H51" s="80" t="inlineStr">
+        <is>
+          <t>部分支持</t>
+        </is>
+      </c>
+      <c r="I51" s="80" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="A2:A50"/>
+  <mergeCells count="40">
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G9:G16"/>
+    <mergeCell ref="B8:B16"/>
+    <mergeCell ref="F43:F45"/>
     <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="B27:B32"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="G17:G22"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="H17:H20"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="I29:I33"/>
+    <mergeCell ref="G43:G45"/>
     <mergeCell ref="B2:B7"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="B8:B15"/>
-    <mergeCell ref="B16:B22"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="G9:G15"/>
-    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="G18:G23"/>
+    <mergeCell ref="I18:I23"/>
     <mergeCell ref="I9:I15"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="H32:H33"/>
     <mergeCell ref="H12:H15"/>
+    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="H37:H38"/>
     <mergeCell ref="F3:F7"/>
     <mergeCell ref="F11:F12"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="I17:I22"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="A2:A51"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="B17:B23"/>
     <mergeCell ref="G3:G7"/>
+    <mergeCell ref="I43:I45"/>
     <mergeCell ref="I3:I7"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="G28:G32"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="I28:I32"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="I40:I41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4935,7 +4967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.2"/>
   <cols>
     <col width="11.7" customWidth="1" style="1" min="1" max="1"/>
@@ -5294,92 +5326,88 @@
       <c r="H11" s="82" t="n"/>
       <c r="I11" s="82" t="n"/>
     </row>
-    <row r="12" ht="126" customHeight="1" s="1">
+    <row r="12" ht="171" customHeight="1" s="1">
       <c r="A12" s="82" t="n"/>
-      <c r="B12" s="80" t="inlineStr">
+      <c r="B12" s="82" t="n"/>
+      <c r="C12" s="81" t="inlineStr">
+        <is>
+          <t>支持WildFire云沙箱文件检测联动（Advanced WildFire）</t>
+        </is>
+      </c>
+      <c r="D12" s="81" t="inlineStr">
+        <is>
+          <t>未知文件云沙箱实时分析+签名秒级下发，策略Actions绑定WildFire配置文件</t>
+        </is>
+      </c>
+      <c r="E12" s="81" t="inlineStr">
+        <is>
+          <t>PA策略Actions可绑定WildFire Analysis配置文件（安全配置文件组含反病毒/漏洞/URL/文件阻断/WildFire，PA Web帮助p304；WildFire提交日志转发p305-306），云沙箱动态分析未知/零日威胁并秒级下发签名；天融信有内置APT沙箱（虚拟运行环境检测未知漏洞威胁）与沙箱联动（天融信手册《高级威胁防护》《APT联动配置》页），无云端动态分析与秒级签名下发证据；工作表1已登记云沙箱联动需求（不支持：公司无此产品），勿重复跟踪；迁移评估项：评估天融信本地APT沙箱与PA云沙箱检测能力等效性</t>
+        </is>
+      </c>
+      <c r="F12" s="82" t="n"/>
+      <c r="G12" s="82" t="n"/>
+      <c r="H12" s="80" t="inlineStr">
+        <is>
+          <t>部分支持</t>
+        </is>
+      </c>
+      <c r="I12" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="126" customHeight="1" s="1">
+      <c r="A13" s="82" t="n"/>
+      <c r="B13" s="80" t="inlineStr">
         <is>
           <t>NAT策略</t>
         </is>
       </c>
-      <c r="C12" s="81" t="inlineStr">
+      <c r="C13" s="81" t="inlineStr">
         <is>
           <t>支持NAT后目的区域路由回查匹配（Dest Zone by route lookup）</t>
         </is>
       </c>
-      <c r="D12" s="81" t="inlineStr">
+      <c r="D13" s="81" t="inlineStr">
         <is>
           <t>目的区域按NAT后路由查找；源/目的地址用NAT前值</t>
         </is>
       </c>
-      <c r="E12" s="81" t="inlineStr">
+      <c r="E13" s="81" t="inlineStr">
         <is>
           <t>PA底层为『先NAT判断后安全策略匹配』的因果倒置：安全策略要求源区域(NAT前)+源地址(NAT前)+目的地址(NAT前)+目的区域(NAT后按路由查找)，极其反直觉；天融信地址转换为独立策略库常规直观映射（安全策略&gt;地址转换，天融信手册《服务器映射》页）；迁移评估项：带目的NAT的策略平移后易因Zone填写错误不通，需制定NAT查表逻辑转换映射规范；对应矩阵#9</t>
         </is>
       </c>
-      <c r="F12" s="80" t="inlineStr">
+      <c r="F13" s="80" t="inlineStr">
         <is>
           <t>高</t>
-        </is>
-      </c>
-      <c r="G12" s="81" t="inlineStr"/>
-      <c r="H12" s="80" t="inlineStr">
-        <is>
-          <t>待评估</t>
-        </is>
-      </c>
-      <c r="I12" s="80" t="inlineStr"/>
-    </row>
-    <row r="13" ht="81" customHeight="1" s="1">
-      <c r="A13" s="82" t="n"/>
-      <c r="B13" s="82" t="n"/>
-      <c r="C13" s="81" t="inlineStr">
-        <is>
-          <t>支持NAT规则主动/主动HA绑定（Active/Active HA Binding）</t>
-        </is>
-      </c>
-      <c r="D13" s="81" t="inlineStr">
-        <is>
-          <t>主动/主动HA下NAT规则绑定会话所有者</t>
-        </is>
-      </c>
-      <c r="E13" s="81" t="inlineStr">
-        <is>
-          <t>PA主动/主动HA配置下NAT规则可绑定会话所有者/会话设置，控制NAT会话的设备绑定，仅A/A模式可见（PA Web帮助p150）；天融信HA为主备双机热备模式（天融信手册《配置双机热备功能》页），无主动/主动模式及NAT规则绑定机制</t>
-        </is>
-      </c>
-      <c r="F13" s="80" t="inlineStr">
-        <is>
-          <t>低</t>
         </is>
       </c>
       <c r="G13" s="81" t="inlineStr"/>
       <c r="H13" s="80" t="inlineStr">
         <is>
-          <t>不支持</t>
+          <t>待评估</t>
         </is>
       </c>
       <c r="I13" s="80" t="inlineStr"/>
     </row>
-    <row r="14" ht="96" customHeight="1" s="1">
+    <row r="14" ht="81" customHeight="1" s="1">
       <c r="A14" s="82" t="n"/>
-      <c r="B14" s="80" t="inlineStr">
-        <is>
-          <t>QoS策略</t>
-        </is>
-      </c>
+      <c r="B14" s="82" t="n"/>
       <c r="C14" s="81" t="inlineStr">
         <is>
-          <t>支持QoS策略规则内直接按DSCP/ToS匹配调度</t>
+          <t>支持NAT规则主动/主动HA绑定（Active/Active HA Binding）</t>
         </is>
       </c>
       <c r="D14" s="81" t="inlineStr">
         <is>
-          <t>QoS策略规则DSCP/ToS直接匹配（非独立流控模块配置）</t>
+          <t>主动/主动HA下NAT规则绑定会话所有者</t>
         </is>
       </c>
       <c r="E14" s="81" t="inlineStr">
         <is>
-          <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
+          <t>PA主动/主动HA配置下NAT规则可绑定会话所有者/会话设置，控制NAT会话的设备绑定，仅A/A模式可见（PA Web帮助p150）；天融信HA为主备双机热备模式（天融信手册《配置双机热备功能》页），无主动/主动模式及NAT规则绑定机制</t>
         </is>
       </c>
       <c r="F14" s="80" t="inlineStr">
@@ -5390,226 +5418,226 @@
       <c r="G14" s="81" t="inlineStr"/>
       <c r="H14" s="80" t="inlineStr">
         <is>
-          <t>部分支持</t>
+          <t>不支持</t>
         </is>
       </c>
       <c r="I14" s="80" t="inlineStr"/>
     </row>
-    <row r="15" ht="111" customHeight="1" s="1">
+    <row r="15" ht="96" customHeight="1" s="1">
       <c r="A15" s="82" t="n"/>
       <c r="B15" s="80" t="inlineStr">
         <is>
-          <t>基于策略转发(PBF)</t>
+          <t>QoS策略</t>
         </is>
       </c>
       <c r="C15" s="81" t="inlineStr">
         <is>
-          <t>支持PBF强制对称返回（非对称路由环境）</t>
+          <t>支持QoS策略规则内直接按DSCP/ToS匹配调度</t>
         </is>
       </c>
       <c r="D15" s="81" t="inlineStr">
         <is>
-          <t>记录入接口MAC，回包强制原路返回</t>
+          <t>QoS策略规则DSCP/ToS直接匹配（非独立流控模块配置）</t>
         </is>
       </c>
       <c r="E15" s="81" t="inlineStr">
         <is>
-          <t>PA对称返回：虚拟路由器替代返回流量的路由查找，将流量引导回接收SYN数据包的MAC地址（ARP表确定下一跳），双ISP双活/非对称路由核心机制（PA管理指南p1294）；天融信手册检索无对称返回/回程机制命中，策略路由与LLB的回程保障能力待验证；迁移评估项：多ISP双活环境需实测天融信回包路由对称性，否则现网业务中断</t>
+          <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
         </is>
       </c>
       <c r="F15" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G15" s="81" t="inlineStr"/>
       <c r="H15" s="80" t="inlineStr">
         <is>
-          <t>待评估</t>
+          <t>部分支持</t>
         </is>
       </c>
       <c r="I15" s="80" t="inlineStr"/>
     </row>
-    <row r="16" ht="51" customHeight="1" s="1">
+    <row r="16" ht="111" customHeight="1" s="1">
       <c r="A16" s="82" t="n"/>
       <c r="B16" s="80" t="inlineStr">
         <is>
-          <t>解密策略(Decryption)</t>
+          <t>基于策略转发(PBF)</t>
         </is>
       </c>
       <c r="C16" s="81" t="inlineStr">
         <is>
-          <t>支持解密流量镜像到专用接口（Decryption Port Mirroring）</t>
+          <t>支持PBF强制对称返回（非对称路由环境）</t>
         </is>
       </c>
       <c r="D16" s="81" t="inlineStr">
         <is>
-          <t>解密后明文流量镜像至专用接口供第三方分析</t>
+          <t>记录入接口MAC，回包强制原路返回</t>
         </is>
       </c>
       <c r="E16" s="81" t="inlineStr">
         <is>
-          <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证（PA管理指南p1059）；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
+          <t>PA对称返回：虚拟路由器替代返回流量的路由查找，将流量引导回接收SYN数据包的MAC地址（ARP表确定下一跳），双ISP双活/非对称路由核心机制（PA管理指南p1294）；天融信手册检索无对称返回/回程机制命中，策略路由与LLB的回程保障能力待验证；迁移评估项：多ISP双活环境需实测天融信回包路由对称性，否则现网业务中断</t>
         </is>
       </c>
       <c r="F16" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G16" s="81" t="inlineStr"/>
       <c r="H16" s="80" t="inlineStr">
         <is>
-          <t>不支持</t>
+          <t>待评估</t>
         </is>
       </c>
       <c r="I16" s="80" t="inlineStr"/>
     </row>
-    <row r="17" ht="126" customHeight="1" s="1">
+    <row r="17" ht="51" customHeight="1" s="1">
       <c r="A17" s="82" t="n"/>
-      <c r="B17" s="82" t="n"/>
+      <c r="B17" s="80" t="inlineStr">
+        <is>
+          <t>解密策略(Decryption)</t>
+        </is>
+      </c>
       <c r="C17" s="81" t="inlineStr">
         <is>
-          <t>支持解密不受信证书分离处理（Forward Untrust Certificate）</t>
+          <t>支持解密流量镜像到专用接口（Decryption Port Mirroring）</t>
         </is>
       </c>
       <c r="D17" s="81" t="inlineStr">
         <is>
-          <t>外部无效证书以不受信转发证书重签，保留浏览器告警</t>
+          <t>解密后明文流量镜像至专用接口供第三方分析</t>
         </is>
       </c>
       <c r="E17" s="81" t="inlineStr">
         <is>
-          <t>PA转发代理遇外部过期/不受信证书时，不用内部信任CA重签，而是专用Forward Untrust Certificate重签名，让浏览器保留不受信告警（PA管理指南p994、p1030）；天融信SSL解密（透明代理/服务器SSL解密，天融信手册《代理策略》页）未见受信/不受信双证书体系；迁移评估项：需验证天融信对外部无效证书的处理方式，避免直接阻断（白屏）或信任重签（掩盖风险）</t>
+          <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证（PA管理指南p1059）；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
         </is>
       </c>
       <c r="F17" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G17" s="81" t="inlineStr"/>
       <c r="H17" s="80" t="inlineStr">
         <is>
-          <t>待评估</t>
+          <t>不支持</t>
         </is>
       </c>
       <c r="I17" s="80" t="inlineStr"/>
     </row>
-    <row r="18" ht="66" customHeight="1" s="1">
+    <row r="18" ht="126" customHeight="1" s="1">
       <c r="A18" s="82" t="n"/>
       <c r="B18" s="82" t="n"/>
       <c r="C18" s="81" t="inlineStr">
         <is>
-          <t>支持解密规则按URL类别选择性解密（URL Category）</t>
+          <t>支持解密不受信证书分离处理（Forward Untrust Certificate）</t>
         </is>
       </c>
       <c r="D18" s="81" t="inlineStr">
         <is>
-          <t>按URL类别圈定解密范围，排除银行/医疗等敏感类</t>
+          <t>外部无效证书以不受信转发证书重签，保留浏览器告警</t>
         </is>
       </c>
       <c r="E18" s="81" t="inlineStr">
         <is>
-          <t>PA解密规则可按URL类别（含自定义类别）选择解密范围，可排除银行/医疗等敏感类别不解密（PA Web帮助p164）；天融信SSL解密（代理策略/代理模板）无按URL类别选择解密机制（检索无命中）</t>
+          <t>PA转发代理遇外部过期/不受信证书时，不用内部信任CA重签，而是专用Forward Untrust Certificate重签名，让浏览器保留不受信告警（PA管理指南p994、p1030）；天融信SSL解密（透明代理/服务器SSL解密，天融信手册《代理策略》页）未见受信/不受信双证书体系；迁移评估项：需验证天融信对外部无效证书的处理方式，避免直接阻断（白屏）或信任重签（掩盖风险）</t>
         </is>
       </c>
       <c r="F18" s="80" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G18" s="82" t="n"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G18" s="81" t="inlineStr"/>
       <c r="H18" s="80" t="inlineStr">
         <is>
-          <t>不支持</t>
-        </is>
-      </c>
-      <c r="I18" s="82" t="n"/>
-    </row>
-    <row r="19" ht="96" customHeight="1" s="1">
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="I18" s="80" t="inlineStr"/>
+    </row>
+    <row r="19" ht="66" customHeight="1" s="1">
       <c r="A19" s="82" t="n"/>
       <c r="B19" s="82" t="n"/>
       <c r="C19" s="81" t="inlineStr">
         <is>
+          <t>支持解密规则按URL类别选择性解密（URL Category）</t>
+        </is>
+      </c>
+      <c r="D19" s="81" t="inlineStr">
+        <is>
+          <t>按URL类别圈定解密范围，排除银行/医疗等敏感类</t>
+        </is>
+      </c>
+      <c r="E19" s="81" t="inlineStr">
+        <is>
+          <t>PA解密规则可按URL类别（含自定义类别）选择解密范围，可排除银行/医疗等敏感类别不解密（PA Web帮助p164）；天融信SSL解密（代理策略/代理模板）无按URL类别选择解密机制（检索无命中）</t>
+        </is>
+      </c>
+      <c r="F19" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G19" s="82" t="n"/>
+      <c r="H19" s="80" t="inlineStr">
+        <is>
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I19" s="82" t="n"/>
+    </row>
+    <row r="20" ht="96" customHeight="1" s="1">
+      <c r="A20" s="82" t="n"/>
+      <c r="B20" s="82" t="n"/>
+      <c r="C20" s="81" t="inlineStr">
+        <is>
           <t>支持SSH代理解密与SSH隧道控制（SSH Proxy）</t>
         </is>
       </c>
-      <c r="D19" s="81" t="inlineStr">
+      <c r="D20" s="81" t="inlineStr">
         <is>
           <t>SSH代理解密+SSH隧道(ssh-tunnel)识别控制</t>
         </is>
       </c>
-      <c r="E19" s="81" t="inlineStr">
+      <c r="E20" s="81" t="inlineStr">
         <is>
           <t>PA解密策略SSH Proxy类型解密SSH通信，可通过ssh-tunnel App-ID在策略中控制SSH隧道（端口转发/内网穿透），正常SSH管理流量放行；含不受支持算法检查/资源不足阻断会话等防护（PA Web帮助p164、p318-319）；天融信手册检索无SSH代理/SSH隧道控制命中</t>
         </is>
       </c>
-      <c r="F19" s="82" t="n"/>
-      <c r="G19" s="82" t="n"/>
-      <c r="H19" s="82" t="n"/>
-      <c r="I19" s="82" t="n"/>
-    </row>
-    <row r="20" ht="111" customHeight="1" s="1">
-      <c r="A20" s="82" t="n"/>
-      <c r="B20" s="80" t="inlineStr">
+      <c r="F20" s="82" t="n"/>
+      <c r="G20" s="82" t="n"/>
+      <c r="H20" s="82" t="n"/>
+      <c r="I20" s="82" t="n"/>
+    </row>
+    <row r="21" ht="111" customHeight="1" s="1">
+      <c r="A21" s="82" t="n"/>
+      <c r="B21" s="80" t="inlineStr">
         <is>
           <t>网络数据包代理(NPBroker)</t>
         </is>
       </c>
-      <c r="C20" s="81" t="inlineStr">
+      <c r="C21" s="81" t="inlineStr">
         <is>
           <t>支持内联数据包代理策略将流量转发第三方安全链（NPBroker）</t>
         </is>
       </c>
-      <c r="D20" s="81" t="inlineStr">
+      <c r="D21" s="81" t="inlineStr">
         <is>
           <t>已解密/未解密流量内联转发第三方安全链，L3路由转发</t>
         </is>
       </c>
-      <c r="E20" s="81" t="inlineStr">
+      <c r="E21" s="81" t="inlineStr">
         <is>
           <t>PA网络数据包代理策略将已解密/未解密TLS/非TLS流量内联转发至第三方安全工具，路径选择选项卡应用数据包代理配置文件定义经路由L3安全链的转发方式（PA Web帮助p167-170）；天融信无网络数据包代理模块，最接近手段为WAF旁路联动（经交换机镜像引流，天融信手册《与WAF联动》页），非内联且无回注路径；对应矩阵#122</t>
         </is>
       </c>
-      <c r="F20" s="80" t="inlineStr">
+      <c r="F21" s="80" t="inlineStr">
         <is>
           <t>高</t>
-        </is>
-      </c>
-      <c r="G20" s="81" t="inlineStr"/>
-      <c r="H20" s="80" t="inlineStr">
-        <is>
-          <t>不支持</t>
-        </is>
-      </c>
-      <c r="I20" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="66" customHeight="1" s="1">
-      <c r="A21" s="82" t="n"/>
-      <c r="B21" s="82" t="n"/>
-      <c r="C21" s="81" t="inlineStr">
-        <is>
-          <t>支持NPBroker转发流量类型选择（TLS解密/未解密/非TLS）</t>
-        </is>
-      </c>
-      <c r="D21" s="81" t="inlineStr">
-        <is>
-          <t>TLS解密/未解密/非TLS流量类型选择</t>
-        </is>
-      </c>
-      <c r="E21" s="81" t="inlineStr">
-        <is>
-          <t>PA规则可选Forward TLS(Decrypted)/未解密/非TLS多种流量类型；需免费许可证（PA Web帮助p167）；天融信无网络数据包代理模块（矩阵#122）</t>
-        </is>
-      </c>
-      <c r="F21" s="80" t="inlineStr">
-        <is>
-          <t>中</t>
         </is>
       </c>
       <c r="G21" s="81" t="inlineStr"/>
@@ -5618,33 +5646,33 @@
           <t>不支持</t>
         </is>
       </c>
-      <c r="I21" s="80" t="inlineStr"/>
-    </row>
-    <row r="22" ht="96" customHeight="1" s="1">
+      <c r="I21" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="66" customHeight="1" s="1">
       <c r="A22" s="82" t="n"/>
-      <c r="B22" s="80" t="inlineStr">
-        <is>
-          <t>隧道检测(Tunnel Inspection)</t>
-        </is>
-      </c>
+      <c r="B22" s="82" t="n"/>
       <c r="C22" s="81" t="inlineStr">
         <is>
-          <t>支持GTP-U/VXLAN/非加密IPSec隧道内层检测</t>
+          <t>支持NPBroker转发流量类型选择（TLS解密/未解密/非TLS）</t>
         </is>
       </c>
       <c r="D22" s="81" t="inlineStr">
         <is>
-          <t>GTP-U/VXLAN/NULL加密IPSec(AH)隧道内层流量检测</t>
+          <t>TLS解密/未解密/非TLS流量类型选择</t>
         </is>
       </c>
       <c r="E22" s="81" t="inlineStr">
         <is>
-          <t>PA隧道检测支持GTP-U/VXLAN/非加密IPSec（NULL加密/AH传输模式）内层检测（PA Web帮助p172-173）；天融信VXLAN仅隧道封装转发与三层网关（天融信手册《业务接入端》《三层VXLAN网关》页），无内层安全检测，GTP检测检索无命中；对应矩阵#128/37</t>
+          <t>PA规则可选Forward TLS(Decrypted)/未解密/非TLS多种流量类型；需免费许可证（PA Web帮助p167）；天融信无网络数据包代理模块（矩阵#122）</t>
         </is>
       </c>
       <c r="F22" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G22" s="81" t="inlineStr"/>
@@ -5655,27 +5683,31 @@
       </c>
       <c r="I22" s="80" t="inlineStr"/>
     </row>
-    <row r="23" ht="51" customHeight="1" s="1">
+    <row r="23" ht="96" customHeight="1" s="1">
       <c r="A23" s="82" t="n"/>
-      <c r="B23" s="82" t="n"/>
+      <c r="B23" s="80" t="inlineStr">
+        <is>
+          <t>隧道检测(Tunnel Inspection)</t>
+        </is>
+      </c>
       <c r="C23" s="81" t="inlineStr">
         <is>
-          <t>支持最大封装级数防护（max_encap）</t>
+          <t>支持GTP-U/VXLAN/非加密IPSec隧道内层检测</t>
         </is>
       </c>
       <c r="D23" s="81" t="inlineStr">
         <is>
-          <t>隧道嵌套封装最大级数限制，超限丢弃</t>
+          <t>GTP-U/VXLAN/NULL加密IPSec(AH)隧道内层流量检测</t>
         </is>
       </c>
       <c r="E23" s="81" t="inlineStr">
         <is>
-          <t>PA对隧道最大封装级数超限丢包防护，防隧道嵌套绕过（PA管理指南p655）；天融信手册无封装级数防护（检索无命中）</t>
+          <t>PA隧道检测支持GTP-U/VXLAN/非加密IPSec（NULL加密/AH传输模式）内层检测（PA Web帮助p172-173）；天融信VXLAN仅隧道封装转发与三层网关（天融信手册《业务接入端》《三层VXLAN网关》页），无内层安全检测，GTP检测检索无命中；对应矩阵#128/37</t>
         </is>
       </c>
       <c r="F23" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G23" s="81" t="inlineStr"/>
@@ -5686,66 +5718,62 @@
       </c>
       <c r="I23" s="80" t="inlineStr"/>
     </row>
-    <row r="24" ht="96" customHeight="1" s="1">
+    <row r="24" ht="51" customHeight="1" s="1">
       <c r="A24" s="82" t="n"/>
-      <c r="B24" s="80" t="inlineStr">
-        <is>
-          <t>应用覆盖(App Override)</t>
-        </is>
-      </c>
+      <c r="B24" s="82" t="n"/>
       <c r="C24" s="81" t="inlineStr">
         <is>
-          <t>支持应用替代流量跳过七层检测等效配置</t>
+          <t>支持最大封装级数防护（max_encap）</t>
         </is>
       </c>
       <c r="D24" s="81" t="inlineStr">
         <is>
-          <t>匹配覆盖策略的流量跳过七层检测，四层快速转发</t>
+          <t>隧道嵌套封装最大级数限制，超限丢弃</t>
         </is>
       </c>
       <c r="E24" s="81" t="inlineStr">
         <is>
-          <t>PA应用替代策略明确绕过第7层处理与威胁检查，改用第4层状态检查以加速（PA管理指南p1307）；天融信自定义应用加入规则库后仍默认经安全引擎检测（天融信手册《自定义应用》页）；迁移评估项：PA应用替代多为私有大流量业务加速，转换时需同步关闭对应策略的IPS/七层检测，否则性能被拖垮或误阻断</t>
+          <t>PA对隧道最大封装级数超限丢包防护，防隧道嵌套绕过（PA管理指南p655）；天融信手册无封装级数防护（检索无命中）</t>
         </is>
       </c>
       <c r="F24" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G24" s="81" t="inlineStr"/>
       <c r="H24" s="80" t="inlineStr">
         <is>
-          <t>待评估</t>
+          <t>不支持</t>
         </is>
       </c>
       <c r="I24" s="80" t="inlineStr"/>
     </row>
-    <row r="25" ht="81" customHeight="1" s="1">
+    <row r="25" ht="96" customHeight="1" s="1">
       <c r="A25" s="82" t="n"/>
       <c r="B25" s="80" t="inlineStr">
         <is>
-          <t>身份验证(Authentication)</t>
+          <t>应用覆盖(App Override)</t>
         </is>
       </c>
       <c r="C25" s="81" t="inlineStr">
         <is>
-          <t>支持认证策略超时与单次认证（SSO）</t>
+          <t>支持应用替代流量跳过七层检测等效配置</t>
         </is>
       </c>
       <c r="D25" s="81" t="inlineStr">
         <is>
-          <t>认证超时+单次认证(SSO)</t>
+          <t>匹配覆盖策略的流量跳过七层检测，四层快速转发</t>
         </is>
       </c>
       <c r="E25" s="81" t="inlineStr">
         <is>
-          <t>PA支持认证超时减少重复质询、Kerberos/SAML/RADIUS等对接（PA Web帮助p186）；天融信手册检索认证超时/单点登录/SSO无命中（仅在线用户在线时长查看与强制下线）；迁移评估项：需核实天融信认证会话有效期配置与SSO对接能力</t>
+          <t>PA应用替代策略明确绕过第7层处理与威胁检查，改用第4层状态检查以加速（PA管理指南p1307）；天融信自定义应用加入规则库后仍默认经安全引擎检测（天融信手册《自定义应用》页）；迁移评估项：PA应用替代多为私有大流量业务加速，转换时需同步关闭对应策略的IPS/七层检测，否则性能被拖垮或误阻断</t>
         </is>
       </c>
       <c r="F25" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G25" s="81" t="inlineStr"/>
@@ -5756,22 +5784,26 @@
       </c>
       <c r="I25" s="80" t="inlineStr"/>
     </row>
-    <row r="26" ht="126" customHeight="1" s="1">
+    <row r="26" ht="81" customHeight="1" s="1">
       <c r="A26" s="82" t="n"/>
-      <c r="B26" s="82" t="n"/>
+      <c r="B26" s="80" t="inlineStr">
+        <is>
+          <t>身份验证(Authentication)</t>
+        </is>
+      </c>
       <c r="C26" s="81" t="inlineStr">
         <is>
-          <t>支持流量策略触发多因素认证质询（MFA Enforcement）</t>
+          <t>支持认证策略超时与单次认证（SSO）</t>
         </is>
       </c>
       <c r="D26" s="81" t="inlineStr">
         <is>
-          <t>流量策略匹配触发MFA质询（非登录场景，MFA供应商API/RADIUS）</t>
+          <t>认证超时+单次认证(SSO)</t>
         </is>
       </c>
       <c r="E26" s="81" t="inlineStr">
         <is>
-          <t>PA身份验证策略通过Authentication Enforcement对象对匹配流量强制质询，支持多因素身份验证（每因素独立超时，防火墙记录时间戳），MFA供应商API/RADIUS对接（PA Web帮助p185-186、p310、p735-742）；天融信双因子认证（密码+短信/证书/Ukey）仅限管理员/用户登录场景（天融信手册《登录安全策略》页），无流量策略触发MFA质询</t>
+          <t>PA支持认证超时减少重复质询、Kerberos/SAML/RADIUS等对接（PA Web帮助p186）；天融信手册检索认证超时/单点登录/SSO无命中（仅在线用户在线时长查看与强制下线）；迁移评估项：需核实天融信认证会话有效期配置与SSO对接能力</t>
         </is>
       </c>
       <c r="F26" s="80" t="inlineStr">
@@ -5782,89 +5814,89 @@
       <c r="G26" s="81" t="inlineStr"/>
       <c r="H26" s="80" t="inlineStr">
         <is>
-          <t>不支持</t>
+          <t>待评估</t>
         </is>
       </c>
       <c r="I26" s="80" t="inlineStr"/>
     </row>
-    <row r="27" ht="96" customHeight="1" s="1">
+    <row r="27" ht="126" customHeight="1" s="1">
       <c r="A27" s="82" t="n"/>
       <c r="B27" s="82" t="n"/>
       <c r="C27" s="81" t="inlineStr">
         <is>
+          <t>支持流量策略触发多因素认证质询（MFA Enforcement）</t>
+        </is>
+      </c>
+      <c r="D27" s="81" t="inlineStr">
+        <is>
+          <t>流量策略匹配触发MFA质询（非登录场景，MFA供应商API/RADIUS）</t>
+        </is>
+      </c>
+      <c r="E27" s="81" t="inlineStr">
+        <is>
+          <t>PA身份验证策略通过Authentication Enforcement对象对匹配流量强制质询，支持多因素身份验证（每因素独立超时，防火墙记录时间戳），MFA供应商API/RADIUS对接（PA Web帮助p185-186、p310、p735-742）；天融信双因子认证（密码+短信/证书/Ukey）仅限管理员/用户登录场景（天融信手册《登录安全策略》页），无流量策略触发MFA质询</t>
+        </is>
+      </c>
+      <c r="F27" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G27" s="81" t="inlineStr"/>
+      <c r="H27" s="80" t="inlineStr">
+        <is>
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I27" s="80" t="inlineStr"/>
+    </row>
+    <row r="28" ht="96" customHeight="1" s="1">
+      <c r="A28" s="82" t="n"/>
+      <c r="B28" s="82" t="n"/>
+      <c r="C28" s="81" t="inlineStr">
+        <is>
           <t>支持User-ID动态映射时效性等效（AD日志毫秒级更新）</t>
         </is>
       </c>
-      <c r="D27" s="81" t="inlineStr">
+      <c r="D28" s="81" t="inlineStr">
         <is>
           <t>AD域事件日志毫秒级IP-用户映射更新</t>
         </is>
       </c>
-      <c r="E27" s="81" t="inlineStr">
+      <c r="E28" s="81" t="inlineStr">
         <is>
           <t>PA无代理架构通过读取域控事件日志实现IP-用户毫秒级动态映射，大规模部署有专项规划（PA管理指南p866-867）；天融信AD对接的轮询间隔与并发认证能力手册未量化；迁移评估项：数万AD用户且移动频繁场景需实测天融信映射更新时延，避免基于用户的策略出现间歇性未授权拦截</t>
         </is>
       </c>
-      <c r="F27" s="82" t="n"/>
-      <c r="G27" s="82" t="n"/>
-      <c r="H27" s="80" t="inlineStr">
+      <c r="F28" s="82" t="n"/>
+      <c r="G28" s="82" t="n"/>
+      <c r="H28" s="80" t="inlineStr">
         <is>
           <t>待评估</t>
         </is>
       </c>
-      <c r="I27" s="82" t="n"/>
-    </row>
-    <row r="28" ht="171" customHeight="1" s="1">
-      <c r="A28" s="82" t="n"/>
-      <c r="B28" s="80" t="inlineStr">
+      <c r="I28" s="82" t="n"/>
+    </row>
+    <row r="29" ht="171" customHeight="1" s="1">
+      <c r="A29" s="82" t="n"/>
+      <c r="B29" s="80" t="inlineStr">
         <is>
           <t>动态对象(Dynamic Objects)</t>
         </is>
       </c>
-      <c r="C28" s="81" t="inlineStr">
+      <c r="C29" s="81" t="inlineStr">
         <is>
           <t>支持外部动态列表作为策略地址对象（EDL）</t>
         </is>
       </c>
-      <c r="D28" s="81" t="inlineStr">
+      <c r="D29" s="81" t="inlineStr">
         <is>
           <t>HTTP/HTTPS外部文本列表(IP/域名/URL)自动拉取，策略直接引用</t>
         </is>
       </c>
-      <c r="E28" s="81" t="inlineStr">
+      <c r="E29" s="81" t="inlineStr">
         <is>
           <t>PA外部动态列表：基于HTTP/HTTPS托管的文本文件创建IP/URL/域名/IMEI/IMSI地址对象，防火墙定时自动拉取更新，策略中直接引用（Objects&gt;External Dynamic Lists，PA Web帮助p236-239；策略源/目标可直接选EDL，p196-197）；天融信手册检索外部动态列表/EDL无命中，仅内置威胁情报库与云端威胁情报库（规则集管理，天融信手册《威胁情报》《配置规则集》页），无策略直接引用任意外部文本列表机制；迁移评估项：PA策略中引用的EDL需转换为天融信静态地址组定期导入或威胁情报联动</t>
-        </is>
-      </c>
-      <c r="F28" s="80" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G28" s="81" t="inlineStr"/>
-      <c r="H28" s="80" t="inlineStr">
-        <is>
-          <t>不支持</t>
-        </is>
-      </c>
-      <c r="I28" s="80" t="inlineStr"/>
-    </row>
-    <row r="29" ht="126" customHeight="1" s="1">
-      <c r="A29" s="82" t="n"/>
-      <c r="B29" s="82" t="n"/>
-      <c r="C29" s="81" t="inlineStr">
-        <is>
-          <t>支持基于标记的动态地址组（DAG）</t>
-        </is>
-      </c>
-      <c r="D29" s="81" t="inlineStr">
-        <is>
-          <t>Tag标记过滤器动态地址组，成员随IP变化自动更新</t>
-        </is>
-      </c>
-      <c r="E29" s="81" t="inlineStr">
-        <is>
-          <t>PA动态地址组：查找标记(Tag)+基于标记的过滤器（AND/OR匹配）动态填充成员，VM信息源注册或XML/REST API定义标记，IP变化时策略自动生效（PA Web帮助p207-208、p228）；天融信手册检索动态地址组/标签/SDN/云平台联动无命中，地址组为静态IP/子网绑定（天融信手册《地址》页）；迁移评估项：PA云环境Tag微隔离策略需转换为静态地址组，IP漂移场景需人工或API维护</t>
         </is>
       </c>
       <c r="F29" s="80" t="inlineStr">
@@ -5880,66 +5912,62 @@
       </c>
       <c r="I29" s="80" t="inlineStr"/>
     </row>
-    <row r="30" ht="81" customHeight="1" s="1">
+    <row r="30" ht="126" customHeight="1" s="1">
       <c r="A30" s="82" t="n"/>
-      <c r="B30" s="80" t="inlineStr">
-        <is>
-          <t>SD-WAN策略</t>
-        </is>
-      </c>
+      <c r="B30" s="82" t="n"/>
       <c r="C30" s="81" t="inlineStr">
         <is>
-          <t>支持按应用配置链路路径管理与链路质量探测</t>
+          <t>支持基于标记的动态地址组（DAG）</t>
         </is>
       </c>
       <c r="D30" s="81" t="inlineStr">
         <is>
-          <t>按应用分配链路与流量分发（天融信以策略路由+LLB近似实现）</t>
+          <t>Tag标记过滤器动态地址组，成员随IP变化自动更新</t>
         </is>
       </c>
       <c r="E30" s="81" t="inlineStr">
         <is>
-          <t>PA SD-WAN策略按应用/抖动/延迟/丢包指标分配链路，流量分发（PA Web帮助p197）；天融信为策略路由+链路负载均衡近似实现（天融信手册《策略路由》《链路负载均衡》页），无SD-WAN策略模型；对应矩阵#129/120</t>
+          <t>PA动态地址组：查找标记(Tag)+基于标记的过滤器（AND/OR匹配）动态填充成员，VM信息源注册或XML/REST API定义标记，IP变化时策略自动生效（PA Web帮助p207-208、p228）；天融信手册检索动态地址组/标签/SDN/云平台联动无命中，地址组为静态IP/子网绑定（天融信手册《地址》页）；迁移评估项：PA云环境Tag微隔离策略需转换为静态地址组，IP漂移场景需人工或API维护</t>
         </is>
       </c>
       <c r="F30" s="80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G30" s="81" t="inlineStr"/>
       <c r="H30" s="80" t="inlineStr">
         <is>
-          <t>部分支持</t>
-        </is>
-      </c>
-      <c r="I30" s="80" t="inlineStr">
-        <is>
-          <t>产品线</t>
-        </is>
-      </c>
+          <t>不支持</t>
+        </is>
+      </c>
+      <c r="I30" s="80" t="inlineStr"/>
     </row>
     <row r="31" ht="81" customHeight="1" s="1">
       <c r="A31" s="82" t="n"/>
-      <c r="B31" s="82" t="n"/>
+      <c r="B31" s="80" t="inlineStr">
+        <is>
+          <t>SD-WAN策略</t>
+        </is>
+      </c>
       <c r="C31" s="81" t="inlineStr">
         <is>
-          <t>支持SD-WAN路径选择与链路质量监测（jitter/latency/loss）</t>
+          <t>支持按应用配置链路路径管理与链路质量探测</t>
         </is>
       </c>
       <c r="D31" s="81" t="inlineStr">
         <is>
-          <t>抖动/延迟/丢包多维指标选路（天融信现仅延迟探测）</t>
+          <t>按应用分配链路与流量分发（天融信以策略路由+LLB近似实现）</t>
         </is>
       </c>
       <c r="E31" s="81" t="inlineStr">
         <is>
-          <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路（PA Web帮助p195）；天融信有链路探测(ping)+智能选路(最小延迟优先)（天融信手册《策略路由》页），无jitter/latency/loss多维指标</t>
+          <t>PA SD-WAN策略按应用/抖动/延迟/丢包指标分配链路，流量分发（PA Web帮助p197）；天融信为策略路由+链路负载均衡近似实现（天融信手册《策略路由》《链路负载均衡》页），无SD-WAN策略模型；对应矩阵#129/120</t>
         </is>
       </c>
       <c r="F31" s="80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G31" s="81" t="inlineStr"/>
@@ -5948,35 +5976,71 @@
           <t>部分支持</t>
         </is>
       </c>
-      <c r="I31" s="80" t="inlineStr"/>
+      <c r="I31" s="80" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="81" customHeight="1" s="1">
+      <c r="A32" s="82" t="n"/>
+      <c r="B32" s="82" t="n"/>
+      <c r="C32" s="81" t="inlineStr">
+        <is>
+          <t>支持SD-WAN路径选择与链路质量监测（jitter/latency/loss）</t>
+        </is>
+      </c>
+      <c r="D32" s="81" t="inlineStr">
+        <is>
+          <t>抖动/延迟/丢包多维指标选路（天融信现仅延迟探测）</t>
+        </is>
+      </c>
+      <c r="E32" s="81" t="inlineStr">
+        <is>
+          <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路（PA Web帮助p195）；天融信有链路探测(ping)+智能选路(最小延迟优先)（天融信手册《策略路由》页），无jitter/latency/loss多维指标</t>
+        </is>
+      </c>
+      <c r="F32" s="80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G32" s="81" t="inlineStr"/>
+      <c r="H32" s="80" t="inlineStr">
+        <is>
+          <t>部分支持</t>
+        </is>
+      </c>
+      <c r="I32" s="80" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="B12:B13"/>
+  <mergeCells count="26">
+    <mergeCell ref="I18:I20"/>
     <mergeCell ref="I6:I11"/>
+    <mergeCell ref="G6:G12"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B5:B11"/>
-    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A2:A32"/>
+    <mergeCell ref="B26:B28"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="F27:F28"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="G6:G11"/>
-    <mergeCell ref="B20:B21"/>
     <mergeCell ref="B2:B4"/>
-    <mergeCell ref="A2:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G27:G28"/>
     <mergeCell ref="H8:H11"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="B5:B12"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="B31:B32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA替代需求列表.xlsx
+++ b/PA替代需求列表.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="261">
   <si>
     <t>一级需求</t>
   </si>
@@ -576,43 +576,43 @@
     <t>PA支持设备对象构建块（对应矩阵#3/4）；天融信经EDR联动上报终端资产并下发管控策略（天融信手册《与EDR联动》页），无独立设备对象</t>
   </si>
   <si>
+    <t>支持端口(L4)规则向应用(L7)规则迁移工作流</t>
+  </si>
+  <si>
+    <t>端口规则一键迁移为应用规则</t>
+  </si>
+  <si>
+    <t>PA策略优化器提供新应用查看器与端口→App-ID规则迁移工作流（PA Web帮助p142）；天融信策略统计仅显示规则命中数（天融信手册《配置访问控制策略》页），无迁移工具（命中统计能力已另列已支持行）；对应矩阵#132</t>
+  </si>
+  <si>
+    <t>支持应用匹配时强制校验标准端口</t>
+  </si>
+  <si>
+    <t>应用规则匹配时同时校验应用的标准端口，非标准端口流量不匹配</t>
+  </si>
+  <si>
+    <t>PA安全策略默认服务为application-default：放行应用同时强制其使用标准端口（如SSH仅22），非标准端口不匹配即拦截（PA管理指南p904）；天融信策略为五元组+应用识别组合（天融信手册《配置访问控制策略》页）；迁移评估项：直接转换若仅保留应用识别不限端口将扩大安全敞口，需制定应用标准端口映射限制（App-Default）转换方案；对应矩阵#2</t>
+  </si>
+  <si>
+    <t>支持将隐式默认规则显式化</t>
+  </si>
+  <si>
+    <t>同区域默认放行/跨区域默认拒绝的两条隐式系统规则可被提取为显式规则</t>
+  </si>
+  <si>
+    <t>PA安全策略库末尾自带两条隐式系统规则：区域内默认（同Zone默认放行）与区域间默认（跨Zone默认拒绝），可被替代配置，替代字段含日志转发配置文件与Log at Session End在会话结束时记录（PA Web帮助p134-136）；天融信未见同区域默认放行的隐式规则机制；迁移评估项：①必须提取intrazone-default同Zone互访需求并显式转换为放行规则，否则割接后同Zone不同网段/VLAN互访将被默认拦截；②需在新设备补齐底部兜底Deny-All并开启日志，否则被拒流量查无日志、排障困难</t>
+  </si>
+  <si>
+    <t>支持WildFire云沙箱文件检测联动</t>
+  </si>
+  <si>
+    <t>策略动作绑定WildFire配置文件</t>
+  </si>
+  <si>
+    <t>PA策略Actions可绑定WildFire Analysis配置文件（安全配置文件组含反病毒/漏洞/URL/文件阻断/WildFire，PA Web帮助p304；WildFire提交日志转发p305-306），云沙箱动态分析未知/零日威胁并秒级下发签名；天融信有内置APT沙箱（虚拟运行环境检测未知漏洞威胁）与沙箱联动（天融信手册《高级威胁防护》《APT联动配置》页），无云端动态分析与秒级签名下发证据；工作表1已登记云沙箱联动需求（不支持：公司无此产品），勿重复跟踪；迁移评估项：评估天融信本地APT沙箱与PA云沙箱检测能力等效性</t>
+  </si>
+  <si>
     <t>部分支持</t>
-  </si>
-  <si>
-    <t>支持端口(L4)规则向应用(L7)规则迁移工作流</t>
-  </si>
-  <si>
-    <t>端口规则一键迁移为应用规则</t>
-  </si>
-  <si>
-    <t>PA策略优化器提供新应用查看器与端口→App-ID规则迁移工作流（PA Web帮助p142）；天融信策略统计仅显示规则命中数（天融信手册《配置访问控制策略》页），无迁移工具（命中统计能力已另列已支持行）；对应矩阵#132</t>
-  </si>
-  <si>
-    <t>支持应用匹配时强制校验标准端口</t>
-  </si>
-  <si>
-    <t>应用规则匹配时同时校验应用的标准端口，非标准端口流量不匹配</t>
-  </si>
-  <si>
-    <t>PA安全策略默认服务为application-default：放行应用同时强制其使用标准端口（如SSH仅22），非标准端口不匹配即拦截（PA管理指南p904）；天融信策略为五元组+应用识别组合（天融信手册《配置访问控制策略》页）；迁移评估项：直接转换若仅保留应用识别不限端口将扩大安全敞口，需制定应用标准端口映射限制（App-Default）转换方案；对应矩阵#2</t>
-  </si>
-  <si>
-    <t>支持将隐式默认规则显式化</t>
-  </si>
-  <si>
-    <t>同区域默认放行/跨区域默认拒绝的两条隐式系统规则可被提取为显式规则</t>
-  </si>
-  <si>
-    <t>PA安全策略库末尾自带两条隐式系统规则：区域内默认（同Zone默认放行）与区域间默认（跨Zone默认拒绝），可被替代配置，替代字段含日志转发配置文件与Log at Session End在会话结束时记录（PA Web帮助p134-136）；天融信未见同区域默认放行的隐式规则机制；迁移评估项：①必须提取intrazone-default同Zone互访需求并显式转换为放行规则，否则割接后同Zone不同网段/VLAN互访将被默认拦截；②需在新设备补齐底部兜底Deny-All并开启日志，否则被拒流量查无日志、排障困难</t>
-  </si>
-  <si>
-    <t>支持WildFire云沙箱文件检测联动</t>
-  </si>
-  <si>
-    <t>策略动作绑定WildFire配置文件</t>
-  </si>
-  <si>
-    <t>PA策略Actions可绑定WildFire Analysis配置文件（安全配置文件组含反病毒/漏洞/URL/文件阻断/WildFire，PA Web帮助p304；WildFire提交日志转发p305-306），云沙箱动态分析未知/零日威胁并秒级下发签名；天融信有内置APT沙箱（虚拟运行环境检测未知漏洞威胁）与沙箱联动（天融信手册《高级威胁防护》《APT联动配置》页），无云端动态分析与秒级签名下发证据；工作表1已登记云沙箱联动需求（不支持：公司无此产品），勿重复跟踪；迁移评估项：评估天融信本地APT沙箱与PA云沙箱检测能力等效性</t>
   </si>
   <si>
     <t>支持配置源、目的域名</t>
@@ -1648,6 +1648,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1679,9 +1685,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1745,9 +1748,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2205,88 +2205,88 @@
     <col min="5" max="5" width="7.70909090909091" style="1" customWidth="1"/>
     <col min="6" max="6" width="37.8545454545455" style="1" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="9.70909090909091" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.70909090909091" style="10" customWidth="1"/>
+    <col min="8" max="8" width="9.70909090909091" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="12" t="s">
+      <c r="F1" s="15"/>
+      <c r="G1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="17" t="s">
+      <c r="D2" s="18"/>
+      <c r="E2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:8">
       <c r="A3" s="6"/>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:8">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="18" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="6"/>
@@ -2297,10 +2297,10 @@
     <row r="5" ht="36" customHeight="1" spans="1:8">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="7"/>
@@ -2310,35 +2310,35 @@
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:8">
       <c r="A6" s="6"/>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:8">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="6"/>
@@ -2349,10 +2349,10 @@
     <row r="8" ht="14.25" customHeight="1" spans="1:8">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="6"/>
@@ -2363,10 +2363,10 @@
     <row r="9" ht="14.25" customHeight="1" spans="1:8">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="6"/>
@@ -2377,10 +2377,10 @@
     <row r="10" ht="14.25" customHeight="1" spans="1:8">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="16"/>
+      <c r="D10" s="18"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -2389,10 +2389,10 @@
     <row r="11" ht="14.25" customHeight="1" spans="1:8">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="16"/>
+      <c r="D11" s="18"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -2401,10 +2401,10 @@
     <row r="12" ht="14.25" customHeight="1" spans="1:8">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="16"/>
+      <c r="D12" s="18"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -2412,58 +2412,58 @@
     </row>
     <row r="13" ht="28.5" customHeight="1" spans="1:8">
       <c r="A13" s="7"/>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A15" s="24"/>
+      <c r="A15" s="25"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="18" t="s">
         <v>43</v>
       </c>
       <c r="D15" s="6"/>
@@ -2473,9 +2473,9 @@
       <c r="H15" s="6"/>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A16" s="24"/>
+      <c r="A16" s="25"/>
       <c r="B16" s="6"/>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="18" t="s">
         <v>44</v>
       </c>
       <c r="D16" s="6"/>
@@ -2485,9 +2485,9 @@
       <c r="H16" s="6"/>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A17" s="24"/>
+      <c r="A17" s="25"/>
       <c r="B17" s="6"/>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="18" t="s">
         <v>45</v>
       </c>
       <c r="D17" s="6"/>
@@ -2497,9 +2497,9 @@
       <c r="H17" s="6"/>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A18" s="24"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="6"/>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="18" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="6"/>
@@ -2509,9 +2509,9 @@
       <c r="H18" s="6"/>
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A19" s="24"/>
+      <c r="A19" s="25"/>
       <c r="B19" s="6"/>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="18" t="s">
         <v>47</v>
       </c>
       <c r="D19" s="6"/>
@@ -2521,9 +2521,9 @@
       <c r="H19" s="6"/>
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A20" s="24"/>
+      <c r="A20" s="25"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="18" t="s">
         <v>48</v>
       </c>
       <c r="D20" s="6"/>
@@ -2533,9 +2533,9 @@
       <c r="H20" s="6"/>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A21" s="24"/>
+      <c r="A21" s="25"/>
       <c r="B21" s="6"/>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="18" t="s">
         <v>49</v>
       </c>
       <c r="D21" s="6"/>
@@ -2545,9 +2545,9 @@
       <c r="H21" s="6"/>
     </row>
     <row r="22" ht="32.25" customHeight="1" spans="1:8">
-      <c r="A22" s="25"/>
+      <c r="A22" s="26"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="18" t="s">
         <v>50</v>
       </c>
       <c r="D22" s="7"/>
@@ -2557,125 +2557,125 @@
       <c r="H22" s="7"/>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="26" t="s">
+      <c r="F23" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H23" s="19" t="s">
+      <c r="H23" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="27" t="s">
+      <c r="F24" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="19" t="s">
+      <c r="H24" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="19" t="s">
+      <c r="H25" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" s="9" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A26" s="24"/>
-      <c r="B26" s="21" t="s">
+    <row r="26" s="11" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
+      <c r="A26" s="25"/>
+      <c r="B26" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="28"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="19"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="8"/>
     </row>
     <row r="27" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A27" s="24"/>
-      <c r="B27" s="21" t="s">
+      <c r="A27" s="25"/>
+      <c r="B27" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="F27" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="16" t="s">
+      <c r="G27" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H27" s="19" t="s">
+      <c r="H27" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A28" s="24"/>
+      <c r="A28" s="25"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="18" t="s">
         <v>71</v>
       </c>
       <c r="D28" s="7"/>
@@ -2685,99 +2685,99 @@
       <c r="H28" s="7"/>
     </row>
     <row r="29" ht="60" customHeight="1" spans="1:8">
-      <c r="A29" s="24"/>
-      <c r="B29" s="21" t="s">
+      <c r="A29" s="25"/>
+      <c r="B29" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="30" t="s">
+      <c r="F29" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="G29" s="16" t="s">
+      <c r="G29" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H29" s="19" t="s">
+      <c r="H29" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A30" s="24"/>
+      <c r="A30" s="25"/>
       <c r="B30" s="6"/>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="6"/>
-      <c r="G30" s="16" t="s">
+      <c r="G30" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H30" s="19" t="s">
+      <c r="H30" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A31" s="25"/>
+      <c r="A31" s="26"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="31" t="s">
+      <c r="E31" s="32" t="s">
         <v>10</v>
       </c>
       <c r="F31" s="7"/>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="19" t="s">
+      <c r="H31" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="19" t="s">
+      <c r="H32" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A33" s="25"/>
+      <c r="A33" s="26"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="18" t="s">
         <v>84</v>
       </c>
       <c r="D33" s="7"/>
@@ -2787,99 +2787,99 @@
       <c r="H33" s="7"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="17" t="s">
+      <c r="D34" s="18"/>
+      <c r="E34" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="18" t="s">
+      <c r="F34" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H34" s="19" t="s">
+      <c r="H34" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A35" s="24"/>
+      <c r="A35" s="25"/>
       <c r="B35" s="6"/>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="16"/>
+      <c r="D35" s="18"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A36" s="24"/>
+      <c r="A36" s="25"/>
       <c r="B36" s="6"/>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="16"/>
+      <c r="D36" s="18"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A37" s="25"/>
+      <c r="A37" s="26"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="32" t="s">
+      <c r="C37" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="D37" s="32"/>
+      <c r="D37" s="33"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="33" t="s">
+      <c r="C38" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="D38" s="33"/>
-      <c r="E38" s="31" t="s">
+      <c r="D38" s="34"/>
+      <c r="E38" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="34" t="s">
+      <c r="F38" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="16" t="s">
+      <c r="G38" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H38" s="19" t="s">
+      <c r="H38" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" spans="1:8">
       <c r="A39" s="6"/>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="33" t="s">
+      <c r="C39" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="D39" s="33"/>
-      <c r="E39" s="31" t="s">
+      <c r="D39" s="34"/>
+      <c r="E39" s="32" t="s">
         <v>60</v>
       </c>
       <c r="F39" s="7"/>
@@ -2888,176 +2888,176 @@
     </row>
     <row r="40" ht="28.5" customHeight="1" spans="1:8">
       <c r="A40" s="6"/>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="33" t="s">
+      <c r="C40" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="D40" s="35" t="s">
+      <c r="D40" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="31" t="s">
+      <c r="E40" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="30" t="s">
+      <c r="F40" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="G40" s="16" t="s">
+      <c r="G40" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H40" s="19" t="s">
+      <c r="H40" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" spans="1:8">
       <c r="A41" s="6"/>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D41" s="33" t="s">
+      <c r="D41" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E41" s="31" t="s">
+      <c r="E41" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="F41" s="30" t="s">
+      <c r="F41" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="G41" s="16" t="s">
+      <c r="G41" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="H41" s="19" t="s">
+      <c r="H41" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:8">
       <c r="A42" s="6"/>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="33"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="19"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="8"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:8">
       <c r="A43" s="7"/>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="33" t="s">
+      <c r="C43" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="33"/>
-      <c r="E43" s="31" t="s">
+      <c r="D43" s="34"/>
+      <c r="E43" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="F43" s="30" t="s">
+      <c r="F43" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="G43" s="16" t="s">
+      <c r="G43" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="H43" s="19" t="s">
+      <c r="H43" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A44" s="36" t="s">
+      <c r="A44" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="37" t="s">
+      <c r="B44" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C44" s="38" t="s">
+      <c r="C44" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="38" t="s">
+      <c r="D44" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="E44" s="39" t="s">
+      <c r="E44" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="40" t="s">
+      <c r="F44" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="G44" s="41" t="s">
+      <c r="G44" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="H44" s="42" t="s">
+      <c r="H44" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A45" s="24"/>
+      <c r="A45" s="25"/>
       <c r="B45" s="6"/>
-      <c r="C45" s="33" t="s">
+      <c r="C45" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="D45" s="33" t="s">
+      <c r="D45" s="34" t="s">
         <v>116</v>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="G45" s="16" t="s">
+      <c r="G45" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="19" t="s">
+      <c r="H45" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A46" s="24"/>
+      <c r="A46" s="25"/>
       <c r="B46" s="6"/>
-      <c r="C46" s="33" t="s">
+      <c r="C46" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="D46" s="33"/>
+      <c r="D46" s="34"/>
       <c r="E46" s="6"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
     </row>
     <row r="47" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A47" s="24"/>
+      <c r="A47" s="25"/>
       <c r="B47" s="6"/>
-      <c r="C47" s="33" t="s">
+      <c r="C47" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="D47" s="33"/>
+      <c r="D47" s="34"/>
       <c r="E47" s="6"/>
       <c r="F47" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="G47" s="16" t="s">
+      <c r="G47" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H47" s="19" t="s">
+      <c r="H47" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A48" s="25"/>
+      <c r="A48" s="26"/>
       <c r="B48" s="7"/>
       <c r="C48" s="44" t="s">
         <v>119</v>
       </c>
       <c r="D48" s="44"/>
       <c r="E48" s="7"/>
-      <c r="F48" s="26" t="s">
+      <c r="F48" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="G48" s="32" t="s">
+      <c r="G48" s="33" t="s">
         <v>12</v>
       </c>
       <c r="H48" s="45" t="s">
@@ -3145,122 +3145,122 @@
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A53" s="37" t="s">
+      <c r="A53" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="B53" s="37" t="s">
+      <c r="B53" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="C53" s="38" t="s">
+      <c r="C53" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="D53" s="38"/>
-      <c r="E53" s="39" t="s">
+      <c r="D53" s="39"/>
+      <c r="E53" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="F53" s="40" t="s">
+      <c r="F53" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="G53" s="41" t="s">
+      <c r="G53" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H53" s="42" t="s">
+      <c r="H53" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="54" ht="28.5" customHeight="1" spans="1:8">
       <c r="A54" s="7"/>
-      <c r="B54" s="21" t="s">
+      <c r="B54" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D54" s="35" t="s">
+      <c r="D54" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="E54" s="31" t="s">
+      <c r="E54" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="F54" s="30" t="s">
+      <c r="F54" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="G54" s="16" t="s">
+      <c r="G54" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="H54" s="19" t="s">
+      <c r="H54" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A55" s="22" t="s">
+      <c r="A55" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="B55" s="21" t="s">
+      <c r="B55" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="C55" s="33" t="s">
+      <c r="C55" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="D55" s="33"/>
-      <c r="E55" s="31" t="s">
+      <c r="D55" s="34"/>
+      <c r="E55" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="F55" s="30"/>
-      <c r="G55" s="16" t="s">
+      <c r="F55" s="31"/>
+      <c r="G55" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="H55" s="19" t="s">
+      <c r="H55" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="56" ht="42.75" customHeight="1" spans="1:8">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="B56" s="21" t="s">
+      <c r="B56" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="C56" s="33" t="s">
+      <c r="C56" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="D56" s="35" t="s">
+      <c r="D56" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="E56" s="31" t="s">
+      <c r="E56" s="32" t="s">
         <v>40</v>
       </c>
       <c r="F56" s="43" t="s">
         <v>145</v>
       </c>
-      <c r="G56" s="16"/>
-      <c r="H56" s="19" t="s">
+      <c r="G56" s="18"/>
+      <c r="H56" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="57" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A57" s="21" t="s">
+      <c r="A57" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="C57" s="33" t="s">
+      <c r="C57" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="33" t="s">
+      <c r="D57" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="E57" s="31" t="s">
+      <c r="E57" s="32" t="s">
         <v>60</v>
       </c>
       <c r="F57" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="G57" s="16" t="s">
+      <c r="G57" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="H57" s="19" t="s">
+      <c r="H57" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       <c r="B58" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="C58" s="32" t="s">
+      <c r="C58" s="33" t="s">
         <v>151</v>
       </c>
       <c r="D58" s="44" t="s">
@@ -3283,7 +3283,7 @@
       <c r="F58" s="63" t="s">
         <v>153</v>
       </c>
-      <c r="G58" s="32" t="s">
+      <c r="G58" s="33" t="s">
         <v>103</v>
       </c>
       <c r="H58" s="45" t="s">
@@ -3305,7 +3305,7 @@
         <v>10</v>
       </c>
       <c r="F59" s="56"/>
-      <c r="G59" s="32" t="s">
+      <c r="G59" s="33" t="s">
         <v>103</v>
       </c>
       <c r="H59" s="57" t="s">
@@ -3496,7 +3496,7 @@
         <v>172</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>109</v>
@@ -3521,7 +3521,7 @@
         <v>60</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>162</v>
@@ -3531,13 +3531,13 @@
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>178</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>179</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>10</v>
@@ -3551,13 +3551,13 @@
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>182</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>40</v>
@@ -3569,16 +3569,16 @@
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>40</v>
+      <c r="F9" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
@@ -3587,17 +3587,19 @@
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="4" t="s">
-        <v>176</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>13</v>
@@ -3606,15 +3608,15 @@
     <row r="11" ht="56" customHeight="1" spans="1:8">
       <c r="A11" s="6"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8" t="s">
+      <c r="D11" s="10"/>
+      <c r="E11" s="10" t="s">
         <v>190</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>109</v>
@@ -3687,7 +3689,7 @@
         <v>60</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>162</v>
@@ -4043,7 +4045,7 @@
         <v>40</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>13</v>
@@ -4065,14 +4067,14 @@
         <v>10</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>162</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
     <mergeCell ref="A2:A31"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B11"/>
@@ -4084,7 +4086,6 @@
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F9:F10"/>
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="G3:G4"/>

--- a/PA替代需求列表.xlsx
+++ b/PA替代需求列表.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\zt\ggz\研发部\3.7项目\需求分析\PA-替代需求\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="18390" activeTab="1"/>
+    <workbookView windowHeight="15880" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="258">
   <si>
     <t>一级需求</t>
   </si>
@@ -622,15 +617,6 @@
   </si>
   <si>
     <t>NAT策略</t>
-  </si>
-  <si>
-    <t>支持NAT后目的区域路由回查匹配（Dest Zone by route lookup）</t>
-  </si>
-  <si>
-    <t>目的区域按NAT后路由查找；源/目的地址用NAT前值</t>
-  </si>
-  <si>
-    <t>PA底层为『先NAT判断后安全策略匹配』的因果倒置：安全策略要求源区域(NAT前)+源地址(NAT前)+目的地址(NAT前)+目的区域(NAT后按路由查找)，极其反直觉；天融信地址转换为独立策略库常规直观映射（安全策略&gt;地址转换，天融信手册《服务器映射》页）；迁移评估项：带目的NAT的策略平移后易因Zone填写错误不通，需制定NAT查表逻辑转换映射规范；对应矩阵#9</t>
   </si>
   <si>
     <t>支持NAT规则主动/主动HA绑定（Active/Active HA Binding）</t>
@@ -1629,7 +1615,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1656,6 +1642,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1892,7 +1884,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6799580" y="6399530"/>
+          <a:off x="6471920" y="6399530"/>
           <a:ext cx="2200275" cy="349885"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1915,7 +1907,7 @@
                   <a:alpha val="19999"/>
                 </a:srgbClr>
               </a:solidFill>
-              <a:latin typeface="Arial" panose="020B0604020202020204"/>
+              <a:latin typeface="Arial" panose="020B0604020202090204"/>
               <a:ea typeface="宋体" panose="02010600030101010101" pitchFamily="7" charset="-122"/>
             </a:rPr>
             <a:t>AI 生成</a:t>
@@ -1926,7 +1918,7 @@
                 <a:alpha val="19999"/>
               </a:srgbClr>
             </a:solidFill>
-            <a:latin typeface="Arial" panose="020B0604020202020204"/>
+            <a:latin typeface="Arial" panose="020B0604020202090204"/>
             <a:ea typeface="宋体" panose="02010600030101010101" pitchFamily="7" charset="-122"/>
           </a:endParaRPr>
         </a:p>
@@ -2196,60 +2188,60 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="11.7090909090909" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7090909090909" style="1" customWidth="1"/>
-    <col min="3" max="3" width="54.7090909090909" style="1" customWidth="1"/>
-    <col min="4" max="4" width="45.2909090909091" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.70909090909091" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.8545454545455" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.70909090909091" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.70909090909091" style="12" customWidth="1"/>
+    <col min="1" max="1" width="11.7115384615385" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7115384615385" style="1" customWidth="1"/>
+    <col min="3" max="3" width="54.7115384615385" style="1" customWidth="1"/>
+    <col min="4" max="4" width="45.2884615384615" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.71153846153846" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37.8557692307692" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.71153846153846" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.71153846153846" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15"/>
-      <c r="G1" s="14" t="s">
+      <c r="F1" s="17"/>
+      <c r="G1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="19" t="s">
+      <c r="D2" s="20"/>
+      <c r="E2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="8" t="s">
@@ -2258,22 +2250,22 @@
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:8">
       <c r="A3" s="6"/>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="20" t="s">
         <v>18</v>
       </c>
       <c r="H3" s="8" t="s">
@@ -2283,10 +2275,10 @@
     <row r="4" ht="36" customHeight="1" spans="1:8">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="20" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="6"/>
@@ -2297,10 +2289,10 @@
     <row r="5" ht="36" customHeight="1" spans="1:8">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="20" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="7"/>
@@ -2310,22 +2302,22 @@
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:8">
       <c r="A6" s="6"/>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -2335,10 +2327,10 @@
     <row r="7" ht="14.25" customHeight="1" spans="1:8">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="20" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="6"/>
@@ -2349,10 +2341,10 @@
     <row r="8" ht="14.25" customHeight="1" spans="1:8">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="20" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="6"/>
@@ -2363,10 +2355,10 @@
     <row r="9" ht="14.25" customHeight="1" spans="1:8">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="20" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="6"/>
@@ -2377,10 +2369,10 @@
     <row r="10" ht="14.25" customHeight="1" spans="1:8">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="18"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -2389,10 +2381,10 @@
     <row r="11" ht="14.25" customHeight="1" spans="1:8">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="18"/>
+      <c r="D11" s="20"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -2401,10 +2393,10 @@
     <row r="12" ht="14.25" customHeight="1" spans="1:8">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="18"/>
+      <c r="D12" s="20"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -2412,22 +2404,22 @@
     </row>
     <row r="13" ht="28.5" customHeight="1" spans="1:8">
       <c r="A13" s="7"/>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="20" t="s">
         <v>35</v>
       </c>
       <c r="H13" s="8" t="s">
@@ -2435,25 +2427,25 @@
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="20" t="s">
         <v>38</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="20" t="s">
         <v>42</v>
       </c>
       <c r="H14" s="8" t="s">
@@ -2461,9 +2453,9 @@
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A15" s="25"/>
+      <c r="A15" s="27"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="20" t="s">
         <v>43</v>
       </c>
       <c r="D15" s="6"/>
@@ -2473,9 +2465,9 @@
       <c r="H15" s="6"/>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A16" s="25"/>
+      <c r="A16" s="27"/>
       <c r="B16" s="6"/>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="20" t="s">
         <v>44</v>
       </c>
       <c r="D16" s="6"/>
@@ -2485,9 +2477,9 @@
       <c r="H16" s="6"/>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A17" s="25"/>
+      <c r="A17" s="27"/>
       <c r="B17" s="6"/>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="20" t="s">
         <v>45</v>
       </c>
       <c r="D17" s="6"/>
@@ -2497,9 +2489,9 @@
       <c r="H17" s="6"/>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A18" s="25"/>
+      <c r="A18" s="27"/>
       <c r="B18" s="6"/>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="20" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="6"/>
@@ -2509,9 +2501,9 @@
       <c r="H18" s="6"/>
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A19" s="25"/>
+      <c r="A19" s="27"/>
       <c r="B19" s="6"/>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="20" t="s">
         <v>47</v>
       </c>
       <c r="D19" s="6"/>
@@ -2521,9 +2513,9 @@
       <c r="H19" s="6"/>
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A20" s="25"/>
+      <c r="A20" s="27"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="20" t="s">
         <v>48</v>
       </c>
       <c r="D20" s="6"/>
@@ -2533,9 +2525,9 @@
       <c r="H20" s="6"/>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A21" s="25"/>
+      <c r="A21" s="27"/>
       <c r="B21" s="6"/>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="20" t="s">
         <v>49</v>
       </c>
       <c r="D21" s="6"/>
@@ -2545,9 +2537,9 @@
       <c r="H21" s="6"/>
     </row>
     <row r="22" ht="32.25" customHeight="1" spans="1:8">
-      <c r="A22" s="26"/>
+      <c r="A22" s="28"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="20" t="s">
         <v>50</v>
       </c>
       <c r="D22" s="7"/>
@@ -2557,25 +2549,25 @@
       <c r="H22" s="7"/>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="27" t="s">
+      <c r="F23" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H23" s="8" t="s">
@@ -2583,25 +2575,25 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="28" t="s">
+      <c r="F24" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H24" s="8" t="s">
@@ -2609,63 +2601,63 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="F25" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" s="11" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A26" s="25"/>
-      <c r="B26" s="22" t="s">
+    <row r="26" s="13" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
+      <c r="A26" s="27"/>
+      <c r="B26" s="24" t="s">
         <v>66</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="29"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="18"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="20"/>
       <c r="H26" s="8"/>
     </row>
     <row r="27" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A27" s="25"/>
-      <c r="B27" s="22" t="s">
+      <c r="A27" s="27"/>
+      <c r="B27" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="F27" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H27" s="8" t="s">
@@ -2673,9 +2665,9 @@
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A28" s="25"/>
+      <c r="A28" s="27"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="20" t="s">
         <v>71</v>
       </c>
       <c r="D28" s="7"/>
@@ -2685,23 +2677,23 @@
       <c r="H28" s="7"/>
     </row>
     <row r="29" ht="60" customHeight="1" spans="1:8">
-      <c r="A29" s="25"/>
-      <c r="B29" s="22" t="s">
+      <c r="A29" s="27"/>
+      <c r="B29" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="20" t="s">
         <v>73</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="31" t="s">
+      <c r="F29" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="G29" s="18" t="s">
+      <c r="G29" s="20" t="s">
         <v>35</v>
       </c>
       <c r="H29" s="8" t="s">
@@ -2709,19 +2701,19 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A30" s="25"/>
+      <c r="A30" s="27"/>
       <c r="B30" s="6"/>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="21" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="6"/>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H30" s="8" t="s">
@@ -2729,19 +2721,19 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A31" s="26"/>
+      <c r="A31" s="28"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F31" s="7"/>
-      <c r="G31" s="18" t="s">
+      <c r="G31" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H31" s="8" t="s">
@@ -2749,25 +2741,25 @@
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="F32" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H32" s="8" t="s">
@@ -2775,9 +2767,9 @@
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A33" s="26"/>
+      <c r="A33" s="28"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="20" t="s">
         <v>84</v>
       </c>
       <c r="D33" s="7"/>
@@ -2787,23 +2779,23 @@
       <c r="H33" s="7"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="18"/>
-      <c r="E34" s="19" t="s">
+      <c r="D34" s="20"/>
+      <c r="E34" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="F34" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="G34" s="18" t="s">
+      <c r="G34" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H34" s="8" t="s">
@@ -2811,59 +2803,59 @@
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A35" s="25"/>
+      <c r="A35" s="27"/>
       <c r="B35" s="6"/>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="18"/>
+      <c r="D35" s="20"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A36" s="25"/>
+      <c r="A36" s="27"/>
       <c r="B36" s="6"/>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="18"/>
+      <c r="D36" s="20"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A37" s="26"/>
+      <c r="A37" s="28"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="33" t="s">
+      <c r="C37" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="D37" s="33"/>
+      <c r="D37" s="35"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="22" t="s">
+      <c r="B38" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="34" t="s">
+      <c r="C38" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="D38" s="34"/>
-      <c r="E38" s="32" t="s">
+      <c r="D38" s="36"/>
+      <c r="E38" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="35" t="s">
+      <c r="F38" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="18" t="s">
+      <c r="G38" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H38" s="8" t="s">
@@ -2872,14 +2864,14 @@
     </row>
     <row r="39" ht="15.75" customHeight="1" spans="1:8">
       <c r="A39" s="6"/>
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C39" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="D39" s="34"/>
-      <c r="E39" s="32" t="s">
+      <c r="D39" s="36"/>
+      <c r="E39" s="34" t="s">
         <v>60</v>
       </c>
       <c r="F39" s="7"/>
@@ -2888,22 +2880,22 @@
     </row>
     <row r="40" ht="28.5" customHeight="1" spans="1:8">
       <c r="A40" s="6"/>
-      <c r="B40" s="22" t="s">
+      <c r="B40" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="34" t="s">
+      <c r="C40" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="32" t="s">
+      <c r="E40" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="31" t="s">
+      <c r="F40" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="G40" s="18" t="s">
+      <c r="G40" s="20" t="s">
         <v>35</v>
       </c>
       <c r="H40" s="8" t="s">
@@ -2912,22 +2904,22 @@
     </row>
     <row r="41" ht="15.75" customHeight="1" spans="1:8">
       <c r="A41" s="6"/>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D41" s="34" t="s">
+      <c r="D41" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="E41" s="32" t="s">
+      <c r="E41" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F41" s="31" t="s">
+      <c r="F41" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="G41" s="18" t="s">
+      <c r="G41" s="20" t="s">
         <v>103</v>
       </c>
       <c r="H41" s="8" t="s">
@@ -2936,34 +2928,34 @@
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:8">
       <c r="A42" s="6"/>
-      <c r="B42" s="22" t="s">
+      <c r="B42" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="34"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="18"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="20"/>
       <c r="H42" s="8"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:8">
       <c r="A43" s="7"/>
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="34" t="s">
+      <c r="C43" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="34"/>
-      <c r="E43" s="32" t="s">
+      <c r="D43" s="36"/>
+      <c r="E43" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F43" s="31" t="s">
+      <c r="F43" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="G43" s="18" t="s">
+      <c r="G43" s="20" t="s">
         <v>109</v>
       </c>
       <c r="H43" s="8" t="s">
@@ -2971,25 +2963,25 @@
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A44" s="37" t="s">
+      <c r="A44" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="38" t="s">
+      <c r="B44" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="C44" s="39" t="s">
+      <c r="C44" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="39" t="s">
+      <c r="D44" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="E44" s="40" t="s">
+      <c r="E44" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="41" t="s">
+      <c r="F44" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G44" s="42" t="s">
+      <c r="G44" s="44" t="s">
         <v>35</v>
       </c>
       <c r="H44" s="9" t="s">
@@ -2997,19 +2989,19 @@
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A45" s="25"/>
+      <c r="A45" s="27"/>
       <c r="B45" s="6"/>
-      <c r="C45" s="34" t="s">
+      <c r="C45" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="D45" s="34" t="s">
+      <c r="D45" s="36" t="s">
         <v>116</v>
       </c>
       <c r="E45" s="6"/>
-      <c r="F45" s="43" t="s">
+      <c r="F45" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="G45" s="18" t="s">
+      <c r="G45" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H45" s="8" t="s">
@@ -3017,29 +3009,29 @@
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A46" s="25"/>
+      <c r="A46" s="27"/>
       <c r="B46" s="6"/>
-      <c r="C46" s="34" t="s">
+      <c r="C46" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="D46" s="34"/>
+      <c r="D46" s="36"/>
       <c r="E46" s="6"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
     </row>
     <row r="47" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A47" s="25"/>
+      <c r="A47" s="27"/>
       <c r="B47" s="6"/>
-      <c r="C47" s="34" t="s">
+      <c r="C47" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="D47" s="34"/>
+      <c r="D47" s="36"/>
       <c r="E47" s="6"/>
-      <c r="F47" s="43" t="s">
+      <c r="F47" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="G47" s="18" t="s">
+      <c r="G47" s="20" t="s">
         <v>12</v>
       </c>
       <c r="H47" s="8" t="s">
@@ -3047,121 +3039,121 @@
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A48" s="26"/>
+      <c r="A48" s="28"/>
       <c r="B48" s="7"/>
-      <c r="C48" s="44" t="s">
+      <c r="C48" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="D48" s="44"/>
+      <c r="D48" s="46"/>
       <c r="E48" s="7"/>
-      <c r="F48" s="27" t="s">
+      <c r="F48" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="G48" s="33" t="s">
+      <c r="G48" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="H48" s="45" t="s">
+      <c r="H48" s="47" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="49" ht="42.75" customHeight="1" spans="1:8">
-      <c r="A49" s="46" t="s">
+      <c r="A49" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="B49" s="46" t="s">
+      <c r="B49" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="C49" s="47" t="s">
+      <c r="C49" s="49" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="48" t="s">
+      <c r="D49" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="E49" s="49" t="s">
+      <c r="E49" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="50"/>
-      <c r="G49" s="51" t="s">
+      <c r="F49" s="52"/>
+      <c r="G49" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="H49" s="52"/>
+      <c r="H49" s="54"/>
     </row>
     <row r="50" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A50" s="53"/>
-      <c r="B50" s="53"/>
-      <c r="C50" s="47" t="s">
+      <c r="A50" s="55"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="D50" s="54" t="s">
+      <c r="D50" s="56" t="s">
         <v>124</v>
       </c>
-      <c r="E50" s="55" t="s">
+      <c r="E50" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="F50" s="56"/>
-      <c r="G50" s="51" t="s">
+      <c r="F50" s="58"/>
+      <c r="G50" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="H50" s="57"/>
+      <c r="H50" s="59"/>
     </row>
     <row r="51" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A51" s="53"/>
-      <c r="B51" s="53"/>
-      <c r="C51" s="47" t="s">
+      <c r="A51" s="55"/>
+      <c r="B51" s="55"/>
+      <c r="C51" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="D51" s="58" t="s">
+      <c r="D51" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="E51" s="55" t="s">
+      <c r="E51" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="F51" s="50"/>
-      <c r="G51" s="51" t="s">
+      <c r="F51" s="52"/>
+      <c r="G51" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="H51" s="52"/>
+      <c r="H51" s="54"/>
     </row>
     <row r="52" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A52" s="59"/>
-      <c r="B52" s="59"/>
-      <c r="C52" s="58" t="s">
+      <c r="A52" s="61"/>
+      <c r="B52" s="61"/>
+      <c r="C52" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="D52" s="48" t="s">
+      <c r="D52" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="E52" s="60" t="s">
+      <c r="E52" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="50" t="s">
+      <c r="F52" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="G52" s="51" t="s">
+      <c r="G52" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="H52" s="52" t="s">
+      <c r="H52" s="54" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A53" s="38" t="s">
+      <c r="A53" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="B53" s="38" t="s">
+      <c r="B53" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="C53" s="39" t="s">
+      <c r="C53" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="D53" s="39"/>
-      <c r="E53" s="40" t="s">
+      <c r="D53" s="41"/>
+      <c r="E53" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="F53" s="41" t="s">
+      <c r="F53" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="G53" s="42" t="s">
+      <c r="G53" s="44" t="s">
         <v>12</v>
       </c>
       <c r="H53" s="9" t="s">
@@ -3170,22 +3162,22 @@
     </row>
     <row r="54" ht="28.5" customHeight="1" spans="1:8">
       <c r="A54" s="7"/>
-      <c r="B54" s="22" t="s">
+      <c r="B54" s="24" t="s">
         <v>133</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D54" s="36" t="s">
+      <c r="D54" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="E54" s="32" t="s">
+      <c r="E54" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F54" s="31" t="s">
+      <c r="F54" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="G54" s="18" t="s">
+      <c r="G54" s="20" t="s">
         <v>103</v>
       </c>
       <c r="H54" s="8" t="s">
@@ -3193,21 +3185,21 @@
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A55" s="23" t="s">
+      <c r="A55" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="B55" s="22" t="s">
+      <c r="B55" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="C55" s="34" t="s">
+      <c r="C55" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D55" s="34"/>
-      <c r="E55" s="32" t="s">
+      <c r="D55" s="36"/>
+      <c r="E55" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F55" s="31"/>
-      <c r="G55" s="18" t="s">
+      <c r="F55" s="33"/>
+      <c r="G55" s="20" t="s">
         <v>140</v>
       </c>
       <c r="H55" s="8" t="s">
@@ -3215,49 +3207,49 @@
       </c>
     </row>
     <row r="56" ht="42.75" customHeight="1" spans="1:8">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B56" s="22" t="s">
+      <c r="B56" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="C56" s="34" t="s">
+      <c r="C56" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="D56" s="36" t="s">
+      <c r="D56" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="E56" s="32" t="s">
+      <c r="E56" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="F56" s="43" t="s">
+      <c r="F56" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="G56" s="18"/>
+      <c r="G56" s="20"/>
       <c r="H56" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="57" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="B57" s="22" t="s">
+      <c r="B57" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="C57" s="34" t="s">
+      <c r="C57" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="34" t="s">
+      <c r="D57" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="E57" s="32" t="s">
+      <c r="E57" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F57" s="43" t="s">
+      <c r="F57" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="G57" s="18" t="s">
+      <c r="G57" s="20" t="s">
         <v>103</v>
       </c>
       <c r="H57" s="8" t="s">
@@ -3265,50 +3257,50 @@
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A58" s="61" t="s">
+      <c r="A58" s="63" t="s">
         <v>150</v>
       </c>
-      <c r="B58" s="61" t="s">
+      <c r="B58" s="63" t="s">
         <v>150</v>
       </c>
-      <c r="C58" s="33" t="s">
+      <c r="C58" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="D58" s="44" t="s">
+      <c r="D58" s="46" t="s">
         <v>152</v>
       </c>
-      <c r="E58" s="62" t="s">
+      <c r="E58" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="F58" s="63" t="s">
+      <c r="F58" s="65" t="s">
         <v>153</v>
       </c>
-      <c r="G58" s="33" t="s">
+      <c r="G58" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="H58" s="45" t="s">
+      <c r="H58" s="47" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="59" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A59" s="46" t="s">
+      <c r="A59" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="B59" s="46" t="s">
+      <c r="B59" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="C59" s="64" t="s">
+      <c r="C59" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="D59" s="56"/>
-      <c r="E59" s="60" t="s">
+      <c r="D59" s="58"/>
+      <c r="E59" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="F59" s="56"/>
-      <c r="G59" s="33" t="s">
+      <c r="F59" s="58"/>
+      <c r="G59" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="H59" s="57" t="s">
+      <c r="H59" s="59" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3379,16 +3371,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="11.7" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7019230769231" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7019230769231" style="1" customWidth="1"/>
     <col min="3" max="3" width="40" style="1" customWidth="1"/>
-    <col min="4" max="4" width="41.4545454545455" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.4519230769231" style="1" customWidth="1"/>
     <col min="5" max="5" width="62" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.7" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.70192307692308" style="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.70192307692308" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8">
@@ -3625,9 +3617,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="126" customHeight="1" spans="1:8">
+    <row r="12" ht="81" customHeight="1" spans="1:8">
       <c r="A12" s="6"/>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="11" t="s">
         <v>191</v>
       </c>
       <c r="C12" s="5" t="s">
@@ -3640,10 +3632,10 @@
         <v>194</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>162</v>
@@ -3651,39 +3643,29 @@
     </row>
     <row r="13" ht="81" customHeight="1" spans="1:8">
       <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
+      <c r="B13" s="12"/>
       <c r="C13" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>162</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" ht="96" customHeight="1" spans="1:8">
       <c r="A14" s="6"/>
       <c r="B14" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>198</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>60</v>
@@ -3698,16 +3680,16 @@
     <row r="15" ht="111" customHeight="1" spans="1:8">
       <c r="A15" s="6"/>
       <c r="B15" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>40</v>
@@ -3722,16 +3704,16 @@
     <row r="16" ht="51" customHeight="1" spans="1:8">
       <c r="A16" s="6"/>
       <c r="B16" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>10</v>
@@ -3747,13 +3729,13 @@
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>40</v>
@@ -3769,13 +3751,13 @@
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>10</v>
@@ -3789,13 +3771,13 @@
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -3804,16 +3786,16 @@
     <row r="20" ht="111" customHeight="1" spans="1:8">
       <c r="A20" s="6"/>
       <c r="B20" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>222</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>40</v>
@@ -3829,13 +3811,13 @@
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>10</v>
@@ -3850,16 +3832,16 @@
     <row r="22" ht="96" customHeight="1" spans="1:8">
       <c r="A22" s="6"/>
       <c r="B22" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>226</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>229</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>40</v>
@@ -3875,13 +3857,13 @@
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>10</v>
@@ -3896,16 +3878,16 @@
     <row r="24" ht="96" customHeight="1" spans="1:8">
       <c r="A24" s="6"/>
       <c r="B24" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>233</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>236</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>40</v>
@@ -3920,16 +3902,16 @@
     <row r="25" ht="81" customHeight="1" spans="1:8">
       <c r="A25" s="6"/>
       <c r="B25" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>240</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>10</v>
@@ -3945,13 +3927,13 @@
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>10</v>
@@ -3967,13 +3949,13 @@
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="4" t="s">
@@ -3984,16 +3966,16 @@
     <row r="28" ht="171" customHeight="1" spans="1:8">
       <c r="A28" s="6"/>
       <c r="B28" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>250</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>10</v>
@@ -4009,13 +3991,13 @@
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>10</v>
@@ -4030,16 +4012,16 @@
     <row r="30" ht="81" customHeight="1" spans="1:8">
       <c r="A30" s="6"/>
       <c r="B30" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>254</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>257</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>40</v>
@@ -4055,13 +4037,13 @@
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>10</v>
@@ -4074,11 +4056,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
     <mergeCell ref="A2:A31"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B11"/>
-    <mergeCell ref="B12:B13"/>
     <mergeCell ref="B16:B19"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="B22:B23"/>

--- a/PA替代需求列表.xlsx
+++ b/PA替代需求列表.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
-    <sheet name="策略需求差异" sheetId="3" r:id="rId2"/>
+    <sheet name="策略需求差异" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="259">
   <si>
     <t>一级需求</t>
   </si>
@@ -619,13 +619,16 @@
     <t>NAT策略</t>
   </si>
   <si>
-    <t>支持NAT规则主动/主动HA绑定（Active/Active HA Binding）</t>
-  </si>
-  <si>
-    <t>主动/主动HA下NAT规则绑定会话所有者</t>
-  </si>
-  <si>
-    <t>PA主动/主动HA配置下NAT规则可绑定会话所有者/会话设置，控制NAT会话的设备绑定，仅A/A模式可见（PA Web帮助p150）；天融信HA为主备双机热备模式（天融信手册《配置双机热备功能》页），无主动/主动模式及NAT规则绑定机制</t>
+    <t>支持双活HA下的NAT规则会话绑定</t>
+  </si>
+  <si>
+    <t>双活HA模式下，NAT规则可绑定会话所有者并指定会话设置，控制NAT会话归属设备</t>
+  </si>
+  <si>
+    <t>PA双活（Active/Active）HA配置下NAT规则可绑定会话所有者/会话设置，控制NAT会话的设备绑定，仅A/A模式可见（PA Web帮助p150）；天融信HA为主备双机热备模式（天融信手册《配置双机热备功能》页），无双活模式及NAT规则绑定机制</t>
+  </si>
+  <si>
+    <t>平台</t>
   </si>
   <si>
     <t>QoS策略</t>
@@ -1615,7 +1618,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1643,10 +1646,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1867,13 +1867,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>784010</xdr:colOff>
+      <xdr:colOff>1111670</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>18250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2984010</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>320820</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>187275</xdr:rowOff>
     </xdr:to>
@@ -1884,7 +1884,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6471920" y="6399530"/>
+          <a:off x="6799580" y="6399530"/>
           <a:ext cx="2200275" cy="349885"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1908,7 +1908,7 @@
                 </a:srgbClr>
               </a:solidFill>
               <a:latin typeface="Arial" panose="020B0604020202090204"/>
-              <a:ea typeface="宋体" panose="02010600030101010101" pitchFamily="7" charset="-122"/>
+              <a:ea typeface="宋体"/>
             </a:rPr>
             <a:t>AI 生成</a:t>
           </a:r>
@@ -1919,7 +1919,74 @@
               </a:srgbClr>
             </a:solidFill>
             <a:latin typeface="Arial" panose="020B0604020202090204"/>
-            <a:ea typeface="宋体" panose="02010600030101010101" pitchFamily="7" charset="-122"/>
+            <a:ea typeface="宋体"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2084490</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>469100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1547005</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>819100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6799580" y="6399530"/>
+          <a:ext cx="2200275" cy="349885"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202090204"/>
+              <a:ea typeface="宋体"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" sz="1600" dirty="0">
+            <a:solidFill>
+              <a:srgbClr val="808080">
+                <a:alpha val="19999"/>
+              </a:srgbClr>
+            </a:solidFill>
+            <a:latin typeface="Arial" panose="020B0604020202090204"/>
+            <a:ea typeface="宋体"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2197,51 +2264,51 @@
     <col min="5" max="5" width="7.71153846153846" style="1" customWidth="1"/>
     <col min="6" max="6" width="37.8557692307692" style="1" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="9.71153846153846" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.71153846153846" style="14" customWidth="1"/>
+    <col min="8" max="8" width="9.71153846153846" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="16" t="s">
+      <c r="F1" s="16"/>
+      <c r="G1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="21" t="s">
+      <c r="D2" s="19"/>
+      <c r="E2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="19" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="8" t="s">
@@ -2250,22 +2317,22 @@
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:8">
       <c r="A3" s="6"/>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="19" t="s">
         <v>18</v>
       </c>
       <c r="H3" s="8" t="s">
@@ -2275,10 +2342,10 @@
     <row r="4" ht="36" customHeight="1" spans="1:8">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="19" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="6"/>
@@ -2289,10 +2356,10 @@
     <row r="5" ht="36" customHeight="1" spans="1:8">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="19" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="7"/>
@@ -2302,22 +2369,22 @@
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:8">
       <c r="A6" s="6"/>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="19" t="s">
         <v>12</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -2327,10 +2394,10 @@
     <row r="7" ht="14.25" customHeight="1" spans="1:8">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="19" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="6"/>
@@ -2341,10 +2408,10 @@
     <row r="8" ht="14.25" customHeight="1" spans="1:8">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="19" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="6"/>
@@ -2355,10 +2422,10 @@
     <row r="9" ht="14.25" customHeight="1" spans="1:8">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="19" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="6"/>
@@ -2369,10 +2436,10 @@
     <row r="10" ht="14.25" customHeight="1" spans="1:8">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="20"/>
+      <c r="D10" s="19"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -2381,10 +2448,10 @@
     <row r="11" ht="14.25" customHeight="1" spans="1:8">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="20"/>
+      <c r="D11" s="19"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -2393,10 +2460,10 @@
     <row r="12" ht="14.25" customHeight="1" spans="1:8">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="20"/>
+      <c r="D12" s="19"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -2404,22 +2471,22 @@
     </row>
     <row r="13" ht="28.5" customHeight="1" spans="1:8">
       <c r="A13" s="7"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="19" t="s">
         <v>35</v>
       </c>
       <c r="H13" s="8" t="s">
@@ -2427,25 +2494,25 @@
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="19" t="s">
         <v>38</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="19" t="s">
         <v>42</v>
       </c>
       <c r="H14" s="8" t="s">
@@ -2453,9 +2520,9 @@
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A15" s="27"/>
+      <c r="A15" s="26"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>43</v>
       </c>
       <c r="D15" s="6"/>
@@ -2465,9 +2532,9 @@
       <c r="H15" s="6"/>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A16" s="27"/>
+      <c r="A16" s="26"/>
       <c r="B16" s="6"/>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="19" t="s">
         <v>44</v>
       </c>
       <c r="D16" s="6"/>
@@ -2477,9 +2544,9 @@
       <c r="H16" s="6"/>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A17" s="27"/>
+      <c r="A17" s="26"/>
       <c r="B17" s="6"/>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="19" t="s">
         <v>45</v>
       </c>
       <c r="D17" s="6"/>
@@ -2489,9 +2556,9 @@
       <c r="H17" s="6"/>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A18" s="27"/>
+      <c r="A18" s="26"/>
       <c r="B18" s="6"/>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="19" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="6"/>
@@ -2501,9 +2568,9 @@
       <c r="H18" s="6"/>
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A19" s="27"/>
+      <c r="A19" s="26"/>
       <c r="B19" s="6"/>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D19" s="6"/>
@@ -2513,9 +2580,9 @@
       <c r="H19" s="6"/>
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A20" s="27"/>
+      <c r="A20" s="26"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="19" t="s">
         <v>48</v>
       </c>
       <c r="D20" s="6"/>
@@ -2525,9 +2592,9 @@
       <c r="H20" s="6"/>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A21" s="27"/>
+      <c r="A21" s="26"/>
       <c r="B21" s="6"/>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="19" t="s">
         <v>49</v>
       </c>
       <c r="D21" s="6"/>
@@ -2537,9 +2604,9 @@
       <c r="H21" s="6"/>
     </row>
     <row r="22" ht="32.25" customHeight="1" spans="1:8">
-      <c r="A22" s="28"/>
+      <c r="A22" s="27"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="19" t="s">
         <v>50</v>
       </c>
       <c r="D22" s="7"/>
@@ -2549,25 +2616,25 @@
       <c r="H22" s="7"/>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="29" t="s">
+      <c r="F23" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="19" t="s">
         <v>12</v>
       </c>
       <c r="H23" s="8" t="s">
@@ -2575,25 +2642,25 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="30" t="s">
+      <c r="F24" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="G24" s="19" t="s">
         <v>12</v>
       </c>
       <c r="H24" s="8" t="s">
@@ -2601,63 +2668,63 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="D25" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="E25" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="F25" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="G25" s="20" t="s">
+      <c r="G25" s="19" t="s">
         <v>12</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" s="13" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A26" s="27"/>
-      <c r="B26" s="24" t="s">
+    <row r="26" s="12" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
+      <c r="A26" s="26"/>
+      <c r="B26" s="23" t="s">
         <v>66</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="31"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="20"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="19"/>
       <c r="H26" s="8"/>
     </row>
     <row r="27" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A27" s="27"/>
-      <c r="B27" s="24" t="s">
+      <c r="A27" s="26"/>
+      <c r="B27" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="20" t="s">
+      <c r="G27" s="19" t="s">
         <v>12</v>
       </c>
       <c r="H27" s="8" t="s">
@@ -2665,9 +2732,9 @@
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A28" s="27"/>
+      <c r="A28" s="26"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="19" t="s">
         <v>71</v>
       </c>
       <c r="D28" s="7"/>
@@ -2677,23 +2744,23 @@
       <c r="H28" s="7"/>
     </row>
     <row r="29" ht="60" customHeight="1" spans="1:8">
-      <c r="A29" s="27"/>
-      <c r="B29" s="24" t="s">
+      <c r="A29" s="26"/>
+      <c r="B29" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="19" t="s">
         <v>73</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="F29" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="G29" s="19" t="s">
         <v>35</v>
       </c>
       <c r="H29" s="8" t="s">
@@ -2701,19 +2768,19 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A30" s="27"/>
+      <c r="A30" s="26"/>
       <c r="B30" s="6"/>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="20" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="6"/>
-      <c r="G30" s="20" t="s">
+      <c r="G30" s="19" t="s">
         <v>12</v>
       </c>
       <c r="H30" s="8" t="s">
@@ -2721,19 +2788,19 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A31" s="28"/>
+      <c r="A31" s="27"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="34" t="s">
+      <c r="E31" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F31" s="7"/>
-      <c r="G31" s="20" t="s">
+      <c r="G31" s="19" t="s">
         <v>12</v>
       </c>
       <c r="H31" s="8" t="s">
@@ -2741,25 +2808,25 @@
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="22" t="s">
+      <c r="F32" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="G32" s="19" t="s">
         <v>12</v>
       </c>
       <c r="H32" s="8" t="s">
@@ -2767,9 +2834,9 @@
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A33" s="28"/>
+      <c r="A33" s="27"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="20" t="s">
+      <c r="C33" s="19" t="s">
         <v>84</v>
       </c>
       <c r="D33" s="7"/>
@@ -2779,23 +2846,23 @@
       <c r="H33" s="7"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="21" t="s">
+      <c r="D34" s="19"/>
+      <c r="E34" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="G34" s="20" t="s">
+      <c r="G34" s="19" t="s">
         <v>12</v>
       </c>
       <c r="H34" s="8" t="s">
@@ -2803,59 +2870,59 @@
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A35" s="27"/>
+      <c r="A35" s="26"/>
       <c r="B35" s="6"/>
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="20"/>
+      <c r="D35" s="19"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A36" s="27"/>
+      <c r="A36" s="26"/>
       <c r="B36" s="6"/>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="20"/>
+      <c r="D36" s="19"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A37" s="28"/>
+      <c r="A37" s="27"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="35" t="s">
+      <c r="C37" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="D37" s="35"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="36" t="s">
+      <c r="C38" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="D38" s="36"/>
-      <c r="E38" s="34" t="s">
+      <c r="D38" s="35"/>
+      <c r="E38" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="37" t="s">
+      <c r="F38" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="20" t="s">
+      <c r="G38" s="19" t="s">
         <v>12</v>
       </c>
       <c r="H38" s="8" t="s">
@@ -2864,14 +2931,14 @@
     </row>
     <row r="39" ht="15.75" customHeight="1" spans="1:8">
       <c r="A39" s="6"/>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="36" t="s">
+      <c r="C39" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="D39" s="36"/>
-      <c r="E39" s="34" t="s">
+      <c r="D39" s="35"/>
+      <c r="E39" s="33" t="s">
         <v>60</v>
       </c>
       <c r="F39" s="7"/>
@@ -2880,22 +2947,22 @@
     </row>
     <row r="40" ht="28.5" customHeight="1" spans="1:8">
       <c r="A40" s="6"/>
-      <c r="B40" s="24" t="s">
+      <c r="B40" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="36" t="s">
+      <c r="C40" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="34" t="s">
+      <c r="E40" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="33" t="s">
+      <c r="F40" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="G40" s="20" t="s">
+      <c r="G40" s="19" t="s">
         <v>35</v>
       </c>
       <c r="H40" s="8" t="s">
@@ -2904,22 +2971,22 @@
     </row>
     <row r="41" ht="15.75" customHeight="1" spans="1:8">
       <c r="A41" s="6"/>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D41" s="36" t="s">
+      <c r="D41" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="E41" s="34" t="s">
+      <c r="E41" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="F41" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="G41" s="20" t="s">
+      <c r="G41" s="19" t="s">
         <v>103</v>
       </c>
       <c r="H41" s="8" t="s">
@@ -2928,34 +2995,34 @@
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:8">
       <c r="A42" s="6"/>
-      <c r="B42" s="24" t="s">
+      <c r="B42" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="36"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="20"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="19"/>
       <c r="H42" s="8"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:8">
       <c r="A43" s="7"/>
-      <c r="B43" s="24" t="s">
+      <c r="B43" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="36" t="s">
+      <c r="C43" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="36"/>
-      <c r="E43" s="34" t="s">
+      <c r="D43" s="35"/>
+      <c r="E43" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="F43" s="33" t="s">
+      <c r="F43" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="G43" s="20" t="s">
+      <c r="G43" s="19" t="s">
         <v>109</v>
       </c>
       <c r="H43" s="8" t="s">
@@ -2963,25 +3030,25 @@
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A44" s="39" t="s">
+      <c r="A44" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="40" t="s">
+      <c r="B44" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="C44" s="41" t="s">
+      <c r="C44" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="41" t="s">
+      <c r="D44" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="E44" s="42" t="s">
+      <c r="E44" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="43" t="s">
+      <c r="F44" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G44" s="44" t="s">
+      <c r="G44" s="43" t="s">
         <v>35</v>
       </c>
       <c r="H44" s="9" t="s">
@@ -2989,19 +3056,19 @@
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A45" s="27"/>
+      <c r="A45" s="26"/>
       <c r="B45" s="6"/>
-      <c r="C45" s="36" t="s">
+      <c r="C45" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="D45" s="36" t="s">
+      <c r="D45" s="35" t="s">
         <v>116</v>
       </c>
       <c r="E45" s="6"/>
-      <c r="F45" s="45" t="s">
+      <c r="F45" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="G45" s="20" t="s">
+      <c r="G45" s="19" t="s">
         <v>12</v>
       </c>
       <c r="H45" s="8" t="s">
@@ -3009,29 +3076,29 @@
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A46" s="27"/>
+      <c r="A46" s="26"/>
       <c r="B46" s="6"/>
-      <c r="C46" s="36" t="s">
+      <c r="C46" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="D46" s="36"/>
+      <c r="D46" s="35"/>
       <c r="E46" s="6"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
     </row>
     <row r="47" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A47" s="27"/>
+      <c r="A47" s="26"/>
       <c r="B47" s="6"/>
-      <c r="C47" s="36" t="s">
+      <c r="C47" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="D47" s="36"/>
+      <c r="D47" s="35"/>
       <c r="E47" s="6"/>
-      <c r="F47" s="45" t="s">
+      <c r="F47" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="G47" s="20" t="s">
+      <c r="G47" s="19" t="s">
         <v>12</v>
       </c>
       <c r="H47" s="8" t="s">
@@ -3039,121 +3106,121 @@
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A48" s="28"/>
+      <c r="A48" s="27"/>
       <c r="B48" s="7"/>
-      <c r="C48" s="46" t="s">
+      <c r="C48" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="D48" s="46"/>
+      <c r="D48" s="45"/>
       <c r="E48" s="7"/>
-      <c r="F48" s="29" t="s">
+      <c r="F48" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="G48" s="35" t="s">
+      <c r="G48" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="H48" s="47" t="s">
+      <c r="H48" s="46" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="49" ht="42.75" customHeight="1" spans="1:8">
-      <c r="A49" s="48" t="s">
+      <c r="A49" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="B49" s="48" t="s">
+      <c r="B49" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="C49" s="49" t="s">
+      <c r="C49" s="48" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="50" t="s">
+      <c r="D49" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="E49" s="51" t="s">
+      <c r="E49" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="52"/>
-      <c r="G49" s="53" t="s">
+      <c r="F49" s="51"/>
+      <c r="G49" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="H49" s="54"/>
+      <c r="H49" s="53"/>
     </row>
     <row r="50" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A50" s="55"/>
-      <c r="B50" s="55"/>
-      <c r="C50" s="49" t="s">
+      <c r="A50" s="54"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="48" t="s">
         <v>123</v>
       </c>
-      <c r="D50" s="56" t="s">
+      <c r="D50" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="E50" s="57" t="s">
+      <c r="E50" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="F50" s="58"/>
-      <c r="G50" s="53" t="s">
+      <c r="F50" s="57"/>
+      <c r="G50" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="H50" s="59"/>
+      <c r="H50" s="58"/>
     </row>
     <row r="51" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A51" s="55"/>
-      <c r="B51" s="55"/>
-      <c r="C51" s="49" t="s">
+      <c r="A51" s="54"/>
+      <c r="B51" s="54"/>
+      <c r="C51" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="D51" s="60" t="s">
+      <c r="D51" s="59" t="s">
         <v>126</v>
       </c>
-      <c r="E51" s="57" t="s">
+      <c r="E51" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="F51" s="52"/>
-      <c r="G51" s="53" t="s">
+      <c r="F51" s="51"/>
+      <c r="G51" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="H51" s="54"/>
+      <c r="H51" s="53"/>
     </row>
     <row r="52" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A52" s="61"/>
-      <c r="B52" s="61"/>
-      <c r="C52" s="60" t="s">
+      <c r="A52" s="60"/>
+      <c r="B52" s="60"/>
+      <c r="C52" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="D52" s="50" t="s">
+      <c r="D52" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="E52" s="62" t="s">
+      <c r="E52" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="52" t="s">
+      <c r="F52" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="G52" s="53" t="s">
+      <c r="G52" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="H52" s="54" t="s">
+      <c r="H52" s="53" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A53" s="40" t="s">
+      <c r="A53" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="B53" s="40" t="s">
+      <c r="B53" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="C53" s="41" t="s">
+      <c r="C53" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="D53" s="41"/>
-      <c r="E53" s="42" t="s">
+      <c r="D53" s="40"/>
+      <c r="E53" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="F53" s="43" t="s">
+      <c r="F53" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="G53" s="44" t="s">
+      <c r="G53" s="43" t="s">
         <v>12</v>
       </c>
       <c r="H53" s="9" t="s">
@@ -3162,22 +3229,22 @@
     </row>
     <row r="54" ht="28.5" customHeight="1" spans="1:8">
       <c r="A54" s="7"/>
-      <c r="B54" s="24" t="s">
+      <c r="B54" s="23" t="s">
         <v>133</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D54" s="38" t="s">
+      <c r="D54" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="E54" s="34" t="s">
+      <c r="E54" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="F54" s="33" t="s">
+      <c r="F54" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="G54" s="20" t="s">
+      <c r="G54" s="19" t="s">
         <v>103</v>
       </c>
       <c r="H54" s="8" t="s">
@@ -3185,21 +3252,21 @@
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="C55" s="36" t="s">
+      <c r="C55" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="D55" s="36"/>
-      <c r="E55" s="34" t="s">
+      <c r="D55" s="35"/>
+      <c r="E55" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="F55" s="33"/>
-      <c r="G55" s="20" t="s">
+      <c r="F55" s="32"/>
+      <c r="G55" s="19" t="s">
         <v>140</v>
       </c>
       <c r="H55" s="8" t="s">
@@ -3207,49 +3274,49 @@
       </c>
     </row>
     <row r="56" ht="42.75" customHeight="1" spans="1:8">
-      <c r="A56" s="25" t="s">
+      <c r="A56" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="B56" s="24" t="s">
+      <c r="B56" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="C56" s="36" t="s">
+      <c r="C56" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="D56" s="38" t="s">
+      <c r="D56" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="E56" s="34" t="s">
+      <c r="E56" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="F56" s="45" t="s">
+      <c r="F56" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="G56" s="20"/>
+      <c r="G56" s="19"/>
       <c r="H56" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="57" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A57" s="24" t="s">
+      <c r="A57" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="B57" s="24" t="s">
+      <c r="B57" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="C57" s="36" t="s">
+      <c r="C57" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="36" t="s">
+      <c r="D57" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="E57" s="34" t="s">
+      <c r="E57" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="F57" s="45" t="s">
+      <c r="F57" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="G57" s="20" t="s">
+      <c r="G57" s="19" t="s">
         <v>103</v>
       </c>
       <c r="H57" s="8" t="s">
@@ -3257,50 +3324,50 @@
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A58" s="63" t="s">
+      <c r="A58" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="B58" s="63" t="s">
+      <c r="B58" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="C58" s="35" t="s">
+      <c r="C58" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="D58" s="46" t="s">
+      <c r="D58" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="E58" s="64" t="s">
+      <c r="E58" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="F58" s="65" t="s">
+      <c r="F58" s="64" t="s">
         <v>153</v>
       </c>
-      <c r="G58" s="35" t="s">
+      <c r="G58" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="H58" s="47" t="s">
+      <c r="H58" s="46" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="59" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A59" s="48" t="s">
+      <c r="A59" s="47" t="s">
         <v>154</v>
       </c>
-      <c r="B59" s="48" t="s">
+      <c r="B59" s="47" t="s">
         <v>154</v>
       </c>
-      <c r="C59" s="66" t="s">
+      <c r="C59" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="D59" s="58"/>
-      <c r="E59" s="62" t="s">
+      <c r="D59" s="57"/>
+      <c r="E59" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="F59" s="58"/>
-      <c r="G59" s="35" t="s">
+      <c r="F59" s="57"/>
+      <c r="G59" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="H59" s="59" t="s">
+      <c r="H59" s="58" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3370,7 +3437,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.2" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="11.7019230769231" style="1" customWidth="1"/>
@@ -3632,195 +3699,207 @@
         <v>194</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>109</v>
       </c>
       <c r="H12" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" ht="96" customHeight="1" spans="1:8">
+      <c r="A13" s="6"/>
+      <c r="B13" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="13" ht="81" customHeight="1" spans="1:8">
-      <c r="A13" s="6"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" ht="96" customHeight="1" spans="1:8">
+    <row r="14" ht="111" customHeight="1" spans="1:8">
       <c r="A14" s="6"/>
       <c r="B14" s="4" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="15" ht="111" customHeight="1" spans="1:8">
+    <row r="15" ht="51" customHeight="1" spans="1:8">
       <c r="A15" s="6"/>
       <c r="B15" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="16" ht="51" customHeight="1" spans="1:8">
+    <row r="16" ht="126" customHeight="1" spans="1:8">
       <c r="A16" s="6"/>
-      <c r="B16" s="4" t="s">
-        <v>203</v>
-      </c>
+      <c r="B16" s="6"/>
       <c r="C16" s="5" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="17" ht="126" customHeight="1" spans="1:8">
+    <row r="17" ht="66" customHeight="1" spans="1:8">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" ht="96" customHeight="1" spans="1:8">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" ht="111" customHeight="1" spans="1:8">
+      <c r="A19" s="6"/>
+      <c r="B19" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="18" ht="66" customHeight="1" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="F18" s="4" t="s">
+      <c r="G19" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" ht="66" customHeight="1" spans="1:8">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" ht="96" customHeight="1" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" ht="111" customHeight="1" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>109</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" ht="66" customHeight="1" spans="1:8">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" ht="96" customHeight="1" spans="1:8">
       <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
+      <c r="B21" s="4" t="s">
+        <v>224</v>
+      </c>
       <c r="C21" s="5" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>109</v>
@@ -3829,22 +3908,20 @@
         <v>162</v>
       </c>
     </row>
-    <row r="22" ht="96" customHeight="1" spans="1:8">
+    <row r="22" ht="51" customHeight="1" spans="1:8">
       <c r="A22" s="6"/>
-      <c r="B22" s="4" t="s">
-        <v>223</v>
-      </c>
+      <c r="B22" s="7"/>
       <c r="C22" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>109</v>
@@ -3853,44 +3930,46 @@
         <v>162</v>
       </c>
     </row>
-    <row r="23" ht="51" customHeight="1" spans="1:8">
+    <row r="23" ht="96" customHeight="1" spans="1:8">
       <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
+      <c r="B23" s="4" t="s">
+        <v>231</v>
+      </c>
       <c r="C23" s="5" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="24" ht="96" customHeight="1" spans="1:8">
+    <row r="24" ht="81" customHeight="1" spans="1:8">
       <c r="A24" s="6"/>
       <c r="B24" s="4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>103</v>
@@ -3899,83 +3978,81 @@
         <v>162</v>
       </c>
     </row>
-    <row r="25" ht="81" customHeight="1" spans="1:8">
+    <row r="25" ht="126" customHeight="1" spans="1:8">
       <c r="A25" s="6"/>
-      <c r="B25" s="4" t="s">
-        <v>234</v>
-      </c>
+      <c r="B25" s="6"/>
       <c r="C25" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="26" ht="126" customHeight="1" spans="1:8">
+    <row r="26" ht="96" customHeight="1" spans="1:8">
       <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
+      <c r="B26" s="7"/>
       <c r="C26" s="5" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="F26" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" ht="171" customHeight="1" spans="1:8">
+      <c r="A27" s="6"/>
+      <c r="B27" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H27" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="27" ht="96" customHeight="1" spans="1:8">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H27" s="7"/>
-    </row>
-    <row r="28" ht="171" customHeight="1" spans="1:8">
+    <row r="28" ht="126" customHeight="1" spans="1:8">
       <c r="A28" s="6"/>
-      <c r="B28" s="4" t="s">
-        <v>244</v>
-      </c>
+      <c r="B28" s="7"/>
       <c r="C28" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>10</v>
@@ -3987,97 +4064,76 @@
         <v>162</v>
       </c>
     </row>
-    <row r="29" ht="126" customHeight="1" spans="1:8">
+    <row r="29" ht="81" customHeight="1" spans="1:8">
       <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
+      <c r="B29" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="C29" s="5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" ht="81" customHeight="1" spans="1:8">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="30" ht="81" customHeight="1" spans="1:8">
-      <c r="A30" s="6"/>
-      <c r="B30" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" ht="81" customHeight="1" spans="1:8">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="H31" s="4" t="s">
         <v>162</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A2:A31"/>
+    <mergeCell ref="A2:A30"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B11"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="F25:F26"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G17:G18"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="H6:H9"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H16:H18"/>
+    <mergeCell ref="H25:H26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/PA替代需求列表.xlsx
+++ b/PA替代需求列表.xlsx
@@ -637,7 +637,7 @@
     <t>支持QoS策略规则内直接按DSCP/ToS匹配调度</t>
   </si>
   <si>
-    <t>QoS策略规则DSCP/ToS直接匹配（非独立流控模块配置）</t>
+    <t>QoS策略规则DSCP/ToS直接匹配</t>
   </si>
   <si>
     <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
@@ -646,7 +646,7 @@
     <t>基于策略转发(PBF)</t>
   </si>
   <si>
-    <t>支持PBF强制对称返回（非对称路由环境）</t>
+    <t>支持PBF强制对称返回</t>
   </si>
   <si>
     <t>记录入接口MAC，回包强制原路返回</t>
@@ -3726,10 +3726,10 @@
         <v>60</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>188</v>
+        <v>109</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" ht="111" customHeight="1" spans="1:8">
@@ -3747,13 +3747,13 @@
         <v>203</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" ht="51" customHeight="1" spans="1:8">

--- a/PA替代需求列表.xlsx
+++ b/PA替代需求列表.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="256">
   <si>
     <t>一级需求</t>
   </si>
@@ -550,7 +550,7 @@
     <t>PA除全局TCP/UDP会话超时外，可在应用程序对象上定义专用超时，匹配该应用的流量覆盖全局值（PA Web帮助p215、p695）；天融信手册未见应用级超时覆盖（仅SSLVPN会话超时设置与黑名单老化）；迁移评估项：需排查现网PA为数据库/长连接业务单独配置的应用超时并逐条转换，否则长连接业务频繁中断</t>
   </si>
   <si>
-    <t>安全策略(Security)</t>
+    <t>安全策略</t>
   </si>
   <si>
     <t>支持配置HIP主机信息配置文件</t>
@@ -643,7 +643,7 @@
     <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
   </si>
   <si>
-    <t>基于策略转发(PBF)</t>
+    <t>基于策略转发</t>
   </si>
   <si>
     <t>支持PBF强制对称返回</t>
@@ -655,10 +655,10 @@
     <t>PA对称返回：虚拟路由器替代返回流量的路由查找，将流量引导回接收SYN数据包的MAC地址（ARP表确定下一跳），双ISP双活/非对称路由核心机制（PA管理指南p1294）；天融信手册检索无对称返回/回程机制命中，策略路由与LLB的回程保障能力待验证；迁移评估项：多ISP双活环境需实测天融信回包路由对称性，否则现网业务中断</t>
   </si>
   <si>
-    <t>解密策略(Decryption)</t>
-  </si>
-  <si>
-    <t>支持解密流量镜像到专用接口（Decryption Port Mirroring）</t>
+    <t>解密策略</t>
+  </si>
+  <si>
+    <t>支持解密流量镜像到专用接口</t>
   </si>
   <si>
     <t>解密后明文流量镜像至专用接口供第三方分析</t>
@@ -667,7 +667,7 @@
     <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证（PA管理指南p1059）；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
   </si>
   <si>
-    <t>支持解密不受信证书分离处理（Forward Untrust Certificate）</t>
+    <t>支持解密不受信证书分离处理</t>
   </si>
   <si>
     <t>外部无效证书以不受信转发证书重签，保留浏览器告警</t>
@@ -676,7 +676,7 @@
     <t>PA转发代理遇外部过期/不受信证书时，不用内部信任CA重签，而是专用Forward Untrust Certificate重签名，让浏览器保留不受信告警（PA管理指南p994、p1030）；天融信SSL解密（透明代理/服务器SSL解密，天融信手册《代理策略》页）未见受信/不受信双证书体系；迁移评估项：需验证天融信对外部无效证书的处理方式，避免直接阻断（白屏）或信任重签（掩盖风险）</t>
   </si>
   <si>
-    <t>支持解密规则按URL类别选择性解密（URL Category）</t>
+    <t>支持解密规则按URL类别选择性解密</t>
   </si>
   <si>
     <t>按URL类别圈定解密范围，排除银行/医疗等敏感类</t>
@@ -685,7 +685,7 @@
     <t>PA解密规则可按URL类别（含自定义类别）选择解密范围，可排除银行/医疗等敏感类别不解密（PA Web帮助p164）；天融信SSL解密（代理策略/代理模板）无按URL类别选择解密机制（检索无命中）</t>
   </si>
   <si>
-    <t>支持SSH代理解密与SSH隧道控制（SSH Proxy）</t>
+    <t>支持SSH代理解密与SSH隧道控制</t>
   </si>
   <si>
     <t>SSH代理解密+SSH隧道(ssh-tunnel)识别控制</t>
@@ -697,22 +697,13 @@
     <t>网络数据包代理(NPBroker)</t>
   </si>
   <si>
-    <t>支持内联数据包代理策略将流量转发第三方安全链（NPBroker）</t>
-  </si>
-  <si>
-    <t>已解密/未解密流量内联转发第三方安全链，L3路由转发</t>
+    <t>支持内联数据包代理策略将流量转发第三方安全链</t>
+  </si>
+  <si>
+    <t>已解密/未解密/非TLS流量内联转发第三方安全链，L3路由转发，支持转发流量类型选择</t>
   </si>
   <si>
     <t>PA网络数据包代理策略将已解密/未解密TLS/非TLS流量内联转发至第三方安全工具，路径选择选项卡应用数据包代理配置文件定义经路由L3安全链的转发方式（PA Web帮助p167-170）；天融信无网络数据包代理模块，最接近手段为WAF旁路联动（经交换机镜像引流，天融信手册《与WAF联动》页），非内联且无回注路径；对应矩阵#122</t>
-  </si>
-  <si>
-    <t>支持NPBroker转发流量类型选择（TLS解密/未解密/非TLS）</t>
-  </si>
-  <si>
-    <t>TLS解密/未解密/非TLS流量类型选择</t>
-  </si>
-  <si>
-    <t>PA规则可选Forward TLS(Decrypted)/未解密/非TLS多种流量类型；需免费许可证（PA Web帮助p167）；天融信无网络数据包代理模块（矩阵#122）</t>
   </si>
   <si>
     <t>隧道检测(Tunnel Inspection)</t>
@@ -1618,11 +1609,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1637,11 +1636,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1652,6 +1651,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1677,6 +1677,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1740,6 +1743,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1860,140 +1866,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1111670</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>18250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>320820</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>187275</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6799580" y="6399530"/>
-          <a:ext cx="2200275" cy="349885"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial" panose="020B0604020202090204"/>
-              <a:ea typeface="宋体"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" sz="1600" dirty="0">
-            <a:solidFill>
-              <a:srgbClr val="808080">
-                <a:alpha val="19999"/>
-              </a:srgbClr>
-            </a:solidFill>
-            <a:latin typeface="Arial" panose="020B0604020202090204"/>
-            <a:ea typeface="宋体"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2084490</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>469100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1547005</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>819100</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6799580" y="6399530"/>
-          <a:ext cx="2200275" cy="349885"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial" panose="020B0604020202090204"/>
-              <a:ea typeface="宋体"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" sz="1600" dirty="0">
-            <a:solidFill>
-              <a:srgbClr val="808080">
-                <a:alpha val="19999"/>
-              </a:srgbClr>
-            </a:solidFill>
-            <a:latin typeface="Arial" panose="020B0604020202090204"/>
-            <a:ea typeface="宋体"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2257,1117 +2129,1117 @@
   <dimension ref="A1:H59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="11.7115384615385" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7115384615385" style="1" customWidth="1"/>
-    <col min="3" max="3" width="54.7115384615385" style="1" customWidth="1"/>
-    <col min="4" max="4" width="45.2884615384615" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.71153846153846" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.8557692307692" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.71153846153846" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.71153846153846" style="13" customWidth="1"/>
+    <col min="1" max="1" width="11.7115384615385" style="15" customWidth="1"/>
+    <col min="2" max="2" width="19.7115384615385" style="15" customWidth="1"/>
+    <col min="3" max="3" width="54.7115384615385" style="15" customWidth="1"/>
+    <col min="4" max="4" width="45.2884615384615" style="15" customWidth="1"/>
+    <col min="5" max="5" width="7.71153846153846" style="15" customWidth="1"/>
+    <col min="6" max="6" width="37.8557692307692" style="15" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.71153846153846" style="15" customWidth="1"/>
+    <col min="8" max="8" width="9.71153846153846" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16"/>
-      <c r="G1" s="15" t="s">
+      <c r="F1" s="19"/>
+      <c r="G1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="22"/>
+      <c r="E2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:8">
-      <c r="A3" s="6"/>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:8">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="19" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:8">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="19" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A6" s="6"/>
-      <c r="B6" s="23" t="s">
+      <c r="A6" s="8"/>
+      <c r="B6" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="19" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="19" t="s">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="19" t="s">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="19" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="19" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="19" t="s">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
     </row>
     <row r="13" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A13" s="7"/>
-      <c r="B13" s="23" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A15" s="26"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="19" t="s">
+      <c r="A15" s="30"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A16" s="26"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="19" t="s">
+      <c r="A16" s="30"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A17" s="26"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="19" t="s">
+      <c r="A17" s="30"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A18" s="26"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="19" t="s">
+      <c r="A18" s="30"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A19" s="26"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="19" t="s">
+      <c r="A19" s="30"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A20" s="26"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="19" t="s">
+      <c r="A20" s="30"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A21" s="26"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="19" t="s">
+      <c r="A21" s="30"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
     </row>
     <row r="22" ht="32.25" customHeight="1" spans="1:8">
-      <c r="A22" s="27"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="19" t="s">
+      <c r="A22" s="31"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="D25" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="21" t="s">
+      <c r="F25" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="25" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" s="12" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A26" s="26"/>
-      <c r="B26" s="23" t="s">
+    <row r="26" s="14" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
+      <c r="A26" s="30"/>
+      <c r="B26" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="30"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="8"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="25"/>
     </row>
     <row r="27" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A27" s="26"/>
-      <c r="B27" s="23" t="s">
+      <c r="A27" s="30"/>
+      <c r="B27" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="21" t="s">
+      <c r="F27" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G27" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A28" s="26"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="19" t="s">
+      <c r="A28" s="30"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
     </row>
     <row r="29" ht="60" customHeight="1" spans="1:8">
-      <c r="A29" s="26"/>
-      <c r="B29" s="23" t="s">
+      <c r="A29" s="30"/>
+      <c r="B29" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="32" t="s">
+      <c r="F29" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A30" s="26"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="19" t="s">
+      <c r="A30" s="30"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="19" t="s">
+      <c r="F30" s="8"/>
+      <c r="G30" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A31" s="27"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="19" t="s">
+      <c r="A31" s="31"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="33" t="s">
+      <c r="E31" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="19" t="s">
+      <c r="F31" s="9"/>
+      <c r="G31" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A32" s="24" t="s">
+      <c r="A32" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="F32" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="19" t="s">
+      <c r="G32" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A33" s="27"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="19" t="s">
+      <c r="A33" s="31"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="23" t="s">
+      <c r="B34" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="20" t="s">
+      <c r="D34" s="22"/>
+      <c r="E34" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="21" t="s">
+      <c r="F34" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="G34" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A35" s="26"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="19" t="s">
+      <c r="A35" s="30"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="19"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
     </row>
     <row r="36" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A36" s="26"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="19" t="s">
+      <c r="A36" s="30"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="19"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
     </row>
     <row r="37" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A37" s="27"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="34" t="s">
+      <c r="A37" s="31"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="D37" s="34"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="35" t="s">
+      <c r="C38" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="D38" s="35"/>
-      <c r="E38" s="33" t="s">
+      <c r="D38" s="39"/>
+      <c r="E38" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="36" t="s">
+      <c r="F38" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="19" t="s">
+      <c r="G38" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="23" t="s">
+      <c r="A39" s="8"/>
+      <c r="B39" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="35" t="s">
+      <c r="C39" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="D39" s="35"/>
-      <c r="E39" s="33" t="s">
+      <c r="D39" s="39"/>
+      <c r="E39" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
     </row>
     <row r="40" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="23" t="s">
+      <c r="A40" s="8"/>
+      <c r="B40" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="35" t="s">
+      <c r="C40" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="D40" s="37" t="s">
+      <c r="D40" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="33" t="s">
+      <c r="E40" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="32" t="s">
+      <c r="F40" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="G40" s="19" t="s">
+      <c r="G40" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A41" s="6"/>
-      <c r="B41" s="23" t="s">
+      <c r="A41" s="8"/>
+      <c r="B41" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D41" s="35" t="s">
+      <c r="D41" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="E41" s="33" t="s">
+      <c r="E41" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F41" s="32" t="s">
+      <c r="F41" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="G41" s="19" t="s">
+      <c r="G41" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="23" t="s">
+      <c r="A42" s="8"/>
+      <c r="B42" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C42" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="35"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="8"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="25"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A43" s="7"/>
-      <c r="B43" s="23" t="s">
+      <c r="A43" s="9"/>
+      <c r="B43" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="35" t="s">
+      <c r="C43" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="35"/>
-      <c r="E43" s="33" t="s">
+      <c r="D43" s="39"/>
+      <c r="E43" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F43" s="32" t="s">
+      <c r="F43" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="G43" s="19" t="s">
+      <c r="G43" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A44" s="38" t="s">
+      <c r="A44" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="39" t="s">
+      <c r="B44" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="C44" s="40" t="s">
+      <c r="C44" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="40" t="s">
+      <c r="D44" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="E44" s="41" t="s">
+      <c r="E44" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="42" t="s">
+      <c r="F44" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="G44" s="43" t="s">
+      <c r="G44" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H44" s="48" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A45" s="26"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="35" t="s">
+      <c r="A45" s="30"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="D45" s="35" t="s">
+      <c r="D45" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="E45" s="6"/>
-      <c r="F45" s="44" t="s">
+      <c r="E45" s="8"/>
+      <c r="F45" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="G45" s="19" t="s">
+      <c r="G45" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="8" t="s">
+      <c r="H45" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A46" s="26"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="35" t="s">
+      <c r="A46" s="30"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="D46" s="35"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
     </row>
     <row r="47" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A47" s="26"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="35" t="s">
+      <c r="A47" s="30"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="D47" s="35"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="44" t="s">
+      <c r="D47" s="39"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="G47" s="19" t="s">
+      <c r="G47" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H47" s="8" t="s">
+      <c r="H47" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A48" s="27"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="45" t="s">
+      <c r="A48" s="31"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="D48" s="45"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="28" t="s">
+      <c r="D48" s="50"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="G48" s="34" t="s">
+      <c r="G48" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="H48" s="46" t="s">
+      <c r="H48" s="51" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="49" ht="42.75" customHeight="1" spans="1:8">
-      <c r="A49" s="47" t="s">
+      <c r="A49" s="52" t="s">
         <v>120</v>
       </c>
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="52" t="s">
         <v>120</v>
       </c>
-      <c r="C49" s="48" t="s">
+      <c r="C49" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="49" t="s">
+      <c r="D49" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="E49" s="50" t="s">
+      <c r="E49" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="51"/>
-      <c r="G49" s="52" t="s">
+      <c r="F49" s="56"/>
+      <c r="G49" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="H49" s="53"/>
+      <c r="H49" s="58"/>
     </row>
     <row r="50" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A50" s="54"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="48" t="s">
+      <c r="A50" s="59"/>
+      <c r="B50" s="59"/>
+      <c r="C50" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="D50" s="55" t="s">
+      <c r="D50" s="60" t="s">
         <v>124</v>
       </c>
-      <c r="E50" s="56" t="s">
+      <c r="E50" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="F50" s="57"/>
-      <c r="G50" s="52" t="s">
+      <c r="F50" s="62"/>
+      <c r="G50" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="H50" s="58"/>
+      <c r="H50" s="63"/>
     </row>
     <row r="51" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A51" s="54"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="48" t="s">
+      <c r="A51" s="59"/>
+      <c r="B51" s="59"/>
+      <c r="C51" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="D51" s="59" t="s">
+      <c r="D51" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="E51" s="56" t="s">
+      <c r="E51" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="F51" s="51"/>
-      <c r="G51" s="52" t="s">
+      <c r="F51" s="56"/>
+      <c r="G51" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="H51" s="53"/>
+      <c r="H51" s="58"/>
     </row>
     <row r="52" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A52" s="60"/>
-      <c r="B52" s="60"/>
-      <c r="C52" s="59" t="s">
+      <c r="A52" s="65"/>
+      <c r="B52" s="65"/>
+      <c r="C52" s="64" t="s">
         <v>127</v>
       </c>
-      <c r="D52" s="49" t="s">
+      <c r="D52" s="54" t="s">
         <v>128</v>
       </c>
-      <c r="E52" s="61" t="s">
+      <c r="E52" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="51" t="s">
+      <c r="F52" s="56" t="s">
         <v>129</v>
       </c>
-      <c r="G52" s="52" t="s">
+      <c r="G52" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="H52" s="53" t="s">
+      <c r="H52" s="58" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A53" s="39" t="s">
+      <c r="A53" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="B53" s="39" t="s">
+      <c r="B53" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="C53" s="40" t="s">
+      <c r="C53" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="D53" s="40"/>
-      <c r="E53" s="41" t="s">
+      <c r="D53" s="44"/>
+      <c r="E53" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="F53" s="42" t="s">
+      <c r="F53" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="G53" s="43" t="s">
+      <c r="G53" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="H53" s="9" t="s">
+      <c r="H53" s="48" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="54" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A54" s="7"/>
-      <c r="B54" s="23" t="s">
+      <c r="A54" s="9"/>
+      <c r="B54" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="D54" s="37" t="s">
+      <c r="D54" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="E54" s="33" t="s">
+      <c r="E54" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F54" s="32" t="s">
+      <c r="F54" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="G54" s="19" t="s">
+      <c r="G54" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="H54" s="8" t="s">
+      <c r="H54" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A55" s="24" t="s">
+      <c r="A55" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="C55" s="35" t="s">
+      <c r="C55" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="D55" s="35"/>
-      <c r="E55" s="33" t="s">
+      <c r="D55" s="39"/>
+      <c r="E55" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F55" s="32"/>
-      <c r="G55" s="19" t="s">
+      <c r="F55" s="36"/>
+      <c r="G55" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="H55" s="8" t="s">
+      <c r="H55" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="56" ht="42.75" customHeight="1" spans="1:8">
-      <c r="A56" s="24" t="s">
+      <c r="A56" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="B56" s="23" t="s">
+      <c r="B56" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="C56" s="35" t="s">
+      <c r="C56" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="D56" s="37" t="s">
+      <c r="D56" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="E56" s="33" t="s">
+      <c r="E56" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="F56" s="44" t="s">
+      <c r="F56" s="49" t="s">
         <v>145</v>
       </c>
-      <c r="G56" s="19"/>
-      <c r="H56" s="8" t="s">
+      <c r="G56" s="22"/>
+      <c r="H56" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="57" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A57" s="23" t="s">
+      <c r="A57" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="B57" s="23" t="s">
+      <c r="B57" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="C57" s="35" t="s">
+      <c r="C57" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="35" t="s">
+      <c r="D57" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="E57" s="33" t="s">
+      <c r="E57" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F57" s="44" t="s">
+      <c r="F57" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="G57" s="19" t="s">
+      <c r="G57" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="H57" s="8" t="s">
+      <c r="H57" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A58" s="62" t="s">
+      <c r="A58" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="B58" s="62" t="s">
+      <c r="B58" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="C58" s="34" t="s">
+      <c r="C58" s="38" t="s">
         <v>151</v>
       </c>
-      <c r="D58" s="45" t="s">
+      <c r="D58" s="50" t="s">
         <v>152</v>
       </c>
-      <c r="E58" s="63" t="s">
+      <c r="E58" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="F58" s="64" t="s">
+      <c r="F58" s="69" t="s">
         <v>153</v>
       </c>
-      <c r="G58" s="34" t="s">
+      <c r="G58" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="H58" s="46" t="s">
+      <c r="H58" s="51" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="59" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A59" s="47" t="s">
+      <c r="A59" s="52" t="s">
         <v>154</v>
       </c>
-      <c r="B59" s="47" t="s">
+      <c r="B59" s="52" t="s">
         <v>154</v>
       </c>
-      <c r="C59" s="65" t="s">
+      <c r="C59" s="70" t="s">
         <v>155</v>
       </c>
-      <c r="D59" s="57"/>
-      <c r="E59" s="61" t="s">
+      <c r="D59" s="62"/>
+      <c r="E59" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="F59" s="57"/>
-      <c r="G59" s="34" t="s">
+      <c r="F59" s="62"/>
+      <c r="G59" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="H59" s="58" t="s">
+      <c r="H59" s="63" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3430,710 +3302,690 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="11.7019230769231" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7019230769231" style="1" customWidth="1"/>
-    <col min="3" max="3" width="40" style="1" customWidth="1"/>
-    <col min="4" max="4" width="41.4519230769231" style="1" customWidth="1"/>
-    <col min="5" max="5" width="62" style="1" customWidth="1"/>
+    <col min="1" max="2" width="19.3942307692308" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.4519230769231" style="2" customWidth="1"/>
+    <col min="5" max="5" width="62" style="2" customWidth="1"/>
     <col min="6" max="6" width="7.70192307692308" style="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.70192307692308" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="51" customHeight="1" spans="1:8">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="6" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="3" ht="84" customHeight="1" spans="1:8">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="6" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="4" ht="70" customHeight="1" spans="1:8">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="5" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
     </row>
     <row r="5" ht="51" customHeight="1" spans="1:8">
-      <c r="A5" s="6"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="6" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="6" ht="51" customHeight="1" spans="1:8">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="5" t="s">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="6" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1" spans="1:8">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="5" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H7" s="6"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" ht="84" customHeight="1" spans="1:8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="5" t="s">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="6"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="8"/>
     </row>
     <row r="9" ht="112" customHeight="1" spans="1:8">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="5" t="s">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
     </row>
     <row r="10" ht="171" customHeight="1" spans="1:8">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="5" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1" spans="1:8">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="10" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="12"/>
+      <c r="E11" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" ht="81" customHeight="1" spans="1:8">
-      <c r="A12" s="6"/>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="8"/>
+      <c r="B12" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="6" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="13" ht="96" customHeight="1" spans="1:8">
-      <c r="A13" s="6"/>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="6" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="14" ht="111" customHeight="1" spans="1:8">
-      <c r="A14" s="6"/>
-      <c r="B14" s="4" t="s">
+      <c r="A14" s="8"/>
+      <c r="B14" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="6" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="15" ht="51" customHeight="1" spans="1:8">
-      <c r="A15" s="6"/>
-      <c r="B15" s="4" t="s">
+      <c r="A15" s="8"/>
+      <c r="B15" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" ht="126" customHeight="1" spans="1:8">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" ht="66" customHeight="1" spans="1:8">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" ht="96" customHeight="1" spans="1:8">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" ht="111" customHeight="1" spans="1:8">
+      <c r="A19" s="8"/>
+      <c r="B19" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" ht="96" customHeight="1" spans="1:8">
+      <c r="A20" s="8"/>
+      <c r="B20" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="16" ht="126" customHeight="1" spans="1:8">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="F16" s="4" t="s">
+    <row r="21" ht="51" customHeight="1" spans="1:8">
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" ht="96" customHeight="1" spans="1:8">
+      <c r="A22" s="8"/>
+      <c r="B22" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G22" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H22" s="6" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="17" ht="66" customHeight="1" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="F17" s="4" t="s">
+    <row r="23" ht="81" customHeight="1" spans="1:8">
+      <c r="A23" s="8"/>
+      <c r="B23" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G23" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" ht="126" customHeight="1" spans="1:8">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" ht="96" customHeight="1" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" ht="111" customHeight="1" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="F19" s="4" t="s">
+      <c r="H24" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" ht="96" customHeight="1" spans="1:8">
+      <c r="A25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F25" s="9"/>
+      <c r="G25" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H25" s="9"/>
+    </row>
+    <row r="26" ht="171" customHeight="1" spans="1:8">
+      <c r="A26" s="8"/>
+      <c r="B26" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" ht="126" customHeight="1" spans="1:8">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" ht="81" customHeight="1" spans="1:8">
+      <c r="A28" s="8"/>
+      <c r="B28" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H19" s="4" t="s">
+      <c r="G28" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" ht="66" customHeight="1" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="F20" s="4" t="s">
+    <row r="29" ht="81" customHeight="1" spans="1:8">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="F29" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H20" s="4" t="s">
+      <c r="G29" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H29" s="6" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="21" ht="96" customHeight="1" spans="1:8">
-      <c r="A21" s="6"/>
-      <c r="B21" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="22" ht="51" customHeight="1" spans="1:8">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="23" ht="96" customHeight="1" spans="1:8">
-      <c r="A23" s="6"/>
-      <c r="B23" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" ht="81" customHeight="1" spans="1:8">
-      <c r="A24" s="6"/>
-      <c r="B24" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="25" ht="126" customHeight="1" spans="1:8">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="26" ht="96" customHeight="1" spans="1:8">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H26" s="7"/>
-    </row>
-    <row r="27" ht="171" customHeight="1" spans="1:8">
-      <c r="A27" s="6"/>
-      <c r="B27" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="28" ht="126" customHeight="1" spans="1:8">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="29" ht="81" customHeight="1" spans="1:8">
-      <c r="A29" s="6"/>
-      <c r="B29" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" ht="81" customHeight="1" spans="1:8">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A2:A30"/>
+  <mergeCells count="15">
+    <mergeCell ref="A2:A29"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B28:B29"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="F24:F25"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G17:G18"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="H6:H9"/>
-    <mergeCell ref="H16:H18"/>
-    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H24:H25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/PA替代需求列表.xlsx
+++ b/PA替代需求列表.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\topsec\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="15880" activeTab="1"/>
+    <workbookView windowHeight="18390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="309">
   <si>
     <t>一级需求</t>
   </si>
@@ -694,40 +699,168 @@
     <t>PA解密策略SSH Proxy类型解密SSH通信，可通过ssh-tunnel App-ID在策略中控制SSH隧道（端口转发/内网穿透），正常SSH管理流量放行；含不受支持算法检查/资源不足阻断会话等防护（PA Web帮助p164、p318-319）；天融信手册检索无SSH代理/SSH隧道控制命中</t>
   </si>
   <si>
-    <t>网络数据包代理(NPBroker)</t>
+    <t>网络数据包代理</t>
   </si>
   <si>
     <t>支持内联数据包代理策略将流量转发第三方安全链</t>
   </si>
   <si>
-    <t>已解密/未解密/非TLS流量内联转发第三方安全链，L3路由转发，支持转发流量类型选择</t>
+    <t>已解密/未解密/非TLS流量均可内联转发第三方安全链，</t>
   </si>
   <si>
     <t>PA网络数据包代理策略将已解密/未解密TLS/非TLS流量内联转发至第三方安全工具，路径选择选项卡应用数据包代理配置文件定义经路由L3安全链的转发方式（PA Web帮助p167-170）；天融信无网络数据包代理模块，最接近手段为WAF旁路联动（经交换机镜像引流，天融信手册《与WAF联动》页），非内联且无回注路径；对应矩阵#122</t>
   </si>
   <si>
-    <t>隧道检测(Tunnel Inspection)</t>
-  </si>
-  <si>
-    <t>支持GTP-U/VXLAN/非加密IPSec隧道内层检测</t>
-  </si>
-  <si>
-    <t>GTP-U/VXLAN/NULL加密IPSec(AH)隧道内层流量检测</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">隧道检测(Tunnel Inspection)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>修改第1、2条需求描述(标红是修改后的)及补充4条需求</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">支持GTP-U/VXLAN/非加密IPSec隧道内层检测
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>支持 GRE/GTP-U/非加密 IPSec/VXLAN 明文隧道内层流量检测</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">GTP-U/VXLAN/NULL加密IPSec(AH)隧道内层流量检测
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>解封装并深度检测 GRE、GTP-U、NULL/AH IPSec、VXLAN 隧道内的嵌套流量</t>
+    </r>
   </si>
   <si>
     <t>PA隧道检测支持GTP-U/VXLAN/非加密IPSec（NULL加密/AH传输模式）内层检测（PA Web帮助p172-173）；天融信VXLAN仅隧道封装转发与三层网关（天融信手册《业务接入端》《三层VXLAN网关》页），无内层安全检测，GTP检测检索无命中；对应矩阵#128/37</t>
   </si>
   <si>
-    <t>支持最大封装级数防护（max_encap）</t>
-  </si>
-  <si>
-    <t>隧道嵌套封装最大级数限制，超限丢弃</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">支持最大封装级数防护（max_encap）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>支持最大隧道检测级别控制（一级/两级）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">隧道嵌套封装最大级数限制，超限丢弃
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>解封装并深度检测 GRE、GTP-U、NULL/AH IPSec、VXLAN 隧道内的嵌套流量</t>
+    </r>
   </si>
   <si>
     <t>PA对隧道最大封装级数超限丢包防护，防隧道嵌套绕过（PA管理指南p655）；天融信手册无封装级数防护（检索无命中）</t>
   </si>
   <si>
-    <t>应用覆盖(App Override)</t>
+    <t>支持隧道协议严格标头检查与未知协议丢弃</t>
+  </si>
+  <si>
+    <t>对 GRE 等协议按 RFC 校验标头，不符或未知协议可选丢弃</t>
+  </si>
+  <si>
+    <t>支持安全选项与隧道源/目的区域独立分配</t>
+  </si>
+  <si>
+    <t>内部流量来源属于 Tunnel Source Zone，目标属于 Tunnel Destination Zone，独立匹配安全策略</t>
+  </si>
+  <si>
+    <t>支持隧道监控名称、监控标记与独立日志</t>
+  </si>
+  <si>
+    <t>配置 Monitor Name/Tag 分组；会话开始/结束日志；独立日志转发配置文件</t>
+  </si>
+  <si>
+    <t>支持 VXLAN 返回扫描到源（Return Scanned VXLAN Tunnel to Source）</t>
+  </si>
+  <si>
+    <t>将返回流量封装回原始 VXLAN 隧道端点（VTEP）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">应用覆盖(App Override)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>整个需求重新整理（标红项是重新整理的）</t>
+    </r>
   </si>
   <si>
     <t>支持应用替代流量跳过七层检测等效配置</t>
@@ -739,7 +872,43 @@
     <t>PA应用替代策略明确绕过第7层处理与威胁检查，改用第4层状态检查以加速（PA管理指南p1307）；天融信自定义应用加入规则库后仍默认经安全引擎检测（天融信手册《自定义应用》页）；迁移评估项：PA应用替代多为私有大流量业务加速，转换时需同步关闭对应策略的IPS/七层检测，否则性能被拖垮或误阻断</t>
   </si>
   <si>
-    <t>身份验证(Authentication)</t>
+    <t>支持基于源/目的区域、地址、协议/端口的应用替代策略匹配</t>
+  </si>
+  <si>
+    <t>在源/目标选项卡配置区域和地址，在协议/应用程序选项卡配置 TCP/UDP 端口范围及替代后的应用名称</t>
+  </si>
+  <si>
+    <t>支持强制识别为指定应用并绕过 App-ID 深度检测</t>
+  </si>
+  <si>
+    <t>匹配流量不再经过常规 App-ID 七层解码，直接按指定应用名处理</t>
+  </si>
+  <si>
+    <t>支持应用替代流量仅执行四层状态检测（跳过七层威胁检测）</t>
+  </si>
+  <si>
+    <t>应用替代后的流量仅做 L4 状态转发，不触发 IPS/Threat/URL 等七层安全配置文件检测</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">身份验证(Authentication)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>整个需求重新整理（标红的）</t>
+    </r>
   </si>
   <si>
     <t>支持认证策略超时与单次认证（SSO）</t>
@@ -769,6 +938,144 @@
     <t>PA无代理架构通过读取域控事件日志实现IP-用户毫秒级动态映射，大规模部署有专项规划（PA管理指南p866-867）；天融信AD对接的轮询间隔与并发认证能力手册未量化；迁移评估项：数万AD用户且移动频繁场景需实测天融信映射更新时延，避免基于用户的策略出现间歇性未授权拦截</t>
   </si>
   <si>
+    <t>支持身份验证策略规则的多维匹配与 Enforcement 对象</t>
+  </si>
+  <si>
+    <t>策略支持基于源/目的区域、地址、用户、HIP、设备匹配；绑定 Authentication Enforcement 对象指定认证方式（web-form、Kerberos、client-cert 等）</t>
+  </si>
+  <si>
+    <t>支持多种身份验证协议与级联认证</t>
+  </si>
+  <si>
+    <t>Authentication Profile 支持 LDAP、RADIUS、TACACS+、Kerberos、SAML、Local DB、MFA；Authentication Sequence 支持多源级联</t>
+  </si>
+  <si>
+    <t>支持 User-ID IP-用户映射多源采集</t>
+  </si>
+  <si>
+    <t>支持 AD 安全日志、Syslog、XML API、WMI、DHCP 日志、TS Agent、VM 信息源等多渠道映射</t>
+  </si>
+  <si>
+    <t>支持认证门户与超时控制</t>
+  </si>
+  <si>
+    <t>未认证流量重定向至 Captive Portal；支持 Authentication Timeout 与 Idle Timeout</t>
+  </si>
+  <si>
+    <t>支持 User-ID 动态映射时效性与可信源过滤</t>
+  </si>
+  <si>
+    <t>支持 IP-用户映射老化时间配置；支持 Trusted Source Address 过滤无效映射（p884）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">DoS防护(DoS Protection)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>修改第1第一条需求规格、第2条需求描述及补充3条需求</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">支持针对关键资源的分类/聚合DoS防护
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">分类(源/目的IP粒度)+聚合(全局)双层阈值限流
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PA DoS 策略基于源/目的区域（Zone）、地址、服务定义 Allow/Deny/Protect 动作</t>
+    </r>
+  </si>
+  <si>
+    <t>PA DoS策略基于源/目的接口、区域、地址、服务定义允许/拒绝/告警，规则可选聚合与分类双层DoS保护配置文件设定阈值速率（PA Web帮助p189-191、PA管理指南p1354）；天融信DDoS防护模块按防护对象（目的服务器）设阈值（pps/bps），可达目的IP粒度（天融信手册《配置策略模板》《日志查看》页）；对应矩阵#52/42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">支持DoS聚合配置文件（连接/秒阈值）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>支持分类与聚合双层 DoS 配置文件</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">连接数/秒阈值告警+最大速率限制
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>聚合（Aggregate）配置文件：针对总流量统一阈值（连接/秒、数据包/秒），超限全局告警/限速/阻断；
+分类（Classified）配置文件：针对单 IP 独立计数阈值，超限仅处理该 IP；
+两者均支持配置告警阈值、最大速率、阻断时长</t>
+    </r>
+  </si>
+  <si>
+    <t>PA聚合DoS配置文件按传入连接数/秒触发告警与最大速率限制；天融信DDoS防护模块按阈值（pps/bps）监视并触发防护（天融信手册《配置策略模板》页）</t>
+  </si>
+  <si>
+    <t>支持阻止 IP 列表联动与硬件/软件双重阻断</t>
+  </si>
+  <si>
+    <t>Protect 动作触发后自动加入 Block IP List，支持 hw（硬件快速阻断）与 sw（软件回退）及 Block Duration</t>
+  </si>
+  <si>
+    <t>支持 DoS 策略多动作（Allow / Deny / Protect）</t>
+  </si>
+  <si>
+    <t>不同流量可分别配置放行、直接拒绝或防护限速</t>
+  </si>
+  <si>
     <t>动态对象(Dynamic Objects)</t>
   </si>
   <si>
@@ -790,7 +1097,27 @@
     <t>PA动态地址组：查找标记(Tag)+基于标记的过滤器（AND/OR匹配）动态填充成员，VM信息源注册或XML/REST API定义标记，IP变化时策略自动生效（PA Web帮助p207-208、p228）；天融信手册检索动态地址组/标签/SDN/云平台联动无命中，地址组为静态IP/子网绑定（天融信手册《地址》页）；迁移评估项：PA云环境Tag微隔离策略需转换为静态地址组，IP漂移场景需人工或API维护</t>
   </si>
   <si>
-    <t>SD-WAN</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SD-WAN
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>补充6条需求</t>
+    </r>
   </si>
   <si>
     <t>支持按应用配置链路路径管理与链路质量探测</t>
@@ -809,6 +1136,64 @@
   </si>
   <si>
     <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路（PA Web帮助p195）；天融信有链路探测(ping)+智能选路(最小延迟优先)（天融信手册《策略路由》页），无jitter/latency/loss多维指标</t>
+  </si>
+  <si>
+    <t>支持 SaaS 应用质量优化</t>
+  </si>
+  <si>
+    <t>针对 Office 365、Salesforce、Zoom 等 SaaS 应用，提供独立的探测和选路策略，直接优选通向云服务商的最佳 POP 点路径。</t>
+  </si>
+  <si>
+    <t>文档依据：Objects &gt; SD-WAN Link Management &gt; SaaS Quality Profile (p325)</t>
+  </si>
+  <si>
+    <t>支持多链路流量分发策略</t>
+  </si>
+  <si>
+    <t>定义在多链路（MPLS + 宽带 + 4G/5G）场景下的负载分担模式，如按会话数、按字节、主备切换、加权轮询等。</t>
+  </si>
+  <si>
+    <t>Objects &gt; SD-WAN Link Management &gt; Traffic Distribution Profile (p326)</t>
+  </si>
+  <si>
+    <t>支持丢包敏感业务的前向纠错</t>
+  </si>
+  <si>
+    <t>对语音、视频会议等实时应用，在单条链路质量劣化时启用 FEC（Forward Error Correction），通过冗余包补偿丢包，无需重传</t>
+  </si>
+  <si>
+    <t>Objects &gt; SD-WAN Link Management &gt; Error Correction Profile (p327)</t>
+  </si>
+  <si>
+    <t>支持 SD-WAN 逻辑接口绑定与物理链路聚合</t>
+  </si>
+  <si>
+    <t>将多个物理 WAN 接口（Ethernet、PPPoE、Cellular 等）绑定为一个 SD-WAN 接口组，作为统一出口被策略引用。</t>
+  </si>
+  <si>
+    <t>Network &gt; Interfaces &gt; SD-WAN (p422)</t>
+  </si>
+  <si>
+    <t>支持 Panorama 集中式 SD-WAN 管理与 VPN 集群</t>
+  </si>
+  <si>
+    <t>在 Panorama 上集中管理所有分支 SD-WAN 设备、配置 SD-WAN VPN 集群（站点间自动 VPN 互联）、查看跨站点链路状态与隧道健康度。</t>
+  </si>
+  <si>
+    <t>文档依据：Panorama &gt; SD-WAN (p1074-1078)，包含：
+SD-WAN 设备管理
+SD-WAN VPN 集群
+SD-WAN 监控
+SD-WAN 报告</t>
+  </si>
+  <si>
+    <t>支持 SD-WAN 隧道/链路的集中监控与日志审计</t>
+  </si>
+  <si>
+    <t>在 ACC 或 Monitor 中查看 SD-WAN 链路切换事件、质量告警、隧道状态变化，并生成报告。</t>
+  </si>
+  <si>
+    <t>文档依据：Monitor &gt; Logs / ACC（与 SD-WAN 策略命中、链路质量事件相关）</t>
   </si>
 </sst>
 </file>
@@ -822,7 +1207,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="36">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -846,6 +1231,32 @@
       <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.25"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="8" tint="-0.25"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1026,6 +1437,29 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1229,7 +1663,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1244,6 +1678,19 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -1281,9 +1728,7 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -1296,17 +1741,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1338,6 +1772,43 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1346,6 +1817,30 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1464,152 +1959,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="15">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="16">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="19">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="19">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="21">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="23">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1625,6 +2120,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1634,120 +2132,209 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1759,14 +2346,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1775,11 +2359,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1791,20 +2375,20 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2127,1119 +2711,1119 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.2" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="11.7115384615385" style="15" customWidth="1"/>
-    <col min="2" max="2" width="19.7115384615385" style="15" customWidth="1"/>
-    <col min="3" max="3" width="54.7115384615385" style="15" customWidth="1"/>
-    <col min="4" max="4" width="45.2884615384615" style="15" customWidth="1"/>
-    <col min="5" max="5" width="7.71153846153846" style="15" customWidth="1"/>
-    <col min="6" max="6" width="37.8557692307692" style="15" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.71153846153846" style="15" customWidth="1"/>
-    <col min="8" max="8" width="9.71153846153846" style="16" customWidth="1"/>
+    <col min="1" max="1" width="11.7090909090909" style="51" customWidth="1"/>
+    <col min="2" max="2" width="19.7090909090909" style="51" customWidth="1"/>
+    <col min="3" max="3" width="54.7090909090909" style="51" customWidth="1"/>
+    <col min="4" max="4" width="45.2909090909091" style="51" customWidth="1"/>
+    <col min="5" max="5" width="7.70909090909091" style="51" customWidth="1"/>
+    <col min="6" max="6" width="37.8545454545455" style="51" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.70909090909091" style="51" customWidth="1"/>
+    <col min="8" max="8" width="9.70909090909091" style="52" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="18" t="s">
+      <c r="F1" s="55"/>
+      <c r="G1" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="54" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="23" t="s">
+      <c r="D2" s="58"/>
+      <c r="E2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:8">
-      <c r="A3" s="8"/>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="10"/>
+      <c r="B3" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H3" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:8">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="22" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:8">
-      <c r="A5" s="8"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="22" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A6" s="8"/>
-      <c r="B6" s="27" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="22" t="s">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="22" t="s">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="22" t="s">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="22" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="22" t="s">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="22" t="s">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
     </row>
     <row r="13" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A13" s="9"/>
-      <c r="B13" s="27" t="s">
+      <c r="A13" s="11"/>
+      <c r="B13" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="25" t="s">
+      <c r="H13" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F14" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="H14" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A15" s="30"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="22" t="s">
+      <c r="A15" s="13"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A16" s="30"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="22" t="s">
+      <c r="A16" s="13"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A17" s="30"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="22" t="s">
+      <c r="A17" s="13"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A18" s="30"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="22" t="s">
+      <c r="A18" s="13"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A19" s="30"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="22" t="s">
+      <c r="A19" s="13"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A20" s="30"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="22" t="s">
+      <c r="A20" s="13"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A21" s="30"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="22" t="s">
+      <c r="A21" s="13"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
     </row>
     <row r="22" ht="32.25" customHeight="1" spans="1:8">
-      <c r="A22" s="31"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="22" t="s">
+      <c r="A22" s="12"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="32" t="s">
+      <c r="F23" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H23" s="25" t="s">
+      <c r="H23" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="33" t="s">
+      <c r="F24" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="25" t="s">
+      <c r="H24" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="34" t="s">
+      <c r="D25" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="E25" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="24" t="s">
+      <c r="F25" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="G25" s="22" t="s">
+      <c r="G25" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="25" t="s">
+      <c r="H25" s="30" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" s="14" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A26" s="30"/>
-      <c r="B26" s="27" t="s">
+    <row r="26" s="50" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
+      <c r="A26" s="13"/>
+      <c r="B26" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="34"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="25"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="30"/>
     </row>
     <row r="27" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A27" s="30"/>
-      <c r="B27" s="27" t="s">
+      <c r="A27" s="13"/>
+      <c r="B27" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="24" t="s">
+      <c r="F27" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="22" t="s">
+      <c r="G27" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H27" s="25" t="s">
+      <c r="H27" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A28" s="30"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="22" t="s">
+      <c r="A28" s="13"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
     </row>
     <row r="29" ht="60" customHeight="1" spans="1:8">
-      <c r="A29" s="30"/>
-      <c r="B29" s="27" t="s">
+      <c r="A29" s="13"/>
+      <c r="B29" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="25" t="s">
+      <c r="D29" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="E29" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="36" t="s">
+      <c r="F29" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="G29" s="22" t="s">
+      <c r="G29" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="H29" s="25" t="s">
+      <c r="H29" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A30" s="30"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="22" t="s">
+      <c r="A30" s="13"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="E30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="22" t="s">
+      <c r="F30" s="10"/>
+      <c r="G30" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H30" s="25" t="s">
+      <c r="H30" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A31" s="31"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="22" t="s">
+      <c r="A31" s="12"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="37" t="s">
+      <c r="E31" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="22" t="s">
+      <c r="F31" s="11"/>
+      <c r="G31" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="25" t="s">
+      <c r="H31" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="24" t="s">
+      <c r="F32" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="22" t="s">
+      <c r="G32" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="25" t="s">
+      <c r="H32" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A33" s="31"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="22" t="s">
+      <c r="A33" s="12"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="22"/>
-      <c r="E34" s="23" t="s">
+      <c r="D34" s="58"/>
+      <c r="E34" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="24" t="s">
+      <c r="F34" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H34" s="25" t="s">
+      <c r="H34" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A35" s="30"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="22" t="s">
+      <c r="A35" s="13"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="22"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
     </row>
     <row r="36" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A36" s="30"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="22" t="s">
+      <c r="A36" s="13"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="58" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="22"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
     </row>
     <row r="37" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A37" s="31"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="38" t="s">
+      <c r="A37" s="12"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="D37" s="38"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="D38" s="39"/>
-      <c r="E38" s="37" t="s">
+      <c r="D38" s="72"/>
+      <c r="E38" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="40" t="s">
+      <c r="F38" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H38" s="25" t="s">
+      <c r="H38" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A39" s="8"/>
-      <c r="B39" s="27" t="s">
+      <c r="A39" s="10"/>
+      <c r="B39" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="39" t="s">
+      <c r="C39" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="D39" s="39"/>
-      <c r="E39" s="37" t="s">
+      <c r="D39" s="72"/>
+      <c r="E39" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
     </row>
     <row r="40" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A40" s="8"/>
-      <c r="B40" s="27" t="s">
+      <c r="A40" s="10"/>
+      <c r="B40" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="39" t="s">
+      <c r="C40" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="D40" s="41" t="s">
+      <c r="D40" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="37" t="s">
+      <c r="E40" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="36" t="s">
+      <c r="F40" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="G40" s="22" t="s">
+      <c r="G40" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="H40" s="25" t="s">
+      <c r="H40" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A41" s="8"/>
-      <c r="B41" s="27" t="s">
+      <c r="A41" s="10"/>
+      <c r="B41" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="D41" s="39" t="s">
+      <c r="D41" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="E41" s="37" t="s">
+      <c r="E41" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="F41" s="36" t="s">
+      <c r="F41" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="G41" s="22" t="s">
+      <c r="G41" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="H41" s="25" t="s">
+      <c r="H41" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A42" s="8"/>
-      <c r="B42" s="27" t="s">
+      <c r="A42" s="10"/>
+      <c r="B42" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="58" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="39"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="25"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="69"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="30"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A43" s="9"/>
-      <c r="B43" s="27" t="s">
+      <c r="A43" s="11"/>
+      <c r="B43" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="39" t="s">
+      <c r="C43" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="39"/>
-      <c r="E43" s="37" t="s">
+      <c r="D43" s="72"/>
+      <c r="E43" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="F43" s="36" t="s">
+      <c r="F43" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="G43" s="22" t="s">
+      <c r="G43" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="H43" s="25" t="s">
+      <c r="H43" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A44" s="42" t="s">
+      <c r="A44" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="43" t="s">
+      <c r="B44" s="76" t="s">
         <v>111</v>
       </c>
-      <c r="C44" s="44" t="s">
+      <c r="C44" s="77" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="44" t="s">
+      <c r="D44" s="77" t="s">
         <v>113</v>
       </c>
-      <c r="E44" s="45" t="s">
+      <c r="E44" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="46" t="s">
+      <c r="F44" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="G44" s="47" t="s">
+      <c r="G44" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="H44" s="48" t="s">
+      <c r="H44" s="31" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A45" s="30"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="39" t="s">
+      <c r="A45" s="13"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="D45" s="39" t="s">
+      <c r="D45" s="72" t="s">
         <v>116</v>
       </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="49" t="s">
+      <c r="E45" s="10"/>
+      <c r="F45" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="G45" s="22" t="s">
+      <c r="G45" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="25" t="s">
+      <c r="H45" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A46" s="30"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="39" t="s">
+      <c r="A46" s="13"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="72" t="s">
         <v>117</v>
       </c>
-      <c r="D46" s="39"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
     </row>
     <row r="47" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A47" s="30"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="39" t="s">
+      <c r="A47" s="13"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="D47" s="39"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="49" t="s">
+      <c r="D47" s="72"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="G47" s="22" t="s">
+      <c r="G47" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H47" s="25" t="s">
+      <c r="H47" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A48" s="31"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="50" t="s">
+      <c r="A48" s="12"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="D48" s="50"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="32" t="s">
+      <c r="D48" s="82"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="G48" s="38" t="s">
+      <c r="G48" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="H48" s="51" t="s">
+      <c r="H48" s="83" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="49" ht="42.75" customHeight="1" spans="1:8">
-      <c r="A49" s="52" t="s">
+      <c r="A49" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="B49" s="52" t="s">
+      <c r="B49" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="C49" s="53" t="s">
+      <c r="C49" s="85" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="54" t="s">
+      <c r="D49" s="86" t="s">
         <v>122</v>
       </c>
-      <c r="E49" s="55" t="s">
+      <c r="E49" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="56"/>
-      <c r="G49" s="57" t="s">
+      <c r="F49" s="87"/>
+      <c r="G49" s="88" t="s">
         <v>103</v>
       </c>
-      <c r="H49" s="58"/>
+      <c r="H49" s="89"/>
     </row>
     <row r="50" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A50" s="59"/>
-      <c r="B50" s="59"/>
-      <c r="C50" s="53" t="s">
+      <c r="A50" s="90"/>
+      <c r="B50" s="90"/>
+      <c r="C50" s="85" t="s">
         <v>123</v>
       </c>
-      <c r="D50" s="60" t="s">
+      <c r="D50" s="91" t="s">
         <v>124</v>
       </c>
-      <c r="E50" s="61" t="s">
+      <c r="E50" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="F50" s="62"/>
-      <c r="G50" s="57" t="s">
+      <c r="F50" s="93"/>
+      <c r="G50" s="88" t="s">
         <v>103</v>
       </c>
-      <c r="H50" s="63"/>
+      <c r="H50" s="94"/>
     </row>
     <row r="51" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A51" s="59"/>
-      <c r="B51" s="59"/>
-      <c r="C51" s="53" t="s">
+      <c r="A51" s="90"/>
+      <c r="B51" s="90"/>
+      <c r="C51" s="85" t="s">
         <v>125</v>
       </c>
-      <c r="D51" s="64" t="s">
+      <c r="D51" s="95" t="s">
         <v>126</v>
       </c>
-      <c r="E51" s="61" t="s">
+      <c r="E51" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="F51" s="56"/>
-      <c r="G51" s="57" t="s">
+      <c r="F51" s="87"/>
+      <c r="G51" s="88" t="s">
         <v>103</v>
       </c>
-      <c r="H51" s="58"/>
+      <c r="H51" s="89"/>
     </row>
     <row r="52" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A52" s="65"/>
-      <c r="B52" s="65"/>
-      <c r="C52" s="64" t="s">
+      <c r="A52" s="96"/>
+      <c r="B52" s="96"/>
+      <c r="C52" s="95" t="s">
         <v>127</v>
       </c>
-      <c r="D52" s="54" t="s">
+      <c r="D52" s="86" t="s">
         <v>128</v>
       </c>
-      <c r="E52" s="66" t="s">
+      <c r="E52" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="56" t="s">
+      <c r="F52" s="87" t="s">
         <v>129</v>
       </c>
-      <c r="G52" s="57" t="s">
+      <c r="G52" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="H52" s="58" t="s">
+      <c r="H52" s="89" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A53" s="43" t="s">
+      <c r="A53" s="76" t="s">
         <v>130</v>
       </c>
-      <c r="B53" s="43" t="s">
+      <c r="B53" s="76" t="s">
         <v>131</v>
       </c>
-      <c r="C53" s="44" t="s">
+      <c r="C53" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="D53" s="44"/>
-      <c r="E53" s="45" t="s">
+      <c r="D53" s="77"/>
+      <c r="E53" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="F53" s="46" t="s">
+      <c r="F53" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="G53" s="47" t="s">
+      <c r="G53" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="H53" s="48" t="s">
+      <c r="H53" s="31" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="54" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A54" s="9"/>
-      <c r="B54" s="27" t="s">
+      <c r="A54" s="11"/>
+      <c r="B54" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="C54" s="25" t="s">
+      <c r="C54" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="D54" s="41" t="s">
+      <c r="D54" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="E54" s="37" t="s">
+      <c r="E54" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="F54" s="36" t="s">
+      <c r="F54" s="69" t="s">
         <v>136</v>
       </c>
-      <c r="G54" s="22" t="s">
+      <c r="G54" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="H54" s="25" t="s">
+      <c r="H54" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A55" s="28" t="s">
+      <c r="A55" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="62" t="s">
         <v>138</v>
       </c>
-      <c r="C55" s="39" t="s">
+      <c r="C55" s="72" t="s">
         <v>139</v>
       </c>
-      <c r="D55" s="39"/>
-      <c r="E55" s="37" t="s">
+      <c r="D55" s="72"/>
+      <c r="E55" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="F55" s="36"/>
-      <c r="G55" s="22" t="s">
+      <c r="F55" s="69"/>
+      <c r="G55" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="H55" s="25" t="s">
+      <c r="H55" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="56" ht="42.75" customHeight="1" spans="1:8">
-      <c r="A56" s="28" t="s">
+      <c r="A56" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="62" t="s">
         <v>142</v>
       </c>
-      <c r="C56" s="39" t="s">
+      <c r="C56" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="D56" s="41" t="s">
+      <c r="D56" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="E56" s="37" t="s">
+      <c r="E56" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="F56" s="49" t="s">
+      <c r="F56" s="81" t="s">
         <v>145</v>
       </c>
-      <c r="G56" s="22"/>
-      <c r="H56" s="25" t="s">
+      <c r="G56" s="58"/>
+      <c r="H56" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="57" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A57" s="27" t="s">
+      <c r="A57" s="62" t="s">
         <v>141</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="62" t="s">
         <v>146</v>
       </c>
-      <c r="C57" s="39" t="s">
+      <c r="C57" s="72" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="39" t="s">
+      <c r="D57" s="72" t="s">
         <v>148</v>
       </c>
-      <c r="E57" s="37" t="s">
+      <c r="E57" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="F57" s="49" t="s">
+      <c r="F57" s="81" t="s">
         <v>149</v>
       </c>
-      <c r="G57" s="22" t="s">
+      <c r="G57" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="H57" s="25" t="s">
+      <c r="H57" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A58" s="67" t="s">
+      <c r="A58" s="98" t="s">
         <v>150</v>
       </c>
-      <c r="B58" s="67" t="s">
+      <c r="B58" s="98" t="s">
         <v>150</v>
       </c>
-      <c r="C58" s="38" t="s">
+      <c r="C58" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="D58" s="50" t="s">
+      <c r="D58" s="82" t="s">
         <v>152</v>
       </c>
-      <c r="E58" s="68" t="s">
+      <c r="E58" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="F58" s="69" t="s">
+      <c r="F58" s="100" t="s">
         <v>153</v>
       </c>
-      <c r="G58" s="38" t="s">
+      <c r="G58" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="H58" s="51" t="s">
+      <c r="H58" s="83" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="59" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A59" s="52" t="s">
+      <c r="A59" s="84" t="s">
         <v>154</v>
       </c>
-      <c r="B59" s="52" t="s">
+      <c r="B59" s="84" t="s">
         <v>154</v>
       </c>
-      <c r="C59" s="70" t="s">
+      <c r="C59" s="101" t="s">
         <v>155</v>
       </c>
-      <c r="D59" s="62"/>
-      <c r="E59" s="66" t="s">
+      <c r="D59" s="93"/>
+      <c r="E59" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="F59" s="62"/>
-      <c r="G59" s="38" t="s">
+      <c r="F59" s="93"/>
+      <c r="G59" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="H59" s="63" t="s">
+      <c r="H59" s="94" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3308,17 +3892,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.2" outlineLevelCol="7"/>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="2" width="19.3942307692308" style="1" customWidth="1"/>
-    <col min="3" max="3" width="40" style="2" customWidth="1"/>
-    <col min="4" max="4" width="41.4519230769231" style="2" customWidth="1"/>
-    <col min="5" max="5" width="62" style="2" customWidth="1"/>
-    <col min="6" max="6" width="7.70192307692308" style="1" customWidth="1"/>
+    <col min="1" max="2" width="19.3909090909091" style="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7181818181818" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.4545454545455" style="2" customWidth="1"/>
+    <col min="5" max="5" width="76.5727272727273" style="2" customWidth="1"/>
+    <col min="6" max="6" width="7.69090909090909" style="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.70192307692308" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.69090909090909" style="1" customWidth="1"/>
+    <col min="9" max="16383" width="9" style="3" customWidth="1"/>
+    <col min="16384" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8">
@@ -3343,647 +3928,982 @@
       <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="51" customHeight="1" spans="1:8">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="9" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="3" ht="84" customHeight="1" spans="1:8">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7" t="s">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="9" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="4" ht="70" customHeight="1" spans="1:8">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="7" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
     </row>
     <row r="5" ht="51" customHeight="1" spans="1:8">
-      <c r="A5" s="8"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="9" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="6" ht="51" customHeight="1" spans="1:8">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="7" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="9" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1" spans="1:8">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="7" t="s">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H7" s="8"/>
+      <c r="H7" s="13"/>
     </row>
     <row r="8" ht="84" customHeight="1" spans="1:8">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="7" t="s">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="8"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" ht="112" customHeight="1" spans="1:8">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="7" t="s">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="12"/>
     </row>
     <row r="10" ht="171" customHeight="1" spans="1:8">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="7" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1" spans="1:8">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="12" t="s">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12" t="s">
+      <c r="D11" s="16"/>
+      <c r="E11" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" ht="81" customHeight="1" spans="1:8">
-      <c r="A12" s="8"/>
-      <c r="B12" s="13" t="s">
+      <c r="A12" s="10"/>
+      <c r="B12" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="9" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="13" ht="96" customHeight="1" spans="1:8">
-      <c r="A13" s="8"/>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="9" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="14" ht="111" customHeight="1" spans="1:8">
-      <c r="A14" s="8"/>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="9" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="15" ht="51" customHeight="1" spans="1:8">
-      <c r="A15" s="8"/>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="10"/>
+      <c r="B15" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" ht="126" customHeight="1" spans="1:8">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="7" t="s">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" ht="66" customHeight="1" spans="1:8">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="7" t="s">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" ht="96" customHeight="1" spans="1:8">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="7" t="s">
+      <c r="A18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" ht="111" customHeight="1" spans="1:8">
-      <c r="A19" s="8"/>
-      <c r="B19" s="6" t="s">
+      <c r="A19" s="10"/>
+      <c r="B19" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" ht="96" customHeight="1" spans="1:8">
-      <c r="A20" s="8"/>
-      <c r="B20" s="6" t="s">
+      <c r="A20" s="10"/>
+      <c r="B20" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="21" ht="51" customHeight="1" spans="1:8">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="7" t="s">
+    <row r="21" ht="96" customHeight="1" spans="1:8">
+      <c r="A21" s="10"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="9"/>
+    </row>
+    <row r="22" ht="54" customHeight="1" spans="1:8">
+      <c r="A22" s="10"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E22" s="23"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="9"/>
+    </row>
+    <row r="23" ht="50" customHeight="1" spans="1:8">
+      <c r="A23" s="10"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="E23" s="23"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="9"/>
+    </row>
+    <row r="24" ht="45" customHeight="1" spans="1:8">
+      <c r="A24" s="10"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="E24" s="23"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="9"/>
+    </row>
+    <row r="25" ht="42" customHeight="1" spans="1:8">
+      <c r="A25" s="10"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E25" s="23"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="9"/>
+    </row>
+    <row r="26" ht="51" customHeight="1" spans="1:8">
+      <c r="A26" s="10"/>
+      <c r="B26" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" s="9"/>
+    </row>
+    <row r="27" ht="51" customHeight="1" spans="1:8">
+      <c r="A27" s="10"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="9"/>
+    </row>
+    <row r="28" ht="51" customHeight="1" spans="1:8">
+      <c r="A28" s="10"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="9"/>
+    </row>
+    <row r="29" ht="51" customHeight="1" spans="1:8">
+      <c r="A29" s="10"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="9"/>
+    </row>
+    <row r="30" ht="81" customHeight="1" spans="1:8">
+      <c r="A30" s="10"/>
+      <c r="B30" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" s="29" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="22" ht="96" customHeight="1" spans="1:8">
-      <c r="A22" s="8"/>
-      <c r="B22" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="F22" s="6" t="s">
+    <row r="31" ht="126" customHeight="1" spans="1:8">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" ht="126" customHeight="1" spans="1:8">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="F32" s="31"/>
+      <c r="G32" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H32" s="24"/>
+    </row>
+    <row r="33" ht="69" customHeight="1" spans="1:8">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="28" t="s">
+        <v>256</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="24"/>
+    </row>
+    <row r="34" ht="74" customHeight="1" spans="1:8">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="24"/>
+    </row>
+    <row r="35" ht="54" customHeight="1" spans="1:8">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="24"/>
+    </row>
+    <row r="36" ht="47" customHeight="1" spans="1:8">
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="D36" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="E36" s="8"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="24"/>
+    </row>
+    <row r="37" ht="47" customHeight="1" spans="1:8">
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="E37" s="8"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="24"/>
+    </row>
+    <row r="38" ht="96" customHeight="1" spans="1:8">
+      <c r="A38" s="13"/>
+      <c r="B38" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H22" s="6" t="s">
+      <c r="G38" s="8" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="23" ht="81" customHeight="1" spans="1:8">
-      <c r="A23" s="8"/>
-      <c r="B23" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="F23" s="6" t="s">
+      <c r="H38" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" ht="117" customHeight="1" spans="1:8">
+      <c r="A39" s="13"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F39" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H23" s="6" t="s">
+      <c r="G39" s="8" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="24" ht="126" customHeight="1" spans="1:8">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="F24" s="6" t="s">
+      <c r="H39" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" ht="96" customHeight="1" spans="1:8">
+      <c r="A40" s="13"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="E40" s="8"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="7"/>
+    </row>
+    <row r="41" ht="96" customHeight="1" spans="1:8">
+      <c r="A41" s="13"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="E41" s="8"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="20"/>
+    </row>
+    <row r="42" ht="171" customHeight="1" spans="1:8">
+      <c r="A42" s="10"/>
+      <c r="B42" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="C42" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="D42" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="E42" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="F42" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G42" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H42" s="40" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="25" ht="96" customHeight="1" spans="1:8">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" ht="171" customHeight="1" spans="1:8">
-      <c r="A26" s="8"/>
-      <c r="B26" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="F26" s="6" t="s">
+    <row r="43" ht="126" customHeight="1" spans="1:8">
+      <c r="A43" s="10"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D43" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="E43" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="F43" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G43" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H43" s="40" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="27" ht="126" customHeight="1" spans="1:8">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="F27" s="6" t="s">
+    <row r="44" ht="81" customHeight="1" spans="1:8">
+      <c r="A44" s="13"/>
+      <c r="B44" s="42" t="s">
+        <v>284</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="H44" s="24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" ht="81" customHeight="1" spans="1:8">
+      <c r="A45" s="13"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="F45" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="H27" s="6" t="s">
+      <c r="G45" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="H45" s="24" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="28" ht="81" customHeight="1" spans="1:8">
-      <c r="A28" s="8"/>
-      <c r="B28" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" ht="81" customHeight="1" spans="1:8">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>162</v>
-      </c>
+    <row r="46" ht="42" spans="1:8">
+      <c r="A46" s="45"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="46" t="s">
+        <v>291</v>
+      </c>
+      <c r="D46" s="47" t="s">
+        <v>292</v>
+      </c>
+      <c r="E46" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="F46" s="48"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="48"/>
+    </row>
+    <row r="47" ht="42" spans="1:8">
+      <c r="A47" s="45"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="D47" s="47" t="s">
+        <v>295</v>
+      </c>
+      <c r="E47" s="46" t="s">
+        <v>296</v>
+      </c>
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="48"/>
+    </row>
+    <row r="48" ht="56" spans="1:8">
+      <c r="A48" s="45"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="D48" s="47" t="s">
+        <v>298</v>
+      </c>
+      <c r="E48" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="F48" s="48"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="48"/>
+    </row>
+    <row r="49" ht="42" spans="1:8">
+      <c r="A49" s="45"/>
+      <c r="B49" s="43"/>
+      <c r="C49" s="46" t="s">
+        <v>300</v>
+      </c>
+      <c r="D49" s="47" t="s">
+        <v>301</v>
+      </c>
+      <c r="E49" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
+    </row>
+    <row r="50" ht="70" spans="1:8">
+      <c r="A50" s="45"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="D50" s="47" t="s">
+        <v>304</v>
+      </c>
+      <c r="E50" s="47" t="s">
+        <v>305</v>
+      </c>
+      <c r="F50" s="48"/>
+      <c r="G50" s="48"/>
+      <c r="H50" s="48"/>
+    </row>
+    <row r="51" ht="42" spans="1:8">
+      <c r="A51" s="45"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="D51" s="47" t="s">
+        <v>307</v>
+      </c>
+      <c r="E51" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A2:A29"/>
+  <mergeCells count="16">
+    <mergeCell ref="A2:A45"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B37"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B51"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F24:F25"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="H6:H9"/>
-    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H31:H37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/PA替代需求列表.xlsx
+++ b/PA替代需求列表.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="300">
   <si>
     <t>一级需求</t>
   </si>
@@ -736,7 +736,7 @@
     <t>PA隧道检测策略可选启用：超过最大隧道检测级别的封装数据包丢弃（PA Web帮助p174）；天融信手册无对应选项（检索无命中）</t>
   </si>
   <si>
-    <t>支持解封装内层流量的独立安全区域映射与策略匹配</t>
+    <t>支持解配置内层流量的独立安全区域映射与策略匹配</t>
   </si>
   <si>
     <t>内层流量独立分配至指定的隧道源安全区域与隧道目的安全区域，实现隧道内层流量与原始外层流量的安全策略解耦与独立匹配</t>
@@ -754,7 +754,7 @@
     <t>经安全检测引擎处理完毕后，将响应流量自动重新封装并原路送回初始 VTEP 端点</t>
   </si>
   <si>
-    <t>应用覆盖(App Override)</t>
+    <t>应用覆盖</t>
   </si>
   <si>
     <t>支持应用替代流量跳过七层检测等效配置</t>
@@ -766,24 +766,6 @@
     <t>PA应用替代策略明确绕过第7层处理与威胁检查，改用第4层状态检查以加速（PA管理指南p1307）；天融信自定义应用加入规则库后仍默认经安全引擎检测（天融信手册《自定义应用》页）；迁移评估项：PA应用替代多为私有大流量业务加速，转换时需同步关闭对应策略的IPS/七层检测，否则性能被拖垮或误阻断</t>
   </si>
   <si>
-    <t>支持基于源/目的区域、地址、协议/端口的应用替代策略匹配</t>
-  </si>
-  <si>
-    <t>在源/目标选项卡配置区域和地址，在协议/应用程序选项卡配置 TCP/UDP 端口范围及替代后的应用名称</t>
-  </si>
-  <si>
-    <t>支持强制识别为指定应用并绕过 App-ID 深度检测</t>
-  </si>
-  <si>
-    <t>匹配流量不再经过常规 App-ID 七层解码，直接按指定应用名处理</t>
-  </si>
-  <si>
-    <t>支持应用替代流量仅执行四层状态检测（跳过七层威胁检测）</t>
-  </si>
-  <si>
-    <t>应用替代后的流量仅做 L4 状态转发，不触发 IPS/Threat/URL 等七层安全配置文件检测</t>
-  </si>
-  <si>
     <t>身份验证(Authentication)</t>
   </si>
   <si>
@@ -796,24 +778,15 @@
     <t>PA支持认证超时减少重复质询、Kerberos/SAML/RADIUS等对接（PA Web帮助p186）；天融信手册检索认证超时/单点登录/SSO无命中（仅在线用户在线时长查看与强制下线）；迁移评估项：需核实天融信认证会话有效期配置与SSO对接能力</t>
   </si>
   <si>
-    <t>支持流量策略触发多因素认证质询（MFA Enforcement）</t>
-  </si>
-  <si>
-    <t>流量策略匹配触发MFA质询（非登录场景，MFA供应商API/RADIUS）</t>
+    <t>支持基于应用与流量策略触发的业务级MF 质询</t>
+  </si>
+  <si>
+    <t>根据安全策略直接对高敏感业务流量触发 MFA 质询</t>
   </si>
   <si>
     <t>PA身份验证策略通过Authentication Enforcement对象对匹配流量强制质询，支持多因素身份验证（每因素独立超时，防火墙记录时间戳），MFA供应商API/RADIUS对接（PA Web帮助p185-186、p310、p735-742）；天融信双因子认证（密码+短信/证书/Ukey）仅限管理员/用户登录场景（天融信手册《登录安全策略》页），无流量策略触发MFA质询</t>
   </si>
   <si>
-    <t>支持User-ID动态映射时效性等效（AD日志毫秒级更新）</t>
-  </si>
-  <si>
-    <t>AD域事件日志毫秒级IP-用户映射更新</t>
-  </si>
-  <si>
-    <t>PA无代理架构通过读取域控事件日志实现IP-用户毫秒级动态映射，大规模部署有专项规划（PA管理指南p866-867）；天融信AD对接的轮询间隔与并发认证能力手册未量化；迁移评估项：数万AD用户且移动频繁场景需实测天融信映射更新时延，避免基于用户的策略出现间歇性未授权拦截</t>
-  </si>
-  <si>
     <t>支持身份验证策略规则的多维匹配与 Enforcement 对象</t>
   </si>
   <si>
@@ -823,34 +796,16 @@
     <t>PA身份验证策略支持源/目的区域、地址、用户、HIP等多维匹配，并绑定Authentication Enforcement对象指定认证方式与MFA供应商（PA Web帮助p182-186）；天融信无独立认证策略库，认证绑定于用户访问策略与门户认证（天融信手册《管理用户》页）；对应矩阵#35</t>
   </si>
   <si>
-    <t>支持多种身份验证协议与级联认证</t>
-  </si>
-  <si>
-    <t>Authentication Profile 支持 LDAP、RADIUS、TACACS+、Kerberos、SAML、Local DB、MFA；Authentication Sequence 支持多源级联</t>
-  </si>
-  <si>
-    <t>PA Authentication Profile支持LDAP/RADIUS/TACACS+/Kerberos/SAML/本地/MFA，Authentication Sequence支持多源级联认证（PA Web帮助p182-186）；天融信联动外部认证服务器支持RADIUS/LDAP/TACACS（天融信手册《用户管理》页），SAML对接与多源级联认证手册未见；部分支持</t>
-  </si>
-  <si>
-    <t>支持 User-ID IP-用户映射多源采集</t>
-  </si>
-  <si>
-    <t>支持 AD 安全日志、Syslog、XML API、WMI、DHCP 日志、TS Agent、VM 信息源等多渠道映射</t>
-  </si>
-  <si>
-    <t>PA User-ID支持AD安全日志/Syslog/XML API/WMI/DHCP日志/TS Agent等多源IP-用户映射采集（PA管理指南p866起）；天融信用户认证经AD/LDAP/RADIUS联动实现（天融信手册《用户管理》《添加Radius服务器》页），XML API/WMI/TS Agent等多源采集机制手册未见；部分支持</t>
-  </si>
-  <si>
-    <t>支持认证门户与超时控制</t>
-  </si>
-  <si>
-    <t>未认证流量重定向至 Captive Portal；支持 Authentication Timeout 与 Idle Timeout</t>
-  </si>
-  <si>
-    <t>支持 User-ID 动态映射时效性与可信源过滤</t>
-  </si>
-  <si>
-    <t>支持 IP-用户映射老化时间配置；支持 Trusted Source Address 过滤无效映射（p884）</t>
+    <t>支持 IP-用户映射的可信源地址过滤</t>
+  </si>
+  <si>
+    <t>配置可信源地址（Trusted Source Address）白名单，仅允许指定的域控、日志服务器或 Agent 提交 IP-用户映射关系，自动识别并过滤来自代理设备（Proxy/NAT）或非授权日志源的无效映射</t>
+  </si>
+  <si>
+    <t>支持 IP-用户映射关系的独立老化控制</t>
+  </si>
+  <si>
+    <t>对动态采集的 IP-用户映射关系配置独立的老化超时时间（Mapping Timeout），支持根据用户离线或超时事件自动清空映射表项，防止 IP 重用导致的身份误判。</t>
   </si>
   <si>
     <t>DoS防护(DoS Protection)</t>
@@ -1884,7 +1839,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1959,9 +1914,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1974,30 +1926,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -2633,95 +2585,95 @@
   <dimension ref="A1:H59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="11.7115384615385" style="54" customWidth="1"/>
-    <col min="2" max="2" width="19.7115384615385" style="54" customWidth="1"/>
-    <col min="3" max="3" width="54.7115384615385" style="54" customWidth="1"/>
-    <col min="4" max="4" width="45.2884615384615" style="54" customWidth="1"/>
-    <col min="5" max="5" width="7.71153846153846" style="54" customWidth="1"/>
-    <col min="6" max="6" width="37.8557692307692" style="54" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.71153846153846" style="54" customWidth="1"/>
-    <col min="8" max="8" width="9.71153846153846" style="55" customWidth="1"/>
+    <col min="1" max="1" width="11.7115384615385" style="53" customWidth="1"/>
+    <col min="2" max="2" width="19.7115384615385" style="53" customWidth="1"/>
+    <col min="3" max="3" width="54.7115384615385" style="53" customWidth="1"/>
+    <col min="4" max="4" width="45.2884615384615" style="53" customWidth="1"/>
+    <col min="5" max="5" width="7.71153846153846" style="53" customWidth="1"/>
+    <col min="6" max="6" width="37.8557692307692" style="53" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.71153846153846" style="53" customWidth="1"/>
+    <col min="8" max="8" width="9.71153846153846" style="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="57" t="s">
+      <c r="C1" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="57" t="s">
+      <c r="D1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="58" t="s">
+      <c r="E1" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="58"/>
-      <c r="G1" s="57" t="s">
+      <c r="F1" s="57"/>
+      <c r="G1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="57" t="s">
+      <c r="H1" s="56" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="61"/>
-      <c r="E2" s="62" t="s">
+      <c r="D2" s="60"/>
+      <c r="E2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="63" t="s">
+      <c r="F2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:8">
       <c r="A3" s="11"/>
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="61" t="s">
+      <c r="D3" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="62" t="s">
+      <c r="E3" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="64" t="s">
+      <c r="F3" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="61" t="s">
+      <c r="G3" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:8">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="61" t="s">
+      <c r="D4" s="60" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="11"/>
@@ -2732,10 +2684,10 @@
     <row r="5" ht="36" customHeight="1" spans="1:8">
       <c r="A5" s="11"/>
       <c r="B5" s="12"/>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="61" t="s">
+      <c r="D5" s="60" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="12"/>
@@ -2745,35 +2697,35 @@
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:8">
       <c r="A6" s="11"/>
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="62" t="s">
+      <c r="E6" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="63" t="s">
+      <c r="F6" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="61" t="s">
+      <c r="G6" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:8">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
-      <c r="C7" s="61" t="s">
+      <c r="C7" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="61" t="s">
+      <c r="D7" s="60" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="11"/>
@@ -2784,10 +2736,10 @@
     <row r="8" ht="14.25" customHeight="1" spans="1:8">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="61" t="s">
+      <c r="D8" s="60" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="11"/>
@@ -2798,10 +2750,10 @@
     <row r="9" ht="14.25" customHeight="1" spans="1:8">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
-      <c r="C9" s="61" t="s">
+      <c r="C9" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="61" t="s">
+      <c r="D9" s="60" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="11"/>
@@ -2812,10 +2764,10 @@
     <row r="10" ht="14.25" customHeight="1" spans="1:8">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="61"/>
+      <c r="D10" s="60"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
@@ -2824,10 +2776,10 @@
     <row r="11" ht="14.25" customHeight="1" spans="1:8">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="61"/>
+      <c r="D11" s="60"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
@@ -2836,10 +2788,10 @@
     <row r="12" ht="14.25" customHeight="1" spans="1:8">
       <c r="A12" s="11"/>
       <c r="B12" s="12"/>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="61"/>
+      <c r="D12" s="60"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
@@ -2847,58 +2799,58 @@
     </row>
     <row r="13" ht="28.5" customHeight="1" spans="1:8">
       <c r="A13" s="12"/>
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="61" t="s">
+      <c r="D13" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="62" t="s">
+      <c r="E13" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="63" t="s">
+      <c r="F13" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="61" t="s">
+      <c r="G13" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="37" t="s">
+      <c r="H13" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="62" t="s">
+      <c r="E14" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="63" t="s">
+      <c r="F14" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="61" t="s">
+      <c r="G14" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="H14" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:8">
       <c r="A15" s="14"/>
       <c r="B15" s="11"/>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="60" t="s">
         <v>43</v>
       </c>
       <c r="D15" s="11"/>
@@ -2910,7 +2862,7 @@
     <row r="16" ht="14.25" customHeight="1" spans="1:8">
       <c r="A16" s="14"/>
       <c r="B16" s="11"/>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="60" t="s">
         <v>44</v>
       </c>
       <c r="D16" s="11"/>
@@ -2922,7 +2874,7 @@
     <row r="17" ht="14.25" customHeight="1" spans="1:8">
       <c r="A17" s="14"/>
       <c r="B17" s="11"/>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="60" t="s">
         <v>45</v>
       </c>
       <c r="D17" s="11"/>
@@ -2934,7 +2886,7 @@
     <row r="18" ht="14.25" customHeight="1" spans="1:8">
       <c r="A18" s="14"/>
       <c r="B18" s="11"/>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="60" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="11"/>
@@ -2946,7 +2898,7 @@
     <row r="19" ht="14.25" customHeight="1" spans="1:8">
       <c r="A19" s="14"/>
       <c r="B19" s="11"/>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="60" t="s">
         <v>47</v>
       </c>
       <c r="D19" s="11"/>
@@ -2958,7 +2910,7 @@
     <row r="20" ht="14.25" customHeight="1" spans="1:8">
       <c r="A20" s="14"/>
       <c r="B20" s="11"/>
-      <c r="C20" s="61" t="s">
+      <c r="C20" s="60" t="s">
         <v>48</v>
       </c>
       <c r="D20" s="11"/>
@@ -2970,7 +2922,7 @@
     <row r="21" ht="14.25" customHeight="1" spans="1:8">
       <c r="A21" s="14"/>
       <c r="B21" s="11"/>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="60" t="s">
         <v>49</v>
       </c>
       <c r="D21" s="11"/>
@@ -2982,7 +2934,7 @@
     <row r="22" ht="32.25" customHeight="1" spans="1:8">
       <c r="A22" s="13"/>
       <c r="B22" s="12"/>
-      <c r="C22" s="61" t="s">
+      <c r="C22" s="60" t="s">
         <v>50</v>
       </c>
       <c r="D22" s="12"/>
@@ -2992,125 +2944,125 @@
       <c r="H22" s="12"/>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="65" t="s">
+      <c r="B23" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="61" t="s">
+      <c r="D23" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="62" t="s">
+      <c r="E23" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="68" t="s">
+      <c r="F23" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="G23" s="61" t="s">
+      <c r="G23" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H23" s="37" t="s">
+      <c r="H23" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A24" s="66" t="s">
+      <c r="A24" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="65" t="s">
+      <c r="B24" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="61" t="s">
+      <c r="D24" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="62" t="s">
+      <c r="E24" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="69" t="s">
+      <c r="F24" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="61" t="s">
+      <c r="G24" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="37" t="s">
+      <c r="H24" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A25" s="66" t="s">
+      <c r="A25" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="65" t="s">
+      <c r="B25" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="70" t="s">
+      <c r="D25" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="62" t="s">
+      <c r="E25" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="63" t="s">
+      <c r="F25" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="G25" s="61" t="s">
+      <c r="G25" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="37" t="s">
+      <c r="H25" s="35" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" s="53" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
+    <row r="26" s="52" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
       <c r="A26" s="14"/>
-      <c r="B26" s="65" t="s">
+      <c r="B26" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="70"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="37"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="35"/>
     </row>
     <row r="27" ht="14.25" customHeight="1" spans="1:8">
       <c r="A27" s="14"/>
-      <c r="B27" s="65" t="s">
+      <c r="B27" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="61" t="s">
+      <c r="D27" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="62" t="s">
+      <c r="E27" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="63" t="s">
+      <c r="F27" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="61" t="s">
+      <c r="G27" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H27" s="37" t="s">
+      <c r="H27" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1" spans="1:8">
       <c r="A28" s="14"/>
       <c r="B28" s="12"/>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="60" t="s">
         <v>71</v>
       </c>
       <c r="D28" s="12"/>
@@ -3121,98 +3073,98 @@
     </row>
     <row r="29" ht="60" customHeight="1" spans="1:8">
       <c r="A29" s="14"/>
-      <c r="B29" s="65" t="s">
+      <c r="B29" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="37" t="s">
+      <c r="D29" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="62" t="s">
+      <c r="E29" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="72" t="s">
+      <c r="F29" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="G29" s="61" t="s">
+      <c r="G29" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="H29" s="37" t="s">
+      <c r="H29" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:8">
       <c r="A30" s="14"/>
       <c r="B30" s="11"/>
-      <c r="C30" s="61" t="s">
+      <c r="C30" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="61" t="s">
+      <c r="D30" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="62" t="s">
+      <c r="E30" s="61" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="11"/>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H30" s="37" t="s">
+      <c r="H30" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:8">
       <c r="A31" s="13"/>
       <c r="B31" s="12"/>
-      <c r="C31" s="61" t="s">
+      <c r="C31" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="61" t="s">
+      <c r="D31" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="73" t="s">
+      <c r="E31" s="72" t="s">
         <v>10</v>
       </c>
       <c r="F31" s="12"/>
-      <c r="G31" s="61" t="s">
+      <c r="G31" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="37" t="s">
+      <c r="H31" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A32" s="66" t="s">
+      <c r="A32" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="B32" s="65" t="s">
+      <c r="B32" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="61" t="s">
+      <c r="C32" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="61" t="s">
+      <c r="D32" s="60" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="62" t="s">
+      <c r="E32" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="63" t="s">
+      <c r="F32" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="61" t="s">
+      <c r="G32" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="37" t="s">
+      <c r="H32" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:8">
       <c r="A33" s="13"/>
       <c r="B33" s="12"/>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="60" t="s">
         <v>84</v>
       </c>
       <c r="D33" s="12"/>
@@ -3222,36 +3174,36 @@
       <c r="H33" s="12"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A34" s="66" t="s">
+      <c r="A34" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="65" t="s">
+      <c r="B34" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="61" t="s">
+      <c r="C34" s="60" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="61"/>
-      <c r="E34" s="62" t="s">
+      <c r="D34" s="60"/>
+      <c r="E34" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="63" t="s">
+      <c r="F34" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="G34" s="61" t="s">
+      <c r="G34" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H34" s="37" t="s">
+      <c r="H34" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" spans="1:8">
       <c r="A35" s="14"/>
       <c r="B35" s="11"/>
-      <c r="C35" s="61" t="s">
+      <c r="C35" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="61"/>
+      <c r="D35" s="60"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
@@ -3260,10 +3212,10 @@
     <row r="36" ht="14.25" customHeight="1" spans="1:8">
       <c r="A36" s="14"/>
       <c r="B36" s="11"/>
-      <c r="C36" s="61" t="s">
+      <c r="C36" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="61"/>
+      <c r="D36" s="60"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="11"/>
@@ -3272,49 +3224,49 @@
     <row r="37" ht="14.25" customHeight="1" spans="1:8">
       <c r="A37" s="13"/>
       <c r="B37" s="12"/>
-      <c r="C37" s="74" t="s">
+      <c r="C37" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="D37" s="74"/>
+      <c r="D37" s="73"/>
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A38" s="65" t="s">
+      <c r="A38" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="65" t="s">
+      <c r="B38" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="75" t="s">
+      <c r="C38" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="D38" s="75"/>
-      <c r="E38" s="73" t="s">
+      <c r="D38" s="74"/>
+      <c r="E38" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="76" t="s">
+      <c r="F38" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="61" t="s">
+      <c r="G38" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H38" s="37" t="s">
+      <c r="H38" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" spans="1:8">
       <c r="A39" s="11"/>
-      <c r="B39" s="65" t="s">
+      <c r="B39" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="75" t="s">
+      <c r="C39" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="D39" s="75"/>
-      <c r="E39" s="73" t="s">
+      <c r="D39" s="74"/>
+      <c r="E39" s="72" t="s">
         <v>60</v>
       </c>
       <c r="F39" s="12"/>
@@ -3323,141 +3275,141 @@
     </row>
     <row r="40" ht="28.5" customHeight="1" spans="1:8">
       <c r="A40" s="11"/>
-      <c r="B40" s="65" t="s">
+      <c r="B40" s="64" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="75" t="s">
+      <c r="C40" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="D40" s="77" t="s">
+      <c r="D40" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="73" t="s">
+      <c r="E40" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="72" t="s">
+      <c r="F40" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="G40" s="61" t="s">
+      <c r="G40" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="H40" s="37" t="s">
+      <c r="H40" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" spans="1:8">
       <c r="A41" s="11"/>
-      <c r="B41" s="65" t="s">
+      <c r="B41" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="61" t="s">
+      <c r="C41" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="D41" s="75" t="s">
+      <c r="D41" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="E41" s="73" t="s">
+      <c r="E41" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="F41" s="72" t="s">
+      <c r="F41" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="G41" s="61" t="s">
+      <c r="G41" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="H41" s="37" t="s">
+      <c r="H41" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:8">
       <c r="A42" s="11"/>
-      <c r="B42" s="65" t="s">
+      <c r="B42" s="64" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="61" t="s">
+      <c r="C42" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="75"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="37"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="60"/>
+      <c r="H42" s="35"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:8">
       <c r="A43" s="12"/>
-      <c r="B43" s="65" t="s">
+      <c r="B43" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="75" t="s">
+      <c r="C43" s="74" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="75"/>
-      <c r="E43" s="73" t="s">
+      <c r="D43" s="74"/>
+      <c r="E43" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="F43" s="72" t="s">
+      <c r="F43" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="G43" s="61" t="s">
+      <c r="G43" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="H43" s="37" t="s">
+      <c r="H43" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A44" s="78" t="s">
+      <c r="A44" s="77" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="79" t="s">
+      <c r="B44" s="78" t="s">
         <v>111</v>
       </c>
-      <c r="C44" s="80" t="s">
+      <c r="C44" s="79" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="80" t="s">
+      <c r="D44" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="E44" s="81" t="s">
+      <c r="E44" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="82" t="s">
+      <c r="F44" s="81" t="s">
         <v>114</v>
       </c>
-      <c r="G44" s="83" t="s">
+      <c r="G44" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="H44" s="39" t="s">
+      <c r="H44" s="38" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" spans="1:8">
       <c r="A45" s="14"/>
       <c r="B45" s="11"/>
-      <c r="C45" s="75" t="s">
+      <c r="C45" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="D45" s="75" t="s">
+      <c r="D45" s="74" t="s">
         <v>116</v>
       </c>
       <c r="E45" s="11"/>
-      <c r="F45" s="84" t="s">
+      <c r="F45" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="G45" s="61" t="s">
+      <c r="G45" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="37" t="s">
+      <c r="H45" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" spans="1:8">
       <c r="A46" s="14"/>
       <c r="B46" s="11"/>
-      <c r="C46" s="75" t="s">
+      <c r="C46" s="74" t="s">
         <v>117</v>
       </c>
-      <c r="D46" s="75"/>
+      <c r="D46" s="74"/>
       <c r="E46" s="11"/>
       <c r="F46" s="12"/>
       <c r="G46" s="12"/>
@@ -3466,284 +3418,284 @@
     <row r="47" ht="14.25" customHeight="1" spans="1:8">
       <c r="A47" s="14"/>
       <c r="B47" s="11"/>
-      <c r="C47" s="75" t="s">
+      <c r="C47" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="D47" s="75"/>
+      <c r="D47" s="74"/>
       <c r="E47" s="11"/>
-      <c r="F47" s="84" t="s">
+      <c r="F47" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="G47" s="61" t="s">
+      <c r="G47" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H47" s="37" t="s">
+      <c r="H47" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" spans="1:8">
       <c r="A48" s="13"/>
       <c r="B48" s="12"/>
-      <c r="C48" s="85" t="s">
+      <c r="C48" s="84" t="s">
         <v>119</v>
       </c>
-      <c r="D48" s="85"/>
+      <c r="D48" s="84"/>
       <c r="E48" s="12"/>
-      <c r="F48" s="68" t="s">
+      <c r="F48" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="G48" s="74" t="s">
+      <c r="G48" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="H48" s="86" t="s">
+      <c r="H48" s="85" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="49" ht="42.75" customHeight="1" spans="1:8">
-      <c r="A49" s="87" t="s">
+      <c r="A49" s="86" t="s">
         <v>120</v>
       </c>
-      <c r="B49" s="87" t="s">
+      <c r="B49" s="86" t="s">
         <v>120</v>
       </c>
-      <c r="C49" s="88" t="s">
+      <c r="C49" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="89" t="s">
+      <c r="D49" s="88" t="s">
         <v>122</v>
       </c>
-      <c r="E49" s="90" t="s">
+      <c r="E49" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="91"/>
-      <c r="G49" s="92" t="s">
+      <c r="F49" s="90"/>
+      <c r="G49" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="H49" s="93"/>
+      <c r="H49" s="92"/>
     </row>
     <row r="50" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A50" s="94"/>
-      <c r="B50" s="94"/>
-      <c r="C50" s="88" t="s">
+      <c r="A50" s="93"/>
+      <c r="B50" s="93"/>
+      <c r="C50" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="D50" s="95" t="s">
+      <c r="D50" s="94" t="s">
         <v>124</v>
       </c>
-      <c r="E50" s="96" t="s">
+      <c r="E50" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="F50" s="97"/>
-      <c r="G50" s="92" t="s">
+      <c r="F50" s="96"/>
+      <c r="G50" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="H50" s="98"/>
+      <c r="H50" s="97"/>
     </row>
     <row r="51" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A51" s="94"/>
-      <c r="B51" s="94"/>
-      <c r="C51" s="88" t="s">
+      <c r="A51" s="93"/>
+      <c r="B51" s="93"/>
+      <c r="C51" s="87" t="s">
         <v>125</v>
       </c>
-      <c r="D51" s="99" t="s">
+      <c r="D51" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="E51" s="96" t="s">
+      <c r="E51" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="F51" s="91"/>
-      <c r="G51" s="92" t="s">
+      <c r="F51" s="90"/>
+      <c r="G51" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="H51" s="93"/>
+      <c r="H51" s="92"/>
     </row>
     <row r="52" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A52" s="100"/>
-      <c r="B52" s="100"/>
-      <c r="C52" s="99" t="s">
+      <c r="A52" s="99"/>
+      <c r="B52" s="99"/>
+      <c r="C52" s="98" t="s">
         <v>127</v>
       </c>
-      <c r="D52" s="89" t="s">
+      <c r="D52" s="88" t="s">
         <v>128</v>
       </c>
-      <c r="E52" s="101" t="s">
+      <c r="E52" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="91" t="s">
+      <c r="F52" s="90" t="s">
         <v>129</v>
       </c>
-      <c r="G52" s="92" t="s">
+      <c r="G52" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="H52" s="93" t="s">
+      <c r="H52" s="92" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A53" s="79" t="s">
+      <c r="A53" s="78" t="s">
         <v>130</v>
       </c>
-      <c r="B53" s="79" t="s">
+      <c r="B53" s="78" t="s">
         <v>131</v>
       </c>
-      <c r="C53" s="80" t="s">
+      <c r="C53" s="79" t="s">
         <v>132</v>
       </c>
-      <c r="D53" s="80"/>
-      <c r="E53" s="81" t="s">
+      <c r="D53" s="79"/>
+      <c r="E53" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="F53" s="82" t="s">
+      <c r="F53" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="G53" s="83" t="s">
+      <c r="G53" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="H53" s="39" t="s">
+      <c r="H53" s="38" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="54" ht="28.5" customHeight="1" spans="1:8">
       <c r="A54" s="12"/>
-      <c r="B54" s="65" t="s">
+      <c r="B54" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="C54" s="37" t="s">
+      <c r="C54" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="D54" s="77" t="s">
+      <c r="D54" s="76" t="s">
         <v>135</v>
       </c>
-      <c r="E54" s="73" t="s">
+      <c r="E54" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="F54" s="72" t="s">
+      <c r="F54" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="G54" s="61" t="s">
+      <c r="G54" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="H54" s="37" t="s">
+      <c r="H54" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A55" s="66" t="s">
+      <c r="A55" s="65" t="s">
         <v>137</v>
       </c>
-      <c r="B55" s="65" t="s">
+      <c r="B55" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="C55" s="75" t="s">
+      <c r="C55" s="74" t="s">
         <v>139</v>
       </c>
-      <c r="D55" s="75"/>
-      <c r="E55" s="73" t="s">
+      <c r="D55" s="74"/>
+      <c r="E55" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="F55" s="72"/>
-      <c r="G55" s="61" t="s">
+      <c r="F55" s="71"/>
+      <c r="G55" s="60" t="s">
         <v>140</v>
       </c>
-      <c r="H55" s="37" t="s">
+      <c r="H55" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="56" ht="42.75" customHeight="1" spans="1:8">
-      <c r="A56" s="66" t="s">
+      <c r="A56" s="65" t="s">
         <v>141</v>
       </c>
-      <c r="B56" s="65" t="s">
+      <c r="B56" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="C56" s="75" t="s">
+      <c r="C56" s="74" t="s">
         <v>143</v>
       </c>
-      <c r="D56" s="77" t="s">
+      <c r="D56" s="76" t="s">
         <v>144</v>
       </c>
-      <c r="E56" s="73" t="s">
+      <c r="E56" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="F56" s="84" t="s">
+      <c r="F56" s="83" t="s">
         <v>145</v>
       </c>
-      <c r="G56" s="61"/>
-      <c r="H56" s="37" t="s">
+      <c r="G56" s="60"/>
+      <c r="H56" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="57" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A57" s="65" t="s">
+      <c r="A57" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="B57" s="65" t="s">
+      <c r="B57" s="64" t="s">
         <v>146</v>
       </c>
-      <c r="C57" s="75" t="s">
+      <c r="C57" s="74" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="75" t="s">
+      <c r="D57" s="74" t="s">
         <v>148</v>
       </c>
-      <c r="E57" s="73" t="s">
+      <c r="E57" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="F57" s="84" t="s">
+      <c r="F57" s="83" t="s">
         <v>149</v>
       </c>
-      <c r="G57" s="61" t="s">
+      <c r="G57" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="H57" s="37" t="s">
+      <c r="H57" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A58" s="102" t="s">
+      <c r="A58" s="101" t="s">
         <v>150</v>
       </c>
-      <c r="B58" s="102" t="s">
+      <c r="B58" s="101" t="s">
         <v>150</v>
       </c>
-      <c r="C58" s="74" t="s">
+      <c r="C58" s="73" t="s">
         <v>151</v>
       </c>
-      <c r="D58" s="85" t="s">
+      <c r="D58" s="84" t="s">
         <v>152</v>
       </c>
-      <c r="E58" s="103" t="s">
+      <c r="E58" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="F58" s="104" t="s">
+      <c r="F58" s="103" t="s">
         <v>153</v>
       </c>
-      <c r="G58" s="74" t="s">
+      <c r="G58" s="73" t="s">
         <v>103</v>
       </c>
-      <c r="H58" s="86" t="s">
+      <c r="H58" s="85" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="59" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A59" s="87" t="s">
+      <c r="A59" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="B59" s="87" t="s">
+      <c r="B59" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="C59" s="105" t="s">
+      <c r="C59" s="104" t="s">
         <v>155</v>
       </c>
-      <c r="D59" s="97"/>
-      <c r="E59" s="101" t="s">
+      <c r="D59" s="96"/>
+      <c r="E59" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="F59" s="97"/>
-      <c r="G59" s="74" t="s">
+      <c r="F59" s="96"/>
+      <c r="G59" s="73" t="s">
         <v>103</v>
       </c>
-      <c r="H59" s="98" t="s">
+      <c r="H59" s="97" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3813,7 +3765,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.2" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="19.3942307692308" style="2" customWidth="1"/>
@@ -4283,7 +4235,7 @@
         <v>227</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>109</v>
@@ -4303,7 +4255,7 @@
         <v>230</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>109</v>
@@ -4320,7 +4272,7 @@
       </c>
       <c r="E23" s="24"/>
       <c r="F23" s="25" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>109</v>
@@ -4362,17 +4314,17 @@
     <row r="26" ht="51" customHeight="1" spans="1:8">
       <c r="A26" s="11"/>
       <c r="B26" s="12"/>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D26" s="23" t="s">
         <v>236</v>
       </c>
-      <c r="E26" s="29"/>
-      <c r="F26" s="30" t="s">
+      <c r="E26" s="28"/>
+      <c r="F26" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="G26" s="30" t="s">
         <v>109</v>
       </c>
       <c r="H26" s="10" t="s">
@@ -4384,13 +4336,13 @@
       <c r="B27" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="E27" s="32" t="s">
+      <c r="E27" s="31" t="s">
         <v>240</v>
       </c>
       <c r="F27" s="16" t="s">
@@ -4401,514 +4353,413 @@
       </c>
       <c r="H27" s="10"/>
     </row>
-    <row r="28" ht="51" customHeight="1" spans="1:8">
+    <row r="28" ht="126" customHeight="1" spans="1:8">
       <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="33" t="s">
+      <c r="B28" s="32" t="s">
         <v>241</v>
       </c>
-      <c r="D28" s="33" t="s">
+      <c r="C28" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="10"/>
-    </row>
-    <row r="29" ht="51" customHeight="1" spans="1:8">
+      <c r="D28" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H28" s="33" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" ht="126" customHeight="1" spans="1:8">
       <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="D29" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="10"/>
-    </row>
-    <row r="30" ht="81" customHeight="1" spans="1:8">
+      <c r="B29" s="34"/>
+      <c r="C29" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H29" s="36"/>
+    </row>
+    <row r="30" ht="74" customHeight="1" spans="1:8">
       <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="33" t="s">
-        <v>245</v>
-      </c>
-      <c r="D30" s="33" t="s">
-        <v>246</v>
-      </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="10"/>
-    </row>
-    <row r="31" ht="126" customHeight="1" spans="1:8">
+      <c r="B30" s="34"/>
+      <c r="C30" s="37" t="s">
+        <v>248</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H30" s="39"/>
+    </row>
+    <row r="31" ht="96" customHeight="1" spans="1:8">
       <c r="A31" s="11"/>
-      <c r="B31" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F31" s="8" t="s">
+      <c r="B31" s="34"/>
+      <c r="C31" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="E31" s="9"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="36"/>
+    </row>
+    <row r="32" ht="96" customHeight="1" spans="1:8">
+      <c r="A32" s="11"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="36"/>
+    </row>
+    <row r="33" ht="117" customHeight="1" spans="1:8">
+      <c r="A33" s="11"/>
+      <c r="B33" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>256</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" ht="96" customHeight="1" spans="1:8">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="41" t="s">
+        <v>259</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="F34" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G31" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="H31" s="35" t="s">
+      <c r="G34" s="9" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="32" ht="126" customHeight="1" spans="1:8">
-      <c r="A32" s="11"/>
-      <c r="B32" s="36"/>
-      <c r="C32" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="F32" s="37" t="s">
+      <c r="H34" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" ht="96" customHeight="1" spans="1:8">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="D35" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="H35" s="8"/>
+    </row>
+    <row r="36" ht="171" customHeight="1" spans="1:8">
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="D36" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="H36" s="21"/>
+    </row>
+    <row r="37" ht="126" customHeight="1" spans="1:8">
+      <c r="A37" s="11"/>
+      <c r="B37" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="D37" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="F37" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G37" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H32" s="38"/>
-    </row>
-    <row r="33" ht="69" customHeight="1" spans="1:8">
-      <c r="A33" s="11"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="F33" s="39"/>
-      <c r="G33" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="H33" s="40"/>
-    </row>
-    <row r="34" ht="74" customHeight="1" spans="1:8">
-      <c r="A34" s="11"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="D34" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="F34" s="39" t="s">
+      <c r="H37" s="46" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="38" ht="81" customHeight="1" spans="1:8">
+      <c r="A38" s="11"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="43" t="s">
+        <v>272</v>
+      </c>
+      <c r="D38" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>274</v>
+      </c>
+      <c r="F38" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="G34" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H34" s="40"/>
-    </row>
-    <row r="35" ht="54" customHeight="1" spans="1:8">
-      <c r="A35" s="11"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="33" t="s">
-        <v>260</v>
-      </c>
-      <c r="D35" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F35" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H35" s="40"/>
-    </row>
-    <row r="36" ht="47" customHeight="1" spans="1:8">
-      <c r="A36" s="11"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="D36" s="33" t="s">
-        <v>264</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="F36" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H36" s="40"/>
-    </row>
-    <row r="37" ht="47" customHeight="1" spans="1:8">
-      <c r="A37" s="11"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="D37" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="40"/>
-    </row>
-    <row r="38" ht="96" customHeight="1" spans="1:8">
-      <c r="A38" s="11"/>
-      <c r="B38" s="36"/>
-      <c r="C38" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="D38" s="33" t="s">
-        <v>269</v>
-      </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="38"/>
-    </row>
-    <row r="39" ht="117" customHeight="1" spans="1:8">
+      <c r="G38" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="H38" s="46" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" ht="81" customHeight="1" spans="1:8">
       <c r="A39" s="11"/>
-      <c r="B39" s="7" t="s">
-        <v>270</v>
+      <c r="B39" s="36" t="s">
+        <v>275</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H39" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" ht="68" customHeight="1" spans="1:8">
+      <c r="A40" s="11"/>
+      <c r="B40" s="39"/>
+      <c r="C40" s="47" t="s">
+        <v>279</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="H40" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="H39" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" ht="96" customHeight="1" spans="1:8">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="F40" s="8" t="s">
+    </row>
+    <row r="41" ht="51" customHeight="1" spans="1:8">
+      <c r="A41" s="11"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="49" t="s">
+        <v>282</v>
+      </c>
+      <c r="D41" s="50" t="s">
+        <v>283</v>
+      </c>
+      <c r="E41" s="49" t="s">
+        <v>284</v>
+      </c>
+      <c r="F41" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="G40" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" ht="96" customHeight="1" spans="1:8">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="42" t="s">
-        <v>277</v>
-      </c>
-      <c r="D41" s="33" t="s">
-        <v>278</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="F41" s="8" t="s">
+      <c r="G41" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="H41" s="51"/>
+    </row>
+    <row r="42" ht="68" customHeight="1" spans="1:8">
+      <c r="A42" s="11"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="49" t="s">
+        <v>285</v>
+      </c>
+      <c r="D42" s="50" t="s">
+        <v>286</v>
+      </c>
+      <c r="E42" s="49" t="s">
+        <v>287</v>
+      </c>
+      <c r="F42" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="H42" s="51"/>
+    </row>
+    <row r="43" ht="51" customHeight="1" spans="1:8">
+      <c r="A43" s="11"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="49" t="s">
+        <v>288</v>
+      </c>
+      <c r="D43" s="50" t="s">
+        <v>289</v>
+      </c>
+      <c r="E43" s="49" t="s">
+        <v>290</v>
+      </c>
+      <c r="F43" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="H43" s="51"/>
+    </row>
+    <row r="44" ht="84" customHeight="1" spans="1:8">
+      <c r="A44" s="11"/>
+      <c r="B44" s="39"/>
+      <c r="C44" s="49" t="s">
+        <v>291</v>
+      </c>
+      <c r="D44" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="E44" s="49" t="s">
+        <v>293</v>
+      </c>
+      <c r="F44" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G44" s="51" t="s">
         <v>188</v>
       </c>
-      <c r="H41" s="8"/>
-    </row>
-    <row r="42" ht="171" customHeight="1" spans="1:8">
-      <c r="A42" s="11"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="42" t="s">
-        <v>280</v>
-      </c>
-      <c r="D42" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="F42" s="8" t="s">
+      <c r="H44" s="51"/>
+    </row>
+    <row r="45" ht="51" customHeight="1" spans="1:8">
+      <c r="A45" s="11"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="49" t="s">
+        <v>294</v>
+      </c>
+      <c r="D45" s="50" t="s">
+        <v>295</v>
+      </c>
+      <c r="E45" s="50" t="s">
+        <v>296</v>
+      </c>
+      <c r="F45" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="G45" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="H45" s="51"/>
+    </row>
+    <row r="46" ht="51" spans="1:8">
+      <c r="A46" s="12"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="49" t="s">
+        <v>297</v>
+      </c>
+      <c r="D46" s="50" t="s">
+        <v>298</v>
+      </c>
+      <c r="E46" s="49" t="s">
+        <v>299</v>
+      </c>
+      <c r="F46" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="G46" s="51" t="s">
         <v>188</v>
       </c>
-      <c r="H42" s="21"/>
-    </row>
-    <row r="43" ht="126" customHeight="1" spans="1:8">
-      <c r="A43" s="11"/>
-      <c r="B43" s="43" t="s">
-        <v>283</v>
-      </c>
-      <c r="C43" s="44" t="s">
-        <v>284</v>
-      </c>
-      <c r="D43" s="44" t="s">
-        <v>285</v>
-      </c>
-      <c r="E43" s="44" t="s">
-        <v>286</v>
-      </c>
-      <c r="F43" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="46" t="s">
-        <v>109</v>
-      </c>
-      <c r="H43" s="47" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="44" ht="81" customHeight="1" spans="1:8">
-      <c r="A44" s="11"/>
-      <c r="B44" s="43"/>
-      <c r="C44" s="44" t="s">
-        <v>287</v>
-      </c>
-      <c r="D44" s="44" t="s">
-        <v>288</v>
-      </c>
-      <c r="E44" s="44" t="s">
-        <v>289</v>
-      </c>
-      <c r="F44" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="46" t="s">
-        <v>109</v>
-      </c>
-      <c r="H44" s="47" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="45" ht="81" customHeight="1" spans="1:8">
-      <c r="A45" s="11"/>
-      <c r="B45" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="C45" s="41" t="s">
-        <v>291</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H45" s="30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" ht="68" customHeight="1" spans="1:8">
-      <c r="A46" s="11"/>
-      <c r="B46" s="40"/>
-      <c r="C46" s="48" t="s">
-        <v>294</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="F46" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="H46" s="30" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="47" ht="51" customHeight="1" spans="1:8">
-      <c r="A47" s="11"/>
-      <c r="B47" s="40"/>
-      <c r="C47" s="50" t="s">
-        <v>297</v>
-      </c>
-      <c r="D47" s="51" t="s">
-        <v>298</v>
-      </c>
-      <c r="E47" s="50" t="s">
-        <v>299</v>
-      </c>
-      <c r="F47" s="52" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="H47" s="52"/>
-    </row>
-    <row r="48" ht="68" customHeight="1" spans="1:8">
-      <c r="A48" s="11"/>
-      <c r="B48" s="40"/>
-      <c r="C48" s="50" t="s">
-        <v>300</v>
-      </c>
-      <c r="D48" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="E48" s="50" t="s">
-        <v>302</v>
-      </c>
-      <c r="F48" s="52" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="H48" s="52"/>
-    </row>
-    <row r="49" ht="51" customHeight="1" spans="1:8">
-      <c r="A49" s="11"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="50" t="s">
-        <v>303</v>
-      </c>
-      <c r="D49" s="51" t="s">
-        <v>304</v>
-      </c>
-      <c r="E49" s="50" t="s">
-        <v>305</v>
-      </c>
-      <c r="F49" s="52" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="H49" s="52"/>
-    </row>
-    <row r="50" ht="84" customHeight="1" spans="1:8">
-      <c r="A50" s="11"/>
-      <c r="B50" s="40"/>
-      <c r="C50" s="50" t="s">
-        <v>306</v>
-      </c>
-      <c r="D50" s="51" t="s">
-        <v>307</v>
-      </c>
-      <c r="E50" s="50" t="s">
-        <v>308</v>
-      </c>
-      <c r="F50" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="G50" s="52" t="s">
-        <v>188</v>
-      </c>
-      <c r="H50" s="52"/>
-    </row>
-    <row r="51" ht="51" customHeight="1" spans="1:8">
-      <c r="A51" s="11"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="50" t="s">
-        <v>309</v>
-      </c>
-      <c r="D51" s="51" t="s">
-        <v>310</v>
-      </c>
-      <c r="E51" s="51" t="s">
-        <v>311</v>
-      </c>
-      <c r="F51" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="G51" s="52" t="s">
-        <v>109</v>
-      </c>
-      <c r="H51" s="52"/>
-    </row>
-    <row r="52" ht="51" spans="1:8">
-      <c r="A52" s="12"/>
-      <c r="B52" s="38"/>
-      <c r="C52" s="50" t="s">
-        <v>312</v>
-      </c>
-      <c r="D52" s="51" t="s">
-        <v>313</v>
-      </c>
-      <c r="E52" s="50" t="s">
-        <v>314</v>
-      </c>
-      <c r="F52" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="G52" s="52" t="s">
-        <v>188</v>
-      </c>
-      <c r="H52" s="52"/>
+      <c r="H46" s="51"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A2:A52"/>
+  <mergeCells count="15">
+    <mergeCell ref="A2:A46"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B15:B18"/>
     <mergeCell ref="B20:B26"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="B31:B38"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B45:B52"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B39:B46"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="H6:H9"/>
-    <mergeCell ref="H32:H38"/>
+    <mergeCell ref="H29:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/PA替代需求列表.xlsx
+++ b/PA替代需求列表.xlsx
@@ -1,15 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\zt\ggz\研发部\3.7项目\需求分析\PA-替代需求\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="15880" activeTab="1"/>
+    <workbookView windowHeight="18390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
     <sheet name="策略需求差异" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">策略需求差异!$A$1:$G$83</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -28,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="271">
   <si>
     <t>一级需求</t>
   </si>
@@ -511,64 +519,76 @@
     <t>支持解密端口镜像流量，将解密后的明文流量镜像到专用接口供取证或第三方分析</t>
   </si>
   <si>
-    <t>对比依据（PA证据·天融信现状）</t>
-  </si>
-  <si>
     <t>策略</t>
   </si>
   <si>
     <t>策略基础管理</t>
   </si>
   <si>
-    <t>支持审核注释存档（Audit Comment Archive）</t>
-  </si>
-  <si>
-    <t>提交/修改策略须填写审核注释并留存历史，可导出</t>
-  </si>
-  <si>
-    <t>PA记录规则的审核注释历史/配置日志/规则更改历史，可CSV导出，用于策略变更审计（PA Web帮助p116-117）；天融信仅规则描述字段，无审核注释存档</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>支持Panorama前置/后置规则层级拆解（Pre-Rules/Post-Rules）</t>
-  </si>
-  <si>
-    <t>前置规则→本地规则→后置规则三层按序合并为单层规则链</t>
-  </si>
-  <si>
-    <t>PA在Panorama集中管理下策略分为前置规则（设备组共享，最优先）/本地规则/后置规则三层按序匹配（层级机制属Panorama管理平台，PA两册手册未详载）；天融信为自上而下单层规则链一张表走到底（天融信手册《配置访问控制策略》页）；迁移评估项：需制定全局多级策略到单层扁平化策略的合并清洗规则（Pre→本地→Post按序展开映射）</t>
-  </si>
-  <si>
-    <t>支持应用级会话超时覆盖（Application Timeout Override）</t>
-  </si>
-  <si>
-    <t>应用程序对象级会话超时，覆盖全局TCP/UDP超时</t>
-  </si>
-  <si>
-    <t>PA除全局TCP/UDP会话超时外，可在应用程序对象上定义专用超时，匹配该应用的流量覆盖全局值（PA Web帮助p215、p695）；天融信手册未见应用级超时覆盖（仅SSLVPN会话超时设置与黑名单老化）；迁移评估项：需排查现网PA为数据库/长连接业务单独配置的应用超时并逐条转换，否则长连接业务频繁中断</t>
+    <t>支持审核注释存档</t>
+  </si>
+  <si>
+    <t>访问控制/NAT/QoS/基于策略的转发/解密、隧道检测/应用程序替代/身份验证/Dos保护/SD-WAN策略</t>
+  </si>
+  <si>
+    <t>平台</t>
+  </si>
+  <si>
+    <t>支持突出显示未使用的策略</t>
+  </si>
+  <si>
+    <t>平台/产品线</t>
+  </si>
+  <si>
+    <t>支持分组查看策略</t>
+  </si>
+  <si>
+    <t>按标记分组查看访问控制/NAT/QoS/基于策略的转发/解密、隧道检测/应用程序替代/身份验证/Dos保护/SD-WAN策略</t>
+  </si>
+  <si>
+    <t>部分支持</t>
+  </si>
+  <si>
+    <t>支持重置策略命中计数</t>
+  </si>
+  <si>
+    <t>支持测试策略匹配</t>
+  </si>
+  <si>
+    <t>访问控制/NAT/QoS/基于策略的转发/解密、隧道检测/身份验证/Dos保护/SD-WAN策略</t>
+  </si>
+  <si>
+    <t>支持查询未使用/最近30天未使用/最近90天未使用策略</t>
   </si>
   <si>
     <t>安全策略</t>
   </si>
   <si>
+    <t>支持添加策略标记</t>
+  </si>
+  <si>
+    <t>支持按标记对规则分组</t>
+  </si>
+  <si>
     <t>支持配置HIP主机信息配置文件</t>
   </si>
   <si>
     <t>终端安全态势（补丁安装状态、杀软/反间谍/防火墙运行状态、磁盘加密开启状态、磁盘加密算法、OS版本）作为策略匹配条件</t>
   </si>
   <si>
-    <t>PA规则构建块支持HIP配置文件匹配终端安全态势（对应矩阵#3/4）；天融信手册检索HIP/主机信息配置文件无命中，无终端安全态势匹配等价物</t>
-  </si>
-  <si>
-    <t>支持终端设备对象作为策略匹配条件</t>
+    <t>支持根据外部动态列表地址匹配</t>
+  </si>
+  <si>
+    <t>支持对地址取反后进行匹配</t>
+  </si>
+  <si>
+    <t>支持终端设备匹配</t>
   </si>
   <si>
     <t>终端设备类型（手机/平板/IoT等设备对象）作为策略构建块</t>
   </si>
   <si>
-    <t>PA支持设备对象构建块（对应矩阵#3/4）；天融信经EDR联动上报终端资产并下发管控策略（天融信手册《与EDR联动》页），无独立设备对象</t>
+    <t>支持URL类别匹配</t>
   </si>
   <si>
     <t>支持端口(L4)规则向应用(L7)规则迁移工作流</t>
@@ -577,43 +597,49 @@
     <t>端口规则一键迁移为应用规则</t>
   </si>
   <si>
-    <t>PA策略优化器提供新应用查看器与端口→App-ID规则迁移工作流（PA Web帮助p142）；天融信策略统计仅显示规则命中数（天融信手册《配置访问控制策略》页），无迁移工具（命中统计能力已另列已支持行）；对应矩阵#132</t>
-  </si>
-  <si>
     <t>支持应用匹配时强制校验标准端口</t>
   </si>
   <si>
     <t>应用规则匹配时同时校验应用的标准端口，非标准端口流量不匹配</t>
   </si>
   <si>
-    <t>PA安全策略默认服务为application-default：放行应用同时强制其使用标准端口（如SSH仅22），非标准端口不匹配即拦截（PA管理指南p904）；天融信策略为五元组+应用识别组合（天融信手册《配置访问控制策略》页）；迁移评估项：直接转换若仅保留应用识别不限端口将扩大安全敞口，需制定应用标准端口映射限制（App-Default）转换方案；对应矩阵#2</t>
-  </si>
-  <si>
     <t>支持将隐式默认规则显式化</t>
   </si>
   <si>
     <t>同区域默认放行/跨区域默认拒绝的两条隐式系统规则可被提取为显式规则</t>
   </si>
   <si>
-    <t>PA安全策略库末尾自带两条隐式系统规则：区域内默认（同Zone默认放行）与区域间默认（跨Zone默认拒绝），可被替代配置，替代字段含日志转发配置文件与Log at Session End在会话结束时记录（PA Web帮助p134-136）；天融信未见同区域默认放行的隐式规则机制；迁移评估项：①必须提取intrazone-default同Zone互访需求并显式转换为放行规则，否则割接后同Zone不同网段/VLAN互访将被默认拦截；②需在新设备补齐底部兜底Deny-All并开启日志，否则被拒流量查无日志、排障困难</t>
-  </si>
-  <si>
     <t>支持WildFire云沙箱文件检测联动</t>
   </si>
   <si>
     <t>策略动作绑定WildFire配置文件</t>
   </si>
   <si>
-    <t>PA策略Actions可绑定WildFire Analysis配置文件（安全配置文件组含反病毒/漏洞/URL/文件阻断/WildFire，PA Web帮助p304；WildFire提交日志转发p305-306），云沙箱动态分析未知/零日威胁并秒级下发签名；天融信有内置APT沙箱（虚拟运行环境检测未知漏洞威胁）与沙箱联动（天融信手册《高级威胁防护》《APT联动配置》页），无云端动态分析与秒级签名下发证据；工作表1已登记云沙箱联动需求（不支持：公司无此产品），勿重复跟踪；迁移评估项：评估天融信本地APT沙箱与PA云沙箱检测能力等效性</t>
-  </si>
-  <si>
-    <t>部分支持</t>
+    <t>支持配置URL类别</t>
+  </si>
+  <si>
+    <t>支持配置漏洞保护</t>
+  </si>
+  <si>
+    <t>引用漏洞保护配置文件</t>
   </si>
   <si>
     <t>支持配置源、目的域名</t>
   </si>
   <si>
-    <t>PA支持FQDN类型地址对象(Objects-&gt;Addresses-&gt;FQDN)，定期主动解析刷新；天融信手册支持"域名资源"(资源管理-&gt;域名)，可引用至访问控制规则，但工作方式为DNS流量检测被动缓存。两者机制不同，天融信不支持主动解析模式</t>
+    <t>支持查看第一次命中时间</t>
+  </si>
+  <si>
+    <t>支持查看命中策略的应用协议</t>
+  </si>
+  <si>
+    <t>支持根据策略命中的应用协议克隆策略</t>
+  </si>
+  <si>
+    <t>支持将策略命中的应用协议配置到策略中</t>
+  </si>
+  <si>
+    <t>当前策略、其它策略</t>
   </si>
   <si>
     <t>NAT策略</t>
@@ -625,12 +651,6 @@
     <t>双活HA模式下，NAT规则可绑定会话所有者并指定会话设置，控制NAT会话归属设备</t>
   </si>
   <si>
-    <t>PA双活（Active/Active）HA配置下NAT规则可绑定会话所有者/会话设置，控制NAT会话的设备绑定，仅A/A模式可见（PA Web帮助p150）；天融信HA为主备双机热备模式（天融信手册《配置双机热备功能》页），无双活模式及NAT规则绑定机制</t>
-  </si>
-  <si>
-    <t>平台</t>
-  </si>
-  <si>
     <t>QoS策略</t>
   </si>
   <si>
@@ -640,9 +660,6 @@
     <t>QoS策略规则DSCP/ToS直接匹配</t>
   </si>
   <si>
-    <t>PA QoS规则可直接按DSCP值或IP优先级/ToS匹配调度（PA Web帮助p155）；天融信支持DSCP/802.1p(CoS)识别与重标记，但需在独立流量管理模块配置（虚拟通道+限制/保证带宽+通道优先级，天融信手册《流量管理》页），未直接耦合在基础访问控制策略表内（联网核实厂商流控资料，手册未详载）</t>
-  </si>
-  <si>
     <t>基于策略转发</t>
   </si>
   <si>
@@ -652,9 +669,6 @@
     <t>记录入接口MAC，回包强制原路返回</t>
   </si>
   <si>
-    <t>PA对称返回：虚拟路由器替代返回流量的路由查找，将流量引导回接收SYN数据包的MAC地址（ARP表确定下一跳），双ISP双活/非对称路由核心机制（PA管理指南p1294）；天融信手册检索无对称返回/回程机制命中，策略路由与LLB的回程保障能力待验证；迁移评估项：多ISP双活环境需实测天融信回包路由对称性，否则现网业务中断</t>
-  </si>
-  <si>
     <t>解密策略</t>
   </si>
   <si>
@@ -664,36 +678,24 @@
     <t>解密后明文流量镜像至专用接口供第三方分析</t>
   </si>
   <si>
-    <t>PA解密后将明文流量镜像到专用接口供IDS/抓包，需激活免费许可证（PA管理指南p1059）；天融信无解密流量镜像专用功能（仅SSL卸载+WAF镜像联动）</t>
-  </si>
-  <si>
     <t>支持解密不受信证书分离处理</t>
   </si>
   <si>
     <t>外部无效证书以不受信转发证书重签，保留浏览器告警</t>
   </si>
   <si>
-    <t>PA转发代理遇外部过期/不受信证书时，不用内部信任CA重签，而是专用Forward Untrust Certificate重签名，让浏览器保留不受信告警（PA管理指南p994、p1030）；天融信SSL解密（透明代理/服务器SSL解密，天融信手册《代理策略》页）未见受信/不受信双证书体系；迁移评估项：需验证天融信对外部无效证书的处理方式，避免直接阻断（白屏）或信任重签（掩盖风险）</t>
-  </si>
-  <si>
     <t>支持解密规则按URL类别选择性解密</t>
   </si>
   <si>
     <t>按URL类别圈定解密范围，排除银行/医疗等敏感类</t>
   </si>
   <si>
-    <t>PA解密规则可按URL类别（含自定义类别）选择解密范围，可排除银行/医疗等敏感类别不解密（PA Web帮助p164）；天融信SSL解密（代理策略/代理模板）无按URL类别选择解密机制（检索无命中）</t>
-  </si>
-  <si>
     <t>支持SSH代理解密与SSH隧道控制</t>
   </si>
   <si>
     <t>SSH代理解密+SSH隧道(ssh-tunnel)识别控制</t>
   </si>
   <si>
-    <t>PA解密策略SSH Proxy类型解密SSH通信，可通过ssh-tunnel App-ID在策略中控制SSH隧道（端口转发/内网穿透），正常SSH管理流量放行；含不受支持算法检查/资源不足阻断会话等防护（PA Web帮助p164、p318-319）；天融信手册检索无SSH代理/SSH隧道控制命中</t>
-  </si>
-  <si>
     <t>网络数据包代理</t>
   </si>
   <si>
@@ -703,9 +705,6 @@
     <t>已解密/未解密/非TLS流量均可内联转发第三方安全链</t>
   </si>
   <si>
-    <t>PA网络数据包代理策略将已解密/未解密TLS/非TLS流量内联转发至第三方安全工具，路径选择选项卡应用数据包代理配置文件定义经路由L3安全链的转发方式（PA Web帮助p167-170）；天融信无网络数据包代理模块，最接近手段为WAF旁路联动（经交换机镜像引流，天融信手册《与WAF联动》页），非内联且无回注路径；对应矩阵#122</t>
-  </si>
-  <si>
     <t>隧道检测</t>
   </si>
   <si>
@@ -715,27 +714,18 @@
     <t>解封装并检测GTP-U/VXLAN/非加密IPSec隧道内层嵌套流量</t>
   </si>
   <si>
-    <t>PA隧道检测支持GTP-U/VXLAN/非加密IPSec（NULL加密/AH传输模式）明文隧道内层检测，GTP-U仅支持GTP的防火墙可用（PA Web帮助p172-174）；天融信VXLAN仅隧道封装转发与三层网关、无内层安全检测（天融信手册《业务接入端》《三层VXLAN网关》页），GTP检测检索无命中；GRE天融信解封装后内层按普通流量检测（天融信手册《GRE隧道》页）已支持，故不列入本差异项；对应矩阵#128/37</t>
-  </si>
-  <si>
     <t>支持最大隧道检测级别设置</t>
   </si>
   <si>
     <t>指定检测一级或两级封装级别，VXLAN仅支持一级检测</t>
   </si>
   <si>
-    <t>PA隧道检测策略最大检测级别可选One Level（默认）或Two Levels(Tunnel In Tunnel)，VXLAN仅外层一级检测（PA Web帮助p174）；天融信手册无隧道检测级别控制（检索无命中）</t>
-  </si>
-  <si>
     <t>支持隧道异常报文丢弃选项</t>
   </si>
   <si>
     <t>超限封装、隧道协议标头严格检查失败、隧道内未知协议的报文，可分别配置丢弃</t>
   </si>
   <si>
-    <t>PA隧道检测策略可选启用：超过最大隧道检测级别的封装数据包丢弃（PA Web帮助p174）；天融信手册无对应选项（检索无命中）</t>
-  </si>
-  <si>
     <t>支持解配置内层流量的独立安全区域映射与策略匹配</t>
   </si>
   <si>
@@ -763,43 +753,13 @@
     <t>匹配覆盖策略的流量跳过七层检测，四层快速转发</t>
   </si>
   <si>
-    <t>PA应用替代策略明确绕过第7层处理与威胁检查，改用第4层状态检查以加速（PA管理指南p1307）；天融信自定义应用加入规则库后仍默认经安全引擎检测（天融信手册《自定义应用》页）；迁移评估项：PA应用替代多为私有大流量业务加速，转换时需同步关闭对应策略的IPS/七层检测，否则性能被拖垮或误阻断</t>
-  </si>
-  <si>
-    <t>身份验证(Authentication)</t>
-  </si>
-  <si>
-    <t>支持认证策略超时与单次认证（SSO）</t>
-  </si>
-  <si>
-    <t>认证超时+单次认证(SSO)</t>
-  </si>
-  <si>
-    <t>PA支持认证超时减少重复质询、Kerberos/SAML/RADIUS等对接（PA Web帮助p186）；天融信手册检索认证超时/单点登录/SSO无命中（仅在线用户在线时长查看与强制下线）；迁移评估项：需核实天融信认证会话有效期配置与SSO对接能力</t>
-  </si>
-  <si>
-    <t>支持基于应用与流量策略触发的业务级MF 质询</t>
-  </si>
-  <si>
-    <t>根据安全策略直接对高敏感业务流量触发 MFA 质询</t>
-  </si>
-  <si>
-    <t>PA身份验证策略通过Authentication Enforcement对象对匹配流量强制质询，支持多因素身份验证（每因素独立超时，防火墙记录时间戳），MFA供应商API/RADIUS对接（PA Web帮助p185-186、p310、p735-742）；天融信双因子认证（密码+短信/证书/Ukey）仅限管理员/用户登录场景（天融信手册《登录安全策略》页），无流量策略触发MFA质询</t>
-  </si>
-  <si>
-    <t>支持身份验证策略规则的多维匹配与 Enforcement 对象</t>
-  </si>
-  <si>
-    <t>策略支持基于源/目的区域、地址、用户、HIP、设备匹配；绑定 Authentication Enforcement 对象指定认证方式（web-form、Kerberos、client-cert 等）</t>
-  </si>
-  <si>
-    <t>PA身份验证策略支持源/目的区域、地址、用户、HIP等多维匹配，并绑定Authentication Enforcement对象指定认证方式与MFA供应商（PA Web帮助p182-186）；天融信无独立认证策略库，认证绑定于用户访问策略与门户认证（天融信手册《管理用户》页）；对应矩阵#35</t>
+    <t>身份验证</t>
   </si>
   <si>
     <t>支持 IP-用户映射的可信源地址过滤</t>
   </si>
   <si>
-    <t>配置可信源地址（Trusted Source Address）白名单，仅允许指定的域控、日志服务器或 Agent 提交 IP-用户映射关系，自动识别并过滤来自代理设备（Proxy/NAT）或非授权日志源的无效映射</t>
+    <t>配置可信源地址白名单，仅接受来自指定域控、User-ID 代理或 Syslog 发件人的 IP-用户映射，丢弃非可信来源的映射；代理场景可启用 XFF（X-Forwarded-For）标头提取真实客户端 IP，避免将代理地址误映射为用户</t>
   </si>
   <si>
     <t>支持 IP-用户映射关系的独立老化控制</t>
@@ -808,94 +768,79 @@
     <t>对动态采集的 IP-用户映射关系配置独立的老化超时时间（Mapping Timeout），支持根据用户离线或超时事件自动清空映射表项，防止 IP 重用导致的身份误判。</t>
   </si>
   <si>
-    <t>DoS防护(DoS Protection)</t>
-  </si>
-  <si>
-    <t>支持针对关键资源的分类/聚合DoS防护</t>
-  </si>
-  <si>
-    <t>分类(源/目的IP粒度)+聚合(全局)双层阈值限流</t>
-  </si>
-  <si>
-    <t>PA DoS策略基于源/目的接口、区域、地址、服务定义允许/拒绝/告警，规则可选聚合与分类双层DoS保护配置文件设定阈值速率（PA Web帮助p189-191、PA管理指南p1354）；天融信DDoS防护模块按防护对象（目的服务器）设阈值（pps/bps），可达目的IP粒度（天融信手册《配置策略模板》《日志查看》页）；对应矩阵#52/42</t>
-  </si>
-  <si>
-    <t>支持分类与聚合双层DoS配置文件</t>
-  </si>
-  <si>
-    <t>聚合配置文件：针对总流量统一阈值（连接/秒、数据包/秒），超限全局告警/限速；分类配置文件：针对单IP独立计数阈值，超限仅处理该IP；两者均支持告警阈值、最大速率与阻断时长</t>
-  </si>
-  <si>
-    <t>PA DoS保护配置文件分聚合（Aggregate）与分类（Classified）双层，按传入连接/数据包速率设告警与最大速率限制（PA Web帮助p189-191）；天融信DDoS防护按阈值（pps/bps）监视触发防护，无聚合/分类双层配置文件形态（天融信手册《配置策略模板》页）；对应矩阵#52/42</t>
-  </si>
-  <si>
-    <t>支持阻止 IP 列表联动与硬件/软件双重阻断</t>
-  </si>
-  <si>
-    <t>Protect 动作触发后自动加入 Block IP List，支持 hw（硬件快速阻断）与 sw（软件回退）及 Block Duration</t>
-  </si>
-  <si>
-    <t>PA DoS策略Protect动作触发后可联动Block IP（硬件hw快速阻断/软件sw回退，含Block Duration时长）（PA Web帮助p189-191）；天融信DDoS防护触发防御动作后可将源IP加入DOS防护动态黑名单（天融信手册《配置策略模板》页），无硬件/软件双重阻断细分；部分支持</t>
-  </si>
-  <si>
-    <t>支持 DoS 策略多动作（Allow / Deny / Protect）</t>
-  </si>
-  <si>
-    <t>不同流量可分别配置放行、直接拒绝或防护限速</t>
-  </si>
-  <si>
-    <t>PA DoS策略规则支持Allow/Deny/Protect三种动作（PA Web帮助p189）；天融信DDoS防护策略模板可配置检测阈值和防御动作（天融信手册《配置策略模板》页），放行/拒绝经黑白名单实现（天融信手册《黑白名单》页）</t>
-  </si>
-  <si>
-    <t>动态对象(Dynamic Objects)</t>
-  </si>
-  <si>
-    <t>支持外部动态列表作为策略地址对象（EDL）</t>
-  </si>
-  <si>
-    <t>HTTP/HTTPS外部文本列表(IP/域名/URL)自动拉取，策略直接引用</t>
-  </si>
-  <si>
-    <t>PA外部动态列表：基于HTTP/HTTPS托管的文本文件创建IP/URL/域名/IMEI/IMSI地址对象，防火墙定时自动拉取更新，策略中直接引用（Objects&gt;External Dynamic Lists，PA Web帮助p236-239；策略源/目标可直接选EDL，p196-197）；天融信手册检索外部动态列表/EDL无命中，仅内置威胁情报库与云端威胁情报库（规则集管理，天融信手册《威胁情报》《配置规则集》页），无策略直接引用任意外部文本列表机制；迁移评估项：PA策略中引用的EDL需转换为天融信静态地址组定期导入或威胁情报联动</t>
-  </si>
-  <si>
-    <t>支持基于标记的动态地址组（DAG）</t>
-  </si>
-  <si>
-    <t>Tag标记过滤器动态地址组，成员随IP变化自动更新</t>
-  </si>
-  <si>
-    <t>PA动态地址组：查找标记(Tag)+基于标记的过滤器（AND/OR匹配）动态填充成员，VM信息源注册或XML/REST API定义标记，IP变化时策略自动生效（PA Web帮助p207-208、p228）；天融信手册检索动态地址组/标签/SDN/云平台联动无命中，地址组为静态IP/子网绑定（天融信手册《地址》页）；迁移评估项：PA云环境Tag微隔离策略需转换为静态地址组，IP漂移场景需人工或API维护</t>
+    <t>支持身份验证策略规则的多维匹配与身份验证执行对象</t>
+  </si>
+  <si>
+    <t>规则匹配条件涵盖源/目的区域、地址、用户、HIP、服务（TCP/UDP 端口）与 URL 类别；通过身份验证执行对象绑定身份验证配置文件，指定 Web 表单、Kerberos SSO、客户端证书等认证方式</t>
+  </si>
+  <si>
+    <t>支持身份验证策略超时与单点登录（SSO）</t>
+  </si>
+  <si>
+    <t>身份验证策略规则可配置超时时间窗口，窗口期内用户重复访问资源免于再次质询；支持 Kerberos 单点登录（SSO），SSO 失败时可回退 Web 表单或客户端证书认证</t>
+  </si>
+  <si>
+    <t>支持基于业务流量触发的 MFA 多因素质询</t>
+  </si>
+  <si>
+    <t>身份验证策略对高敏感业务流量（按服务、URL 类别或用户匹配）强制触发 MFA 质询；多因素各自独立超时，防火墙记录身份验证时间戳</t>
+  </si>
+  <si>
+    <t>支持记录身份验证日志</t>
+  </si>
+  <si>
+    <t>为匹配身份验证规则的每个请求生成身份验证日志，记录成功/失败及超时重新质询事件；规则可绑定日志转发配置文件，将日志转发至 Panorama 或 syslog 服务器</t>
+  </si>
+  <si>
+    <t>Dos策略</t>
+  </si>
+  <si>
+    <t>支持源区域匹配</t>
+  </si>
+  <si>
+    <t>支持源接口匹配</t>
+  </si>
+  <si>
+    <t>支持源地址匹配</t>
+  </si>
+  <si>
+    <t>支持源用户匹配</t>
+  </si>
+  <si>
+    <t>支持聚合DoS防护</t>
+  </si>
+  <si>
+    <t>支持配置策略生效计划</t>
+  </si>
+  <si>
+    <t xml:space="preserve">循环类型：重复/不重复。
+重复周期：按“每天”或“每周“进行循环。
+时间粒度：支持指定具体的时间范围（如 09:00 - 18:00）
+</t>
   </si>
   <si>
     <t>SD-WAN</t>
   </si>
   <si>
+    <t>支持源/目的区域匹配</t>
+  </si>
+  <si>
+    <t>支持源/目的地址匹配</t>
+  </si>
+  <si>
     <t>支持按应用配置链路路径管理与链路质量探测</t>
   </si>
   <si>
-    <t>按应用分配链路与流量分发（天融信以策略路由+LLB近似实现）</t>
-  </si>
-  <si>
-    <t>PA SD-WAN策略按应用/抖动/延迟/丢包指标分配链路，流量分发（PA Web帮助p197）；天融信为策略路由+链路负载均衡近似实现（天融信手册《策略路由》《链路负载均衡》页），无SD-WAN策略模型；对应矩阵#129/120</t>
-  </si>
-  <si>
-    <t>支持SD-WAN路径选择与链路质量监测（jitter/latency/loss）</t>
-  </si>
-  <si>
-    <t>抖动/延迟/丢包多维指标选路（天融信现仅延迟探测）</t>
-  </si>
-  <si>
-    <t>PA路径质量配置文件基于抖动/延迟/丢包等运行状况指标选路（PA Web帮助p195）；天融信有链路探测(ping)+智能选路(最小延迟优先)（天融信手册《策略路由》页），无jitter/latency/loss多维指标</t>
+    <t>按应用分配链路与流量分发</t>
+  </si>
+  <si>
+    <t>SD-WAN/平台</t>
   </si>
   <si>
     <t>支持 SaaS 应用质量优化</t>
   </si>
   <si>
-    <t>对SaaS应用独立探测路径质量（自适应/IP/FQDN/URL监视模式），质量下降时切换至其他互联网直接接入(DIA)链路</t>
-  </si>
-  <si>
-    <t>PA SaaS质量配置文件按自适应/IP地址/FQDN/HTTP(S) URL监视SaaS应用路径质量，下降时更换路径并故障转移到DIA链路（PA Web帮助p325-326）；天融信无SD-WAN模块，以策略路由+链路负载均衡近似实现（天融信手册《策略路由》《链路负载均衡》页）；对应矩阵#129/120</t>
+    <t>对SaaS应用独立探测路径质量</t>
   </si>
   <si>
     <t>支持多链路流量分发策略</t>
@@ -904,43 +849,22 @@
     <t>多链路场景定义流量分发模式：最佳可用路径、自上而下优先级、加权会话分发（按链路标签百分比）</t>
   </si>
   <si>
-    <t>PA流量分发配置文件支持最佳可用路径/自上而下优先级/加权会话分发三种模式，按链路标签分组选路与故障转移（PA Web帮助p326-327）；天融信无SD-WAN模块，以策略路由+链路负载均衡近似实现（天融信手册《策略路由》《链路负载均衡》页）；对应矩阵#129/120</t>
-  </si>
-  <si>
     <t>支持丢包敏感业务的前向纠错</t>
   </si>
   <si>
-    <t>对语音、视频会议等实时应用，在单条链路质量劣化时启用 FEC（Forward Error Correction），通过冗余包补偿丢包，无需重传</t>
-  </si>
-  <si>
-    <t>PA纠错配置文件支持前向纠错FEC（奇偶校验位恢复丢包）与数据包复制（会话复制到第二隧道），仅建议用于丢包敏感的音频/视频应用（PA Web帮助p327-328）；天融信无SD-WAN模块，以策略路由+链路负载均衡近似实现（天融信手册《策略路由》《链路负载均衡》页）；对应矩阵#129/120</t>
+    <t>对语音、视频会议等实时应用</t>
   </si>
   <si>
     <t>支持 SD-WAN 逻辑接口绑定与物理链路聚合</t>
   </si>
   <si>
-    <t>将多个物理 WAN 接口（Ethernet、PPPoE、Cellular 等）绑定为一个 SD-WAN 接口组，作为统一出口被策略引用。</t>
-  </si>
-  <si>
-    <t>PA SD-WAN虚拟接口将多个物理WAN接口（指向同一目的地）绑定为统一接口，按协议类型（IPv4/IPv6 DIA或VPN隧道）定义，被SD-WAN策略引用（PA Web帮助p422）；天融信链路聚合为L2聚合组（需对端同bond模式，天融信手册《聚合接口》页），LLB按算法选最佳物理链路（天融信手册《链路负载均衡》页），无SD-WAN虚拟接口组</t>
-  </si>
-  <si>
-    <t>支持 Panorama 集中式 SD-WAN 管理与 VPN 集群</t>
-  </si>
-  <si>
-    <t>在 Panorama 上集中管理所有分支 SD-WAN 设备、配置 SD-WAN VPN 集群（站点间自动 VPN 互联）、查看跨站点链路状态与隧道健康度。</t>
-  </si>
-  <si>
-    <t>PA Panorama SD-WAN插件集中管理分支/中心设备、配置SD-WAN VPN集群（站点间自动互联）、监控路径运行状况并生成报告（PA Web帮助p1074-1078）；天融信无集中SD-WAN管理平台，天融信无SD-WAN模块，以策略路由+链路负载均衡近似实现（天融信手册《策略路由》《链路负载均衡》页）；对应矩阵#129/120</t>
-  </si>
-  <si>
-    <t>支持 SD-WAN 隧道/链路的集中监控与日志审计</t>
-  </si>
-  <si>
-    <t>在 ACC 或 Monitor 中查看 SD-WAN 链路切换事件、质量告警、隧道状态变化，并生成报告。</t>
-  </si>
-  <si>
-    <t>PA可在ACC/Monitor查看SD-WAN链路质量事件与策略命中，Panorama集中监控路径运行状况指标并生成报告（PA Web帮助p1074-1078）；天融信LLB模块可查看链路池和本地各链路流量负载（天融信手册《链路负载均衡》页），无SD-WAN链路质量告警与切换事件审计；部分支持</t>
+    <t>将多个物理 WAN 接口绑定为一个 SD-WAN 接口组，作为统一出口被策略引用</t>
+  </si>
+  <si>
+    <t>支持 Panorama 集中式 SD-WAN 管理</t>
+  </si>
+  <si>
+    <t>在 Panorama 上集中管理所有分支 SD-WAN 设备</t>
   </si>
 </sst>
 </file>
@@ -954,7 +878,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="28">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -963,46 +887,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="8" tint="-0.25"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1019,6 +914,11 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -1380,7 +1280,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1446,9 +1346,7 @@
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1457,7 +1355,9 @@
       </left>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1486,85 +1386,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1694,439 +1515,344 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="21">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="21">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="23">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="24">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="25">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2195,13 +1921,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1111670</xdr:colOff>
+      <xdr:colOff>784010</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>18250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>320820</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2984010</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>187275</xdr:rowOff>
     </xdr:to>
@@ -2235,8 +1961,8 @@
                   <a:alpha val="19999"/>
                 </a:srgbClr>
               </a:solidFill>
-              <a:latin typeface="Arial" panose="020B0604020202090204"/>
-              <a:ea typeface="宋体"/>
+              <a:latin typeface="Arial" panose="020B0604020202020204"/>
+              <a:ea typeface="宋体" panose="02010600030101010101" pitchFamily="7" charset="-122"/>
             </a:rPr>
             <a:t>AI 生成</a:t>
           </a:r>
@@ -2246,75 +1972,8 @@
                 <a:alpha val="19999"/>
               </a:srgbClr>
             </a:solidFill>
-            <a:latin typeface="Arial" panose="020B0604020202090204"/>
-            <a:ea typeface="宋体"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1285025</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>469100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>747540</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>819100</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6799580" y="6399530"/>
-          <a:ext cx="2200275" cy="349885"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial" panose="020B0604020202090204"/>
-              <a:ea typeface="宋体"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" sz="1600" dirty="0">
-            <a:solidFill>
-              <a:srgbClr val="808080">
-                <a:alpha val="19999"/>
-              </a:srgbClr>
-            </a:solidFill>
-            <a:latin typeface="Arial" panose="020B0604020202090204"/>
-            <a:ea typeface="宋体"/>
+            <a:latin typeface="Arial" panose="020B0604020202020204"/>
+            <a:ea typeface="宋体" panose="02010600030101010101" pitchFamily="7" charset="-122"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2583,1119 +2242,1119 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.2" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="11.7115384615385" style="53" customWidth="1"/>
-    <col min="2" max="2" width="19.7115384615385" style="53" customWidth="1"/>
-    <col min="3" max="3" width="54.7115384615385" style="53" customWidth="1"/>
-    <col min="4" max="4" width="45.2884615384615" style="53" customWidth="1"/>
-    <col min="5" max="5" width="7.71153846153846" style="53" customWidth="1"/>
-    <col min="6" max="6" width="37.8557692307692" style="53" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.71153846153846" style="53" customWidth="1"/>
-    <col min="8" max="8" width="9.71153846153846" style="54" customWidth="1"/>
+    <col min="1" max="1" width="11.7090909090909" style="12" customWidth="1"/>
+    <col min="2" max="2" width="19.7090909090909" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.7090909090909" style="12" customWidth="1"/>
+    <col min="4" max="4" width="45.2909090909091" style="12" customWidth="1"/>
+    <col min="5" max="5" width="7.70909090909091" style="12" customWidth="1"/>
+    <col min="6" max="6" width="37.8545454545455" style="12" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.70909090909091" style="12" customWidth="1"/>
+    <col min="8" max="8" width="9.70909090909091" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="56" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="57" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="57"/>
-      <c r="G1" s="56" t="s">
+      <c r="F1" s="16"/>
+      <c r="G1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="60"/>
-      <c r="E2" s="61" t="s">
+      <c r="D2" s="19"/>
+      <c r="E2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="62" t="s">
+      <c r="F2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="G2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="H2" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:8">
-      <c r="A3" s="11"/>
-      <c r="B3" s="59" t="s">
+      <c r="A3" s="23"/>
+      <c r="B3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="60" t="s">
+      <c r="D3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="61" t="s">
+      <c r="E3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="63" t="s">
+      <c r="F3" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="60" t="s">
+      <c r="G3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:8">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="60" t="s">
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:8">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="60" t="s">
+      <c r="A5" s="23"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="60" t="s">
+      <c r="D5" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A6" s="11"/>
-      <c r="B6" s="64" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="61" t="s">
+      <c r="E6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="62" t="s">
+      <c r="F6" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="60" t="s">
+      <c r="G6" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="35" t="s">
+      <c r="H6" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="60" t="s">
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="60" t="s">
+      <c r="D7" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="60" t="s">
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="60" t="s">
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="60" t="s">
+      <c r="D9" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="60" t="s">
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="60"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="60" t="s">
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="60" t="s">
+      <c r="A12" s="23"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
     </row>
     <row r="13" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A13" s="12"/>
-      <c r="B13" s="64" t="s">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="60" t="s">
+      <c r="C13" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="60" t="s">
+      <c r="D13" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="61" t="s">
+      <c r="E13" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="62" t="s">
+      <c r="F13" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="60" t="s">
+      <c r="G13" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="35" t="s">
+      <c r="H13" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A14" s="65" t="s">
+      <c r="A14" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="61" t="s">
+      <c r="E14" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="62" t="s">
+      <c r="F14" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="60" t="s">
+      <c r="G14" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="35" t="s">
+      <c r="H14" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A15" s="14"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="60" t="s">
+      <c r="A15" s="29"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A16" s="14"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="60" t="s">
+      <c r="A16" s="29"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A17" s="14"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="60" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A18" s="14"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="60" t="s">
+      <c r="A18" s="29"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A19" s="14"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="60" t="s">
+      <c r="A19" s="29"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A20" s="14"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="60" t="s">
+      <c r="A20" s="29"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A21" s="14"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="60" t="s">
+      <c r="A21" s="29"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
     </row>
     <row r="22" ht="32.25" customHeight="1" spans="1:8">
-      <c r="A22" s="13"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="60" t="s">
+      <c r="A22" s="30"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A23" s="65" t="s">
+      <c r="A23" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="60" t="s">
+      <c r="C23" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="60" t="s">
+      <c r="D23" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="61" t="s">
+      <c r="E23" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="67" t="s">
+      <c r="F23" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G23" s="60" t="s">
+      <c r="G23" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H23" s="35" t="s">
+      <c r="H23" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A24" s="65" t="s">
+      <c r="A24" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="64" t="s">
+      <c r="B24" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="60" t="s">
+      <c r="D24" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="61" t="s">
+      <c r="E24" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="68" t="s">
+      <c r="F24" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="60" t="s">
+      <c r="G24" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="35" t="s">
+      <c r="H24" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A25" s="65" t="s">
+      <c r="A25" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="64" t="s">
+      <c r="B25" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="60" t="s">
+      <c r="C25" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="69" t="s">
+      <c r="D25" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="61" t="s">
+      <c r="E25" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="62" t="s">
+      <c r="F25" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="G25" s="60" t="s">
+      <c r="G25" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="35" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" s="52" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A26" s="14"/>
-      <c r="B26" s="64" t="s">
+      <c r="H25" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" s="11" customFormat="1" ht="28.5" customHeight="1" spans="1:8">
+      <c r="A26" s="29"/>
+      <c r="B26" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="35" t="s">
+      <c r="C26" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="69"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="35"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="22"/>
     </row>
     <row r="27" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A27" s="14"/>
-      <c r="B27" s="64" t="s">
+      <c r="A27" s="29"/>
+      <c r="B27" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="60" t="s">
+      <c r="C27" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="60" t="s">
+      <c r="D27" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="61" t="s">
+      <c r="E27" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="62" t="s">
+      <c r="F27" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="60" t="s">
+      <c r="G27" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H27" s="35" t="s">
+      <c r="H27" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A28" s="14"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="60" t="s">
+      <c r="A28" s="29"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
     </row>
     <row r="29" ht="60" customHeight="1" spans="1:8">
-      <c r="A29" s="14"/>
-      <c r="B29" s="64" t="s">
+      <c r="A29" s="29"/>
+      <c r="B29" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="60" t="s">
+      <c r="C29" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="35" t="s">
+      <c r="D29" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="61" t="s">
+      <c r="E29" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="71" t="s">
+      <c r="F29" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="G29" s="60" t="s">
+      <c r="G29" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H29" s="35" t="s">
+      <c r="H29" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A30" s="14"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="60" t="s">
+      <c r="A30" s="29"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="60" t="s">
+      <c r="D30" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="61" t="s">
+      <c r="E30" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F30" s="11"/>
-      <c r="G30" s="60" t="s">
+      <c r="F30" s="23"/>
+      <c r="G30" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H30" s="35" t="s">
+      <c r="H30" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A31" s="13"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="60" t="s">
+      <c r="A31" s="30"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="60" t="s">
+      <c r="D31" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="72" t="s">
+      <c r="E31" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="12"/>
-      <c r="G31" s="60" t="s">
+      <c r="F31" s="25"/>
+      <c r="G31" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="35" t="s">
+      <c r="H31" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A32" s="65" t="s">
+      <c r="A32" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="B32" s="64" t="s">
+      <c r="B32" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="60" t="s">
+      <c r="C32" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="60" t="s">
+      <c r="D32" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E32" s="61" t="s">
+      <c r="E32" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="62" t="s">
+      <c r="F32" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="60" t="s">
+      <c r="G32" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="35" t="s">
+      <c r="H32" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A33" s="13"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="60" t="s">
+      <c r="A33" s="30"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A34" s="65" t="s">
+      <c r="A34" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="64" t="s">
+      <c r="B34" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="60" t="s">
+      <c r="C34" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="60"/>
-      <c r="E34" s="61" t="s">
+      <c r="D34" s="19"/>
+      <c r="E34" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="62" t="s">
+      <c r="F34" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="G34" s="60" t="s">
+      <c r="G34" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H34" s="35" t="s">
+      <c r="H34" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A35" s="14"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="60" t="s">
+      <c r="A35" s="29"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="60"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
     </row>
     <row r="36" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A36" s="14"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="60" t="s">
+      <c r="A36" s="29"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="60"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
     </row>
     <row r="37" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A37" s="13"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="73" t="s">
+      <c r="A37" s="30"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="D37" s="73"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A38" s="64" t="s">
+      <c r="A38" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="64" t="s">
+      <c r="B38" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="74" t="s">
+      <c r="C38" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="D38" s="74"/>
-      <c r="E38" s="72" t="s">
+      <c r="D38" s="38"/>
+      <c r="E38" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="75" t="s">
+      <c r="F38" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="60" t="s">
+      <c r="G38" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H38" s="35" t="s">
+      <c r="H38" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A39" s="11"/>
-      <c r="B39" s="64" t="s">
+      <c r="A39" s="23"/>
+      <c r="B39" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="74" t="s">
+      <c r="C39" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="D39" s="74"/>
-      <c r="E39" s="72" t="s">
+      <c r="D39" s="38"/>
+      <c r="E39" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
     </row>
     <row r="40" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A40" s="11"/>
-      <c r="B40" s="64" t="s">
+      <c r="A40" s="23"/>
+      <c r="B40" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="74" t="s">
+      <c r="C40" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="D40" s="76" t="s">
+      <c r="D40" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="72" t="s">
+      <c r="E40" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="71" t="s">
+      <c r="F40" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="G40" s="60" t="s">
+      <c r="G40" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H40" s="35" t="s">
+      <c r="H40" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A41" s="11"/>
-      <c r="B41" s="64" t="s">
+      <c r="A41" s="23"/>
+      <c r="B41" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="60" t="s">
+      <c r="C41" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D41" s="74" t="s">
+      <c r="D41" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="E41" s="72" t="s">
+      <c r="E41" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F41" s="71" t="s">
+      <c r="F41" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="G41" s="60" t="s">
+      <c r="G41" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="H41" s="35" t="s">
+      <c r="H41" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A42" s="11"/>
-      <c r="B42" s="64" t="s">
+      <c r="A42" s="23"/>
+      <c r="B42" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="74"/>
-      <c r="E42" s="72"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="60"/>
-      <c r="H42" s="35"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="22"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A43" s="12"/>
-      <c r="B43" s="64" t="s">
+      <c r="A43" s="25"/>
+      <c r="B43" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="74" t="s">
+      <c r="C43" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="74"/>
-      <c r="E43" s="72" t="s">
+      <c r="D43" s="38"/>
+      <c r="E43" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F43" s="71" t="s">
+      <c r="F43" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="G43" s="60" t="s">
-        <v>109</v>
-      </c>
-      <c r="H43" s="35" t="s">
+      <c r="G43" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H43" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A44" s="77" t="s">
+      <c r="A44" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="78" t="s">
+      <c r="B44" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="C44" s="79" t="s">
+      <c r="C44" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="79" t="s">
+      <c r="D44" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="E44" s="80" t="s">
+      <c r="E44" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="81" t="s">
+      <c r="F44" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="G44" s="82" t="s">
+      <c r="G44" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="H44" s="38" t="s">
+      <c r="H44" s="47" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A45" s="14"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="74" t="s">
+      <c r="A45" s="29"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="D45" s="74" t="s">
+      <c r="D45" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="E45" s="11"/>
-      <c r="F45" s="83" t="s">
+      <c r="E45" s="23"/>
+      <c r="F45" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="G45" s="60" t="s">
+      <c r="G45" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="35" t="s">
+      <c r="H45" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A46" s="14"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="74" t="s">
+      <c r="A46" s="29"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="D46" s="74"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
     </row>
     <row r="47" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A47" s="14"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="74" t="s">
+      <c r="A47" s="29"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="D47" s="74"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="83" t="s">
+      <c r="D47" s="38"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="G47" s="60" t="s">
+      <c r="G47" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H47" s="35" t="s">
+      <c r="H47" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A48" s="13"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="84" t="s">
+      <c r="A48" s="30"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="D48" s="84"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="67" t="s">
+      <c r="D48" s="49"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="G48" s="73" t="s">
+      <c r="G48" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="H48" s="85" t="s">
+      <c r="H48" s="50" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="49" ht="42.75" customHeight="1" spans="1:8">
-      <c r="A49" s="86" t="s">
+      <c r="A49" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="B49" s="86" t="s">
+      <c r="B49" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="C49" s="87" t="s">
+      <c r="C49" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="88" t="s">
+      <c r="D49" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="E49" s="89" t="s">
+      <c r="E49" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="90"/>
-      <c r="G49" s="91" t="s">
+      <c r="F49" s="55"/>
+      <c r="G49" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="H49" s="92"/>
+      <c r="H49" s="57"/>
     </row>
     <row r="50" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A50" s="93"/>
-      <c r="B50" s="93"/>
-      <c r="C50" s="87" t="s">
+      <c r="A50" s="58"/>
+      <c r="B50" s="58"/>
+      <c r="C50" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="D50" s="94" t="s">
+      <c r="D50" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="E50" s="95" t="s">
+      <c r="E50" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="F50" s="96"/>
-      <c r="G50" s="91" t="s">
+      <c r="F50" s="61"/>
+      <c r="G50" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="H50" s="97"/>
+      <c r="H50" s="62"/>
     </row>
     <row r="51" ht="14.25" customHeight="1" spans="1:8">
-      <c r="A51" s="93"/>
-      <c r="B51" s="93"/>
-      <c r="C51" s="87" t="s">
+      <c r="A51" s="58"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="52" t="s">
         <v>125</v>
       </c>
-      <c r="D51" s="98" t="s">
+      <c r="D51" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="E51" s="95" t="s">
+      <c r="E51" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="F51" s="90"/>
-      <c r="G51" s="91" t="s">
+      <c r="F51" s="55"/>
+      <c r="G51" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="H51" s="92"/>
+      <c r="H51" s="57"/>
     </row>
     <row r="52" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A52" s="99"/>
-      <c r="B52" s="99"/>
-      <c r="C52" s="98" t="s">
+      <c r="A52" s="64"/>
+      <c r="B52" s="64"/>
+      <c r="C52" s="63" t="s">
         <v>127</v>
       </c>
-      <c r="D52" s="88" t="s">
+      <c r="D52" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="E52" s="100" t="s">
+      <c r="E52" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="90" t="s">
+      <c r="F52" s="55" t="s">
         <v>129</v>
       </c>
-      <c r="G52" s="91" t="s">
+      <c r="G52" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="H52" s="92" t="s">
+      <c r="H52" s="57" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A53" s="78" t="s">
+      <c r="A53" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="B53" s="78" t="s">
+      <c r="B53" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="C53" s="79" t="s">
+      <c r="C53" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="D53" s="79"/>
-      <c r="E53" s="80" t="s">
+      <c r="D53" s="43"/>
+      <c r="E53" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F53" s="81" t="s">
+      <c r="F53" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="G53" s="82" t="s">
+      <c r="G53" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H53" s="38" t="s">
+      <c r="H53" s="47" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="54" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A54" s="12"/>
-      <c r="B54" s="64" t="s">
+      <c r="A54" s="25"/>
+      <c r="B54" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="C54" s="35" t="s">
+      <c r="C54" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="D54" s="76" t="s">
+      <c r="D54" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="E54" s="72" t="s">
+      <c r="E54" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F54" s="71" t="s">
+      <c r="F54" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="G54" s="60" t="s">
+      <c r="G54" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="H54" s="35" t="s">
+      <c r="H54" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A55" s="65" t="s">
+      <c r="A55" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="B55" s="64" t="s">
+      <c r="B55" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="C55" s="74" t="s">
+      <c r="C55" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="D55" s="74"/>
-      <c r="E55" s="72" t="s">
+      <c r="D55" s="38"/>
+      <c r="E55" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F55" s="71"/>
-      <c r="G55" s="60" t="s">
+      <c r="F55" s="35"/>
+      <c r="G55" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="H55" s="35" t="s">
+      <c r="H55" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="56" ht="42.75" customHeight="1" spans="1:8">
-      <c r="A56" s="65" t="s">
+      <c r="A56" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="B56" s="64" t="s">
+      <c r="B56" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="C56" s="74" t="s">
+      <c r="C56" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="D56" s="76" t="s">
+      <c r="D56" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="E56" s="72" t="s">
+      <c r="E56" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="F56" s="83" t="s">
+      <c r="F56" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="G56" s="60"/>
-      <c r="H56" s="35" t="s">
+      <c r="G56" s="19"/>
+      <c r="H56" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="57" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A57" s="64" t="s">
+      <c r="A57" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="B57" s="64" t="s">
+      <c r="B57" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C57" s="74" t="s">
+      <c r="C57" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="74" t="s">
+      <c r="D57" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="E57" s="72" t="s">
+      <c r="E57" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F57" s="83" t="s">
+      <c r="F57" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="G57" s="60" t="s">
+      <c r="G57" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="H57" s="35" t="s">
+      <c r="H57" s="22" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A58" s="101" t="s">
+      <c r="A58" s="66" t="s">
         <v>150</v>
       </c>
-      <c r="B58" s="101" t="s">
+      <c r="B58" s="66" t="s">
         <v>150</v>
       </c>
-      <c r="C58" s="73" t="s">
+      <c r="C58" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="D58" s="84" t="s">
+      <c r="D58" s="49" t="s">
         <v>152</v>
       </c>
-      <c r="E58" s="102" t="s">
+      <c r="E58" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="F58" s="103" t="s">
+      <c r="F58" s="68" t="s">
         <v>153</v>
       </c>
-      <c r="G58" s="73" t="s">
+      <c r="G58" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="H58" s="85" t="s">
+      <c r="H58" s="50" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="59" ht="28.5" customHeight="1" spans="1:8">
-      <c r="A59" s="86" t="s">
+      <c r="A59" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="B59" s="86" t="s">
+      <c r="B59" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="C59" s="104" t="s">
+      <c r="C59" s="69" t="s">
         <v>155</v>
       </c>
-      <c r="D59" s="96"/>
-      <c r="E59" s="100" t="s">
+      <c r="D59" s="61"/>
+      <c r="E59" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="F59" s="96"/>
-      <c r="G59" s="73" t="s">
+      <c r="F59" s="61"/>
+      <c r="G59" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="H59" s="97" t="s">
+      <c r="H59" s="62" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3765,1004 +3424,1547 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.2" outlineLevelCol="7"/>
+  <dimension ref="A1:G83"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="2" width="19.3942307692308" style="2" customWidth="1"/>
-    <col min="3" max="3" width="44.7211538461538" style="3" customWidth="1"/>
-    <col min="4" max="4" width="41.4519230769231" style="3" customWidth="1"/>
-    <col min="5" max="5" width="76.5769230769231" style="3" customWidth="1"/>
-    <col min="6" max="6" width="7.69230769230769" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.69230769230769" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8.63636363636364" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6363636363636" style="1" customWidth="1"/>
+    <col min="3" max="3" width="49.6363636363636" style="1" customWidth="1"/>
+    <col min="4" max="4" width="58.6363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.63636363636364" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.54545454545454" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.0909090909091" style="1" customWidth="1"/>
+    <col min="8" max="16383" width="9" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:8">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:7">
+      <c r="A2" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" ht="51" customHeight="1" spans="1:8">
-      <c r="A2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E2" s="9" t="s">
+    </row>
+    <row r="3" ht="28" spans="1:7">
+      <c r="A3" s="5"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="D3" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H2" s="10" t="s">
+      <c r="F3" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="3" ht="84" customHeight="1" spans="1:8">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="9" t="s">
+    <row r="4" ht="28" spans="1:7">
+      <c r="A4" s="5"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D4" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G4" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:7">
+      <c r="A5" s="5"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="F5" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:7">
+      <c r="A6" s="5"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:7">
+      <c r="A7" s="5"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="5"/>
+      <c r="B8" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="5"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:7">
+      <c r="A10" s="5"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="5"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="5"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="5"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="5"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="5"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="5"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" ht="28" spans="1:7">
+      <c r="A17" s="5"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="5"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="5"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="5"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="5"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="5"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="5"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="5"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="5"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" ht="28" spans="1:7">
+      <c r="A26" s="5"/>
+      <c r="B26" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="5"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="5"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" s="7"/>
+      <c r="E28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" ht="28" spans="1:7">
+      <c r="A29" s="5"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="5"/>
+      <c r="B30" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="5"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="5"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="5"/>
+      <c r="B33" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="5"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="5"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="5"/>
+      <c r="B36" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="5"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="5"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="5"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="5"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="5"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="5"/>
+      <c r="B42" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="5"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="5"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="5"/>
+      <c r="B45" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="5"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="5"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="5"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" ht="28" spans="1:7">
+      <c r="A49" s="5"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="28" spans="1:7">
+      <c r="A50" s="5"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="1:7">
+      <c r="A51" s="5"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D51" s="7"/>
+      <c r="E51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="1:7">
+      <c r="A52" s="5"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D52" s="7"/>
+      <c r="E52" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="53" ht="28" spans="1:7">
+      <c r="A53" s="5"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="5"/>
+      <c r="B54" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D54" s="7"/>
+      <c r="E54" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="5"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D55" s="7"/>
+      <c r="E55" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="5"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="5"/>
+      <c r="B57" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="5"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" ht="56" spans="1:7">
+      <c r="A59" s="5"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="60" ht="42" spans="1:7">
+      <c r="A60" s="5"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="61" ht="56" spans="1:7">
+      <c r="A61" s="5"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="62" ht="42" spans="1:7">
+      <c r="A62" s="5"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H3" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4" ht="70" customHeight="1" spans="1:8">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" ht="51" customHeight="1" spans="1:8">
-      <c r="A5" s="11"/>
-      <c r="B5" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="G62" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="63" ht="42" spans="1:7">
+      <c r="A63" s="5"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="64" ht="42" spans="1:7">
+      <c r="A64" s="5"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" spans="1:7">
+      <c r="A65" s="5"/>
+      <c r="B65" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="D65" s="4"/>
+      <c r="E65" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" spans="1:7">
+      <c r="A66" s="5"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="D66" s="4"/>
+      <c r="E66" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="6" ht="51" customHeight="1" spans="1:8">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="F6" s="8" t="s">
+      <c r="F66" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" spans="1:7">
+      <c r="A67" s="5"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D67" s="7"/>
+      <c r="E67" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" spans="1:7">
+      <c r="A68" s="5"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D68" s="7"/>
+      <c r="E68" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" spans="1:7">
+      <c r="A69" s="5"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D69" s="7"/>
+      <c r="E69" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" spans="1:7">
+      <c r="A70" s="5"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D70" s="7"/>
+      <c r="E70" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="5"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D71" s="7"/>
+      <c r="E71" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" ht="56" spans="1:7">
+      <c r="A72" s="5"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="5"/>
+      <c r="B73" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="7" ht="56" customHeight="1" spans="1:8">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="F7" s="8" t="s">
+      <c r="F73" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" ht="28" spans="1:7">
+      <c r="A78" s="5"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E78" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" ht="84" customHeight="1" spans="1:8">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="14"/>
-    </row>
-    <row r="9" ht="112" customHeight="1" spans="1:8">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="F78" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="79" ht="28" spans="1:7">
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E79" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" ht="171" customHeight="1" spans="1:8">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F10" s="16" t="s">
+      <c r="F79" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="80" ht="28" spans="1:7">
+      <c r="A80" s="5"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="81" ht="28" spans="1:7">
+      <c r="A81" s="5"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="82" ht="28" spans="1:7">
+      <c r="A82" s="5"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E82" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" ht="56" customHeight="1" spans="1:8">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" ht="81" customHeight="1" spans="1:8">
-      <c r="A12" s="11"/>
-      <c r="B12" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="13" ht="96" customHeight="1" spans="1:8">
-      <c r="A13" s="11"/>
-      <c r="B13" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="F13" s="8" t="s">
+      <c r="F82" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="5"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E83" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" ht="111" customHeight="1" spans="1:8">
-      <c r="A14" s="11"/>
-      <c r="B14" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15" ht="51" customHeight="1" spans="1:8">
-      <c r="A15" s="11"/>
-      <c r="B15" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" ht="126" customHeight="1" spans="1:8">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" ht="66" customHeight="1" spans="1:8">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" ht="96" customHeight="1" spans="1:8">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" ht="111" customHeight="1" spans="1:8">
-      <c r="A19" s="11"/>
-      <c r="B19" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" ht="96" customHeight="1" spans="1:8">
-      <c r="A20" s="11"/>
-      <c r="B20" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="21" ht="96" customHeight="1" spans="1:8">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H21" s="10"/>
-    </row>
-    <row r="22" ht="54" customHeight="1" spans="1:8">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="68" spans="1:8">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="E23" s="24"/>
-      <c r="F23" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="H23" s="27"/>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="17" spans="1:8">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="H24" s="27"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="17" spans="1:8">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="H25" s="27"/>
-    </row>
-    <row r="26" ht="51" customHeight="1" spans="1:8">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="D26" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="27" ht="51" customHeight="1" spans="1:8">
-      <c r="A27" s="11"/>
-      <c r="B27" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="H27" s="10"/>
-    </row>
-    <row r="28" ht="126" customHeight="1" spans="1:8">
-      <c r="A28" s="11"/>
-      <c r="B28" s="32" t="s">
-        <v>241</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="H28" s="33" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="29" ht="126" customHeight="1" spans="1:8">
-      <c r="A29" s="11"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="F29" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H29" s="36"/>
-    </row>
-    <row r="30" ht="74" customHeight="1" spans="1:8">
-      <c r="A30" s="11"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F30" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H30" s="39"/>
-    </row>
-    <row r="31" ht="96" customHeight="1" spans="1:8">
-      <c r="A31" s="11"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="37" t="s">
-        <v>251</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="36"/>
-    </row>
-    <row r="32" ht="96" customHeight="1" spans="1:8">
-      <c r="A32" s="11"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="36"/>
-    </row>
-    <row r="33" ht="117" customHeight="1" spans="1:8">
-      <c r="A33" s="11"/>
-      <c r="B33" s="7" t="s">
+      <c r="F83" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="C33" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="H33" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" ht="96" customHeight="1" spans="1:8">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="41" t="s">
-        <v>259</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" ht="96" customHeight="1" spans="1:8">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="40" t="s">
-        <v>262</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>263</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="H35" s="8"/>
-    </row>
-    <row r="36" ht="171" customHeight="1" spans="1:8">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="40" t="s">
-        <v>265</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="H36" s="21"/>
-    </row>
-    <row r="37" ht="126" customHeight="1" spans="1:8">
-      <c r="A37" s="11"/>
-      <c r="B37" s="42" t="s">
-        <v>268</v>
-      </c>
-      <c r="C37" s="43" t="s">
-        <v>269</v>
-      </c>
-      <c r="D37" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="E37" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="F37" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="H37" s="46" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="38" ht="81" customHeight="1" spans="1:8">
-      <c r="A38" s="11"/>
-      <c r="B38" s="42"/>
-      <c r="C38" s="43" t="s">
-        <v>272</v>
-      </c>
-      <c r="D38" s="43" t="s">
-        <v>273</v>
-      </c>
-      <c r="E38" s="43" t="s">
-        <v>274</v>
-      </c>
-      <c r="F38" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="H38" s="46" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39" ht="81" customHeight="1" spans="1:8">
-      <c r="A39" s="11"/>
-      <c r="B39" s="36" t="s">
-        <v>275</v>
-      </c>
-      <c r="C39" s="41" t="s">
-        <v>276</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H39" s="29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" ht="68" customHeight="1" spans="1:8">
-      <c r="A40" s="11"/>
-      <c r="B40" s="39"/>
-      <c r="C40" s="47" t="s">
-        <v>279</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="E40" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="F40" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="48" t="s">
-        <v>188</v>
-      </c>
-      <c r="H40" s="29" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="41" ht="51" customHeight="1" spans="1:8">
-      <c r="A41" s="11"/>
-      <c r="B41" s="39"/>
-      <c r="C41" s="49" t="s">
-        <v>282</v>
-      </c>
-      <c r="D41" s="50" t="s">
-        <v>283</v>
-      </c>
-      <c r="E41" s="49" t="s">
-        <v>284</v>
-      </c>
-      <c r="F41" s="51" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="51" t="s">
-        <v>109</v>
-      </c>
-      <c r="H41" s="51"/>
-    </row>
-    <row r="42" ht="68" customHeight="1" spans="1:8">
-      <c r="A42" s="11"/>
-      <c r="B42" s="39"/>
-      <c r="C42" s="49" t="s">
-        <v>285</v>
-      </c>
-      <c r="D42" s="50" t="s">
-        <v>286</v>
-      </c>
-      <c r="E42" s="49" t="s">
-        <v>287</v>
-      </c>
-      <c r="F42" s="51" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="51" t="s">
-        <v>109</v>
-      </c>
-      <c r="H42" s="51"/>
-    </row>
-    <row r="43" ht="51" customHeight="1" spans="1:8">
-      <c r="A43" s="11"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="49" t="s">
-        <v>288</v>
-      </c>
-      <c r="D43" s="50" t="s">
-        <v>289</v>
-      </c>
-      <c r="E43" s="49" t="s">
-        <v>290</v>
-      </c>
-      <c r="F43" s="51" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="51" t="s">
-        <v>109</v>
-      </c>
-      <c r="H43" s="51"/>
-    </row>
-    <row r="44" ht="84" customHeight="1" spans="1:8">
-      <c r="A44" s="11"/>
-      <c r="B44" s="39"/>
-      <c r="C44" s="49" t="s">
-        <v>291</v>
-      </c>
-      <c r="D44" s="50" t="s">
-        <v>292</v>
-      </c>
-      <c r="E44" s="49" t="s">
-        <v>293</v>
-      </c>
-      <c r="F44" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="G44" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="H44" s="51"/>
-    </row>
-    <row r="45" ht="51" customHeight="1" spans="1:8">
-      <c r="A45" s="11"/>
-      <c r="B45" s="39"/>
-      <c r="C45" s="49" t="s">
-        <v>294</v>
-      </c>
-      <c r="D45" s="50" t="s">
-        <v>295</v>
-      </c>
-      <c r="E45" s="50" t="s">
-        <v>296</v>
-      </c>
-      <c r="F45" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="G45" s="51" t="s">
-        <v>109</v>
-      </c>
-      <c r="H45" s="51"/>
-    </row>
-    <row r="46" ht="51" spans="1:8">
-      <c r="A46" s="12"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="49" t="s">
-        <v>297</v>
-      </c>
-      <c r="D46" s="50" t="s">
-        <v>298</v>
-      </c>
-      <c r="E46" s="49" t="s">
-        <v>299</v>
-      </c>
-      <c r="F46" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="G46" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="H46" s="51"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A2:A46"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B11"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B20:B26"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B39:B46"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="H29:H31"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G83" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <mergeCells count="13">
+    <mergeCell ref="A2:A83"/>
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="B8:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B53"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="B57:B64"/>
+    <mergeCell ref="B65:B72"/>
+    <mergeCell ref="B73:B83"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>